--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -47706,6 +47706,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2059">
+      <c r="A2059" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2059" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C2059" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="E2059" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="G2059" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -47729,6 +47729,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2060">
+      <c r="A2060" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2060" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C2060" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="D2060" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="E2060" t="n">
+        <v>3.13000011444092</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="G2060" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -47752,6 +47752,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2061">
+      <c r="A2061" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2061" t="n">
+        <v>15700</v>
+      </c>
+      <c r="C2061" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="E2061" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G2061" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -47775,6 +47775,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2062">
+      <c r="A2062" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2062" t="n">
+        <v>5400</v>
+      </c>
+      <c r="C2062" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="D2062" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E2062" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G2062" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -47616,22 +47616,22 @@
     </row>
     <row r="2055">
       <c r="A2055" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2055" t="n">
-        <v>6900</v>
+        <v>6700</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.17000007629395</v>
+        <v>3.13000011444092</v>
       </c>
       <c r="D2055" t="n">
-        <v>3.13000011444092</v>
+        <v>3.07999992370605</v>
       </c>
       <c r="E2055" t="n">
         <v>3.13000011444092</v>
       </c>
       <c r="F2055" t="n">
-        <v>3.16000008583069</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="G2055" t="s">
         <v>7</v>
@@ -47639,22 +47639,22 @@
     </row>
     <row r="2056">
       <c r="A2056" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2056" t="n">
-        <v>13300</v>
+        <v>6900</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.14000010490417</v>
+        <v>3.17000007629395</v>
       </c>
       <c r="D2056" t="n">
-        <v>3.08999991416931</v>
+        <v>3.13000011444092</v>
       </c>
       <c r="E2056" t="n">
-        <v>3.14000010490417</v>
+        <v>3.13000011444092</v>
       </c>
       <c r="F2056" t="n">
-        <v>3.09999990463257</v>
+        <v>3.16000008583069</v>
       </c>
       <c r="G2056" t="s">
         <v>7</v>
@@ -47662,22 +47662,22 @@
     </row>
     <row r="2057">
       <c r="A2057" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2057" t="n">
-        <v>5900</v>
+        <v>13300</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.11999988555908</v>
+        <v>3.14000010490417</v>
       </c>
       <c r="D2057" t="n">
-        <v>3.0699999332428</v>
+        <v>3.08999991416931</v>
       </c>
       <c r="E2057" t="n">
-        <v>3.10999989509583</v>
+        <v>3.14000010490417</v>
       </c>
       <c r="F2057" t="n">
-        <v>3.11999988555908</v>
+        <v>3.09999990463257</v>
       </c>
       <c r="G2057" t="s">
         <v>7</v>
@@ -47685,22 +47685,22 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2058" t="n">
-        <v>4000</v>
+        <v>5900</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.16000008583069</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="D2058" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="E2058" t="n">
+        <v>3.10999989509583</v>
+      </c>
+      <c r="F2058" t="n">
         <v>3.11999988555908</v>
-      </c>
-      <c r="E2058" t="n">
-        <v>3.15000009536743</v>
-      </c>
-      <c r="F2058" t="n">
-        <v>3.16000008583069</v>
       </c>
       <c r="G2058" t="s">
         <v>7</v>
@@ -47708,22 +47708,22 @@
     </row>
     <row r="2059">
       <c r="A2059" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2059" t="n">
-        <v>2400</v>
+        <v>4000</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.15000009536743</v>
+        <v>3.16000008583069</v>
       </c>
       <c r="D2059" t="n">
-        <v>3.15000009536743</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="E2059" t="n">
         <v>3.15000009536743</v>
       </c>
       <c r="F2059" t="n">
-        <v>3.15000009536743</v>
+        <v>3.16000008583069</v>
       </c>
       <c r="G2059" t="s">
         <v>7</v>
@@ -47731,22 +47731,22 @@
     </row>
     <row r="2060">
       <c r="A2060" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2060" t="n">
-        <v>3500</v>
+        <v>2400</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.16000008583069</v>
+        <v>3.15000009536743</v>
       </c>
       <c r="D2060" t="n">
-        <v>3.11999988555908</v>
+        <v>3.15000009536743</v>
       </c>
       <c r="E2060" t="n">
-        <v>3.13000011444092</v>
+        <v>3.15000009536743</v>
       </c>
       <c r="F2060" t="n">
-        <v>3.11999988555908</v>
+        <v>3.15000009536743</v>
       </c>
       <c r="G2060" t="s">
         <v>7</v>
@@ -47754,22 +47754,22 @@
     </row>
     <row r="2061">
       <c r="A2061" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2061" t="n">
-        <v>15700</v>
+        <v>3500</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.19000005722046</v>
+        <v>3.16000008583069</v>
       </c>
       <c r="D2061" t="n">
-        <v>3.08999991416931</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="E2061" t="n">
-        <v>3.08999991416931</v>
+        <v>3.13000011444092</v>
       </c>
       <c r="F2061" t="n">
-        <v>3.14000010490417</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="G2061" t="s">
         <v>7</v>
@@ -47777,24 +47777,47 @@
     </row>
     <row r="2062">
       <c r="A2062" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2062" t="n">
-        <v>5400</v>
+        <v>15700</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.15000009536743</v>
+        <v>3.19000005722046</v>
       </c>
       <c r="D2062" t="n">
-        <v>3.09999990463257</v>
+        <v>3.08999991416931</v>
       </c>
       <c r="E2062" t="n">
-        <v>3.14000010490417</v>
+        <v>3.08999991416931</v>
       </c>
       <c r="F2062" t="n">
         <v>3.14000010490417</v>
       </c>
       <c r="G2062" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2063" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C2063" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D2063" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="E2063" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="F2063" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="G2063" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -473,7 +473,7 @@
         <v>9.70100021362305</v>
       </c>
       <c r="G4" t="n">
-        <v>8.23212051391602</v>
+        <v>8.23212146759033</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>9.61100006103516</v>
       </c>
       <c r="G6" t="n">
-        <v>8.15574836730957</v>
+        <v>8.15574932098389</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11246967315674</v>
+        <v>8.11247062683105</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.13792705535889</v>
+        <v>8.1379280090332</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852745056152</v>
+        <v>8.07852840423584</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.54199981689453</v>
       </c>
       <c r="G25" t="n">
-        <v>8.09719467163086</v>
+        <v>8.09719562530518</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0819206237793</v>
+        <v>8.08192157745361</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.07513236999512</v>
+        <v>8.0751314163208</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.43099975585938</v>
       </c>
       <c r="G34" t="n">
-        <v>8.00300216674805</v>
+        <v>8.00300312042236</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01064014434814</v>
+        <v>8.01063919067383</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.44699954986572</v>
       </c>
       <c r="G36" t="n">
-        <v>8.01658058166504</v>
+        <v>8.01657962799072</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366855621338</v>
+        <v>7.99366760253906</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.37100028991699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.95208787918091</v>
+        <v>7.95208835601807</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.33100032806396</v>
       </c>
       <c r="G39" t="n">
-        <v>7.91814470291138</v>
+        <v>7.91814374923706</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227169036865</v>
+        <v>7.96227121353149</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227169036865</v>
+        <v>7.96227121353149</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.97924327850342</v>
+        <v>7.97924184799194</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.97924327850342</v>
+        <v>7.97924184799194</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G44" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G45" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G48" t="n">
-        <v>7.90880918502808</v>
+        <v>7.90880966186523</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729593276978</v>
+        <v>7.91729545593262</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619735717773</v>
+        <v>7.85619831085205</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.77473258972168</v>
+        <v>7.77473449707031</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G54" t="n">
-        <v>7.78237056732178</v>
+        <v>7.78237104415894</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G55" t="n">
-        <v>7.78237056732178</v>
+        <v>7.78237104415894</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.80698013305664</v>
+        <v>7.8069806098938</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.80698013305664</v>
+        <v>7.8069806098938</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.80698013305664</v>
+        <v>7.8069806098938</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.80528259277344</v>
+        <v>7.8052830696106</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722898483276</v>
+        <v>7.86722803115845</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746175765991</v>
+        <v>7.78746318817139</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746175765991</v>
+        <v>7.78746318817139</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>7.85534858703613</v>
+        <v>7.85534954071045</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761077880859</v>
+        <v>8.02761173248291</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177207946777</v>
+        <v>7.84177160263062</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>7.84516668319702</v>
+        <v>7.84516572952271</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243608474731</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358552932739</v>
+        <v>7.80358505249023</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406715393066</v>
+        <v>7.78406858444214</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098978042603</v>
+        <v>7.89098834991455</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782890319824</v>
+        <v>7.80782794952393</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.76879358291626</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.76879358291626</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408418655396</v>
+        <v>7.92408466339111</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.77048921585083</v>
+        <v>7.77049016952515</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G97" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212028503418</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212028503418</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70514822006226</v>
+        <v>7.70515012741089</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726329803467</v>
+        <v>7.63726282119751</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423536300659</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423536300659</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>7.55240440368652</v>
+        <v>7.55240392684937</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904195785522</v>
+        <v>7.82904243469238</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212028503418</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.10099983215332</v>
       </c>
       <c r="G108" t="n">
-        <v>7.7229700088501</v>
+        <v>7.72296953201294</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G109" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212028503418</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363592147827</v>
+        <v>7.71363544464111</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70514822006226</v>
+        <v>7.70515012741089</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70514822006226</v>
+        <v>7.70515012741089</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817901611328</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902683258057</v>
+        <v>7.68902587890625</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110521316528</v>
+        <v>7.85110569000244</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308639526367</v>
+        <v>7.68308591842651</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G119" t="n">
-        <v>7.69666385650635</v>
+        <v>7.69666290283203</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G120" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212028503418</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G121" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212028503418</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817901611328</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.76879358291626</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.14900016784668</v>
       </c>
       <c r="G124" t="n">
-        <v>7.76370191574097</v>
+        <v>7.76370286941528</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.8655309677124</v>
+        <v>7.86553192138672</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152370452881</v>
+        <v>7.78152275085449</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406715393066</v>
+        <v>7.78406858444214</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303647994995</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303647994995</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243608474731</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.79849338531494</v>
+        <v>7.79849290847778</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000854492188</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000854492188</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445180892944</v>
+        <v>7.94444990158081</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.79849338531494</v>
+        <v>7.79849290847778</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.80698013305664</v>
+        <v>7.8069806098938</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G140" t="n">
-        <v>7.96311950683594</v>
+        <v>7.96311855316162</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.32100009918213</v>
       </c>
       <c r="G148" t="n">
-        <v>7.90965795516968</v>
+        <v>7.90965890884399</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.9283275604248</v>
+        <v>7.92832803726196</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G156" t="n">
-        <v>8.06664657592773</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G157" t="n">
-        <v>8.06664657592773</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G158" t="n">
-        <v>8.06664657592773</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.34700012207031</v>
       </c>
       <c r="G159" t="n">
-        <v>7.93172168731689</v>
+        <v>7.93172121047974</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.44299983978271</v>
       </c>
       <c r="G160" t="n">
-        <v>8.01318454742432</v>
+        <v>8.01318550109863</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.4040002822876</v>
       </c>
       <c r="G163" t="n">
-        <v>7.9800910949707</v>
+        <v>7.98009157180786</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>8.05306816101074</v>
+        <v>8.05306911468506</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.9283275604248</v>
+        <v>7.92832803726196</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G177" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G180" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G209" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G250" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G256" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G265" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G266" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G267" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G293" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G294" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G295" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G296" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G326" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G336" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G337" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G345" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G346" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G347" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G350" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G409" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.25</v>
       </c>
       <c r="G410" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G415" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G420" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G421" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G424" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G427" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G433" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G516" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G518" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>8.44341850280762</v>
+        <v>8.4434175491333</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782915115356</v>
+        <v>7.29782962799072</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>7.12811183929443</v>
+        <v>7.12811136245728</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66139030456543</v>
+        <v>6.66138982772827</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17054080963135</v>
+        <v>7.17054128646851</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>6.68633890151978</v>
+        <v>6.68633937835693</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G571" t="n">
-        <v>6.94854831695557</v>
+        <v>6.94854784011841</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.5</v>
       </c>
       <c r="G580" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G583" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G587" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G588" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.73517799377441</v>
+        <v>7.73517656326294</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56036996841431</v>
+        <v>7.56037044525146</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.73517799377441</v>
+        <v>7.73517656326294</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>8.5</v>
       </c>
       <c r="G606" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>7.60407114028931</v>
+        <v>7.60407161712646</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G609" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G610" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.86628150939941</v>
+        <v>7.86628103256226</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.86628150939941</v>
+        <v>7.86628103256226</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95368432998657</v>
+        <v>7.95368480682373</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.73517799377441</v>
+        <v>7.73517656326294</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.5</v>
       </c>
       <c r="G617" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.5</v>
       </c>
       <c r="G619" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>8.5</v>
       </c>
       <c r="G620" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G632" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G634" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G636" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G646" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G647" t="n">
-        <v>7.12335395812988</v>
+        <v>7.12335443496704</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G648" t="n">
-        <v>7.12335395812988</v>
+        <v>7.12335443496704</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G649" t="n">
-        <v>7.12335395812988</v>
+        <v>7.12335443496704</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G650" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G651" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484714508057</v>
+        <v>6.90484666824341</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G655" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G656" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G663" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>8.5</v>
       </c>
       <c r="G666" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G668" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.86628150939941</v>
+        <v>7.86628103256226</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86628150939941</v>
+        <v>7.86628103256226</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G672" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G673" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.86628150939941</v>
+        <v>7.86628103256226</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.86628150939941</v>
+        <v>7.86628103256226</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.86628150939941</v>
+        <v>7.86628103256226</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.86628150939941</v>
+        <v>7.86628103256226</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G679" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G680" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60407114028931</v>
+        <v>7.60407161712646</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738645553589</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G686" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>7.60407114028931</v>
+        <v>7.60407161712646</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G690" t="n">
-        <v>8.17219161987305</v>
+        <v>8.17219257354736</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738645553589</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G712" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G713" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>9</v>
       </c>
       <c r="G714" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>9</v>
       </c>
       <c r="G715" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G716" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G741" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G749" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.5</v>
       </c>
       <c r="G756" t="n">
-        <v>8.5266580581665</v>
+        <v>8.52665901184082</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G757" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G758" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G761" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G762" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G763" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G767" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G768" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>10</v>
       </c>
       <c r="G774" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>10</v>
       </c>
       <c r="G775" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>9.60370922088623</v>
+        <v>9.60371017456055</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>9.6934642791748</v>
+        <v>9.69346332550049</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G785" t="n">
-        <v>9.6934642791748</v>
+        <v>9.69346332550049</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>10</v>
       </c>
       <c r="G791" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G792" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>10</v>
       </c>
       <c r="G793" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>9.5</v>
       </c>
       <c r="G804" t="n">
-        <v>8.5266580581665</v>
+        <v>8.52665901184082</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G818" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>9.5</v>
       </c>
       <c r="G822" t="n">
-        <v>8.5266580581665</v>
+        <v>8.52665901184082</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>10</v>
       </c>
       <c r="G834" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G843" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G851" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G852" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G855" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>9.5</v>
       </c>
       <c r="G857" t="n">
-        <v>8.5266580581665</v>
+        <v>8.52665901184082</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>10</v>
       </c>
       <c r="G872" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10</v>
       </c>
       <c r="G873" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10</v>
       </c>
       <c r="G875" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10</v>
       </c>
       <c r="G876" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>10</v>
       </c>
       <c r="G889" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>9</v>
       </c>
       <c r="G905" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G907" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G908" t="n">
-        <v>8.03300952911377</v>
+        <v>8.03301048278809</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G909" t="n">
-        <v>8.03300952911377</v>
+        <v>8.03301048278809</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G910" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423757553101</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423757553101</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G914" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862331390381</v>
+        <v>7.80862379074097</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G917" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>9.5</v>
       </c>
       <c r="G918" t="n">
-        <v>8.5266580581665</v>
+        <v>8.52665901184082</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>9.5</v>
       </c>
       <c r="G919" t="n">
-        <v>8.5266580581665</v>
+        <v>8.52665901184082</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>9.5</v>
       </c>
       <c r="G920" t="n">
-        <v>8.5266580581665</v>
+        <v>8.52665901184082</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G921" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10</v>
       </c>
       <c r="G931" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231513977051</v>
+        <v>8.65231418609619</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G933" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.54461002349854</v>
+        <v>8.54460906982422</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821620941162</v>
+        <v>8.68821716308594</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G937" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G938" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>9.5</v>
       </c>
       <c r="G939" t="n">
-        <v>8.5266580581665</v>
+        <v>8.52665901184082</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>9.5</v>
       </c>
       <c r="G940" t="n">
-        <v>8.5266580581665</v>
+        <v>8.52665901184082</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G943" t="n">
-        <v>8.84977340698242</v>
+        <v>8.84977245330811</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G945" t="n">
-        <v>9.0620584487915</v>
+        <v>9.06205749511719</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G949" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G952" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G954" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G957" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>9.0620584487915</v>
+        <v>9.06205749511719</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G959" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G960" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G964" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G965" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G968" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G969" t="n">
-        <v>8.89628791809082</v>
+        <v>8.89628887176514</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>8.78577613830566</v>
+        <v>8.78577518463135</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G971" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G978" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>9</v>
       </c>
       <c r="G989" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>8.14111709594727</v>
+        <v>8.14111614227295</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>9</v>
       </c>
       <c r="G993" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G996" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>9.5</v>
       </c>
       <c r="G997" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423793792725</v>
+        <v>8.45423698425293</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>9</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>9</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>9</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.14111709594727</v>
+        <v>8.14111614227295</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>9</v>
       </c>
       <c r="G1055" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>9.5</v>
       </c>
       <c r="G1060" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>9.5</v>
       </c>
       <c r="G1066" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>9.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>9.5</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>9.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>9.5</v>
       </c>
       <c r="G1100" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>9.5</v>
       </c>
       <c r="G1101" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>9.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>9.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1111" t="n">
-        <v>8.89628791809082</v>
+        <v>8.89628887176514</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1112" t="n">
-        <v>8.89628791809082</v>
+        <v>8.89628887176514</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>9.5</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>9.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>9.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>9.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>9.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>9.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1130" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1131" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1132" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>9.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>8.74893760681152</v>
+        <v>8.74893856048584</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1149" t="n">
-        <v>9.02521991729736</v>
+        <v>9.02522087097168</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1167" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1168" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1178" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1179" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>9</v>
       </c>
       <c r="G1190" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>9</v>
       </c>
       <c r="G1192" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>9</v>
       </c>
       <c r="G1193" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>9</v>
       </c>
       <c r="G1194" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>9</v>
       </c>
       <c r="G1195" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1197" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>9</v>
       </c>
       <c r="G1204" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590230941772</v>
+        <v>7.73590326309204</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1212" t="n">
-        <v>7.64380931854248</v>
+        <v>7.64380979537964</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.60697174072266</v>
+        <v>7.6069712638855</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.49645900726318</v>
+        <v>7.49645853042603</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1215" t="n">
-        <v>7.40436410903931</v>
+        <v>7.40436458587646</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1216" t="n">
-        <v>7.2385950088501</v>
+        <v>7.23859548568726</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1218" t="n">
-        <v>7.22017669677734</v>
+        <v>7.22017621994019</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>7.60697174072266</v>
+        <v>7.6069712638855</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590230941772</v>
+        <v>7.73590326309204</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1233" t="n">
-        <v>7.64380931854248</v>
+        <v>7.64380979537964</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.42175912857056</v>
+        <v>7.4217586517334</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.59347057342529</v>
+        <v>7.59347009658813</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.19280958175659</v>
+        <v>7.19281005859375</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.22307968139648</v>
+        <v>8.22307872772217</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.9178147315979</v>
+        <v>7.91781520843506</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.76518249511719</v>
+        <v>7.76518201828003</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1290" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1294" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1300" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.25004720687866</v>
+        <v>7.2500467300415</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>6.18161916732788</v>
+        <v>6.18161869049072</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>6.25793504714966</v>
+        <v>6.25793552398682</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1344" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>6.73491191864014</v>
+        <v>6.73491239547729</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1362" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1370" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1372" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1382" t="n">
-        <v>6.44872665405273</v>
+        <v>6.44872617721558</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1386" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1394" t="n">
-        <v>6.23885631561279</v>
+        <v>6.23885583877563</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1396" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1400" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1403" t="n">
-        <v>5.85727500915527</v>
+        <v>5.85727453231812</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1408" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.12438201904297</v>
+        <v>6.12438154220581</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1422" t="n">
-        <v>5.95266962051392</v>
+        <v>5.95267009735107</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>5.78095817565918</v>
+        <v>5.78095865249634</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1431" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.32306051254272</v>
+        <v>5.32306098937988</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.53293085098267</v>
+        <v>5.53293037414551</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1442" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1448" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.43753480911255</v>
+        <v>5.43753528594971</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -54062,6 +54062,32 @@
         <v>3.15000009536743</v>
       </c>
       <c r="H2065" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2066" t="n">
+        <v>22400</v>
+      </c>
+      <c r="C2066" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="E2066" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F2066" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="G2066" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="H2066" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -473,7 +473,7 @@
         <v>9.70100021362305</v>
       </c>
       <c r="G4" t="n">
-        <v>8.23212146759033</v>
+        <v>8.23212051391602</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>9.60200023651123</v>
       </c>
       <c r="G5" t="n">
-        <v>8.14811038970947</v>
+        <v>8.14811134338379</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>9.61100006103516</v>
       </c>
       <c r="G6" t="n">
-        <v>8.15574932098389</v>
+        <v>8.15574836730957</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G7" t="n">
-        <v>8.18035697937012</v>
+        <v>8.18035793304443</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11247062683105</v>
+        <v>8.11247158050537</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852840423584</v>
+        <v>8.07852745056152</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G26" t="n">
-        <v>8.20666313171387</v>
+        <v>8.20666217803955</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G27" t="n">
-        <v>8.20666313171387</v>
+        <v>8.20666217803955</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G29" t="n">
-        <v>8.08192157745361</v>
+        <v>8.0819206237793</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.0751314163208</v>
+        <v>8.07513236999512</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01063919067383</v>
+        <v>8.01063823699951</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.44699954986572</v>
       </c>
       <c r="G36" t="n">
-        <v>8.01657962799072</v>
+        <v>8.01658058166504</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.37100028991699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.95208835601807</v>
+        <v>7.95208740234375</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G44" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G45" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G48" t="n">
-        <v>7.90880966186523</v>
+        <v>7.90881061553955</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729545593262</v>
+        <v>7.91729640960693</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G52" t="n">
-        <v>7.75097370147705</v>
+        <v>7.75097274780273</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.77473449707031</v>
+        <v>7.774733543396</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G54" t="n">
-        <v>7.78237104415894</v>
+        <v>7.78237152099609</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G55" t="n">
-        <v>7.78237104415894</v>
+        <v>7.78237152099609</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G56" t="n">
-        <v>7.76709651947021</v>
+        <v>7.76709604263306</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.8069806098938</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76454973220825</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.8069806098938</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.8069806098938</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.8052830696106</v>
+        <v>7.80528211593628</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722803115845</v>
+        <v>7.86722993850708</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746318817139</v>
+        <v>7.78746271133423</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746318817139</v>
+        <v>7.78746271133423</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>7.85534954071045</v>
+        <v>7.85534858703613</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177160263062</v>
+        <v>7.84177255630493</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.79085636138916</v>
+        <v>7.790855884552</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243608474731</v>
+        <v>7.83243703842163</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406858444214</v>
+        <v>7.78406810760498</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.80103921890259</v>
+        <v>7.80103826522827</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G87" t="n">
-        <v>7.81037473678589</v>
+        <v>7.81037378311157</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098834991455</v>
+        <v>7.89098930358887</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408466339111</v>
+        <v>7.92408561706543</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.77049016952515</v>
+        <v>7.7704906463623</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76454973220825</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76454973220825</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G97" t="n">
-        <v>7.72212028503418</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.72212028503418</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70515012741089</v>
+        <v>7.70514965057373</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726282119751</v>
+        <v>7.63726186752319</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423536300659</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423536300659</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904243469238</v>
+        <v>7.8290433883667</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.72212028503418</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72212028503418</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363544464111</v>
+        <v>7.71363592147827</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70515012741089</v>
+        <v>7.70514965057373</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70515012741089</v>
+        <v>7.70514965057373</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817901611328</v>
+        <v>7.68817758560181</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902587890625</v>
+        <v>7.68902635574341</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308591842651</v>
+        <v>7.68308639526367</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G119" t="n">
-        <v>7.69666290283203</v>
+        <v>7.69666385650635</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G120" t="n">
-        <v>7.72212028503418</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G121" t="n">
-        <v>7.72212028503418</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817901611328</v>
+        <v>7.68817758560181</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.14900016784668</v>
       </c>
       <c r="G124" t="n">
-        <v>7.76370286941528</v>
+        <v>7.76370191574097</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152275085449</v>
+        <v>7.78152179718018</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406858444214</v>
+        <v>7.78406810760498</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76454973220825</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303647994995</v>
+        <v>7.77303552627563</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303647994995</v>
+        <v>7.77303552627563</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243608474731</v>
+        <v>7.83243703842163</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.79849290847778</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000759124756</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000759124756</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94444990158081</v>
+        <v>7.94445085525513</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.79849290847778</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.8069806098938</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579875946045</v>
+        <v>8.06579780578613</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.34700012207031</v>
       </c>
       <c r="G159" t="n">
-        <v>7.93172121047974</v>
+        <v>7.93172216415405</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.44299983978271</v>
       </c>
       <c r="G160" t="n">
-        <v>8.01318550109863</v>
+        <v>8.01318645477295</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G177" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G180" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G209" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G250" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G255" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G256" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G296" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G320" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G352" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G353" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.75</v>
       </c>
       <c r="G379" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>9.75</v>
       </c>
       <c r="G394" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G409" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.25</v>
       </c>
       <c r="G410" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G415" t="n">
-        <v>7.97669696807861</v>
+        <v>7.9766960144043</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G420" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G421" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G424" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.75</v>
       </c>
       <c r="G440" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.75</v>
       </c>
       <c r="G443" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.75</v>
       </c>
       <c r="G444" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.75</v>
       </c>
       <c r="G445" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.75</v>
       </c>
       <c r="G446" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>9.75</v>
       </c>
       <c r="G448" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.75</v>
       </c>
       <c r="G449" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>9.75</v>
       </c>
       <c r="G450" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.75</v>
       </c>
       <c r="G451" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.75</v>
       </c>
       <c r="G452" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>9.75</v>
       </c>
       <c r="G453" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.75</v>
       </c>
       <c r="G454" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.75</v>
       </c>
       <c r="G456" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>9.75</v>
       </c>
       <c r="G457" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>9.75</v>
       </c>
       <c r="G460" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>9.75</v>
       </c>
       <c r="G461" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>9.75</v>
       </c>
       <c r="G462" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>9.75</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>9.75</v>
       </c>
       <c r="G464" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.75</v>
       </c>
       <c r="G465" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.75</v>
       </c>
       <c r="G466" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>9.75</v>
       </c>
       <c r="G467" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>9.75</v>
       </c>
       <c r="G468" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.75</v>
       </c>
       <c r="G470" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.75</v>
       </c>
       <c r="G474" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.75</v>
       </c>
       <c r="G475" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.75</v>
       </c>
       <c r="G476" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.75</v>
       </c>
       <c r="G479" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.75</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>9.75</v>
       </c>
       <c r="G481" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G482" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>9.75</v>
       </c>
       <c r="G483" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.75</v>
       </c>
       <c r="G484" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.75</v>
       </c>
       <c r="G485" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>9.75</v>
       </c>
       <c r="G486" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.75</v>
       </c>
       <c r="G509" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>8.23127174377441</v>
+        <v>8.2312707901001</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>9.75</v>
       </c>
       <c r="G541" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.75</v>
       </c>
       <c r="G542" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>8.4434175491333</v>
+        <v>8.44341850280762</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>7.5948338508606</v>
+        <v>7.59483242034912</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G556" t="n">
-        <v>7.5948338508606</v>
+        <v>7.59483242034912</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782962799072</v>
+        <v>7.29782915115356</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66138982772827</v>
+        <v>6.66139030456543</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>6.49167346954346</v>
+        <v>6.49167394638062</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>6.8311071395874</v>
+        <v>6.83110761642456</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867769241333</v>
+        <v>6.78867721557617</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867769241333</v>
+        <v>6.78867721557617</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867769241333</v>
+        <v>6.78867721557617</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>6.68633937835693</v>
+        <v>6.68633890151978</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G571" t="n">
-        <v>6.94854784011841</v>
+        <v>6.94854879379272</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.73004055023193</v>
+        <v>6.73004007339478</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.4678316116333</v>
+        <v>6.46783113479614</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G574" t="n">
-        <v>6.73004055023193</v>
+        <v>6.73004007339478</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G581" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>7.69147443771362</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69147443771362</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G587" t="n">
-        <v>7.69147443771362</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.73517656326294</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56037044525146</v>
+        <v>7.56036996841431</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.73517656326294</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>7.60407161712646</v>
+        <v>7.60407257080078</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.73517656326294</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>7.69147443771362</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G631" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G646" t="n">
-        <v>7.07965326309204</v>
+        <v>7.07965421676636</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G650" t="n">
-        <v>7.07965326309204</v>
+        <v>7.07965421676636</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G651" t="n">
-        <v>7.07965326309204</v>
+        <v>7.07965421676636</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484666824341</v>
+        <v>6.90484619140625</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G655" t="n">
-        <v>7.07965326309204</v>
+        <v>7.07965421676636</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>7.69147443771362</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G671" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998220443726</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60407161712646</v>
+        <v>7.60407257080078</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>7.60407161712646</v>
+        <v>7.60407257080078</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998220443726</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998220443726</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G705" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G709" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G711" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G717" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98813199996948</v>
+        <v>7.98813104629517</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G743" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G745" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G747" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>9.5</v>
       </c>
       <c r="G756" t="n">
-        <v>8.52665901184082</v>
+        <v>8.5266580581665</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G764" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>9.51395606994629</v>
+        <v>9.51395511627197</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>9.96272754669189</v>
+        <v>9.96272850036621</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>9.51395606994629</v>
+        <v>9.51395511627197</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>9.51395606994629</v>
+        <v>9.51395511627197</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>9.69346332550049</v>
+        <v>9.6934642791748</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G785" t="n">
-        <v>9.69346332550049</v>
+        <v>9.6934642791748</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G795" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>9.75</v>
       </c>
       <c r="G802" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>9.5</v>
       </c>
       <c r="G804" t="n">
-        <v>8.52665901184082</v>
+        <v>8.5266580581665</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>9.75</v>
       </c>
       <c r="G808" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>9.75</v>
       </c>
       <c r="G813" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G817" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G820" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>9.5</v>
       </c>
       <c r="G822" t="n">
-        <v>8.52665901184082</v>
+        <v>8.5266580581665</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G836" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>9.75</v>
       </c>
       <c r="G839" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G840" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G841" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>9.75</v>
       </c>
       <c r="G842" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>9.75</v>
       </c>
       <c r="G844" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G854" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>9.5</v>
       </c>
       <c r="G857" t="n">
-        <v>8.52665901184082</v>
+        <v>8.5266580581665</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G859" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G874" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G877" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G898" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G901" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G902" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G904" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G907" t="n">
-        <v>7.98813199996948</v>
+        <v>7.98813104629517</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G908" t="n">
-        <v>8.03301048278809</v>
+        <v>8.03300952911377</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G909" t="n">
-        <v>8.03301048278809</v>
+        <v>8.03300952911377</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.35985231399536</v>
+        <v>7.3598518371582</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G914" t="n">
-        <v>7.98813199996948</v>
+        <v>7.98813104629517</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>9.5</v>
       </c>
       <c r="G918" t="n">
-        <v>8.52665901184082</v>
+        <v>8.5266580581665</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>9.5</v>
       </c>
       <c r="G919" t="n">
-        <v>8.52665901184082</v>
+        <v>8.5266580581665</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>9.5</v>
       </c>
       <c r="G920" t="n">
-        <v>8.52665901184082</v>
+        <v>8.5266580581665</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G923" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G924" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G926" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G927" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G928" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821716308594</v>
+        <v>8.68821620941162</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>9.5</v>
       </c>
       <c r="G939" t="n">
-        <v>8.52665901184082</v>
+        <v>8.5266580581665</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>9.5</v>
       </c>
       <c r="G940" t="n">
-        <v>8.52665901184082</v>
+        <v>8.5266580581665</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G941" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G946" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G948" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G949" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G950" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>9.3015022277832</v>
+        <v>9.30150318145752</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G952" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G953" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G954" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G957" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G960" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G963" t="n">
-        <v>9.04363822937012</v>
+        <v>9.04363918304443</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G967" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G968" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G969" t="n">
-        <v>8.89628887176514</v>
+        <v>8.89628791809082</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>8.78577518463135</v>
+        <v>8.78577613830566</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G971" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G982" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>8.14111614227295</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G996" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>9.5</v>
       </c>
       <c r="G997" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G998" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G999" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1012" t="n">
-        <v>8.17795562744141</v>
+        <v>8.17795467376709</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>7.97534799575806</v>
+        <v>7.9753475189209</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.8832540512085</v>
+        <v>7.88325357437134</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.14111614227295</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1058" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1059" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>9.5</v>
       </c>
       <c r="G1060" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>9.5</v>
       </c>
       <c r="G1066" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.17795562744141</v>
+        <v>8.17795467376709</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>9.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>9.5</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>9.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>9.5</v>
       </c>
       <c r="G1100" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>9.5</v>
       </c>
       <c r="G1101" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>9.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>9.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1111" t="n">
-        <v>8.89628887176514</v>
+        <v>8.89628791809082</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1112" t="n">
-        <v>8.89628887176514</v>
+        <v>8.89628791809082</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>9.5</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>9.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>9.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>9.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>9.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>9.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1135" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1136" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1137" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1139" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1142" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1146" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>9.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1149" t="n">
-        <v>9.02522087097168</v>
+        <v>9.02521991729736</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1150" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1152" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1159" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1165" t="n">
-        <v>8.58316898345947</v>
+        <v>8.58316802978516</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1167" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1168" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1180" t="n">
-        <v>8.58316898345947</v>
+        <v>8.58316802978516</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1182" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1187" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1188" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1189" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>8.5</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.8279972076416</v>
+        <v>7.82799673080444</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1208" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590326309204</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>8.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.8279972076416</v>
+        <v>7.82799673080444</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1212" t="n">
-        <v>7.64380979537964</v>
+        <v>7.64380931854248</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.6069712638855</v>
+        <v>7.60697174072266</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1215" t="n">
-        <v>7.40436458587646</v>
+        <v>7.40436410903931</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1216" t="n">
-        <v>7.23859548568726</v>
+        <v>7.2385950088501</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1217" t="n">
-        <v>7.25701379776001</v>
+        <v>7.25701427459717</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1218" t="n">
-        <v>7.22017621994019</v>
+        <v>7.22017669677734</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.05440664291382</v>
+        <v>7.05440616607666</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.25701379776001</v>
+        <v>7.25701427459717</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>7.6069712638855</v>
+        <v>7.60697174072266</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590326309204</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1233" t="n">
-        <v>7.64380979537964</v>
+        <v>7.64380931854248</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -54088,6 +54088,32 @@
         <v>3.04999995231628</v>
       </c>
       <c r="H2066" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2067" t="n">
+        <v>9600</v>
+      </c>
+      <c r="C2067" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="G2067" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="H2067" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -551,7 +551,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G7" t="n">
-        <v>8.18035793304443</v>
+        <v>8.18035697937012</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11247158050537</v>
+        <v>8.11246967315674</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.1379280090332</v>
+        <v>8.13792705535889</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.54199981689453</v>
       </c>
       <c r="G25" t="n">
-        <v>8.09719562530518</v>
+        <v>8.09719467163086</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G26" t="n">
-        <v>8.20666217803955</v>
+        <v>8.20666408538818</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G27" t="n">
-        <v>8.20666217803955</v>
+        <v>8.20666408538818</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.52799987792969</v>
       </c>
       <c r="G28" t="n">
-        <v>8.08531475067139</v>
+        <v>8.0853157043457</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0819206237793</v>
+        <v>8.08192157745361</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.07513236999512</v>
+        <v>8.07513332366943</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.43099975585938</v>
       </c>
       <c r="G34" t="n">
-        <v>8.00300312042236</v>
+        <v>8.00300216674805</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01063823699951</v>
+        <v>8.01064014434814</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366760253906</v>
+        <v>7.99366855621338</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.37100028991699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.95208740234375</v>
+        <v>7.95208787918091</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.33100032806396</v>
       </c>
       <c r="G39" t="n">
-        <v>7.91814374923706</v>
+        <v>7.91814470291138</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227121353149</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227121353149</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.97924184799194</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.97924184799194</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G44" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G45" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G48" t="n">
-        <v>7.90881061553955</v>
+        <v>7.90880918502808</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729640960693</v>
+        <v>7.91729593276978</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619831085205</v>
+        <v>7.85619735717773</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G52" t="n">
-        <v>7.75097274780273</v>
+        <v>7.75097370147705</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G54" t="n">
-        <v>7.78237152099609</v>
+        <v>7.78237056732178</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G55" t="n">
-        <v>7.78237152099609</v>
+        <v>7.78237056732178</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G56" t="n">
-        <v>7.76709604263306</v>
+        <v>7.76709651947021</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697917938232</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697917938232</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697917938232</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.80528211593628</v>
+        <v>7.80528354644775</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722993850708</v>
+        <v>7.86722898483276</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746271133423</v>
+        <v>7.78746175765991</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746271133423</v>
+        <v>7.78746175765991</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>7.85534858703613</v>
+        <v>7.85534954071045</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761173248291</v>
+        <v>8.02761077880859</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177255630493</v>
+        <v>7.84177160263062</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.790855884552</v>
+        <v>7.79085636138916</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243703842163</v>
+        <v>7.83243656158447</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358505249023</v>
+        <v>7.80358552932739</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.80103826522827</v>
+        <v>7.8010401725769</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G87" t="n">
-        <v>7.81037378311157</v>
+        <v>7.81037473678589</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098930358887</v>
+        <v>7.89098978042603</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782794952393</v>
+        <v>7.80782890319824</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.76879262924194</v>
+        <v>7.76879358291626</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.76879262924194</v>
+        <v>7.76879358291626</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408561706543</v>
+        <v>7.92408514022827</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.7704906463623</v>
+        <v>7.77049016952515</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70514965057373</v>
+        <v>7.70514917373657</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969226837158</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969226837158</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726186752319</v>
+        <v>7.63726234436035</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423583984375</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423583984375</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>7.55240392684937</v>
+        <v>7.55240440368652</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.8290433883667</v>
+        <v>7.82904291152954</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>9.10099983215332</v>
       </c>
       <c r="G108" t="n">
-        <v>7.72296953201294</v>
+        <v>7.7229700088501</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70514965057373</v>
+        <v>7.70514917373657</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70514965057373</v>
+        <v>7.70514917373657</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817758560181</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969226837158</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902635574341</v>
+        <v>7.68902587890625</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110569000244</v>
+        <v>7.85110521316528</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308639526367</v>
+        <v>7.68308734893799</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817758560181</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.76879262924194</v>
+        <v>7.76879358291626</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.86553192138672</v>
+        <v>7.8655309677124</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152179718018</v>
+        <v>7.78152275085449</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303552627563</v>
+        <v>7.77303600311279</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303552627563</v>
+        <v>7.77303600311279</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243703842163</v>
+        <v>7.83243656158447</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.7984938621521</v>
+        <v>7.79849338531494</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000854492188</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000854492188</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445085525513</v>
+        <v>7.94445037841797</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.7984938621521</v>
+        <v>7.79849338531494</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697917938232</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>8.07004165649414</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.32100009918213</v>
       </c>
       <c r="G148" t="n">
-        <v>7.90965890884399</v>
+        <v>7.90965795516968</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579780578613</v>
+        <v>8.06579875946045</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.92832803726196</v>
+        <v>7.92832851409912</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.34700012207031</v>
       </c>
       <c r="G159" t="n">
-        <v>7.93172216415405</v>
+        <v>7.93172168731689</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.44299983978271</v>
       </c>
       <c r="G160" t="n">
-        <v>8.01318645477295</v>
+        <v>8.01318550109863</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.4040002822876</v>
       </c>
       <c r="G163" t="n">
-        <v>7.98009157180786</v>
+        <v>7.9800910949707</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>8.05306911468506</v>
+        <v>8.05306816101074</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.92832803726196</v>
+        <v>7.92832851409912</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G167" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G177" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G180" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G255" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G320" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G352" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G353" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.75</v>
       </c>
       <c r="G379" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>9.75</v>
       </c>
       <c r="G394" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G409" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.25</v>
       </c>
       <c r="G410" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G415" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669553756714</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.75</v>
       </c>
       <c r="G440" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.75</v>
       </c>
       <c r="G443" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.75</v>
       </c>
       <c r="G444" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.75</v>
       </c>
       <c r="G445" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.75</v>
       </c>
       <c r="G446" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>9.75</v>
       </c>
       <c r="G448" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.75</v>
       </c>
       <c r="G449" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>9.75</v>
       </c>
       <c r="G450" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.75</v>
       </c>
       <c r="G451" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.75</v>
       </c>
       <c r="G452" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>9.75</v>
       </c>
       <c r="G453" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.75</v>
       </c>
       <c r="G454" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.75</v>
       </c>
       <c r="G456" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>9.75</v>
       </c>
       <c r="G457" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>9.75</v>
       </c>
       <c r="G460" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>9.75</v>
       </c>
       <c r="G461" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>9.75</v>
       </c>
       <c r="G462" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>9.75</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>9.75</v>
       </c>
       <c r="G464" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.75</v>
       </c>
       <c r="G465" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.75</v>
       </c>
       <c r="G466" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>9.75</v>
       </c>
       <c r="G467" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>9.75</v>
       </c>
       <c r="G468" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.75</v>
       </c>
       <c r="G470" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.75</v>
       </c>
       <c r="G474" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.75</v>
       </c>
       <c r="G475" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.75</v>
       </c>
       <c r="G476" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.75</v>
       </c>
       <c r="G479" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.75</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>9.75</v>
       </c>
       <c r="G481" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G482" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>9.75</v>
       </c>
       <c r="G483" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.75</v>
       </c>
       <c r="G484" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.75</v>
       </c>
       <c r="G485" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>9.75</v>
       </c>
       <c r="G486" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.75</v>
       </c>
       <c r="G509" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>8.2312707901001</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>9.75</v>
       </c>
       <c r="G541" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.75</v>
       </c>
       <c r="G542" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>7.59483242034912</v>
+        <v>7.5948338508606</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G556" t="n">
-        <v>7.59483242034912</v>
+        <v>7.5948338508606</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782915115356</v>
+        <v>7.29782962799072</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>7.12811136245728</v>
+        <v>7.12811231613159</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>6.49167394638062</v>
+        <v>6.49167346954346</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867721557617</v>
+        <v>6.78867816925049</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867721557617</v>
+        <v>6.78867816925049</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867721557617</v>
+        <v>6.78867816925049</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G571" t="n">
-        <v>6.94854879379272</v>
+        <v>6.94854831695557</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.73004007339478</v>
+        <v>6.73004055023193</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.46783113479614</v>
+        <v>6.4678316116333</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G574" t="n">
-        <v>6.73004007339478</v>
+        <v>6.73004055023193</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>8.25</v>
       </c>
       <c r="G575" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>7.16705560684204</v>
+        <v>7.16705656051636</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.5</v>
       </c>
       <c r="G580" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926597595215</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G583" t="n">
-        <v>7.77887773513794</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147539138794</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>7.77887773513794</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147539138794</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G587" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147539138794</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G588" t="n">
-        <v>7.77887773513794</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G596" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56036996841431</v>
+        <v>7.56037044525146</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556432723999</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G605" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>8.5</v>
       </c>
       <c r="G606" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926597595215</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>7.60407257080078</v>
+        <v>7.60407304763794</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G609" t="n">
-        <v>7.77887773513794</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G610" t="n">
-        <v>7.77887773513794</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.86628198623657</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.86628198623657</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95368480682373</v>
+        <v>7.95368432998657</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.5</v>
       </c>
       <c r="G617" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926597595215</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147539138794</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.5</v>
       </c>
       <c r="G619" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926597595215</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>8.5</v>
       </c>
       <c r="G620" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926597595215</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556432723999</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556432723999</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G624" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556432723999</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G626" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.25</v>
       </c>
       <c r="G627" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G632" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816198348999</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G634" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816198348999</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G636" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816198348999</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.16705560684204</v>
+        <v>7.16705656051636</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G646" t="n">
-        <v>7.07965421676636</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G650" t="n">
-        <v>7.07965421676636</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G651" t="n">
-        <v>7.07965421676636</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484619140625</v>
+        <v>6.90484714508057</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G655" t="n">
-        <v>7.07965421676636</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G656" t="n">
-        <v>7.16705560684204</v>
+        <v>7.16705656051636</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>8.25</v>
       </c>
       <c r="G657" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>8.25</v>
       </c>
       <c r="G658" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>7.16705560684204</v>
+        <v>7.16705656051636</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G661" t="n">
-        <v>7.03595161437988</v>
+        <v>7.03595209121704</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556432723999</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G663" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816198348999</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556432723999</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>8.5</v>
       </c>
       <c r="G666" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926597595215</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147539138794</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G668" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.86628198623657</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86628198623657</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G672" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G673" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.86628198623657</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.86628198623657</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.86628198623657</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.86628198623657</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G679" t="n">
-        <v>7.77887773513794</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G680" t="n">
-        <v>7.77887773513794</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60407257080078</v>
+        <v>7.60407304763794</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G683" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738645553589</v>
+        <v>7.99738502502441</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>7.77887773513794</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G686" t="n">
-        <v>7.77887773513794</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>7.60407257080078</v>
+        <v>7.60407304763794</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G689" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G690" t="n">
-        <v>8.17219257354736</v>
+        <v>8.17219161987305</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738645553589</v>
+        <v>7.99738502502441</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>8.12849044799805</v>
+        <v>8.12848949432373</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>8.12849044799805</v>
+        <v>8.12848949432373</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G708" t="n">
-        <v>8.12276363372803</v>
+        <v>8.12276268005371</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G709" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G711" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G712" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G713" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>9</v>
       </c>
       <c r="G714" t="n">
-        <v>8.07788753509521</v>
+        <v>8.07788562774658</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>9</v>
       </c>
       <c r="G715" t="n">
-        <v>8.07788753509521</v>
+        <v>8.07788562774658</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G716" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G717" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G733" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G737" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G738" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98813104629517</v>
+        <v>7.98813247680664</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G740" t="n">
-        <v>8.12276363372803</v>
+        <v>8.12276268005371</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G741" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G743" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G744" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G745" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G749" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G751" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G754" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G757" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G758" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G764" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G772" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>10</v>
       </c>
       <c r="G774" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>10</v>
       </c>
       <c r="G775" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>9.78321838378906</v>
+        <v>9.78321743011475</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>9.96272850036621</v>
+        <v>9.96272754669189</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>9.60371017456055</v>
+        <v>9.60370922088623</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>9.78321838378906</v>
+        <v>9.78321743011475</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G786" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>10</v>
       </c>
       <c r="G791" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>10</v>
       </c>
       <c r="G793" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G795" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>9.75</v>
       </c>
       <c r="G802" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>9.75</v>
       </c>
       <c r="G808" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>9.75</v>
       </c>
       <c r="G813" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G817" t="n">
-        <v>8.43690395355225</v>
+        <v>8.43690299987793</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G818" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G820" t="n">
-        <v>8.43690395355225</v>
+        <v>8.43690299987793</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>8.48178005218506</v>
+        <v>8.48178100585938</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>10</v>
       </c>
       <c r="G834" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G836" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>9.75</v>
       </c>
       <c r="G839" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G840" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G841" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>9.75</v>
       </c>
       <c r="G842" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G843" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>9.75</v>
       </c>
       <c r="G844" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G851" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G852" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G854" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G859" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>10</v>
       </c>
       <c r="G872" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10</v>
       </c>
       <c r="G873" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G874" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10</v>
       </c>
       <c r="G875" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10</v>
       </c>
       <c r="G876" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G877" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>10</v>
       </c>
       <c r="G889" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G898" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G901" t="n">
-        <v>8.43690395355225</v>
+        <v>8.43690299987793</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G904" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>9</v>
       </c>
       <c r="G905" t="n">
-        <v>8.07788753509521</v>
+        <v>8.07788562774658</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>8.12276363372803</v>
+        <v>8.12276268005371</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G907" t="n">
-        <v>7.98813104629517</v>
+        <v>7.98813247680664</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G910" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.3598518371582</v>
+        <v>7.35985231399536</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423805236816</v>
+        <v>7.58423852920532</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423805236816</v>
+        <v>7.58423852920532</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G914" t="n">
-        <v>7.98813104629517</v>
+        <v>7.98813247680664</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862379074097</v>
+        <v>7.80862426757812</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G917" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G921" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G923" t="n">
-        <v>8.48178005218506</v>
+        <v>8.48178100585938</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G924" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G926" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G927" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G928" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10</v>
       </c>
       <c r="G931" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231418609619</v>
+        <v>8.65231513977051</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G933" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.54460906982422</v>
+        <v>8.54461002349854</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821620941162</v>
+        <v>8.68821716308594</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G937" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G938" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G945" t="n">
-        <v>9.06205749511719</v>
+        <v>9.0620584487915</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G946" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G950" t="n">
-        <v>9.11731338500977</v>
+        <v>9.11731433868408</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>9.30150318145752</v>
+        <v>9.3015022277832</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G953" t="n">
-        <v>9.11731338500977</v>
+        <v>9.11731433868408</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>9.06205749511719</v>
+        <v>9.0620584487915</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G959" t="n">
-        <v>9.00680160522461</v>
+        <v>9.00680065155029</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G963" t="n">
-        <v>9.04363918304443</v>
+        <v>9.04363822937012</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G964" t="n">
-        <v>9.00680160522461</v>
+        <v>9.00680065155029</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G965" t="n">
-        <v>8.84103202819824</v>
+        <v>8.84103298187256</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G967" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G978" t="n">
-        <v>8.84103202819824</v>
+        <v>8.84103298187256</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G982" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>9</v>
       </c>
       <c r="G989" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>9</v>
       </c>
       <c r="G993" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G998" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G999" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423698425293</v>
+        <v>8.45423793792725</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1012" t="n">
-        <v>8.17795467376709</v>
+        <v>8.17795562744141</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>9</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>9</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>9</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>7.9753475189209</v>
+        <v>7.97534799575806</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>7.71748447418213</v>
+        <v>7.71748399734497</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.88325357437134</v>
+        <v>7.8832540512085</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.73051929473877</v>
+        <v>8.73051834106445</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>9</v>
       </c>
       <c r="G1055" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1058" t="n">
-        <v>8.73051929473877</v>
+        <v>8.73051834106445</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1059" t="n">
-        <v>8.73051929473877</v>
+        <v>8.73051834106445</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.17795467376709</v>
+        <v>8.17795562744141</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.49107551574707</v>
+        <v>8.49107456207275</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1130" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1131" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1132" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1135" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1136" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1137" t="n">
-        <v>8.73051929473877</v>
+        <v>8.73051834106445</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1139" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1142" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1146" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1150" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1152" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.00680160522461</v>
+        <v>9.00680065155029</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.84103202819824</v>
+        <v>8.84103298187256</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1159" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1165" t="n">
-        <v>8.58316802978516</v>
+        <v>8.58316898345947</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1178" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1179" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1180" t="n">
-        <v>8.58316802978516</v>
+        <v>8.58316898345947</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1182" t="n">
-        <v>8.49107551574707</v>
+        <v>8.49107456207275</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1187" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1188" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1189" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>9</v>
       </c>
       <c r="G1190" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>9</v>
       </c>
       <c r="G1192" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>9</v>
       </c>
       <c r="G1193" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>9</v>
       </c>
       <c r="G1194" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>9</v>
       </c>
       <c r="G1195" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1197" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>9</v>
       </c>
       <c r="G1204" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>8.5</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.82799673080444</v>
+        <v>7.8279972076416</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1208" t="n">
-        <v>7.80957794189453</v>
+        <v>7.80957746505737</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590278625488</v>
+        <v>7.73590230941772</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>8.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.82799673080444</v>
+        <v>7.8279972076416</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.80957794189453</v>
+        <v>7.80957746505737</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.49645853042603</v>
+        <v>7.49645900726318</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1217" t="n">
-        <v>7.25701427459717</v>
+        <v>7.25701379776001</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.05440616607666</v>
+        <v>7.05440664291382</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.25701427459717</v>
+        <v>7.25701379776001</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590278625488</v>
+        <v>7.73590230941772</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.71748447418213</v>
+        <v>7.71748399734497</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.49807548522949</v>
+        <v>7.49807500839233</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.30728387832642</v>
+        <v>7.30728435516357</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.4217586517334</v>
+        <v>7.42175912857056</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.59347009658813</v>
+        <v>7.59347057342529</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.19281005859375</v>
+        <v>7.19280958175659</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.61254978179932</v>
+        <v>7.61254930496216</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.22307872772217</v>
+        <v>8.22307968139648</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.80334091186523</v>
+        <v>7.80334043502808</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.91781520843506</v>
+        <v>7.9178147315979</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.30728387832642</v>
+        <v>7.30728435516357</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.30728387832642</v>
+        <v>7.30728435516357</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.61254978179932</v>
+        <v>7.61254930496216</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.76518201828003</v>
+        <v>7.76518249511719</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1290" t="n">
-        <v>7.80334091186523</v>
+        <v>7.80334043502808</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.86057710647583</v>
+        <v>7.86057758331299</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.86057710647583</v>
+        <v>7.86057758331299</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1294" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1300" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.49807548522949</v>
+        <v>7.49807500839233</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.2500467300415</v>
+        <v>7.25004720687866</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.08622407913208</v>
+        <v>6.08622360229492</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.42964696884155</v>
+        <v>6.42964649200439</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.42964696884155</v>
+        <v>6.42964649200439</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>6.18161869049072</v>
+        <v>6.18161916732788</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>6.25793552398682</v>
+        <v>6.25793504714966</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1344" t="n">
-        <v>6.37240982055664</v>
+        <v>6.37240934371948</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>6.73491239547729</v>
+        <v>6.73491191864014</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.42964696884155</v>
+        <v>6.42964649200439</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1362" t="n">
-        <v>6.62043762207031</v>
+        <v>6.62043809890747</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1370" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.62043762207031</v>
+        <v>6.62043809890747</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1372" t="n">
-        <v>6.62043762207031</v>
+        <v>6.62043809890747</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.62043762207031</v>
+        <v>6.62043809890747</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1382" t="n">
-        <v>6.44872617721558</v>
+        <v>6.44872665405273</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1386" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.42964696884155</v>
+        <v>6.42964649200439</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1394" t="n">
-        <v>6.23885583877563</v>
+        <v>6.23885631561279</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1396" t="n">
-        <v>6.37240982055664</v>
+        <v>6.37240934371948</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>6.08622407913208</v>
+        <v>6.08622360229492</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1400" t="n">
-        <v>6.08622407913208</v>
+        <v>6.08622360229492</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1403" t="n">
-        <v>5.85727453231812</v>
+        <v>5.85727500915527</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1408" t="n">
-        <v>5.91451215744019</v>
+        <v>5.91451168060303</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.08622407913208</v>
+        <v>6.08622360229492</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.12438154220581</v>
+        <v>6.12438201904297</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1422" t="n">
-        <v>5.95267009735107</v>
+        <v>5.95266962051392</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>5.78095865249634</v>
+        <v>5.78095817565918</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1431" t="n">
-        <v>5.91451215744019</v>
+        <v>5.91451168060303</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.32306098937988</v>
+        <v>5.32306051254272</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.53293037414551</v>
+        <v>5.53293085098267</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1442" t="n">
-        <v>5.58062791824341</v>
+        <v>5.58062839508057</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>5.34213972091675</v>
+        <v>5.34214019775391</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1448" t="n">
-        <v>5.34213972091675</v>
+        <v>5.34214019775391</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>5.34213972091675</v>
+        <v>5.34214019775391</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.43753528594971</v>
+        <v>5.43753480911255</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.58062791824341</v>
+        <v>5.58062839508057</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -54114,6 +54114,32 @@
         <v>3.04999995231628</v>
       </c>
       <c r="H2067" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2068" t="n">
+        <v>12600</v>
+      </c>
+      <c r="C2068" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G2068" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="H2068" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -525,7 +525,7 @@
         <v>9.61100006103516</v>
       </c>
       <c r="G6" t="n">
-        <v>8.15574836730957</v>
+        <v>8.15574741363525</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549713134766</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549713134766</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549713134766</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10058975219727</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10058975219727</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549713134766</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549713134766</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10653018951416</v>
+        <v>8.10653114318848</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.13792705535889</v>
+        <v>8.1379280090332</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852745056152</v>
+        <v>8.07852840423584</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G26" t="n">
-        <v>8.20666408538818</v>
+        <v>8.20666313171387</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G27" t="n">
-        <v>8.20666408538818</v>
+        <v>8.20666313171387</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>9.52799987792969</v>
       </c>
       <c r="G28" t="n">
-        <v>8.0853157043457</v>
+        <v>8.08531475067139</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G29" t="n">
-        <v>8.08192157745361</v>
+        <v>8.0819206237793</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>9.50100040435791</v>
       </c>
       <c r="G31" t="n">
-        <v>8.06240367889404</v>
+        <v>8.06240463256836</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10058975219727</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.07513332366943</v>
+        <v>8.07513236999512</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.43099975585938</v>
       </c>
       <c r="G34" t="n">
-        <v>8.00300216674805</v>
+        <v>8.00300312042236</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.44699954986572</v>
       </c>
       <c r="G36" t="n">
-        <v>8.01658058166504</v>
+        <v>8.01657867431641</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366855621338</v>
+        <v>7.99366760253906</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227073669434</v>
+        <v>7.96227169036865</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227073669434</v>
+        <v>7.96227169036865</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924280166626</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924280166626</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G44" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G45" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G48" t="n">
-        <v>7.90880918502808</v>
+        <v>7.90881013870239</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619735717773</v>
+        <v>7.85619783401489</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G52" t="n">
-        <v>7.75097370147705</v>
+        <v>7.75097227096558</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.774733543396</v>
+        <v>7.77473258972168</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.20699977874756</v>
       </c>
       <c r="G69" t="n">
-        <v>7.81291961669922</v>
+        <v>7.81292009353638</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.80528354644775</v>
+        <v>7.8052830696106</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746175765991</v>
+        <v>7.78746318817139</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746175765991</v>
+        <v>7.78746318817139</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>7.85534954071045</v>
+        <v>7.85534906387329</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761077880859</v>
+        <v>8.02761173248291</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177160263062</v>
+        <v>7.84177207946777</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243608474731</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358552932739</v>
+        <v>7.80358505249023</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406810760498</v>
+        <v>7.78406763076782</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.8010401725769</v>
+        <v>7.80103874206543</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782890319824</v>
+        <v>7.8078293800354</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.76879358291626</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.76879358291626</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408514022827</v>
+        <v>7.92408466339111</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G97" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969131469727</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969131469727</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726234436035</v>
+        <v>7.63726282119751</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423583984375</v>
+        <v>7.65423440933228</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423583984375</v>
+        <v>7.65423440933228</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>7.55240440368652</v>
+        <v>7.55240297317505</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904291152954</v>
+        <v>7.82904195785522</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G109" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363592147827</v>
+        <v>7.71363544464111</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817758560181</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969131469727</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110521316528</v>
+        <v>7.8511061668396</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273675918579</v>
+        <v>7.80273771286011</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308734893799</v>
+        <v>7.68308687210083</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G119" t="n">
-        <v>7.69666385650635</v>
+        <v>7.69666433334351</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G120" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G121" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817758560181</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.76879358291626</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152275085449</v>
+        <v>7.78152227401733</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406810760498</v>
+        <v>7.78406763076782</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303552627563</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303552627563</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243608474731</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.79849338531494</v>
+        <v>7.79849243164062</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000759124756</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000759124756</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445037841797</v>
+        <v>7.94445085525513</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.79849338531494</v>
+        <v>7.79849243164062</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G140" t="n">
-        <v>7.96311855316162</v>
+        <v>7.96311902999878</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579875946045</v>
+        <v>8.06579780578613</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.92832851409912</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G156" t="n">
-        <v>8.06664562225342</v>
+        <v>8.06664657592773</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G157" t="n">
-        <v>8.06664562225342</v>
+        <v>8.06664657592773</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G158" t="n">
-        <v>8.06664562225342</v>
+        <v>8.06664657592773</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.34700012207031</v>
       </c>
       <c r="G159" t="n">
-        <v>7.93172168731689</v>
+        <v>7.93172264099121</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.44299983978271</v>
       </c>
       <c r="G160" t="n">
-        <v>8.01318550109863</v>
+        <v>8.01318645477295</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G162" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.92832851409912</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G177" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G180" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G255" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G265" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G266" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G267" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G293" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G294" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G295" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G320" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G326" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G336" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G337" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G345" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G346" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G347" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G350" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G352" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G353" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G409" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G415" t="n">
-        <v>7.97669553756714</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G427" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G433" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G482" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.14641380310059</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G516" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G518" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>8.44341850280762</v>
+        <v>8.4434175491333</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183807373047</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782962799072</v>
+        <v>7.29782867431641</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>7.12811231613159</v>
+        <v>7.12811183929443</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66139030456543</v>
+        <v>6.66138982772827</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G560" t="n">
-        <v>6.10980987548828</v>
+        <v>6.10981035232544</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>6.10980987548828</v>
+        <v>6.10981035232544</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>6.83110761642456</v>
+        <v>6.8311071395874</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>6.7038197517395</v>
+        <v>6.70381927490234</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>6.7038197517395</v>
+        <v>6.70381927490234</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>6.68633890151978</v>
+        <v>6.68633937835693</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G571" t="n">
-        <v>6.94854831695557</v>
+        <v>6.94854879379272</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.73004055023193</v>
+        <v>6.73004007339478</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.4678316116333</v>
+        <v>6.46783113479614</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G574" t="n">
-        <v>6.73004055023193</v>
+        <v>6.73004007339478</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>8.25</v>
       </c>
       <c r="G575" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.5</v>
       </c>
       <c r="G580" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G581" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G583" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887678146362</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887678146362</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G588" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887678146362</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517751693726</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G596" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56037044525146</v>
+        <v>7.56036996841431</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517751693726</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G605" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>8.5</v>
       </c>
       <c r="G606" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>7.60407304763794</v>
+        <v>7.60407209396362</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G609" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887678146362</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G610" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887678146362</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95368432998657</v>
+        <v>7.95368528366089</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517751693726</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.5</v>
       </c>
       <c r="G617" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.5</v>
       </c>
       <c r="G619" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>8.5</v>
       </c>
       <c r="G620" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G624" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G626" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.25</v>
       </c>
       <c r="G627" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G631" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G632" t="n">
-        <v>7.29816198348999</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G634" t="n">
-        <v>7.29816198348999</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G636" t="n">
-        <v>7.29816198348999</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>8</v>
       </c>
       <c r="G640" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>8</v>
       </c>
       <c r="G641" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>8</v>
       </c>
       <c r="G642" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>8</v>
       </c>
       <c r="G644" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>8</v>
       </c>
       <c r="G645" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G647" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G648" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G649" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484714508057</v>
+        <v>6.90484666824341</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>8</v>
       </c>
       <c r="G653" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>8</v>
       </c>
       <c r="G654" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G656" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>8.25</v>
       </c>
       <c r="G657" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>8.25</v>
       </c>
       <c r="G658" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G661" t="n">
-        <v>7.03595209121704</v>
+        <v>7.03595161437988</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G663" t="n">
-        <v>7.29816198348999</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>8.5</v>
       </c>
       <c r="G666" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G671" t="n">
-        <v>7.90998220443726</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G672" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G673" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G679" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887678146362</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G680" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887678146362</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60407304763794</v>
+        <v>7.60407209396362</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G683" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738597869873</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887678146362</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G686" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887678146362</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>7.60407304763794</v>
+        <v>7.60407209396362</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G689" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G690" t="n">
-        <v>8.17219161987305</v>
+        <v>8.17219257354736</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>7.90998220443726</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>7.90998220443726</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738597869873</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>8.12848949432373</v>
+        <v>8.12849044799805</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>8.12848949432373</v>
+        <v>8.12849044799805</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G708" t="n">
-        <v>8.12276268005371</v>
+        <v>8.12276363372803</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G712" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G713" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>9</v>
       </c>
       <c r="G714" t="n">
-        <v>8.07788562774658</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>9</v>
       </c>
       <c r="G715" t="n">
-        <v>8.07788562774658</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G716" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813104629517</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G740" t="n">
-        <v>8.12276268005371</v>
+        <v>8.12276363372803</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G741" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G749" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G757" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G758" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G764" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>10</v>
       </c>
       <c r="G774" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>10</v>
       </c>
       <c r="G775" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>10.5</v>
       </c>
       <c r="G776" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>9.78321743011475</v>
+        <v>9.78321838378906</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>9.78321743011475</v>
+        <v>9.78321838378906</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G786" t="n">
-        <v>9.24469375610352</v>
+        <v>9.2446928024292</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.5</v>
       </c>
       <c r="G787" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>9.33444786071777</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>9.24469375610352</v>
+        <v>9.2446928024292</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>10</v>
       </c>
       <c r="G791" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>10</v>
       </c>
       <c r="G793" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G795" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>9.75</v>
       </c>
       <c r="G802" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>9.75</v>
       </c>
       <c r="G808" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>9.75</v>
       </c>
       <c r="G813" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G817" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G818" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G820" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>9.24469375610352</v>
+        <v>9.2446928024292</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>9.24469375610352</v>
+        <v>9.2446928024292</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>9.33444786071777</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>10</v>
       </c>
       <c r="G834" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G836" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>9.75</v>
       </c>
       <c r="G839" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G840" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G841" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>9.75</v>
       </c>
       <c r="G842" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G843" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>9.75</v>
       </c>
       <c r="G844" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G851" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G852" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G854" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G859" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>9.24469375610352</v>
+        <v>9.2446928024292</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>9.24469375610352</v>
+        <v>9.2446928024292</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>10.5</v>
       </c>
       <c r="G868" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>9.33444786071777</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>9.24469375610352</v>
+        <v>9.2446928024292</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>10</v>
       </c>
       <c r="G872" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10</v>
       </c>
       <c r="G873" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G874" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10</v>
       </c>
       <c r="G875" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10</v>
       </c>
       <c r="G876" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G877" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.5</v>
       </c>
       <c r="G880" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>9.33444786071777</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.5</v>
       </c>
       <c r="G884" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>10.5</v>
       </c>
       <c r="G885" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.5</v>
       </c>
       <c r="G886" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>9.33444786071777</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>10</v>
       </c>
       <c r="G889" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G898" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.065185546875</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G901" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>9</v>
       </c>
       <c r="G905" t="n">
-        <v>8.07788562774658</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>8.12276268005371</v>
+        <v>8.12276363372803</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G907" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813104629517</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G910" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.35985231399536</v>
+        <v>7.3598518371582</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423852920532</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423852920532</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G914" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813104629517</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G917" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G921" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G923" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G924" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G926" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G927" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G928" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10</v>
       </c>
       <c r="G931" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231513977051</v>
+        <v>8.65231418609619</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G933" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821716308594</v>
+        <v>8.68821620941162</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G937" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G938" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G943" t="n">
-        <v>8.84977245330811</v>
+        <v>8.84977340698242</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G945" t="n">
-        <v>9.0620584487915</v>
+        <v>9.06205749511719</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G946" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G950" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>9.3015022277832</v>
+        <v>9.30150318145752</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G953" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>9.0620584487915</v>
+        <v>9.06205749511719</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G959" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G963" t="n">
-        <v>9.04363822937012</v>
+        <v>9.04363918304443</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G964" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G965" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G967" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G978" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G982" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>9</v>
       </c>
       <c r="G989" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>9</v>
       </c>
       <c r="G993" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G998" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G999" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423793792725</v>
+        <v>8.45423698425293</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1012" t="n">
-        <v>8.17795562744141</v>
+        <v>8.17795467376709</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>9</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>9</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>9</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>7.97534799575806</v>
+        <v>7.9753475189209</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.8832540512085</v>
+        <v>7.88325357437134</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>9</v>
       </c>
       <c r="G1055" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1058" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1059" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.17795562744141</v>
+        <v>8.17795467376709</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1130" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1131" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1132" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1135" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1136" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1137" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1139" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1142" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1146" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1150" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1152" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1159" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1165" t="n">
-        <v>8.58316898345947</v>
+        <v>8.58316802978516</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1178" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1179" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1180" t="n">
-        <v>8.58316898345947</v>
+        <v>8.58316802978516</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1182" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1187" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1188" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1189" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>9</v>
       </c>
       <c r="G1190" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>9</v>
       </c>
       <c r="G1192" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>9</v>
       </c>
       <c r="G1193" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>9</v>
       </c>
       <c r="G1194" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>9</v>
       </c>
       <c r="G1195" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1197" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>9</v>
       </c>
       <c r="G1204" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>8.5</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.8279972076416</v>
+        <v>7.82799673080444</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1208" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590230941772</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>8.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.8279972076416</v>
+        <v>7.82799673080444</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.49645900726318</v>
+        <v>7.49645853042603</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1217" t="n">
-        <v>7.25701379776001</v>
+        <v>7.25701427459717</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.05440664291382</v>
+        <v>7.05440616607666</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.25701379776001</v>
+        <v>7.25701427459717</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590230941772</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.42175912857056</v>
+        <v>7.4217586517334</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.59347057342529</v>
+        <v>7.59347009658813</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.19280958175659</v>
+        <v>7.19281005859375</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.22307968139648</v>
+        <v>8.22307872772217</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.9178147315979</v>
+        <v>7.91781520843506</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.76518249511719</v>
+        <v>7.76518201828003</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1290" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1294" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1300" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.25004720687866</v>
+        <v>7.2500467300415</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>6.18161916732788</v>
+        <v>6.18161869049072</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>6.25793504714966</v>
+        <v>6.25793552398682</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1344" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>6.73491191864014</v>
+        <v>6.73491239547729</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1362" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1370" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1372" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1382" t="n">
-        <v>6.44872665405273</v>
+        <v>6.44872617721558</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1386" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1394" t="n">
-        <v>6.23885631561279</v>
+        <v>6.23885583877563</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1396" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1400" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1403" t="n">
-        <v>5.85727500915527</v>
+        <v>5.85727453231812</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1408" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.12438201904297</v>
+        <v>6.12438154220581</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1422" t="n">
-        <v>5.95266962051392</v>
+        <v>5.95267009735107</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>5.78095817565918</v>
+        <v>5.78095865249634</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1431" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.32306051254272</v>
+        <v>5.32306098937988</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.53293085098267</v>
+        <v>5.53293037414551</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1442" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1448" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.43753480911255</v>
+        <v>5.43753528594971</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -54140,6 +54140,32 @@
         <v>3.01999998092651</v>
       </c>
       <c r="H2068" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2069" t="n">
+        <v>13800</v>
+      </c>
+      <c r="C2069" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="D2069" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="G2069" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="H2069" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -421,7 +421,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549713134766</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.1379280090332</v>
+        <v>8.13792705535889</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852745056152</v>
+        <v>8.07852649688721</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.43099975585938</v>
       </c>
       <c r="G34" t="n">
-        <v>8.00300312042236</v>
+        <v>8.00300216674805</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01063919067383</v>
+        <v>8.01064014434814</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.33100032806396</v>
       </c>
       <c r="G39" t="n">
-        <v>7.91814470291138</v>
+        <v>7.91814374923706</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227264404297</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227264404297</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.97924327850342</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.97924327850342</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.93426752090454</v>
+        <v>7.93426656723022</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G52" t="n">
-        <v>7.75097274780273</v>
+        <v>7.75097370147705</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.77473258972168</v>
+        <v>7.77473449707031</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.80698013305664</v>
+        <v>7.80697822570801</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.80698013305664</v>
+        <v>7.80697822570801</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.80698013305664</v>
+        <v>7.80697822570801</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.80528354644775</v>
+        <v>7.80528259277344</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>7.85534858703613</v>
+        <v>7.85534954071045</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.80103921890259</v>
+        <v>7.8010401725769</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G87" t="n">
-        <v>7.81037473678589</v>
+        <v>7.81037378311157</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098978042603</v>
+        <v>7.89099025726318</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782794952393</v>
+        <v>7.80782890319824</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G97" t="n">
-        <v>7.72212028503418</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.72212028503418</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969274520874</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969274520874</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423440933228</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423440933228</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904195785522</v>
+        <v>7.82904291152954</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.72212028503418</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72212028503418</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363544464111</v>
+        <v>7.71363592147827</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817758560181</v>
+        <v>7.68817806243896</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969274520874</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902587890625</v>
+        <v>7.68902540206909</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273675918579</v>
+        <v>7.80273580551147</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308639526367</v>
+        <v>7.68308687210083</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G119" t="n">
-        <v>7.69666337966919</v>
+        <v>7.69666385650635</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G120" t="n">
-        <v>7.72212028503418</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G121" t="n">
-        <v>7.72212028503418</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817758560181</v>
+        <v>7.68817806243896</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152370452881</v>
+        <v>7.78152275085449</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303695678711</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303695678711</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.79849338531494</v>
+        <v>7.79849243164062</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000854492188</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000854492188</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445085525513</v>
+        <v>7.94445037841797</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.5</v>
       </c>
       <c r="G137" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.79849338531494</v>
+        <v>7.79849243164062</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.80698013305664</v>
+        <v>7.80697822570801</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.5</v>
       </c>
       <c r="G141" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.9283275604248</v>
+        <v>7.92832851409912</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.50800037384033</v>
       </c>
       <c r="G155" t="n">
-        <v>8.06834411621094</v>
+        <v>8.06834506988525</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.50800037384033</v>
       </c>
       <c r="G161" t="n">
-        <v>8.06834411621094</v>
+        <v>8.06834506988525</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.4040002822876</v>
       </c>
       <c r="G163" t="n">
-        <v>7.98009014129639</v>
+        <v>7.9800910949707</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.50800037384033</v>
       </c>
       <c r="G164" t="n">
-        <v>8.06834411621094</v>
+        <v>8.06834506988525</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>8.05306816101074</v>
+        <v>8.05306911468506</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.9283275604248</v>
+        <v>7.92832851409912</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.93426752090454</v>
+        <v>7.93426656723022</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.93426752090454</v>
+        <v>7.93426656723022</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.93426752090454</v>
+        <v>7.93426656723022</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.93426752090454</v>
+        <v>7.93426656723022</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.93426752090454</v>
+        <v>7.93426656723022</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.5</v>
       </c>
       <c r="G188" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.5</v>
       </c>
       <c r="G190" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.5</v>
       </c>
       <c r="G192" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.5</v>
       </c>
       <c r="G195" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.5</v>
       </c>
       <c r="G196" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.5</v>
       </c>
       <c r="G205" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.5</v>
       </c>
       <c r="G207" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G209" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.5</v>
       </c>
       <c r="G211" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.5</v>
       </c>
       <c r="G212" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G223" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G250" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G255" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G256" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.5</v>
       </c>
       <c r="G270" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.5</v>
       </c>
       <c r="G275" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.5</v>
       </c>
       <c r="G277" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.5</v>
       </c>
       <c r="G278" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.5</v>
       </c>
       <c r="G281" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.5</v>
       </c>
       <c r="G282" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.5</v>
       </c>
       <c r="G283" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.5</v>
       </c>
       <c r="G290" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.5</v>
       </c>
       <c r="G291" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.5</v>
       </c>
       <c r="G292" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G296" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.5</v>
       </c>
       <c r="G297" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.5</v>
       </c>
       <c r="G301" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.5</v>
       </c>
       <c r="G302" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.5</v>
       </c>
       <c r="G303" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.5</v>
       </c>
       <c r="G304" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.5</v>
       </c>
       <c r="G305" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>9.5</v>
       </c>
       <c r="G308" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G320" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G352" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G353" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G357" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G361" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>9.75</v>
       </c>
       <c r="G379" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G382" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G387" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>9.75</v>
       </c>
       <c r="G394" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.93426752090454</v>
+        <v>7.93426656723022</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.93426752090454</v>
+        <v>7.93426656723022</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.93426752090454</v>
+        <v>7.93426656723022</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.5</v>
       </c>
       <c r="G419" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G420" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G421" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.5</v>
       </c>
       <c r="G423" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G424" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.75</v>
       </c>
       <c r="G440" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.75</v>
       </c>
       <c r="G443" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.75</v>
       </c>
       <c r="G444" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>9.75</v>
       </c>
       <c r="G445" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>9.75</v>
       </c>
       <c r="G446" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>9.75</v>
       </c>
       <c r="G448" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>9.75</v>
       </c>
       <c r="G449" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>9.75</v>
       </c>
       <c r="G450" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>9.75</v>
       </c>
       <c r="G451" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>9.75</v>
       </c>
       <c r="G452" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>9.75</v>
       </c>
       <c r="G453" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>9.75</v>
       </c>
       <c r="G454" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.75</v>
       </c>
       <c r="G456" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>9.75</v>
       </c>
       <c r="G457" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>9.75</v>
       </c>
       <c r="G460" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>9.75</v>
       </c>
       <c r="G461" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>9.75</v>
       </c>
       <c r="G462" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>9.75</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>9.75</v>
       </c>
       <c r="G464" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>9.75</v>
       </c>
       <c r="G465" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>9.75</v>
       </c>
       <c r="G466" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>9.75</v>
       </c>
       <c r="G467" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>9.75</v>
       </c>
       <c r="G468" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>9.75</v>
       </c>
       <c r="G470" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>9.75</v>
       </c>
       <c r="G474" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>9.75</v>
       </c>
       <c r="G475" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>9.75</v>
       </c>
       <c r="G476" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>9.75</v>
       </c>
       <c r="G479" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>9.75</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>9.75</v>
       </c>
       <c r="G481" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G482" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>9.75</v>
       </c>
       <c r="G483" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.75</v>
       </c>
       <c r="G484" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.75</v>
       </c>
       <c r="G485" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>9.75</v>
       </c>
       <c r="G486" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G487" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G492" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G493" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G496" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G502" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G504" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.5</v>
       </c>
       <c r="G506" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>9.75</v>
       </c>
       <c r="G509" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G512" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G513" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G514" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G520" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G521" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G522" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G538" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G539" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G540" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>9.75</v>
       </c>
       <c r="G541" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>9.75</v>
       </c>
       <c r="G542" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G544" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G547" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>8.6555643081665</v>
+        <v>8.65556335449219</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>8.6555643081665</v>
+        <v>8.65556335449219</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>8.31612968444824</v>
+        <v>8.31613063812256</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782962799072</v>
+        <v>7.29783010482788</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>7.12811136245728</v>
+        <v>7.12811183929443</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66138982772827</v>
+        <v>6.66139030456543</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G560" t="n">
-        <v>6.10981035232544</v>
+        <v>6.10980987548828</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>6.10981035232544</v>
+        <v>6.10980987548828</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17054080963135</v>
+        <v>7.17054176330566</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>6.83110761642456</v>
+        <v>6.8311071395874</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G571" t="n">
-        <v>6.94854879379272</v>
+        <v>6.94854831695557</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.46783113479614</v>
+        <v>6.4678316116333</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G581" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G587" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G596" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56036949157715</v>
+        <v>7.56037092208862</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G605" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>7.60407209396362</v>
+        <v>7.60407257080078</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G624" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G626" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G631" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G647" t="n">
-        <v>7.12335443496704</v>
+        <v>7.12335395812988</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G648" t="n">
-        <v>7.12335443496704</v>
+        <v>7.12335395812988</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G649" t="n">
-        <v>7.12335443496704</v>
+        <v>7.12335395812988</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484714508057</v>
+        <v>6.90484666824341</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G661" t="n">
-        <v>7.03595209121704</v>
+        <v>7.03595161437988</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G671" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998220443726</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G672" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G673" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60407209396362</v>
+        <v>7.60407257080078</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G683" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>7.60407209396362</v>
+        <v>7.60407257080078</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G689" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G690" t="n">
-        <v>8.17219161987305</v>
+        <v>8.17219257354736</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998220443726</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998220443726</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G705" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G708" t="n">
-        <v>8.12276363372803</v>
+        <v>8.12276268005371</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>9</v>
       </c>
       <c r="G714" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788562774658</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>9</v>
       </c>
       <c r="G715" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788562774658</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G733" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G737" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G738" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G740" t="n">
-        <v>8.12276363372803</v>
+        <v>8.12276268005371</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G744" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G747" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G751" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G754" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G761" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G762" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G763" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G767" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G768" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G772" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>9.51395606994629</v>
+        <v>9.51395511627197</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>9.78321838378906</v>
+        <v>9.78321743011475</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>9.78321838378906</v>
+        <v>9.78321743011475</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>9.51395606994629</v>
+        <v>9.51395511627197</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>9.51395606994629</v>
+        <v>9.51395511627197</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G786" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G792" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G855" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444786071777</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518459320068</v>
+        <v>9.065185546875</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>8.79592037200928</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G902" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>9</v>
       </c>
       <c r="G905" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788562774658</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>8.12276363372803</v>
+        <v>8.12276268005371</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423757553101</v>
+        <v>7.58423852920532</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423757553101</v>
+        <v>7.58423852920532</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862331390381</v>
+        <v>7.80862426757812</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821620941162</v>
+        <v>8.68821716308594</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G941" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G943" t="n">
-        <v>8.84977340698242</v>
+        <v>8.84977245330811</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -54218,6 +54218,32 @@
         <v>3.04999995231628</v>
       </c>
       <c r="H2071" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2072" t="n">
+        <v>14900</v>
+      </c>
+      <c r="C2072" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D2072" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="G2072" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="H2072" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -48090,8 +48090,31 @@
       <c r="E2075" t="n">
         <v>2.98000001907349</v>
       </c>
-      <c r="F2075"/>
+      <c r="F2075" t="n">
+        <v>3.00999999046326</v>
+      </c>
       <c r="G2075" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2076" t="n">
+        <v>10600</v>
+      </c>
+      <c r="C2076" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="F2076"/>
+      <c r="G2076" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -48113,8 +48113,31 @@
       <c r="E2076" t="n">
         <v>3.00999999046326</v>
       </c>
-      <c r="F2076"/>
+      <c r="F2076" t="n">
+        <v>3.00999999046326</v>
+      </c>
       <c r="G2076" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2077" t="n">
+        <v>2300</v>
+      </c>
+      <c r="C2077" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F2077"/>
+      <c r="G2077" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -48136,8 +48136,31 @@
       <c r="E2077" t="n">
         <v>3.01999998092651</v>
       </c>
-      <c r="F2077"/>
+      <c r="F2077" t="n">
+        <v>3.01999998092651</v>
+      </c>
       <c r="G2077" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F2078"/>
+      <c r="G2078" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -48159,8 +48159,31 @@
       <c r="E2078" t="n">
         <v>3.01999998092651</v>
       </c>
-      <c r="F2078"/>
+      <c r="F2078" t="n">
+        <v>3.01999998092651</v>
+      </c>
       <c r="G2078" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="F2079"/>
+      <c r="G2079" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -48189,6 +48189,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2080">
+      <c r="A2080" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2080" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2080" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2080" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -499,7 +499,7 @@
         <v>9.60200023651123</v>
       </c>
       <c r="G5" t="n">
-        <v>8.14811229705811</v>
+        <v>8.14811134338379</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>9.61100006103516</v>
       </c>
       <c r="G6" t="n">
-        <v>8.15574836730957</v>
+        <v>8.15574741363525</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G7" t="n">
-        <v>8.18035793304443</v>
+        <v>8.18035697937012</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10058784484863</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10058784484863</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10653114318848</v>
+        <v>8.10653018951416</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>8.07003974914551</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852745056152</v>
+        <v>8.07852649688721</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>9.54199981689453</v>
       </c>
       <c r="G25" t="n">
-        <v>8.09719562530518</v>
+        <v>8.09719467163086</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G29" t="n">
-        <v>8.08192157745361</v>
+        <v>8.08192253112793</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>9.50100040435791</v>
       </c>
       <c r="G31" t="n">
-        <v>8.06240367889404</v>
+        <v>8.06240463256836</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10058784484863</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.0751314163208</v>
+        <v>8.07513236999512</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.43099975585938</v>
       </c>
       <c r="G34" t="n">
-        <v>8.00300216674805</v>
+        <v>8.00300312042236</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01063919067383</v>
+        <v>8.01063823699951</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>9.44699954986572</v>
       </c>
       <c r="G36" t="n">
-        <v>8.01658058166504</v>
+        <v>8.01657962799072</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366903305054</v>
+        <v>7.99366855621338</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.37100028991699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.95208740234375</v>
+        <v>7.95208835601807</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>9.33100032806396</v>
       </c>
       <c r="G39" t="n">
-        <v>7.91814470291138</v>
+        <v>7.91814565658569</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924137115479</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924137115479</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G44" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G45" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729497909546</v>
+        <v>7.91729545593262</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619831085205</v>
+        <v>7.85619783401489</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84941005706787</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G54" t="n">
-        <v>7.78237009048462</v>
+        <v>7.78237104415894</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G55" t="n">
-        <v>7.78237009048462</v>
+        <v>7.78237104415894</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G56" t="n">
-        <v>7.7670955657959</v>
+        <v>7.76709604263306</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84941005706787</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697870254517</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697870254517</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84941005706787</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697870254517</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.20699977874756</v>
       </c>
       <c r="G69" t="n">
-        <v>7.81291961669922</v>
+        <v>7.81292009353638</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.8052830696106</v>
+        <v>7.80528211593628</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722898483276</v>
+        <v>7.86722993850708</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746175765991</v>
+        <v>7.78746128082275</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746175765991</v>
+        <v>7.78746128082275</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G75" t="n">
-        <v>8.04882621765137</v>
+        <v>8.04882526397705</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761268615723</v>
+        <v>8.02761173248291</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.79085636138916</v>
+        <v>7.79085683822632</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>7.84516572952271</v>
+        <v>7.84516525268555</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243751525879</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358552932739</v>
+        <v>7.80358505249023</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406810760498</v>
+        <v>7.78406763076782</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.80103969573975</v>
+        <v>7.8010401725769</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098978042603</v>
+        <v>7.89098930358887</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782890319824</v>
+        <v>7.80782794952393</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408609390259</v>
+        <v>7.92408466339111</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.77048969268799</v>
+        <v>7.77049112319946</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G97" t="n">
-        <v>7.72212171554565</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.72212171554565</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70515060424805</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969131469727</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969131469727</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423345565796</v>
+        <v>7.65423440933228</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423345565796</v>
+        <v>7.65423440933228</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904243469238</v>
+        <v>7.8290433883667</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.72212171554565</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72212171554565</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70515060424805</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70515060424805</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817949295044</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969131469727</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902587890625</v>
+        <v>7.68902540206909</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110569000244</v>
+        <v>7.85110664367676</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273580551147</v>
+        <v>7.80273675918579</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308639526367</v>
+        <v>7.68308591842651</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G119" t="n">
-        <v>7.69666337966919</v>
+        <v>7.69666385650635</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G120" t="n">
-        <v>7.72212171554565</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G121" t="n">
-        <v>7.72212171554565</v>
+        <v>7.7221212387085</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817949295044</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9.14900016784668</v>
       </c>
       <c r="G124" t="n">
-        <v>7.76370191574097</v>
+        <v>7.76370286941528</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.86553335189819</v>
+        <v>7.86553192138672</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152179718018</v>
+        <v>7.78152275085449</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406810760498</v>
+        <v>7.78406763076782</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243751525879</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.79849433898926</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84941005706787</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000806808472</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000806808472</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445037841797</v>
+        <v>7.9444522857666</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.5</v>
       </c>
       <c r="G137" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.79849433898926</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697870254517</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G140" t="n">
-        <v>7.96311902999878</v>
+        <v>7.96311855316162</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.5</v>
       </c>
       <c r="G141" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>8.07003974914551</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>8.07003974914551</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>8.07003974914551</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>8.07003974914551</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>8.07003974914551</v>
+        <v>8.07004070281982</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G147" t="n">
-        <v>8.06919097900391</v>
+        <v>8.06919384002686</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.32100009918213</v>
       </c>
       <c r="G148" t="n">
-        <v>7.90965890884399</v>
+        <v>7.90965938568115</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579780578613</v>
+        <v>8.06579875946045</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G152" t="n">
-        <v>8.06919097900391</v>
+        <v>8.06919384002686</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G153" t="n">
-        <v>8.06919097900391</v>
+        <v>8.06919384002686</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.9283275604248</v>
+        <v>7.92832803726196</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.50800037384033</v>
       </c>
       <c r="G155" t="n">
-        <v>8.06834411621094</v>
+        <v>8.06834316253662</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G156" t="n">
-        <v>8.06664657592773</v>
+        <v>8.0666446685791</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G157" t="n">
-        <v>8.06664657592773</v>
+        <v>8.0666446685791</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G158" t="n">
-        <v>8.06664657592773</v>
+        <v>8.0666446685791</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.44299983978271</v>
       </c>
       <c r="G160" t="n">
-        <v>8.01318550109863</v>
+        <v>8.01318645477295</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.50800037384033</v>
       </c>
       <c r="G161" t="n">
-        <v>8.06834411621094</v>
+        <v>8.06834316253662</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G162" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.50800037384033</v>
       </c>
       <c r="G164" t="n">
-        <v>8.06834411621094</v>
+        <v>8.06834316253662</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>8.05307006835938</v>
+        <v>8.05306911468506</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.9283275604248</v>
+        <v>7.92832803726196</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G167" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84941005706787</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84941005706787</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84941005706787</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84941005706787</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G177" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G180" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>9.5</v>
       </c>
       <c r="G188" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.5</v>
       </c>
       <c r="G190" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>9.5</v>
       </c>
       <c r="G192" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.5</v>
       </c>
       <c r="G195" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>9.5</v>
       </c>
       <c r="G196" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>9.5</v>
       </c>
       <c r="G205" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>9.5</v>
       </c>
       <c r="G207" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>9.5</v>
       </c>
       <c r="G211" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>9.5</v>
       </c>
       <c r="G212" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>9.5</v>
       </c>
       <c r="G270" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.5</v>
       </c>
       <c r="G275" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.5</v>
       </c>
       <c r="G277" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.5</v>
       </c>
       <c r="G278" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.5</v>
       </c>
       <c r="G281" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>9.5</v>
       </c>
       <c r="G282" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>9.5</v>
       </c>
       <c r="G283" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>9.5</v>
       </c>
       <c r="G290" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>9.5</v>
       </c>
       <c r="G291" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.5</v>
       </c>
       <c r="G292" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>9.5</v>
       </c>
       <c r="G297" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>9.5</v>
       </c>
       <c r="G301" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>9.5</v>
       </c>
       <c r="G302" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.5</v>
       </c>
       <c r="G303" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.5</v>
       </c>
       <c r="G304" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.5</v>
       </c>
       <c r="G305" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>9.5</v>
       </c>
       <c r="G308" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G409" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>9.25</v>
       </c>
       <c r="G410" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84941005706787</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G415" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>9.5</v>
       </c>
       <c r="G419" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>9.5</v>
       </c>
       <c r="G423" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>9.5</v>
       </c>
       <c r="G506" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G526" t="n">
-        <v>8.4009895324707</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G527" t="n">
-        <v>8.4009895324707</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G528" t="n">
-        <v>8.4009895324707</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G529" t="n">
-        <v>8.4009895324707</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G530" t="n">
-        <v>8.4009895324707</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G532" t="n">
-        <v>8.4009895324707</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G533" t="n">
-        <v>8.4009895324707</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G534" t="n">
-        <v>8.4009895324707</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>8.44341850280762</v>
+        <v>8.4434175491333</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>7.59483289718628</v>
+        <v>7.59483242034912</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G556" t="n">
-        <v>7.59483289718628</v>
+        <v>7.59483242034912</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>7.12811183929443</v>
+        <v>7.12811136245728</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66138982772827</v>
+        <v>6.66139030456543</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>6.49167394638062</v>
+        <v>6.49167346954346</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>6.83110761642456</v>
+        <v>6.8311071395874</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867864608765</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867864608765</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867864608765</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>6.70381927490234</v>
+        <v>6.7038197517395</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>6.70381927490234</v>
+        <v>6.7038197517395</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G571" t="n">
-        <v>6.94854784011841</v>
+        <v>6.94854831695557</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.73004055023193</v>
+        <v>6.73004007339478</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.46783113479614</v>
+        <v>6.4678316116333</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G574" t="n">
-        <v>6.73004055023193</v>
+        <v>6.73004007339478</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>8.25</v>
       </c>
       <c r="G575" t="n">
-        <v>7.21075773239136</v>
+        <v>7.2107572555542</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>8.5</v>
       </c>
       <c r="G580" t="n">
-        <v>7.42926645278931</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G587" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G596" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56037044525146</v>
+        <v>7.56036996841431</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>7.47296714782715</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>7.47296714782715</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G605" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>8.5</v>
       </c>
       <c r="G606" t="n">
-        <v>7.42926645278931</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>7.60407114028931</v>
+        <v>7.60407161712646</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95368528366089</v>
+        <v>7.95368432998657</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>8.5</v>
       </c>
       <c r="G617" t="n">
-        <v>7.42926645278931</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.5</v>
       </c>
       <c r="G619" t="n">
-        <v>7.42926645278931</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>8.5</v>
       </c>
       <c r="G620" t="n">
-        <v>7.42926645278931</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.47296714782715</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G624" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G626" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.25</v>
       </c>
       <c r="G627" t="n">
-        <v>7.21075773239136</v>
+        <v>7.2107572555542</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>7.47296714782715</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>7.47296714782715</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.21075773239136</v>
+        <v>7.2107572555542</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>8</v>
       </c>
       <c r="G640" t="n">
-        <v>6.99225044250488</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>8</v>
       </c>
       <c r="G641" t="n">
-        <v>6.99225044250488</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>8</v>
       </c>
       <c r="G642" t="n">
-        <v>6.99225044250488</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>8</v>
       </c>
       <c r="G644" t="n">
-        <v>6.99225044250488</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>8</v>
       </c>
       <c r="G645" t="n">
-        <v>6.99225044250488</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G646" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G647" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G648" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G649" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G650" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G651" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484666824341</v>
+        <v>6.90484714508057</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>8</v>
       </c>
       <c r="G653" t="n">
-        <v>6.99225044250488</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>8</v>
       </c>
       <c r="G654" t="n">
-        <v>6.99225044250488</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G655" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G656" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>8.25</v>
       </c>
       <c r="G657" t="n">
-        <v>7.21075773239136</v>
+        <v>7.2107572555542</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>8.25</v>
       </c>
       <c r="G658" t="n">
-        <v>7.21075773239136</v>
+        <v>7.2107572555542</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G661" t="n">
-        <v>7.03595209121704</v>
+        <v>7.03595161437988</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>8.5</v>
       </c>
       <c r="G666" t="n">
-        <v>7.42926645278931</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G668" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G671" t="n">
-        <v>7.90998220443726</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G672" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G673" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60407114028931</v>
+        <v>7.60407161712646</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G683" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738597869873</v>
+        <v>7.99738502502441</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777278900146</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>7.60407114028931</v>
+        <v>7.60407161712646</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G689" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>7.90998220443726</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>7.90998220443726</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738597869873</v>
+        <v>7.99738502502441</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>8.12849044799805</v>
+        <v>8.12849140167236</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>8.12849044799805</v>
+        <v>8.12849140167236</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>8.04108715057373</v>
+        <v>8.04108619689941</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G709" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G711" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>9</v>
       </c>
       <c r="G714" t="n">
-        <v>8.07788562774658</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>9</v>
       </c>
       <c r="G715" t="n">
-        <v>8.07788562774658</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G717" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G733" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G737" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G738" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98813152313232</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G743" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G744" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G745" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G751" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G754" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G759" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G760" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G761" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G762" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G763" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G764" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G765" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G766" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G767" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G768" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G772" t="n">
-        <v>8.3471508026123</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G773" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>10</v>
       </c>
       <c r="G774" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>10</v>
       </c>
       <c r="G775" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>10.5</v>
       </c>
       <c r="G776" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>9.78321743011475</v>
+        <v>9.78321838378906</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>9.96272659301758</v>
+        <v>9.96272754669189</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>9.78321743011475</v>
+        <v>9.78321838378906</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G786" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>10.5</v>
       </c>
       <c r="G787" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>10</v>
       </c>
       <c r="G791" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G792" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>10</v>
       </c>
       <c r="G793" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G795" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G797" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G800" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G801" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>9.75</v>
       </c>
       <c r="G802" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G803" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G805" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>9.75</v>
       </c>
       <c r="G808" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G809" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G810" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G811" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G812" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>9.75</v>
       </c>
       <c r="G813" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G814" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G816" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G821" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>10</v>
       </c>
       <c r="G834" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G836" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G838" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>9.75</v>
       </c>
       <c r="G839" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G840" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G841" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>9.75</v>
       </c>
       <c r="G842" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>9.75</v>
       </c>
       <c r="G844" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G848" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G854" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G855" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G859" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G861" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G862" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G863" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>10.5</v>
       </c>
       <c r="G868" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>10</v>
       </c>
       <c r="G872" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10</v>
       </c>
       <c r="G873" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G874" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>10</v>
       </c>
       <c r="G875" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10</v>
       </c>
       <c r="G876" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G877" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.5</v>
       </c>
       <c r="G880" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.5</v>
       </c>
       <c r="G884" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>10.5</v>
       </c>
       <c r="G885" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.5</v>
       </c>
       <c r="G886" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>10</v>
       </c>
       <c r="G889" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G898" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G904" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>9</v>
       </c>
       <c r="G905" t="n">
-        <v>8.07788562774658</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G907" t="n">
-        <v>7.98813152313232</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G908" t="n">
-        <v>8.03300857543945</v>
+        <v>8.03300952911377</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G909" t="n">
-        <v>8.03300857543945</v>
+        <v>8.03300952911377</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.35985231399536</v>
+        <v>7.3598518371582</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423852920532</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423852920532</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G914" t="n">
-        <v>7.98813152313232</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862426757812</v>
+        <v>7.80862331390381</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G923" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G924" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G926" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G927" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G928" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G929" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>10</v>
       </c>
       <c r="G931" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231418609619</v>
+        <v>8.65231513977051</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G946" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G955" t="n">
-        <v>8.96996307373047</v>
+        <v>8.96996402740479</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G962" t="n">
-        <v>8.87787055969238</v>
+        <v>8.87786960601807</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G966" t="n">
-        <v>8.95154571533203</v>
+        <v>8.95154476165771</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G967" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>8.96996307373047</v>
+        <v>8.96996402740479</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G982" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G983" t="n">
-        <v>8.43581867218018</v>
+        <v>8.43581771850586</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>9</v>
       </c>
       <c r="G989" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>8.14111804962158</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>9</v>
       </c>
       <c r="G993" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>9.5</v>
       </c>
       <c r="G997" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1000" t="n">
-        <v>8.43581867218018</v>
+        <v>8.43581771850586</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>9</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>9</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>9</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>7.97534656524658</v>
+        <v>7.9753475189209</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.14111804962158</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>9</v>
       </c>
       <c r="G1055" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1057" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>9.5</v>
       </c>
       <c r="G1060" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>9.5</v>
       </c>
       <c r="G1066" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>9</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>9.5</v>
       </c>
       <c r="G1081" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1082" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>9.5</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1093" t="n">
-        <v>8.96996307373047</v>
+        <v>8.96996402740479</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1094" t="n">
-        <v>8.96996307373047</v>
+        <v>8.96996402740479</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>9.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>9.5</v>
       </c>
       <c r="G1100" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>9.5</v>
       </c>
       <c r="G1101" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>9.5</v>
       </c>
       <c r="G1106" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>9.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1108" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>9.5</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>9.5</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>9.5</v>
       </c>
       <c r="G1120" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>9.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>9.5</v>
       </c>
       <c r="G1122" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>9.5</v>
       </c>
       <c r="G1123" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1126" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1127" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1128" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1129" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1138" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1143" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>9.5</v>
       </c>
       <c r="G1147" t="n">
-        <v>8.74893856048584</v>
+        <v>8.74893760681152</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1148" t="n">
-        <v>8.87787055969238</v>
+        <v>8.87786960601807</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1152" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1160" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1162" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1163" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1164" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1175" t="n">
-        <v>8.43581867218018</v>
+        <v>8.43581771850586</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1176" t="n">
-        <v>8.43581867218018</v>
+        <v>8.43581771850586</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1177" t="n">
-        <v>8.43581867218018</v>
+        <v>8.43581771850586</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1181" t="n">
-        <v>8.56475067138672</v>
+        <v>8.5647497177124</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1182" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>9</v>
       </c>
       <c r="G1190" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>9</v>
       </c>
       <c r="G1192" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>9</v>
       </c>
       <c r="G1193" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>9</v>
       </c>
       <c r="G1194" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>9</v>
       </c>
       <c r="G1195" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1198" t="n">
-        <v>8.27004909515381</v>
+        <v>8.27004814147949</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1199" t="n">
-        <v>8.27004909515381</v>
+        <v>8.27004814147949</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>9</v>
       </c>
       <c r="G1204" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1205" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1206" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1208" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.49645900726318</v>
+        <v>7.49645853042603</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1218" t="n">
-        <v>7.22017621994019</v>
+        <v>7.22017669677734</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.05440664291382</v>
+        <v>7.05440616607666</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G1222" t="n">
-        <v>7.10966348648071</v>
+        <v>7.10966300964355</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1227" t="n">
-        <v>7.09124374389648</v>
+        <v>7.09124422073364</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1229" t="n">
-        <v>7.20175695419312</v>
+        <v>7.20175743103027</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.42175912857056</v>
+        <v>7.4217586517334</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.59347057342529</v>
+        <v>7.59347009658813</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.19280958175659</v>
+        <v>7.19281005859375</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.22307968139648</v>
+        <v>8.22307872772217</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.9178147315979</v>
+        <v>7.91781520843506</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.76518249511719</v>
+        <v>7.76518201828003</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1290" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1294" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1300" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.25004720687866</v>
+        <v>7.2500467300415</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>6.18161916732788</v>
+        <v>6.18161869049072</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>6.25793504714966</v>
+        <v>6.25793552398682</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1344" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>6.73491191864014</v>
+        <v>6.73491239547729</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1362" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1370" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1372" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1382" t="n">
-        <v>6.44872665405273</v>
+        <v>6.44872617721558</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1386" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1394" t="n">
-        <v>6.23885631561279</v>
+        <v>6.23885583877563</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1396" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1400" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1403" t="n">
-        <v>5.85727500915527</v>
+        <v>5.85727453231812</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1408" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.12438201904297</v>
+        <v>6.12438154220581</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1422" t="n">
-        <v>5.95266962051392</v>
+        <v>5.95267009735107</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>5.78095817565918</v>
+        <v>5.78095865249634</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1431" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.32306051254272</v>
+        <v>5.32306098937988</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.53293085098267</v>
+        <v>5.53293037414551</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1442" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1448" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.43753480911255</v>
+        <v>5.43753528594971</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -54530,6 +54530,32 @@
         <v>2.97000002861023</v>
       </c>
       <c r="H2083" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="G2084" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="H2084" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -514,7 +514,7 @@
         <v>9.60200023651123</v>
       </c>
       <c r="G5" t="n">
-        <v>8.14811134338379</v>
+        <v>8.14810943603516</v>
       </c>
       <c r="H5" t="n">
         <v>10000</v>
@@ -543,7 +543,7 @@
         <v>9.61100006103516</v>
       </c>
       <c r="G6" t="n">
-        <v>8.15574932098389</v>
+        <v>8.15574836730957</v>
       </c>
       <c r="H6" t="n">
         <v>14900</v>
@@ -572,7 +572,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G7" t="n">
-        <v>8.18035697937012</v>
+        <v>8.18035793304443</v>
       </c>
       <c r="H7" t="n">
         <v>6500</v>
@@ -630,7 +630,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H9" t="n">
         <v>3500</v>
@@ -659,7 +659,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -746,7 +746,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -804,7 +804,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -833,7 +833,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10058975219727</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H17" t="n">
         <v>1300</v>
@@ -891,7 +891,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10058975219727</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H19" t="n">
         <v>9600</v>
@@ -949,7 +949,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10653114318848</v>
+        <v>8.10653018951416</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1036,7 +1036,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H23" t="n">
         <v>10900</v>
@@ -1065,7 +1065,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852745056152</v>
+        <v>8.07852840423584</v>
       </c>
       <c r="H24" t="n">
         <v>2800</v>
@@ -1094,7 +1094,7 @@
         <v>9.54199981689453</v>
       </c>
       <c r="G25" t="n">
-        <v>8.09719562530518</v>
+        <v>8.09719467163086</v>
       </c>
       <c r="H25" t="n">
         <v>4800</v>
@@ -1210,7 +1210,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G29" t="n">
-        <v>8.08192157745361</v>
+        <v>8.0819206237793</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -1268,7 +1268,7 @@
         <v>9.50100040435791</v>
       </c>
       <c r="G31" t="n">
-        <v>8.06240367889404</v>
+        <v>8.06240272521973</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1297,7 +1297,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10058975219727</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H32" t="n">
         <v>200</v>
@@ -1326,7 +1326,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.07513236999512</v>
+        <v>8.0751314163208</v>
       </c>
       <c r="H33" t="n">
         <v>8000</v>
@@ -1355,7 +1355,7 @@
         <v>9.43099975585938</v>
       </c>
       <c r="G34" t="n">
-        <v>8.00300216674805</v>
+        <v>8.00300121307373</v>
       </c>
       <c r="H34" t="n">
         <v>8100</v>
@@ -1384,7 +1384,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01064014434814</v>
+        <v>8.01063919067383</v>
       </c>
       <c r="H35" t="n">
         <v>7500</v>
@@ -1413,7 +1413,7 @@
         <v>9.44699954986572</v>
       </c>
       <c r="G36" t="n">
-        <v>8.01658058166504</v>
+        <v>8.01657962799072</v>
       </c>
       <c r="H36" t="n">
         <v>2900</v>
@@ -1442,7 +1442,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366807937622</v>
+        <v>7.99366855621338</v>
       </c>
       <c r="H37" t="n">
         <v>12300</v>
@@ -1500,7 +1500,7 @@
         <v>9.33100032806396</v>
       </c>
       <c r="G39" t="n">
-        <v>7.91814374923706</v>
+        <v>7.91814470291138</v>
       </c>
       <c r="H39" t="n">
         <v>400</v>
@@ -1529,7 +1529,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227025985718</v>
+        <v>7.96227216720581</v>
       </c>
       <c r="H40" t="n">
         <v>300</v>
@@ -1558,7 +1558,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227025985718</v>
+        <v>7.96227216720581</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.97924137115479</v>
+        <v>7.97924280166626</v>
       </c>
       <c r="H42" t="n">
         <v>300</v>
@@ -1616,7 +1616,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.97924137115479</v>
+        <v>7.97924280166626</v>
       </c>
       <c r="H43" t="n">
         <v>1700</v>
@@ -1703,7 +1703,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H46" t="n">
         <v>8000</v>
@@ -1732,7 +1732,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1790,7 +1790,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729593276978</v>
+        <v>7.91729545593262</v>
       </c>
       <c r="H49" t="n">
         <v>9200</v>
@@ -1848,7 +1848,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H51" t="n">
         <v>16700</v>
@@ -1877,7 +1877,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G52" t="n">
-        <v>7.75097322463989</v>
+        <v>7.75097370147705</v>
       </c>
       <c r="H52" t="n">
         <v>5200</v>
@@ -1906,7 +1906,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.77473402023315</v>
+        <v>7.77473258972168</v>
       </c>
       <c r="H53" t="n">
         <v>2300</v>
@@ -1935,7 +1935,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G54" t="n">
-        <v>7.78237009048462</v>
+        <v>7.78237056732178</v>
       </c>
       <c r="H54" t="n">
         <v>500</v>
@@ -1964,7 +1964,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G55" t="n">
-        <v>7.78237009048462</v>
+        <v>7.78237056732178</v>
       </c>
       <c r="H55" t="n">
         <v>400</v>
@@ -1993,7 +1993,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G56" t="n">
-        <v>7.76709604263306</v>
+        <v>7.76709651947021</v>
       </c>
       <c r="H56" t="n">
         <v>200</v>
@@ -2022,7 +2022,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H57" t="n">
         <v>12300</v>
@@ -2051,7 +2051,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.80697917938232</v>
+        <v>7.8069806098938</v>
       </c>
       <c r="H58" t="n">
         <v>4100</v>
@@ -2109,7 +2109,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.80697917938232</v>
+        <v>7.8069806098938</v>
       </c>
       <c r="H60" t="n">
         <v>24300</v>
@@ -2138,7 +2138,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H61" t="n">
         <v>4900</v>
@@ -2167,7 +2167,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H62" t="n">
         <v>8400</v>
@@ -2196,7 +2196,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539945602417</v>
       </c>
       <c r="H64" t="n">
         <v>1600</v>
@@ -2254,7 +2254,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.80697917938232</v>
+        <v>7.8069806098938</v>
       </c>
       <c r="H65" t="n">
         <v>7100</v>
@@ -2283,7 +2283,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H66" t="n">
         <v>2500</v>
@@ -2312,7 +2312,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.8052830696106</v>
+        <v>7.80528211593628</v>
       </c>
       <c r="H70" t="n">
         <v>1000</v>
@@ -2428,7 +2428,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722898483276</v>
+        <v>7.86722993850708</v>
       </c>
       <c r="H71" t="n">
         <v>800</v>
@@ -2457,7 +2457,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746271133423</v>
+        <v>7.78746366500854</v>
       </c>
       <c r="H72" t="n">
         <v>700</v>
@@ -2486,7 +2486,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746271133423</v>
+        <v>7.78746366500854</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>7.85534954071045</v>
+        <v>7.85534858703613</v>
       </c>
       <c r="H74" t="n">
         <v>10200</v>
@@ -2544,7 +2544,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G75" t="n">
-        <v>8.04882526397705</v>
+        <v>8.04882621765137</v>
       </c>
       <c r="H75" t="n">
         <v>100</v>
@@ -2573,7 +2573,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761173248291</v>
+        <v>8.02761077880859</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2602,7 +2602,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177207946777</v>
+        <v>7.84177255630493</v>
       </c>
       <c r="H77" t="n">
         <v>4000</v>
@@ -2631,7 +2631,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.790855884552</v>
+        <v>7.79085636138916</v>
       </c>
       <c r="H78" t="n">
         <v>800</v>
@@ -2660,7 +2660,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>7.84516572952271</v>
+        <v>7.84516668319702</v>
       </c>
       <c r="H79" t="n">
         <v>2400</v>
@@ -2689,7 +2689,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243751525879</v>
+        <v>7.83243703842163</v>
       </c>
       <c r="H80" t="n">
         <v>1600</v>
@@ -2718,7 +2718,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358552932739</v>
+        <v>7.80358505249023</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406858444214</v>
+        <v>7.78406763076782</v>
       </c>
       <c r="H82" t="n">
         <v>200</v>
@@ -2776,7 +2776,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539945602417</v>
       </c>
       <c r="H83" t="n">
         <v>1100</v>
@@ -2805,7 +2805,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539945602417</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539945602417</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.8010401725769</v>
+        <v>7.80103826522827</v>
       </c>
       <c r="H86" t="n">
         <v>2900</v>
@@ -2921,7 +2921,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098882675171</v>
+        <v>7.89098930358887</v>
       </c>
       <c r="H88" t="n">
         <v>200</v>
@@ -2950,7 +2950,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782842636108</v>
+        <v>7.80782699584961</v>
       </c>
       <c r="H89" t="n">
         <v>5100</v>
@@ -3037,7 +3037,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408514022827</v>
+        <v>7.92408418655396</v>
       </c>
       <c r="H92" t="n">
         <v>1200</v>
@@ -3066,7 +3066,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.7704906463623</v>
+        <v>7.77048969268799</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539945602417</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3182,7 +3182,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G97" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H97" t="n">
         <v>7500</v>
@@ -3211,7 +3211,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70515012741089</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969179153442</v>
+        <v>7.67969226837158</v>
       </c>
       <c r="H100" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969179153442</v>
+        <v>7.67969226837158</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726234436035</v>
+        <v>7.63726329803467</v>
       </c>
       <c r="H102" t="n">
         <v>700</v>
@@ -3356,7 +3356,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423536300659</v>
+        <v>7.65423440933228</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423536300659</v>
+        <v>7.65423440933228</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>7.55240392684937</v>
+        <v>7.55240440368652</v>
       </c>
       <c r="H105" t="n">
         <v>200</v>
@@ -3443,7 +3443,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904291152954</v>
+        <v>7.82904243469238</v>
       </c>
       <c r="H106" t="n">
         <v>300</v>
@@ -3472,7 +3472,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H107" t="n">
         <v>1100</v>
@@ -3530,7 +3530,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G109" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H109" t="n">
         <v>2200</v>
@@ -3559,7 +3559,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363544464111</v>
+        <v>7.71363496780396</v>
       </c>
       <c r="H110" t="n">
         <v>10000</v>
@@ -3588,7 +3588,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70515012741089</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H111" t="n">
         <v>25500</v>
@@ -3617,7 +3617,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70515012741089</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969179153442</v>
+        <v>7.67969226837158</v>
       </c>
       <c r="H114" t="n">
         <v>100</v>
@@ -3762,7 +3762,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273580551147</v>
+        <v>7.80273771286011</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -3791,7 +3791,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308734893799</v>
+        <v>7.68308544158936</v>
       </c>
       <c r="H118" t="n">
         <v>2400</v>
@@ -3820,7 +3820,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G119" t="n">
-        <v>7.69666433334351</v>
+        <v>7.69666385650635</v>
       </c>
       <c r="H119" t="n">
         <v>2900</v>
@@ -3849,7 +3849,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G120" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H120" t="n">
         <v>2000</v>
@@ -3878,7 +3878,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G121" t="n">
-        <v>7.7221212387085</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H121" t="n">
         <v>5000</v>
@@ -3994,7 +3994,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.86553144454956</v>
+        <v>7.86553192138672</v>
       </c>
       <c r="H125" t="n">
         <v>300</v>
@@ -4023,7 +4023,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152179718018</v>
+        <v>7.78152275085449</v>
       </c>
       <c r="H126" t="n">
         <v>24300</v>
@@ -4052,7 +4052,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406858444214</v>
+        <v>7.78406763076782</v>
       </c>
       <c r="H127" t="n">
         <v>2000</v>
@@ -4168,7 +4168,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243751525879</v>
+        <v>7.83243703842163</v>
       </c>
       <c r="H131" t="n">
         <v>5900</v>
@@ -4197,7 +4197,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.79849338531494</v>
+        <v>7.79849481582642</v>
       </c>
       <c r="H132" t="n">
         <v>300</v>
@@ -4226,7 +4226,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H133" t="n">
         <v>13900</v>
@@ -4255,7 +4255,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.7900071144104</v>
+        <v>7.79000806808472</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.7900071144104</v>
+        <v>7.79000806808472</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94444942474365</v>
+        <v>7.94445180892944</v>
       </c>
       <c r="H136" t="n">
         <v>2500</v>
@@ -4371,7 +4371,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.79849338531494</v>
+        <v>7.79849481582642</v>
       </c>
       <c r="H138" t="n">
         <v>800</v>
@@ -4400,7 +4400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.80697917938232</v>
+        <v>7.8069806098938</v>
       </c>
       <c r="H139" t="n">
         <v>1200</v>
@@ -4429,7 +4429,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G140" t="n">
-        <v>7.96311902999878</v>
+        <v>7.96311950683594</v>
       </c>
       <c r="H140" t="n">
         <v>500</v>
@@ -4487,7 +4487,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H142" t="n">
         <v>400</v>
@@ -4516,7 +4516,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G144" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H144" t="n">
         <v>1300</v>
@@ -4574,7 +4574,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G145" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G146" t="n">
-        <v>8.07004070281982</v>
+        <v>8.07004165649414</v>
       </c>
       <c r="H146" t="n">
         <v>100</v>
@@ -4690,7 +4690,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579875946045</v>
+        <v>8.06579780578613</v>
       </c>
       <c r="H149" t="n">
         <v>300</v>
@@ -4835,7 +4835,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.92832851409912</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H154" t="n">
         <v>1100</v>
@@ -4980,7 +4980,7 @@
         <v>9.34700012207031</v>
       </c>
       <c r="G159" t="n">
-        <v>7.93172264099121</v>
+        <v>7.93172121047974</v>
       </c>
       <c r="H159" t="n">
         <v>800</v>
@@ -5009,7 +5009,7 @@
         <v>9.44299983978271</v>
       </c>
       <c r="G160" t="n">
-        <v>8.01318550109863</v>
+        <v>8.01318645477295</v>
       </c>
       <c r="H160" t="n">
         <v>100</v>
@@ -5154,7 +5154,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>8.05306911468506</v>
+        <v>8.05306816101074</v>
       </c>
       <c r="H165" t="n">
         <v>300</v>
@@ -5183,7 +5183,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.92832851409912</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H166" t="n">
         <v>1200</v>
@@ -5241,7 +5241,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H168" t="n">
         <v>9400</v>
@@ -5270,7 +5270,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H169" t="n">
         <v>6900</v>
@@ -5299,7 +5299,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H170" t="n">
         <v>200</v>
@@ -5328,7 +5328,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H172" t="n">
         <v>3700</v>
@@ -5386,7 +5386,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H173" t="n">
         <v>200</v>
@@ -5415,7 +5415,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H174" t="n">
         <v>600</v>
@@ -5444,7 +5444,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H175" t="n">
         <v>300</v>
@@ -5473,7 +5473,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H176" t="n">
         <v>4900</v>
@@ -5531,7 +5531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H178" t="n">
         <v>300</v>
@@ -5560,7 +5560,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H179" t="n">
         <v>100</v>
@@ -5618,7 +5618,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H181" t="n">
         <v>5000</v>
@@ -5647,7 +5647,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H184" t="n">
         <v>300</v>
@@ -5734,7 +5734,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H185" t="n">
         <v>200</v>
@@ -5763,7 +5763,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H186" t="n">
         <v>700</v>
@@ -5792,7 +5792,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H187" t="n">
         <v>900</v>
@@ -5850,7 +5850,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H189" t="n">
         <v>1900</v>
@@ -5908,7 +5908,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H191" t="n">
         <v>5600</v>
@@ -5966,7 +5966,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H193" t="n">
         <v>3200</v>
@@ -5995,7 +5995,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H194" t="n">
         <v>300</v>
@@ -6082,7 +6082,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6111,7 +6111,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H198" t="n">
         <v>4700</v>
@@ -6140,7 +6140,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H200" t="n">
         <v>2000</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H201" t="n">
         <v>1500</v>
@@ -6227,7 +6227,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H202" t="n">
         <v>800</v>
@@ -6256,7 +6256,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H203" t="n">
         <v>100</v>
@@ -6285,7 +6285,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H204" t="n">
         <v>5900</v>
@@ -6343,7 +6343,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H206" t="n">
         <v>300</v>
@@ -6430,7 +6430,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G209" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6459,7 +6459,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H210" t="n">
         <v>600</v>
@@ -6546,7 +6546,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H213" t="n">
         <v>2600</v>
@@ -6575,7 +6575,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H214" t="n">
         <v>200</v>
@@ -6604,7 +6604,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H215" t="n">
         <v>6600</v>
@@ -6633,7 +6633,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H216" t="n">
         <v>100</v>
@@ -6662,7 +6662,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6691,7 +6691,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H218" t="n">
         <v>900</v>
@@ -6720,7 +6720,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6749,7 +6749,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H220" t="n">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H221" t="n">
         <v>17700</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H224" t="n">
         <v>800</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H225" t="n">
         <v>600</v>
@@ -6923,7 +6923,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H226" t="n">
         <v>100</v>
@@ -6952,7 +6952,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H227" t="n">
         <v>100</v>
@@ -6981,7 +6981,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H228" t="n">
         <v>9100</v>
@@ -7039,7 +7039,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7068,7 +7068,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7126,7 +7126,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H233" t="n">
         <v>5100</v>
@@ -7329,7 +7329,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H240" t="n">
         <v>100</v>
@@ -7358,7 +7358,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H241" t="n">
         <v>400</v>
@@ -7387,7 +7387,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H242" t="n">
         <v>7200</v>
@@ -7416,7 +7416,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H243" t="n">
         <v>100</v>
@@ -7445,7 +7445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H244" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H248" t="n">
         <v>700</v>
@@ -7590,7 +7590,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H249" t="n">
         <v>600</v>
@@ -7619,7 +7619,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G250" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H250" t="n">
         <v>300</v>
@@ -7648,7 +7648,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H251" t="n">
         <v>2100</v>
@@ -7677,7 +7677,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H252" t="n">
         <v>1800</v>
@@ -7706,7 +7706,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H253" t="n">
         <v>1700</v>
@@ -7735,7 +7735,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H254" t="n">
         <v>1800</v>
@@ -7793,7 +7793,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G256" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H256" t="n">
         <v>2300</v>
@@ -7822,7 +7822,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H257" t="n">
         <v>100</v>
@@ -7851,7 +7851,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H258" t="n">
         <v>1200</v>
@@ -7996,7 +7996,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H263" t="n">
         <v>8000</v>
@@ -8141,7 +8141,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H268" t="n">
         <v>11200</v>
@@ -8170,7 +8170,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H269" t="n">
         <v>600</v>
@@ -8228,7 +8228,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H272" t="n">
         <v>100</v>
@@ -8286,7 +8286,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H273" t="n">
         <v>100</v>
@@ -8315,7 +8315,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H274" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H276" t="n">
         <v>100</v>
@@ -8953,7 +8953,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G296" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H296" t="n">
         <v>200</v>
@@ -9011,7 +9011,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H298" t="n">
         <v>10700</v>
@@ -9243,7 +9243,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H309" t="n">
         <v>500</v>
@@ -9359,7 +9359,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H310" t="n">
         <v>3300</v>
@@ -9388,7 +9388,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H311" t="n">
         <v>100</v>
@@ -9417,7 +9417,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H312" t="n">
         <v>100</v>
@@ -9446,7 +9446,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H313" t="n">
         <v>12700</v>
@@ -9475,7 +9475,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H314" t="n">
         <v>7100</v>
@@ -9504,7 +9504,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H318" t="n">
         <v>300</v>
@@ -9736,7 +9736,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H323" t="n">
         <v>26700</v>
@@ -9765,7 +9765,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H324" t="n">
         <v>100</v>
@@ -9794,7 +9794,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H325" t="n">
         <v>20100</v>
@@ -9852,7 +9852,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -9881,7 +9881,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H328" t="n">
         <v>52800</v>
@@ -9910,7 +9910,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H329" t="n">
         <v>10000</v>
@@ -9939,7 +9939,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H330" t="n">
         <v>200</v>
@@ -9968,7 +9968,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H331" t="n">
         <v>900</v>
@@ -9997,7 +9997,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H332" t="n">
         <v>10000</v>
@@ -10026,7 +10026,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H338" t="n">
         <v>400</v>
@@ -10200,7 +10200,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H339" t="n">
         <v>6600</v>
@@ -10229,7 +10229,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H340" t="n">
         <v>400</v>
@@ -10954,7 +10954,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H365" t="n">
         <v>100</v>
@@ -10983,7 +10983,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H367" t="n">
         <v>900</v>
@@ -11070,7 +11070,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H369" t="n">
         <v>100</v>
@@ -11099,7 +11099,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H371" t="n">
         <v>1700</v>
@@ -11157,7 +11157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H372" t="n">
         <v>1200</v>
@@ -11244,7 +11244,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H375" t="n">
         <v>5700</v>
@@ -11331,7 +11331,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H378" t="n">
         <v>30700</v>
@@ -11389,7 +11389,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H380" t="n">
         <v>15200</v>
@@ -11476,7 +11476,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H383" t="n">
         <v>800</v>
@@ -11563,7 +11563,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H386" t="n">
         <v>300</v>
@@ -11621,7 +11621,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H388" t="n">
         <v>800</v>
@@ -11650,7 +11650,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H389" t="n">
         <v>4300</v>
@@ -11679,7 +11679,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H390" t="n">
         <v>300</v>
@@ -12143,7 +12143,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H406" t="n">
         <v>11100</v>
@@ -12259,7 +12259,7 @@
         <v>9.25</v>
       </c>
       <c r="G410" t="n">
-        <v>7.84940910339355</v>
+        <v>7.8494086265564</v>
       </c>
       <c r="H410" t="n">
         <v>13800</v>
@@ -12288,7 +12288,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12317,7 +12317,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H412" t="n">
         <v>13000</v>
@@ -12433,7 +12433,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H416" t="n">
         <v>200</v>
@@ -12462,7 +12462,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12549,7 +12549,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G420" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H420" t="n">
         <v>12500</v>
@@ -12578,7 +12578,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G421" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H421" t="n">
         <v>10000</v>
@@ -12607,7 +12607,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G424" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H424" t="n">
         <v>8900</v>
@@ -12694,7 +12694,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H426" t="n">
         <v>300</v>
@@ -12868,7 +12868,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H431" t="n">
         <v>700</v>
@@ -14521,7 +14521,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H488" t="n">
         <v>140500</v>
@@ -14550,7 +14550,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H489" t="n">
         <v>134000</v>
@@ -14579,7 +14579,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H490" t="n">
         <v>5800</v>
@@ -14608,7 +14608,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H491" t="n">
         <v>129300</v>
@@ -15014,7 +15014,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H505" t="n">
         <v>400</v>
@@ -16261,7 +16261,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>8.44341945648193</v>
+        <v>8.44341850280762</v>
       </c>
       <c r="H548" t="n">
         <v>21900</v>
@@ -16435,7 +16435,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H554" t="n">
         <v>2900</v>
@@ -16522,7 +16522,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782962799072</v>
+        <v>7.29782867431641</v>
       </c>
       <c r="H557" t="n">
         <v>1100</v>
@@ -16551,7 +16551,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>7.12811231613159</v>
+        <v>7.12811183929443</v>
       </c>
       <c r="H558" t="n">
         <v>13900</v>
@@ -16580,7 +16580,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66138982772827</v>
+        <v>6.66139030456543</v>
       </c>
       <c r="H559" t="n">
         <v>9300</v>
@@ -16696,7 +16696,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17054128646851</v>
+        <v>7.17054080963135</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16754,7 +16754,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H565" t="n">
         <v>3800</v>
@@ -16783,7 +16783,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H566" t="n">
         <v>3000</v>
@@ -16812,7 +16812,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>6.70381927490234</v>
+        <v>6.7038197517395</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -16870,7 +16870,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>6.70381927490234</v>
+        <v>6.7038197517395</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.46783113479614</v>
+        <v>6.4678316116333</v>
       </c>
       <c r="H573" t="n">
         <v>4700</v>
@@ -17044,7 +17044,7 @@
         <v>8.25</v>
       </c>
       <c r="G575" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H575" t="n">
         <v>6200</v>
@@ -17073,7 +17073,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H576" t="n">
         <v>24700</v>
@@ -17189,7 +17189,7 @@
         <v>8.5</v>
       </c>
       <c r="G580" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H580" t="n">
         <v>1500</v>
@@ -17276,7 +17276,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G583" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H583" t="n">
         <v>4700</v>
@@ -17305,7 +17305,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H584" t="n">
         <v>3700</v>
@@ -17334,7 +17334,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H585" t="n">
         <v>24200</v>
@@ -17363,7 +17363,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H586" t="n">
         <v>1100</v>
@@ -17392,7 +17392,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G587" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G588" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H588" t="n">
         <v>1000</v>
@@ -17450,7 +17450,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H589" t="n">
         <v>1000</v>
@@ -17479,7 +17479,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H590" t="n">
         <v>600</v>
@@ -17508,7 +17508,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.73517656326294</v>
+        <v>7.73517751693726</v>
       </c>
       <c r="H591" t="n">
         <v>19400</v>
@@ -17537,7 +17537,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H592" t="n">
         <v>300</v>
@@ -17566,7 +17566,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G596" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H596" t="n">
         <v>400</v>
@@ -17682,7 +17682,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H597" t="n">
         <v>2000</v>
@@ -17711,7 +17711,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H598" t="n">
         <v>3300</v>
@@ -17740,7 +17740,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56037044525146</v>
+        <v>7.56036996841431</v>
       </c>
       <c r="H600" t="n">
         <v>100</v>
@@ -17798,7 +17798,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H601" t="n">
         <v>6300</v>
@@ -17827,7 +17827,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H602" t="n">
         <v>12100</v>
@@ -17885,7 +17885,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.73517656326294</v>
+        <v>7.73517751693726</v>
       </c>
       <c r="H604" t="n">
         <v>700</v>
@@ -17914,7 +17914,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G605" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H605" t="n">
         <v>600</v>
@@ -17943,7 +17943,7 @@
         <v>8.5</v>
       </c>
       <c r="G606" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H606" t="n">
         <v>1200</v>
@@ -17972,7 +17972,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H607" t="n">
         <v>300</v>
@@ -18001,7 +18001,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>7.60407257080078</v>
+        <v>7.60407161712646</v>
       </c>
       <c r="H608" t="n">
         <v>200</v>
@@ -18030,7 +18030,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G609" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H609" t="n">
         <v>2600</v>
@@ -18059,7 +18059,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G610" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H610" t="n">
         <v>500</v>
@@ -18088,7 +18088,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H611" t="n">
         <v>800</v>
@@ -18117,7 +18117,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H612" t="n">
         <v>100</v>
@@ -18146,7 +18146,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95368432998657</v>
+        <v>7.95368480682373</v>
       </c>
       <c r="H613" t="n">
         <v>100</v>
@@ -18175,7 +18175,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H614" t="n">
         <v>600</v>
@@ -18204,7 +18204,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.73517656326294</v>
+        <v>7.73517751693726</v>
       </c>
       <c r="H615" t="n">
         <v>1200</v>
@@ -18233,7 +18233,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H616" t="n">
         <v>200</v>
@@ -18262,7 +18262,7 @@
         <v>8.5</v>
       </c>
       <c r="G617" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H617" t="n">
         <v>3800</v>
@@ -18291,7 +18291,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H618" t="n">
         <v>1600</v>
@@ -18320,7 +18320,7 @@
         <v>8.5</v>
       </c>
       <c r="G619" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H619" t="n">
         <v>300</v>
@@ -18349,7 +18349,7 @@
         <v>8.5</v>
       </c>
       <c r="G620" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H623" t="n">
         <v>2000</v>
@@ -18465,7 +18465,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G624" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H624" t="n">
         <v>3600</v>
@@ -18523,7 +18523,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G626" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H626" t="n">
         <v>6200</v>
@@ -18552,7 +18552,7 @@
         <v>8.25</v>
       </c>
       <c r="G627" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H627" t="n">
         <v>2600</v>
@@ -18581,7 +18581,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H628" t="n">
         <v>5100</v>
@@ -18610,7 +18610,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>7.47296762466431</v>
+        <v>7.47296810150146</v>
       </c>
       <c r="H629" t="n">
         <v>1400</v>
@@ -18697,7 +18697,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G632" t="n">
-        <v>7.29816198348999</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H632" t="n">
         <v>900</v>
@@ -18755,7 +18755,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G634" t="n">
-        <v>7.29816198348999</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H634" t="n">
         <v>300</v>
@@ -18784,7 +18784,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H635" t="n">
         <v>3900</v>
@@ -18813,7 +18813,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G636" t="n">
-        <v>7.29816198348999</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H636" t="n">
         <v>2000</v>
@@ -18900,7 +18900,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H639" t="n">
         <v>1100</v>
@@ -19277,7 +19277,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484714508057</v>
+        <v>6.90484666824341</v>
       </c>
       <c r="H652" t="n">
         <v>2400</v>
@@ -19393,7 +19393,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G656" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H656" t="n">
         <v>1100</v>
@@ -19422,7 +19422,7 @@
         <v>8.25</v>
       </c>
       <c r="G657" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H657" t="n">
         <v>8600</v>
@@ -19451,7 +19451,7 @@
         <v>8.25</v>
       </c>
       <c r="G658" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H658" t="n">
         <v>1100</v>
@@ -19480,7 +19480,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>7.16705656051636</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H659" t="n">
         <v>5400</v>
@@ -19538,7 +19538,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G661" t="n">
-        <v>7.03595209121704</v>
+        <v>7.03595161437988</v>
       </c>
       <c r="H661" t="n">
         <v>11500</v>
@@ -19596,7 +19596,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G663" t="n">
-        <v>7.29816198348999</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H663" t="n">
         <v>11900</v>
@@ -19683,7 +19683,7 @@
         <v>8.5</v>
       </c>
       <c r="G666" t="n">
-        <v>7.42926597595215</v>
+        <v>7.42926549911499</v>
       </c>
       <c r="H666" t="n">
         <v>12000</v>
@@ -19712,7 +19712,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>7.69147539138794</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H667" t="n">
         <v>5600</v>
@@ -19741,7 +19741,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G668" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H669" t="n">
         <v>6200</v>
@@ -19799,7 +19799,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H670" t="n">
         <v>2100</v>
@@ -19828,7 +19828,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G671" t="n">
-        <v>7.90998220443726</v>
+        <v>7.90998315811157</v>
       </c>
       <c r="H671" t="n">
         <v>1900</v>
@@ -19857,7 +19857,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G672" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108810424805</v>
       </c>
       <c r="H672" t="n">
         <v>1900</v>
@@ -19886,7 +19886,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G673" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108810424805</v>
       </c>
       <c r="H673" t="n">
         <v>4100</v>
@@ -19915,7 +19915,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H674" t="n">
         <v>2900</v>
@@ -19944,7 +19944,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H675" t="n">
         <v>1300</v>
@@ -19973,7 +19973,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H676" t="n">
         <v>2300</v>
@@ -20002,7 +20002,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.86628103256226</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H677" t="n">
         <v>1800</v>
@@ -20031,7 +20031,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>7.82257986068726</v>
+        <v>7.8225793838501</v>
       </c>
       <c r="H678" t="n">
         <v>1500</v>
@@ -20060,7 +20060,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G679" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H679" t="n">
         <v>700</v>
@@ -20089,7 +20089,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G680" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20118,7 +20118,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60407257080078</v>
+        <v>7.60407161712646</v>
       </c>
       <c r="H681" t="n">
         <v>1400</v>
@@ -20147,7 +20147,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H682" t="n">
         <v>1900</v>
@@ -20176,7 +20176,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G683" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H683" t="n">
         <v>2100</v>
@@ -20205,7 +20205,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738454818726</v>
       </c>
       <c r="H684" t="n">
         <v>3100</v>
@@ -20234,7 +20234,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H685" t="n">
         <v>600</v>
@@ -20263,7 +20263,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G686" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H686" t="n">
         <v>500</v>
@@ -20292,7 +20292,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H687" t="n">
         <v>1500</v>
@@ -20321,7 +20321,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>7.60407257080078</v>
+        <v>7.60407161712646</v>
       </c>
       <c r="H688" t="n">
         <v>1500</v>
@@ -20350,7 +20350,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G689" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666879653931</v>
       </c>
       <c r="H689" t="n">
         <v>12600</v>
@@ -20408,7 +20408,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108810424805</v>
       </c>
       <c r="H691" t="n">
         <v>6500</v>
@@ -20437,7 +20437,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>7.90998220443726</v>
+        <v>7.90998315811157</v>
       </c>
       <c r="H692" t="n">
         <v>12900</v>
@@ -20466,7 +20466,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>7.90998220443726</v>
+        <v>7.90998315811157</v>
       </c>
       <c r="H693" t="n">
         <v>9100</v>
@@ -20495,7 +20495,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108810424805</v>
       </c>
       <c r="H694" t="n">
         <v>5000</v>
@@ -20524,7 +20524,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738454818726</v>
       </c>
       <c r="H695" t="n">
         <v>5300</v>
@@ -20553,7 +20553,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>8.12849044799805</v>
+        <v>8.12849140167236</v>
       </c>
       <c r="H696" t="n">
         <v>5300</v>
@@ -20582,7 +20582,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>8.12849044799805</v>
+        <v>8.12849140167236</v>
       </c>
       <c r="H697" t="n">
         <v>6600</v>
@@ -20611,7 +20611,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>8.04108619689941</v>
+        <v>8.04108810424805</v>
       </c>
       <c r="H698" t="n">
         <v>10400</v>
@@ -20669,7 +20669,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H700" t="n">
         <v>4100</v>
@@ -20698,7 +20698,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H701" t="n">
         <v>3600</v>
@@ -20727,7 +20727,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H702" t="n">
         <v>1900</v>
@@ -20756,7 +20756,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H703" t="n">
         <v>1400</v>
@@ -20814,7 +20814,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G705" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H705" t="n">
         <v>900</v>
@@ -20843,7 +20843,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H706" t="n">
         <v>300</v>
@@ -20872,7 +20872,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H707" t="n">
         <v>5300</v>
@@ -20901,7 +20901,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G708" t="n">
-        <v>8.12276268005371</v>
+        <v>8.12276363372803</v>
       </c>
       <c r="H708" t="n">
         <v>1500</v>
@@ -20930,7 +20930,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G709" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H709" t="n">
         <v>5000</v>
@@ -20988,7 +20988,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G711" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H711" t="n">
         <v>900</v>
@@ -21017,7 +21017,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G712" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H712" t="n">
         <v>9300</v>
@@ -21046,7 +21046,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G713" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H713" t="n">
         <v>800</v>
@@ -21075,7 +21075,7 @@
         <v>9</v>
       </c>
       <c r="G714" t="n">
-        <v>8.07788562774658</v>
+        <v>8.0778865814209</v>
       </c>
       <c r="H714" t="n">
         <v>2100</v>
@@ -21104,7 +21104,7 @@
         <v>9</v>
       </c>
       <c r="G715" t="n">
-        <v>8.07788562774658</v>
+        <v>8.0778865814209</v>
       </c>
       <c r="H715" t="n">
         <v>1600</v>
@@ -21133,7 +21133,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G716" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H716" t="n">
         <v>1200</v>
@@ -21162,7 +21162,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G717" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H717" t="n">
         <v>5900</v>
@@ -21191,7 +21191,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H718" t="n">
         <v>2600</v>
@@ -21220,7 +21220,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H719" t="n">
         <v>900</v>
@@ -21249,7 +21249,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H720" t="n">
         <v>1200</v>
@@ -21307,7 +21307,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H722" t="n">
         <v>55000</v>
@@ -21336,7 +21336,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H723" t="n">
         <v>26400</v>
@@ -21365,7 +21365,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H724" t="n">
         <v>21400</v>
@@ -21394,7 +21394,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H725" t="n">
         <v>70900</v>
@@ -21568,7 +21568,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H731" t="n">
         <v>300</v>
@@ -21800,7 +21800,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H739" t="n">
         <v>18700</v>
@@ -21829,7 +21829,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G740" t="n">
-        <v>8.12276268005371</v>
+        <v>8.12276363372803</v>
       </c>
       <c r="H740" t="n">
         <v>3700</v>
@@ -21858,7 +21858,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G741" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H741" t="n">
         <v>12400</v>
@@ -21916,7 +21916,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G743" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H743" t="n">
         <v>300</v>
@@ -21974,7 +21974,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G745" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H745" t="n">
         <v>400</v>
@@ -22032,7 +22032,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G747" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H747" t="n">
         <v>100</v>
@@ -22090,7 +22090,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G749" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H749" t="n">
         <v>2600</v>
@@ -22815,7 +22815,7 @@
         <v>10</v>
       </c>
       <c r="G774" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H774" t="n">
         <v>23000</v>
@@ -22844,7 +22844,7 @@
         <v>10</v>
       </c>
       <c r="G775" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H775" t="n">
         <v>13400</v>
@@ -22902,7 +22902,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>9.51395511627197</v>
+        <v>9.51395606994629</v>
       </c>
       <c r="H777" t="n">
         <v>16100</v>
@@ -22931,7 +22931,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>9.78321743011475</v>
+        <v>9.78321838378906</v>
       </c>
       <c r="H778" t="n">
         <v>49600</v>
@@ -22960,7 +22960,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>9.96272659301758</v>
+        <v>9.96272754669189</v>
       </c>
       <c r="H779" t="n">
         <v>29900</v>
@@ -23018,7 +23018,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G781" t="n">
-        <v>9.78321743011475</v>
+        <v>9.78321838378906</v>
       </c>
       <c r="H781" t="n">
         <v>7900</v>
@@ -23047,7 +23047,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>9.51395511627197</v>
+        <v>9.51395606994629</v>
       </c>
       <c r="H782" t="n">
         <v>15800</v>
@@ -23076,7 +23076,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>9.51395511627197</v>
+        <v>9.51395606994629</v>
       </c>
       <c r="H783" t="n">
         <v>10600</v>
@@ -23221,7 +23221,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H788" t="n">
         <v>26400</v>
@@ -23308,7 +23308,7 @@
         <v>10</v>
       </c>
       <c r="G791" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H791" t="n">
         <v>7300</v>
@@ -23366,7 +23366,7 @@
         <v>10</v>
       </c>
       <c r="G793" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H793" t="n">
         <v>7200</v>
@@ -23511,7 +23511,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G798" t="n">
-        <v>8.9305534362793</v>
+        <v>8.93055248260498</v>
       </c>
       <c r="H798" t="n">
         <v>700</v>
@@ -23743,7 +23743,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H806" t="n">
         <v>4300</v>
@@ -23772,7 +23772,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H807" t="n">
         <v>9500</v>
@@ -24120,7 +24120,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H819" t="n">
         <v>1100</v>
@@ -24468,7 +24468,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H831" t="n">
         <v>4200</v>
@@ -24526,7 +24526,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H833" t="n">
         <v>1100</v>
@@ -24555,7 +24555,7 @@
         <v>10</v>
       </c>
       <c r="G834" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H834" t="n">
         <v>5900</v>
@@ -24584,7 +24584,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H835" t="n">
         <v>1600</v>
@@ -24874,7 +24874,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H845" t="n">
         <v>3000</v>
@@ -24932,7 +24932,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H847" t="n">
         <v>1100</v>
@@ -25193,7 +25193,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H856" t="n">
         <v>4000</v>
@@ -25425,7 +25425,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H864" t="n">
         <v>2300</v>
@@ -25628,7 +25628,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H871" t="n">
         <v>1200</v>
@@ -25657,7 +25657,7 @@
         <v>10</v>
       </c>
       <c r="G872" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H872" t="n">
         <v>1500</v>
@@ -25686,7 +25686,7 @@
         <v>10</v>
       </c>
       <c r="G873" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H873" t="n">
         <v>3200</v>
@@ -25744,7 +25744,7 @@
         <v>10</v>
       </c>
       <c r="G875" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H875" t="n">
         <v>7800</v>
@@ -25773,7 +25773,7 @@
         <v>10</v>
       </c>
       <c r="G876" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25860,7 +25860,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H879" t="n">
         <v>26500</v>
@@ -25947,7 +25947,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H882" t="n">
         <v>4500</v>
@@ -26121,7 +26121,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G888" t="n">
-        <v>8.9305534362793</v>
+        <v>8.93055248260498</v>
       </c>
       <c r="H888" t="n">
         <v>21000</v>
@@ -26150,7 +26150,7 @@
         <v>10</v>
       </c>
       <c r="G889" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H889" t="n">
         <v>15100</v>
@@ -26266,7 +26266,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H893" t="n">
         <v>2100</v>
@@ -26324,7 +26324,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G895" t="n">
-        <v>8.9305534362793</v>
+        <v>8.93055248260498</v>
       </c>
       <c r="H895" t="n">
         <v>2200</v>
@@ -26353,7 +26353,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H896" t="n">
         <v>1800</v>
@@ -26382,7 +26382,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H897" t="n">
         <v>900</v>
@@ -26440,7 +26440,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H899" t="n">
         <v>500</v>
@@ -26527,7 +26527,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G902" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H902" t="n">
         <v>3900</v>
@@ -26556,7 +26556,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H903" t="n">
         <v>1300</v>
@@ -26585,7 +26585,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G904" t="n">
-        <v>8.21251678466797</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H904" t="n">
         <v>2900</v>
@@ -26614,7 +26614,7 @@
         <v>9</v>
       </c>
       <c r="G905" t="n">
-        <v>8.07788562774658</v>
+        <v>8.0778865814209</v>
       </c>
       <c r="H905" t="n">
         <v>2300</v>
@@ -26643,7 +26643,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>8.12276268005371</v>
+        <v>8.12276363372803</v>
       </c>
       <c r="H906" t="n">
         <v>5400</v>
@@ -26672,7 +26672,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G907" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H907" t="n">
         <v>1400</v>
@@ -26759,7 +26759,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G910" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H910" t="n">
         <v>1300</v>
@@ -26788,7 +26788,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.35985231399536</v>
+        <v>7.3598518371582</v>
       </c>
       <c r="H911" t="n">
         <v>12900</v>
@@ -26817,7 +26817,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423852920532</v>
+        <v>7.58423757553101</v>
       </c>
       <c r="H912" t="n">
         <v>2900</v>
@@ -26846,7 +26846,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423852920532</v>
+        <v>7.58423757553101</v>
       </c>
       <c r="H913" t="n">
         <v>5400</v>
@@ -26875,7 +26875,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G914" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H914" t="n">
         <v>3400</v>
@@ -26904,7 +26904,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862426757812</v>
+        <v>7.80862379074097</v>
       </c>
       <c r="H915" t="n">
         <v>5300</v>
@@ -26933,7 +26933,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H916" t="n">
         <v>2500</v>
@@ -26962,7 +26962,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G917" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H917" t="n">
         <v>2900</v>
@@ -27107,7 +27107,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H922" t="n">
         <v>2700</v>
@@ -27368,7 +27368,7 @@
         <v>10</v>
       </c>
       <c r="G931" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H931" t="n">
         <v>600</v>
@@ -27397,7 +27397,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231418609619</v>
+        <v>8.65231513977051</v>
       </c>
       <c r="H932" t="n">
         <v>500</v>
@@ -27658,7 +27658,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G941" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H941" t="n">
         <v>3000</v>
@@ -27745,7 +27745,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G944" t="n">
-        <v>8.83182239532471</v>
+        <v>8.83182334899902</v>
       </c>
       <c r="H944" t="n">
         <v>4800</v>
@@ -60811,6 +60811,64 @@
         <v>1500</v>
       </c>
       <c r="I2084" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2085" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G2085" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="H2085" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I2085" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2086" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="H2086" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I2086" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -514,7 +514,7 @@
         <v>9.60200023651123</v>
       </c>
       <c r="G5" t="n">
-        <v>8.14810943603516</v>
+        <v>8.14811134338379</v>
       </c>
       <c r="H5" t="n">
         <v>10000</v>
@@ -572,7 +572,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G7" t="n">
-        <v>8.18035793304443</v>
+        <v>8.18035697937012</v>
       </c>
       <c r="H7" t="n">
         <v>6500</v>
@@ -601,7 +601,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11247062683105</v>
+        <v>8.11247253417969</v>
       </c>
       <c r="H8" t="n">
         <v>7000</v>
@@ -717,7 +717,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -746,7 +746,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -804,7 +804,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -833,7 +833,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H17" t="n">
         <v>1300</v>
@@ -891,7 +891,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10653018951416</v>
+        <v>8.10652923583984</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.1379280090332</v>
+        <v>8.13792896270752</v>
       </c>
       <c r="H22" t="n">
         <v>300</v>
@@ -1065,7 +1065,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852840423584</v>
+        <v>8.07852745056152</v>
       </c>
       <c r="H24" t="n">
         <v>2800</v>
@@ -1123,7 +1123,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G26" t="n">
-        <v>8.20666313171387</v>
+        <v>8.20666217803955</v>
       </c>
       <c r="H26" t="n">
         <v>200</v>
@@ -1152,7 +1152,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G27" t="n">
-        <v>8.20666313171387</v>
+        <v>8.20666217803955</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>9.52799987792969</v>
       </c>
       <c r="G28" t="n">
-        <v>8.0853157043457</v>
+        <v>8.08531475067139</v>
       </c>
       <c r="H28" t="n">
         <v>1500</v>
@@ -1210,7 +1210,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G29" t="n">
-        <v>8.0819206237793</v>
+        <v>8.08192157745361</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -1239,7 +1239,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H30" t="n">
         <v>7500</v>
@@ -1297,7 +1297,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10058975219727</v>
       </c>
       <c r="H32" t="n">
         <v>200</v>
@@ -1355,7 +1355,7 @@
         <v>9.43099975585938</v>
       </c>
       <c r="G34" t="n">
-        <v>8.00300121307373</v>
+        <v>8.00300216674805</v>
       </c>
       <c r="H34" t="n">
         <v>8100</v>
@@ -1442,7 +1442,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366855621338</v>
+        <v>7.99366760253906</v>
       </c>
       <c r="H37" t="n">
         <v>12300</v>
@@ -1500,7 +1500,7 @@
         <v>9.33100032806396</v>
       </c>
       <c r="G39" t="n">
-        <v>7.91814470291138</v>
+        <v>7.91814374923706</v>
       </c>
       <c r="H39" t="n">
         <v>400</v>
@@ -1529,7 +1529,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227216720581</v>
+        <v>7.96227121353149</v>
       </c>
       <c r="H40" t="n">
         <v>300</v>
@@ -1558,7 +1558,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227216720581</v>
+        <v>7.96227121353149</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.97924280166626</v>
+        <v>7.97924184799194</v>
       </c>
       <c r="H42" t="n">
         <v>300</v>
@@ -1616,7 +1616,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.97924280166626</v>
+        <v>7.97924184799194</v>
       </c>
       <c r="H43" t="n">
         <v>1700</v>
@@ -1732,7 +1732,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1761,7 +1761,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G48" t="n">
-        <v>7.90880870819092</v>
+        <v>7.90881061553955</v>
       </c>
       <c r="H48" t="n">
         <v>3700</v>
@@ -1819,7 +1819,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619735717773</v>
+        <v>7.85619831085205</v>
       </c>
       <c r="H50" t="n">
         <v>8700</v>
@@ -1906,7 +1906,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.77473258972168</v>
+        <v>7.77473449707031</v>
       </c>
       <c r="H53" t="n">
         <v>2300</v>
@@ -1993,7 +1993,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G56" t="n">
-        <v>7.76709651947021</v>
+        <v>7.76709604263306</v>
       </c>
       <c r="H56" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.8069806098938</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H58" t="n">
         <v>4100</v>
@@ -2080,7 +2080,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76454925537109</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H59" t="n">
         <v>13600</v>
@@ -2109,7 +2109,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.8069806098938</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H60" t="n">
         <v>24300</v>
@@ -2167,7 +2167,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H62" t="n">
         <v>8400</v>
@@ -2196,7 +2196,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H64" t="n">
         <v>1600</v>
@@ -2254,7 +2254,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.8069806098938</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H65" t="n">
         <v>7100</v>
@@ -2283,7 +2283,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H66" t="n">
         <v>2500</v>
@@ -2312,7 +2312,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746366500854</v>
+        <v>7.78746271133423</v>
       </c>
       <c r="H72" t="n">
         <v>700</v>
@@ -2486,7 +2486,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746366500854</v>
+        <v>7.78746271133423</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>7.85534858703613</v>
+        <v>7.85534954071045</v>
       </c>
       <c r="H74" t="n">
         <v>10200</v>
@@ -2573,7 +2573,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761077880859</v>
+        <v>8.02761173248291</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2602,7 +2602,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177255630493</v>
+        <v>7.84177160263062</v>
       </c>
       <c r="H77" t="n">
         <v>4000</v>
@@ -2631,7 +2631,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.79085636138916</v>
+        <v>7.790855884552</v>
       </c>
       <c r="H78" t="n">
         <v>800</v>
@@ -2747,7 +2747,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406763076782</v>
+        <v>7.78406810760498</v>
       </c>
       <c r="H82" t="n">
         <v>200</v>
@@ -2776,7 +2776,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H83" t="n">
         <v>1100</v>
@@ -2805,7 +2805,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.80103826522827</v>
+        <v>7.80103921890259</v>
       </c>
       <c r="H86" t="n">
         <v>2900</v>
@@ -2921,7 +2921,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098930358887</v>
+        <v>7.89099025726318</v>
       </c>
       <c r="H88" t="n">
         <v>200</v>
@@ -2950,7 +2950,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782699584961</v>
+        <v>7.80782794952393</v>
       </c>
       <c r="H89" t="n">
         <v>5100</v>
@@ -2979,7 +2979,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H91" t="n">
         <v>700</v>
@@ -3037,7 +3037,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408418655396</v>
+        <v>7.92408466339111</v>
       </c>
       <c r="H92" t="n">
         <v>1200</v>
@@ -3095,7 +3095,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539945602417</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3124,7 +3124,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76454925537109</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H95" t="n">
         <v>20300</v>
@@ -3153,7 +3153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76454925537109</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G97" t="n">
-        <v>7.72212171554565</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H97" t="n">
         <v>7500</v>
@@ -3211,7 +3211,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.72212171554565</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70514869689941</v>
+        <v>7.70514965057373</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3327,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726329803467</v>
+        <v>7.63726282119751</v>
       </c>
       <c r="H102" t="n">
         <v>700</v>
@@ -3356,7 +3356,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423440933228</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423440933228</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G105" t="n">
-        <v>7.55240440368652</v>
+        <v>7.55240392684937</v>
       </c>
       <c r="H105" t="n">
         <v>200</v>
@@ -3472,7 +3472,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.72212171554565</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H107" t="n">
         <v>1100</v>
@@ -3501,7 +3501,7 @@
         <v>9.10099983215332</v>
       </c>
       <c r="G108" t="n">
-        <v>7.72296953201294</v>
+        <v>7.72296905517578</v>
       </c>
       <c r="H108" t="n">
         <v>2200</v>
@@ -3530,7 +3530,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72212171554565</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H109" t="n">
         <v>2200</v>
@@ -3588,7 +3588,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70514869689941</v>
+        <v>7.70514965057373</v>
       </c>
       <c r="H111" t="n">
         <v>25500</v>
@@ -3617,7 +3617,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70514869689941</v>
+        <v>7.70514965057373</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817758560181</v>
       </c>
       <c r="H113" t="n">
         <v>15900</v>
@@ -3704,7 +3704,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902587890625</v>
+        <v>7.68902635574341</v>
       </c>
       <c r="H115" t="n">
         <v>1500</v>
@@ -3733,7 +3733,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110569000244</v>
+        <v>7.85110473632812</v>
       </c>
       <c r="H116" t="n">
         <v>800</v>
@@ -3762,7 +3762,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273771286011</v>
+        <v>7.80273675918579</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -3791,7 +3791,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308544158936</v>
+        <v>7.68308734893799</v>
       </c>
       <c r="H118" t="n">
         <v>2400</v>
@@ -3849,7 +3849,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G120" t="n">
-        <v>7.72212171554565</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H120" t="n">
         <v>2000</v>
@@ -3878,7 +3878,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G121" t="n">
-        <v>7.72212171554565</v>
+        <v>7.72212219238281</v>
       </c>
       <c r="H121" t="n">
         <v>5000</v>
@@ -3907,7 +3907,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817758560181</v>
       </c>
       <c r="H122" t="n">
         <v>3300</v>
@@ -3936,7 +3936,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H123" t="n">
         <v>100</v>
@@ -3965,7 +3965,7 @@
         <v>9.14900016784668</v>
       </c>
       <c r="G124" t="n">
-        <v>7.76370191574097</v>
+        <v>7.76370286941528</v>
       </c>
       <c r="H124" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.86553192138672</v>
+        <v>7.8655309677124</v>
       </c>
       <c r="H125" t="n">
         <v>300</v>
@@ -4023,7 +4023,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152275085449</v>
+        <v>7.78152179718018</v>
       </c>
       <c r="H126" t="n">
         <v>24300</v>
@@ -4052,7 +4052,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406763076782</v>
+        <v>7.78406810760498</v>
       </c>
       <c r="H127" t="n">
         <v>2000</v>
@@ -4081,7 +4081,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76454925537109</v>
+        <v>7.76455068588257</v>
       </c>
       <c r="H128" t="n">
         <v>100</v>
@@ -4110,7 +4110,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303552627563</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303552627563</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000806808472</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000806808472</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445180892944</v>
+        <v>7.94445085525513</v>
       </c>
       <c r="H136" t="n">
         <v>2500</v>
@@ -4400,7 +4400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.8069806098938</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H139" t="n">
         <v>1200</v>
@@ -4835,7 +4835,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.92832708358765</v>
+        <v>7.92832803726196</v>
       </c>
       <c r="H154" t="n">
         <v>1100</v>
@@ -4893,7 +4893,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G156" t="n">
-        <v>8.06664562225342</v>
+        <v>8.06664657592773</v>
       </c>
       <c r="H156" t="n">
         <v>100</v>
@@ -4922,7 +4922,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G157" t="n">
-        <v>8.06664562225342</v>
+        <v>8.06664657592773</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G158" t="n">
-        <v>8.06664562225342</v>
+        <v>8.06664657592773</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>8.05306816101074</v>
+        <v>8.05306911468506</v>
       </c>
       <c r="H165" t="n">
         <v>300</v>
@@ -5183,7 +5183,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.92832708358765</v>
+        <v>7.92832803726196</v>
       </c>
       <c r="H166" t="n">
         <v>1200</v>
@@ -5357,7 +5357,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H172" t="n">
         <v>3700</v>
@@ -5473,7 +5473,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H176" t="n">
         <v>4900</v>
@@ -5531,7 +5531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H178" t="n">
         <v>300</v>
@@ -5560,7 +5560,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H179" t="n">
         <v>100</v>
@@ -5676,7 +5676,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H184" t="n">
         <v>300</v>
@@ -5734,7 +5734,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H185" t="n">
         <v>200</v>
@@ -5763,7 +5763,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H186" t="n">
         <v>700</v>
@@ -5792,7 +5792,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H187" t="n">
         <v>900</v>
@@ -5850,7 +5850,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H189" t="n">
         <v>1900</v>
@@ -5908,7 +5908,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H191" t="n">
         <v>5600</v>
@@ -5966,7 +5966,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H193" t="n">
         <v>3200</v>
@@ -5995,7 +5995,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H194" t="n">
         <v>300</v>
@@ -6082,7 +6082,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6111,7 +6111,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H198" t="n">
         <v>4700</v>
@@ -6140,7 +6140,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H200" t="n">
         <v>2000</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H201" t="n">
         <v>1500</v>
@@ -6227,7 +6227,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H202" t="n">
         <v>800</v>
@@ -6256,7 +6256,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H203" t="n">
         <v>100</v>
@@ -6285,7 +6285,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H204" t="n">
         <v>5900</v>
@@ -6343,7 +6343,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H206" t="n">
         <v>300</v>
@@ -6401,7 +6401,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6430,7 +6430,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G209" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6459,7 +6459,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H210" t="n">
         <v>600</v>
@@ -6546,7 +6546,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H213" t="n">
         <v>2600</v>
@@ -6575,7 +6575,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H214" t="n">
         <v>200</v>
@@ -6604,7 +6604,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H215" t="n">
         <v>6600</v>
@@ -6633,7 +6633,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H216" t="n">
         <v>100</v>
@@ -6662,7 +6662,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6691,7 +6691,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H218" t="n">
         <v>900</v>
@@ -6720,7 +6720,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6749,7 +6749,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H220" t="n">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H221" t="n">
         <v>17700</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H224" t="n">
         <v>800</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H225" t="n">
         <v>600</v>
@@ -6923,7 +6923,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H226" t="n">
         <v>100</v>
@@ -6952,7 +6952,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H227" t="n">
         <v>100</v>
@@ -6981,7 +6981,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H228" t="n">
         <v>9100</v>
@@ -7010,7 +7010,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H229" t="n">
         <v>100</v>
@@ -7039,7 +7039,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7068,7 +7068,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7097,7 +7097,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H232" t="n">
         <v>5200</v>
@@ -7126,7 +7126,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H233" t="n">
         <v>5100</v>
@@ -7184,7 +7184,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H235" t="n">
         <v>300</v>
@@ -7213,7 +7213,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H236" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H237" t="n">
         <v>100</v>
@@ -7271,7 +7271,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H238" t="n">
         <v>3200</v>
@@ -7300,7 +7300,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H239" t="n">
         <v>100</v>
@@ -7329,7 +7329,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H240" t="n">
         <v>100</v>
@@ -7358,7 +7358,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H241" t="n">
         <v>400</v>
@@ -7387,7 +7387,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H242" t="n">
         <v>7200</v>
@@ -7416,7 +7416,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H243" t="n">
         <v>100</v>
@@ -7445,7 +7445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H244" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H248" t="n">
         <v>700</v>
@@ -7590,7 +7590,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H249" t="n">
         <v>600</v>
@@ -7619,7 +7619,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G250" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H250" t="n">
         <v>300</v>
@@ -7648,7 +7648,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H251" t="n">
         <v>2100</v>
@@ -7677,7 +7677,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H252" t="n">
         <v>1800</v>
@@ -7706,7 +7706,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H253" t="n">
         <v>1700</v>
@@ -7735,7 +7735,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H254" t="n">
         <v>1800</v>
@@ -7793,7 +7793,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G256" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H256" t="n">
         <v>2300</v>
@@ -7822,7 +7822,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H257" t="n">
         <v>100</v>
@@ -7851,7 +7851,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H258" t="n">
         <v>1200</v>
@@ -7880,7 +7880,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H259" t="n">
         <v>25000</v>
@@ -7909,7 +7909,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H263" t="n">
         <v>8000</v>
@@ -8025,7 +8025,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8054,7 +8054,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G265" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H265" t="n">
         <v>100</v>
@@ -8083,7 +8083,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G266" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8112,7 +8112,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G267" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H268" t="n">
         <v>11200</v>
@@ -8170,7 +8170,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H269" t="n">
         <v>600</v>
@@ -8228,7 +8228,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H272" t="n">
         <v>100</v>
@@ -8286,7 +8286,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H273" t="n">
         <v>100</v>
@@ -8315,7 +8315,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H274" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H276" t="n">
         <v>100</v>
@@ -8460,7 +8460,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H279" t="n">
         <v>28000</v>
@@ -8605,7 +8605,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H284" t="n">
         <v>6900</v>
@@ -8634,7 +8634,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H285" t="n">
         <v>200</v>
@@ -8866,7 +8866,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G293" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H293" t="n">
         <v>100</v>
@@ -8895,7 +8895,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G294" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G295" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G296" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H296" t="n">
         <v>200</v>
@@ -9011,7 +9011,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H298" t="n">
         <v>10700</v>
@@ -9040,7 +9040,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9069,7 +9069,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H300" t="n">
         <v>100</v>
@@ -9243,7 +9243,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H309" t="n">
         <v>500</v>
@@ -9359,7 +9359,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H310" t="n">
         <v>3300</v>
@@ -9388,7 +9388,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H311" t="n">
         <v>100</v>
@@ -9417,7 +9417,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H312" t="n">
         <v>100</v>
@@ -9446,7 +9446,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H313" t="n">
         <v>12700</v>
@@ -9475,7 +9475,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H314" t="n">
         <v>7100</v>
@@ -9504,7 +9504,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H318" t="n">
         <v>300</v>
@@ -9736,7 +9736,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H323" t="n">
         <v>26700</v>
@@ -9765,7 +9765,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H324" t="n">
         <v>100</v>
@@ -9794,7 +9794,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H325" t="n">
         <v>20100</v>
@@ -9823,7 +9823,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G326" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H326" t="n">
         <v>100</v>
@@ -9852,7 +9852,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -9881,7 +9881,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H328" t="n">
         <v>52800</v>
@@ -9910,7 +9910,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H329" t="n">
         <v>10000</v>
@@ -9939,7 +9939,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H330" t="n">
         <v>200</v>
@@ -9968,7 +9968,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H331" t="n">
         <v>900</v>
@@ -9997,7 +9997,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H332" t="n">
         <v>10000</v>
@@ -10026,7 +10026,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H334" t="n">
         <v>100</v>
@@ -10084,7 +10084,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H335" t="n">
         <v>2200</v>
@@ -10113,7 +10113,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G336" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H336" t="n">
         <v>100</v>
@@ -10142,7 +10142,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G337" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H337" t="n">
         <v>100</v>
@@ -10171,7 +10171,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H338" t="n">
         <v>400</v>
@@ -10200,7 +10200,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H339" t="n">
         <v>6600</v>
@@ -10229,7 +10229,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H340" t="n">
         <v>400</v>
@@ -10258,7 +10258,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H341" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H344" t="n">
         <v>1700</v>
@@ -10374,7 +10374,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G345" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G346" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H346" t="n">
         <v>3000</v>
@@ -10432,7 +10432,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G347" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G350" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H350" t="n">
         <v>4400</v>
@@ -10548,7 +10548,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H351" t="n">
         <v>1400</v>
@@ -10809,7 +10809,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H360" t="n">
         <v>5000</v>
@@ -10867,7 +10867,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H362" t="n">
         <v>300</v>
@@ -10896,7 +10896,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H363" t="n">
         <v>1100</v>
@@ -10925,7 +10925,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H365" t="n">
         <v>100</v>
@@ -10983,7 +10983,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H367" t="n">
         <v>900</v>
@@ -11041,7 +11041,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H368" t="n">
         <v>300</v>
@@ -11070,7 +11070,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H369" t="n">
         <v>100</v>
@@ -11099,7 +11099,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H371" t="n">
         <v>1700</v>
@@ -11157,7 +11157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H372" t="n">
         <v>1200</v>
@@ -11244,7 +11244,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H375" t="n">
         <v>5700</v>
@@ -11331,7 +11331,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H378" t="n">
         <v>30700</v>
@@ -11360,7 +11360,7 @@
         <v>9.75</v>
       </c>
       <c r="G379" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H379" t="n">
         <v>67200</v>
@@ -11389,7 +11389,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H380" t="n">
         <v>15200</v>
@@ -11476,7 +11476,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H383" t="n">
         <v>800</v>
@@ -11563,7 +11563,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H386" t="n">
         <v>300</v>
@@ -11621,7 +11621,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H388" t="n">
         <v>800</v>
@@ -11650,7 +11650,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H389" t="n">
         <v>4300</v>
@@ -11679,7 +11679,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H390" t="n">
         <v>300</v>
@@ -11795,7 +11795,7 @@
         <v>9.75</v>
       </c>
       <c r="G394" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H394" t="n">
         <v>23100</v>
@@ -11911,7 +11911,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H398" t="n">
         <v>1100</v>
@@ -11998,7 +11998,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H401" t="n">
         <v>7500</v>
@@ -12027,7 +12027,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H402" t="n">
         <v>700</v>
@@ -12056,7 +12056,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H403" t="n">
         <v>2200</v>
@@ -12085,7 +12085,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H404" t="n">
         <v>300</v>
@@ -12114,7 +12114,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H405" t="n">
         <v>100</v>
@@ -12143,7 +12143,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H406" t="n">
         <v>11100</v>
@@ -12288,7 +12288,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12491,7 +12491,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H418" t="n">
         <v>10000</v>
@@ -12549,7 +12549,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G420" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H420" t="n">
         <v>12500</v>
@@ -12578,7 +12578,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G421" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H421" t="n">
         <v>10000</v>
@@ -12607,7 +12607,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G424" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H424" t="n">
         <v>8900</v>
@@ -12694,7 +12694,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H426" t="n">
         <v>300</v>
@@ -12752,7 +12752,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G427" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H427" t="n">
         <v>2000</v>
@@ -12868,7 +12868,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H431" t="n">
         <v>700</v>
@@ -12897,7 +12897,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H432" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G433" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H433" t="n">
         <v>800</v>
@@ -13129,7 +13129,7 @@
         <v>9.75</v>
       </c>
       <c r="G440" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H440" t="n">
         <v>300</v>
@@ -13216,7 +13216,7 @@
         <v>9.75</v>
       </c>
       <c r="G443" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H443" t="n">
         <v>100</v>
@@ -13245,7 +13245,7 @@
         <v>9.75</v>
       </c>
       <c r="G444" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H444" t="n">
         <v>500</v>
@@ -13274,7 +13274,7 @@
         <v>9.75</v>
       </c>
       <c r="G445" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>9.75</v>
       </c>
       <c r="G446" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13361,7 +13361,7 @@
         <v>9.75</v>
       </c>
       <c r="G448" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H448" t="n">
         <v>400</v>
@@ -13390,7 +13390,7 @@
         <v>9.75</v>
       </c>
       <c r="G449" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H449" t="n">
         <v>700</v>
@@ -13419,7 +13419,7 @@
         <v>9.75</v>
       </c>
       <c r="G450" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>9.75</v>
       </c>
       <c r="G451" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>9.75</v>
       </c>
       <c r="G452" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H452" t="n">
         <v>3100</v>
@@ -13506,7 +13506,7 @@
         <v>9.75</v>
       </c>
       <c r="G453" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H453" t="n">
         <v>100</v>
@@ -13535,7 +13535,7 @@
         <v>9.75</v>
       </c>
       <c r="G454" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H454" t="n">
         <v>100000</v>
@@ -13593,7 +13593,7 @@
         <v>9.75</v>
       </c>
       <c r="G456" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H456" t="n">
         <v>15500</v>
@@ -13622,7 +13622,7 @@
         <v>9.75</v>
       </c>
       <c r="G457" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H457" t="n">
         <v>50000</v>
@@ -13709,7 +13709,7 @@
         <v>9.75</v>
       </c>
       <c r="G460" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H460" t="n">
         <v>24400</v>
@@ -13738,7 +13738,7 @@
         <v>9.75</v>
       </c>
       <c r="G461" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>9.75</v>
       </c>
       <c r="G462" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H462" t="n">
         <v>10100</v>
@@ -13796,7 +13796,7 @@
         <v>9.75</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H463" t="n">
         <v>5900</v>
@@ -13825,7 +13825,7 @@
         <v>9.75</v>
       </c>
       <c r="G464" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H464" t="n">
         <v>18200</v>
@@ -13854,7 +13854,7 @@
         <v>9.75</v>
       </c>
       <c r="G465" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>9.75</v>
       </c>
       <c r="G466" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H466" t="n">
         <v>10100</v>
@@ -13912,7 +13912,7 @@
         <v>9.75</v>
       </c>
       <c r="G467" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H467" t="n">
         <v>8000</v>
@@ -13941,7 +13941,7 @@
         <v>9.75</v>
       </c>
       <c r="G468" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H468" t="n">
         <v>5800</v>
@@ -13999,7 +13999,7 @@
         <v>9.75</v>
       </c>
       <c r="G470" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H470" t="n">
         <v>5600</v>
@@ -14115,7 +14115,7 @@
         <v>9.75</v>
       </c>
       <c r="G474" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H474" t="n">
         <v>68300</v>
@@ -14144,7 +14144,7 @@
         <v>9.75</v>
       </c>
       <c r="G475" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H475" t="n">
         <v>88200</v>
@@ -14173,7 +14173,7 @@
         <v>9.75</v>
       </c>
       <c r="G476" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H476" t="n">
         <v>12000</v>
@@ -14260,7 +14260,7 @@
         <v>9.75</v>
       </c>
       <c r="G479" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H479" t="n">
         <v>36400</v>
@@ -14289,7 +14289,7 @@
         <v>9.75</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H480" t="n">
         <v>5300</v>
@@ -14318,7 +14318,7 @@
         <v>9.75</v>
       </c>
       <c r="G481" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H481" t="n">
         <v>22100</v>
@@ -14376,7 +14376,7 @@
         <v>9.75</v>
       </c>
       <c r="G483" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H483" t="n">
         <v>61200</v>
@@ -14405,7 +14405,7 @@
         <v>9.75</v>
       </c>
       <c r="G484" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H484" t="n">
         <v>17600</v>
@@ -14434,7 +14434,7 @@
         <v>9.75</v>
       </c>
       <c r="G485" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H485" t="n">
         <v>20000</v>
@@ -14463,7 +14463,7 @@
         <v>9.75</v>
       </c>
       <c r="G486" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H486" t="n">
         <v>34700</v>
@@ -14521,7 +14521,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H488" t="n">
         <v>140500</v>
@@ -14550,7 +14550,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H489" t="n">
         <v>134000</v>
@@ -14579,7 +14579,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H490" t="n">
         <v>5800</v>
@@ -14608,7 +14608,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35856151580811</v>
       </c>
       <c r="H491" t="n">
         <v>129300</v>
@@ -15014,7 +15014,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641284942627</v>
       </c>
       <c r="H505" t="n">
         <v>400</v>
@@ -15130,7 +15130,7 @@
         <v>9.75</v>
       </c>
       <c r="G509" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H509" t="n">
         <v>109100</v>
@@ -15333,7 +15333,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G516" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H516" t="n">
         <v>5700</v>
@@ -15362,7 +15362,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G518" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H531" t="n">
         <v>200</v>
@@ -16058,7 +16058,7 @@
         <v>9.75</v>
       </c>
       <c r="G541" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H541" t="n">
         <v>1500</v>
@@ -16087,7 +16087,7 @@
         <v>9.75</v>
       </c>
       <c r="G542" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884181976318</v>
       </c>
       <c r="H552" t="n">
         <v>1800</v>
@@ -16406,7 +16406,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H553" t="n">
         <v>1800</v>
@@ -16435,7 +16435,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H554" t="n">
         <v>2900</v>
@@ -16464,7 +16464,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>7.59483337402344</v>
+        <v>7.59483242034912</v>
       </c>
       <c r="H555" t="n">
         <v>5200</v>
@@ -16493,7 +16493,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G556" t="n">
-        <v>7.59483337402344</v>
+        <v>7.59483242034912</v>
       </c>
       <c r="H556" t="n">
         <v>2100</v>
@@ -16522,7 +16522,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782867431641</v>
+        <v>7.29782915115356</v>
       </c>
       <c r="H557" t="n">
         <v>1100</v>
@@ -16580,7 +16580,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66139030456543</v>
+        <v>6.66138982772827</v>
       </c>
       <c r="H559" t="n">
         <v>9300</v>
@@ -16609,7 +16609,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G560" t="n">
-        <v>6.10980939865112</v>
+        <v>6.10980987548828</v>
       </c>
       <c r="H560" t="n">
         <v>3900</v>
@@ -16638,7 +16638,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>6.10980939865112</v>
+        <v>6.10980987548828</v>
       </c>
       <c r="H561" t="n">
         <v>49300</v>
@@ -16667,7 +16667,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>6.49167346954346</v>
+        <v>6.49167394638062</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16725,7 +16725,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>6.8311071395874</v>
+        <v>6.83110761642456</v>
       </c>
       <c r="H564" t="n">
         <v>8800</v>
@@ -16928,7 +16928,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G571" t="n">
-        <v>6.94854784011841</v>
+        <v>6.94854831695557</v>
       </c>
       <c r="H571" t="n">
         <v>1400</v>
@@ -16986,7 +16986,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.4678316116333</v>
+        <v>6.46783113479614</v>
       </c>
       <c r="H573" t="n">
         <v>4700</v>
@@ -17044,7 +17044,7 @@
         <v>8.25</v>
       </c>
       <c r="G575" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H575" t="n">
         <v>6200</v>
@@ -17073,7 +17073,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>7.16705560684204</v>
+        <v>7.1670560836792</v>
       </c>
       <c r="H576" t="n">
         <v>24700</v>
@@ -17218,7 +17218,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G581" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186315536499</v>
       </c>
       <c r="H581" t="n">
         <v>200</v>
@@ -17508,7 +17508,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.73517751693726</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H591" t="n">
         <v>19400</v>
@@ -17798,7 +17798,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>7.47296810150146</v>
+        <v>7.47296667098999</v>
       </c>
       <c r="H601" t="n">
         <v>6300</v>
@@ -17827,7 +17827,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>7.47296810150146</v>
+        <v>7.47296667098999</v>
       </c>
       <c r="H602" t="n">
         <v>12100</v>
@@ -17856,7 +17856,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H603" t="n">
         <v>300</v>
@@ -17885,7 +17885,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.73517751693726</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H604" t="n">
         <v>700</v>
@@ -18204,7 +18204,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.73517751693726</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H615" t="n">
         <v>1200</v>
@@ -18378,7 +18378,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H621" t="n">
         <v>100</v>
@@ -18407,7 +18407,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H622" t="n">
         <v>100</v>
@@ -18436,7 +18436,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.47296810150146</v>
+        <v>7.47296667098999</v>
       </c>
       <c r="H623" t="n">
         <v>2000</v>
@@ -18494,7 +18494,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H625" t="n">
         <v>1000</v>
@@ -18552,7 +18552,7 @@
         <v>8.25</v>
       </c>
       <c r="G627" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H627" t="n">
         <v>2600</v>
@@ -18581,7 +18581,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>7.47296810150146</v>
+        <v>7.47296667098999</v>
       </c>
       <c r="H628" t="n">
         <v>5100</v>
@@ -18610,7 +18610,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>7.47296810150146</v>
+        <v>7.47296667098999</v>
       </c>
       <c r="H629" t="n">
         <v>1400</v>
@@ -18639,7 +18639,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186315536499</v>
       </c>
       <c r="H630" t="n">
         <v>5900</v>
@@ -18668,7 +18668,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G631" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186315536499</v>
       </c>
       <c r="H631" t="n">
         <v>1200</v>
@@ -18726,7 +18726,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186315536499</v>
       </c>
       <c r="H633" t="n">
         <v>4200</v>
@@ -18784,7 +18784,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H635" t="n">
         <v>3900</v>
@@ -18900,7 +18900,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.16705560684204</v>
+        <v>7.1670560836792</v>
       </c>
       <c r="H639" t="n">
         <v>1100</v>
@@ -19103,7 +19103,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G646" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H646" t="n">
         <v>2300</v>
@@ -19219,7 +19219,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G650" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H650" t="n">
         <v>800</v>
@@ -19248,7 +19248,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G651" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H651" t="n">
         <v>400</v>
@@ -19364,7 +19364,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G655" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H655" t="n">
         <v>1800</v>
@@ -19393,7 +19393,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G656" t="n">
-        <v>7.16705560684204</v>
+        <v>7.1670560836792</v>
       </c>
       <c r="H656" t="n">
         <v>1100</v>
@@ -19422,7 +19422,7 @@
         <v>8.25</v>
       </c>
       <c r="G657" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H657" t="n">
         <v>8600</v>
@@ -19451,7 +19451,7 @@
         <v>8.25</v>
       </c>
       <c r="G658" t="n">
-        <v>7.21075773239136</v>
+        <v>7.21075820922852</v>
       </c>
       <c r="H658" t="n">
         <v>1100</v>
@@ -19480,7 +19480,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>7.16705560684204</v>
+        <v>7.1670560836792</v>
       </c>
       <c r="H659" t="n">
         <v>5400</v>
@@ -19567,7 +19567,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H662" t="n">
         <v>7300</v>
@@ -19654,7 +19654,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H665" t="n">
         <v>18900</v>
@@ -20205,7 +20205,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738454818726</v>
+        <v>7.99738645553589</v>
       </c>
       <c r="H684" t="n">
         <v>3100</v>
@@ -20524,7 +20524,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738454818726</v>
+        <v>7.99738645553589</v>
       </c>
       <c r="H695" t="n">
         <v>5300</v>
@@ -20553,7 +20553,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>8.12849140167236</v>
+        <v>8.12849044799805</v>
       </c>
       <c r="H696" t="n">
         <v>5300</v>
@@ -20582,7 +20582,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>8.12849140167236</v>
+        <v>8.12849044799805</v>
       </c>
       <c r="H697" t="n">
         <v>6600</v>
@@ -20756,7 +20756,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227088928223</v>
       </c>
       <c r="H703" t="n">
         <v>1400</v>
@@ -20872,7 +20872,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H707" t="n">
         <v>5300</v>
@@ -20930,7 +20930,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G709" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H709" t="n">
         <v>5000</v>
@@ -20988,7 +20988,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G711" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H711" t="n">
         <v>900</v>
@@ -21075,7 +21075,7 @@
         <v>9</v>
       </c>
       <c r="G714" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H714" t="n">
         <v>2100</v>
@@ -21104,7 +21104,7 @@
         <v>9</v>
       </c>
       <c r="G715" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H715" t="n">
         <v>1600</v>
@@ -21162,7 +21162,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G717" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H717" t="n">
         <v>5900</v>
@@ -21191,7 +21191,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227088928223</v>
       </c>
       <c r="H718" t="n">
         <v>2600</v>
@@ -21220,7 +21220,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227088928223</v>
       </c>
       <c r="H719" t="n">
         <v>900</v>
@@ -21336,7 +21336,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227088928223</v>
       </c>
       <c r="H723" t="n">
         <v>26400</v>
@@ -21365,7 +21365,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227088928223</v>
       </c>
       <c r="H724" t="n">
         <v>21400</v>
@@ -21394,7 +21394,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227088928223</v>
       </c>
       <c r="H725" t="n">
         <v>70900</v>
@@ -21568,7 +21568,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227088928223</v>
       </c>
       <c r="H731" t="n">
         <v>300</v>
@@ -21916,7 +21916,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G743" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H743" t="n">
         <v>300</v>
@@ -21974,7 +21974,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G745" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H745" t="n">
         <v>400</v>
@@ -22670,7 +22670,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H769" t="n">
         <v>1400</v>
@@ -22699,7 +22699,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H771" t="n">
         <v>300</v>
@@ -22815,7 +22815,7 @@
         <v>10</v>
       </c>
       <c r="G774" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H774" t="n">
         <v>23000</v>
@@ -22844,7 +22844,7 @@
         <v>10</v>
       </c>
       <c r="G775" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H775" t="n">
         <v>13400</v>
@@ -22873,7 +22873,7 @@
         <v>10.5</v>
       </c>
       <c r="G776" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H776" t="n">
         <v>25300</v>
@@ -22989,7 +22989,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>9.60370922088623</v>
+        <v>9.60371017456055</v>
       </c>
       <c r="H780" t="n">
         <v>22300</v>
@@ -23192,7 +23192,7 @@
         <v>10.5</v>
       </c>
       <c r="G787" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H787" t="n">
         <v>6800</v>
@@ -23250,7 +23250,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H789" t="n">
         <v>5100</v>
@@ -23308,7 +23308,7 @@
         <v>10</v>
       </c>
       <c r="G791" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H791" t="n">
         <v>7300</v>
@@ -23366,7 +23366,7 @@
         <v>10</v>
       </c>
       <c r="G793" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H793" t="n">
         <v>7200</v>
@@ -23453,7 +23453,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H796" t="n">
         <v>1300</v>
@@ -23540,7 +23540,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H799" t="n">
         <v>2300</v>
@@ -23627,7 +23627,7 @@
         <v>9.75</v>
       </c>
       <c r="G802" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H802" t="n">
         <v>4400</v>
@@ -23772,7 +23772,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H807" t="n">
         <v>9500</v>
@@ -23801,7 +23801,7 @@
         <v>9.75</v>
       </c>
       <c r="G808" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H808" t="n">
         <v>2400</v>
@@ -23946,7 +23946,7 @@
         <v>9.75</v>
       </c>
       <c r="G813" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H813" t="n">
         <v>900</v>
@@ -24120,7 +24120,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H819" t="n">
         <v>1100</v>
@@ -24352,7 +24352,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H827" t="n">
         <v>49700</v>
@@ -24381,7 +24381,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H828" t="n">
         <v>9700</v>
@@ -24410,7 +24410,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H829" t="n">
         <v>12300</v>
@@ -24439,7 +24439,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H830" t="n">
         <v>1900</v>
@@ -24497,7 +24497,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H832" t="n">
         <v>1700</v>
@@ -24555,7 +24555,7 @@
         <v>10</v>
       </c>
       <c r="G834" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H834" t="n">
         <v>5900</v>
@@ -24700,7 +24700,7 @@
         <v>9.75</v>
       </c>
       <c r="G839" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H839" t="n">
         <v>4200</v>
@@ -24729,7 +24729,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G840" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H840" t="n">
         <v>500</v>
@@ -24787,7 +24787,7 @@
         <v>9.75</v>
       </c>
       <c r="G842" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H842" t="n">
         <v>700</v>
@@ -24845,7 +24845,7 @@
         <v>9.75</v>
       </c>
       <c r="G844" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H844" t="n">
         <v>700</v>
@@ -24932,7 +24932,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H847" t="n">
         <v>1100</v>
@@ -24990,7 +24990,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H849" t="n">
         <v>3700</v>
@@ -25019,7 +25019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H850" t="n">
         <v>1700</v>
@@ -25193,7 +25193,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H856" t="n">
         <v>4000</v>
@@ -25251,7 +25251,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H858" t="n">
         <v>3300</v>
@@ -25483,7 +25483,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H866" t="n">
         <v>200</v>
@@ -25541,7 +25541,7 @@
         <v>10.5</v>
       </c>
       <c r="G868" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H868" t="n">
         <v>2200</v>
@@ -25570,7 +25570,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H869" t="n">
         <v>13500</v>
@@ -25657,7 +25657,7 @@
         <v>10</v>
       </c>
       <c r="G872" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H872" t="n">
         <v>1500</v>
@@ -25686,7 +25686,7 @@
         <v>10</v>
       </c>
       <c r="G873" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H873" t="n">
         <v>3200</v>
@@ -25744,7 +25744,7 @@
         <v>10</v>
       </c>
       <c r="G875" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H875" t="n">
         <v>7800</v>
@@ -25773,7 +25773,7 @@
         <v>10</v>
       </c>
       <c r="G876" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H878" t="n">
         <v>23100</v>
@@ -25889,7 +25889,7 @@
         <v>10.5</v>
       </c>
       <c r="G880" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H880" t="n">
         <v>18700</v>
@@ -25918,7 +25918,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H881" t="n">
         <v>21200</v>
@@ -25976,7 +25976,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H883" t="n">
         <v>6700</v>
@@ -26005,7 +26005,7 @@
         <v>10.5</v>
       </c>
       <c r="G884" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H884" t="n">
         <v>11400</v>
@@ -26034,7 +26034,7 @@
         <v>10.5</v>
       </c>
       <c r="G885" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H885" t="n">
         <v>22400</v>
@@ -26063,7 +26063,7 @@
         <v>10.5</v>
       </c>
       <c r="G886" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H886" t="n">
         <v>19400</v>
@@ -26092,7 +26092,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H887" t="n">
         <v>10800</v>
@@ -26150,7 +26150,7 @@
         <v>10</v>
       </c>
       <c r="G889" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H889" t="n">
         <v>15100</v>
@@ -26179,7 +26179,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H890" t="n">
         <v>2500</v>
@@ -26208,7 +26208,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H891" t="n">
         <v>5500</v>
@@ -26237,7 +26237,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H892" t="n">
         <v>1200</v>
@@ -26295,7 +26295,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H894" t="n">
         <v>500</v>
@@ -26585,7 +26585,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G904" t="n">
-        <v>8.21251773834229</v>
+        <v>8.2125186920166</v>
       </c>
       <c r="H904" t="n">
         <v>2900</v>
@@ -26614,7 +26614,7 @@
         <v>9</v>
       </c>
       <c r="G905" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H905" t="n">
         <v>2300</v>
@@ -26788,7 +26788,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.3598518371582</v>
+        <v>7.35985231399536</v>
       </c>
       <c r="H911" t="n">
         <v>12900</v>
@@ -26817,7 +26817,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423757553101</v>
+        <v>7.58423709869385</v>
       </c>
       <c r="H912" t="n">
         <v>2900</v>
@@ -26846,7 +26846,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423757553101</v>
+        <v>7.58423709869385</v>
       </c>
       <c r="H913" t="n">
         <v>5400</v>
@@ -26904,7 +26904,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862379074097</v>
+        <v>7.80862283706665</v>
       </c>
       <c r="H915" t="n">
         <v>5300</v>
@@ -27107,7 +27107,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H922" t="n">
         <v>2700</v>
@@ -27165,7 +27165,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G924" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H924" t="n">
         <v>500</v>
@@ -27194,7 +27194,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -27368,7 +27368,7 @@
         <v>10</v>
       </c>
       <c r="G931" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H931" t="n">
         <v>600</v>
@@ -27397,7 +27397,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231513977051</v>
+        <v>8.65231418609619</v>
       </c>
       <c r="H932" t="n">
         <v>500</v>
@@ -27455,7 +27455,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.54461002349854</v>
+        <v>8.54460906982422</v>
       </c>
       <c r="H934" t="n">
         <v>26000</v>
@@ -27484,7 +27484,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27513,7 +27513,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821620941162</v>
+        <v>8.68821716308594</v>
       </c>
       <c r="H936" t="n">
         <v>15100</v>
@@ -27716,7 +27716,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G943" t="n">
-        <v>8.84977340698242</v>
+        <v>8.84977245330811</v>
       </c>
       <c r="H943" t="n">
         <v>7100</v>
@@ -27745,7 +27745,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G944" t="n">
-        <v>8.83182334899902</v>
+        <v>8.83182239532471</v>
       </c>
       <c r="H944" t="n">
         <v>4800</v>
@@ -27774,7 +27774,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G945" t="n">
-        <v>9.0620584487915</v>
+        <v>9.06205749511719</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G946" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H946" t="n">
         <v>1200</v>
@@ -27832,7 +27832,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H947" t="n">
         <v>4900</v>
@@ -28064,7 +28064,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G955" t="n">
-        <v>8.96996307373047</v>
+        <v>8.96996402740479</v>
       </c>
       <c r="H955" t="n">
         <v>4300</v>
@@ -28093,7 +28093,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H956" t="n">
         <v>18400</v>
@@ -28151,7 +28151,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>9.0620584487915</v>
+        <v>9.06205749511719</v>
       </c>
       <c r="H958" t="n">
         <v>1400</v>
@@ -28180,7 +28180,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G959" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H959" t="n">
         <v>1600</v>
@@ -28267,7 +28267,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G962" t="n">
-        <v>8.87787055969238</v>
+        <v>8.87786960601807</v>
       </c>
       <c r="H962" t="n">
         <v>500</v>
@@ -28325,7 +28325,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G964" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H964" t="n">
         <v>7900</v>
@@ -28383,7 +28383,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G966" t="n">
-        <v>8.95154571533203</v>
+        <v>8.95154476165771</v>
       </c>
       <c r="H966" t="n">
         <v>1500</v>
@@ -28412,7 +28412,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G967" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H967" t="n">
         <v>6400</v>
@@ -28499,7 +28499,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>8.78577613830566</v>
+        <v>8.78577518463135</v>
       </c>
       <c r="H970" t="n">
         <v>5800</v>
@@ -28557,7 +28557,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G972" t="n">
-        <v>8.96996307373047</v>
+        <v>8.96996402740479</v>
       </c>
       <c r="H972" t="n">
         <v>2000</v>
@@ -28615,7 +28615,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H974" t="n">
         <v>500</v>
@@ -28644,7 +28644,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H975" t="n">
         <v>1900</v>
@@ -28673,7 +28673,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H976" t="n">
         <v>5400</v>
@@ -28789,7 +28789,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H980" t="n">
         <v>5400</v>
@@ -28818,7 +28818,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H981" t="n">
         <v>200</v>
@@ -28847,7 +28847,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G982" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H982" t="n">
         <v>2200</v>
@@ -28934,7 +28934,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41739845275879</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H985" t="n">
         <v>1600</v>
@@ -28963,7 +28963,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41739845275879</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -29050,7 +29050,7 @@
         <v>9</v>
       </c>
       <c r="G989" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H989" t="n">
         <v>2200</v>
@@ -29079,7 +29079,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G990" t="n">
-        <v>8.23321151733398</v>
+        <v>8.23321056365967</v>
       </c>
       <c r="H990" t="n">
         <v>4000</v>
@@ -29108,7 +29108,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>8.14111804962158</v>
+        <v>8.14111614227295</v>
       </c>
       <c r="H991" t="n">
         <v>1100</v>
@@ -29166,7 +29166,7 @@
         <v>9</v>
       </c>
       <c r="G993" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H993" t="n">
         <v>5000</v>
@@ -29253,7 +29253,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G996" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H996" t="n">
         <v>800</v>
@@ -29311,7 +29311,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G998" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H998" t="n">
         <v>600</v>
@@ -29398,7 +29398,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41739845275879</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1001" t="n">
         <v>900</v>
@@ -29427,7 +29427,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1002" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1002" t="n">
         <v>2700</v>
@@ -29572,7 +29572,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423793792725</v>
+        <v>8.45423603057861</v>
       </c>
       <c r="H1007" t="n">
         <v>100</v>
@@ -29920,7 +29920,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1019" t="n">
-        <v>8.23321151733398</v>
+        <v>8.23321056365967</v>
       </c>
       <c r="H1019" t="n">
         <v>200</v>
@@ -29949,7 +29949,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1020" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1020" t="n">
         <v>1400</v>
@@ -29978,7 +29978,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1021" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -30007,7 +30007,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1022" t="n">
         <v>100</v>
@@ -30036,7 +30036,7 @@
         <v>9</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1023" t="n">
         <v>100</v>
@@ -30094,7 +30094,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1025" t="n">
         <v>200</v>
@@ -30123,7 +30123,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1026" t="n">
         <v>300</v>
@@ -30152,7 +30152,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1027" t="n">
         <v>100</v>
@@ -30181,7 +30181,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -30268,7 +30268,7 @@
         <v>9</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1031" t="n">
         <v>1000</v>
@@ -30297,7 +30297,7 @@
         <v>9</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -30413,7 +30413,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.01218509674072</v>
+        <v>8.01218414306641</v>
       </c>
       <c r="H1036" t="n">
         <v>300</v>
@@ -30442,7 +30442,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.01218509674072</v>
+        <v>8.01218414306641</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -30471,7 +30471,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1038" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1038" t="n">
         <v>1400</v>
@@ -30500,7 +30500,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1039" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1039" t="n">
         <v>0</v>
@@ -30529,7 +30529,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1040" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1040" t="n">
         <v>1900</v>
@@ -30558,7 +30558,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1041" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1041" t="n">
         <v>100</v>
@@ -30587,7 +30587,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.14111804962158</v>
+        <v>8.14111614227295</v>
       </c>
       <c r="H1042" t="n">
         <v>7000</v>
@@ -30616,7 +30616,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1043" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1043" t="n">
         <v>2400</v>
@@ -30645,7 +30645,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1044" t="n">
         <v>3800</v>
@@ -30674,7 +30674,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41739845275879</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1045" t="n">
         <v>2000</v>
@@ -30703,7 +30703,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1046" t="n">
         <v>900</v>
@@ -30732,7 +30732,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1047" t="n">
         <v>500</v>
@@ -30761,7 +30761,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -30790,7 +30790,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1049" t="n">
         <v>1100</v>
@@ -30819,7 +30819,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1050" t="n">
         <v>11300</v>
@@ -30848,7 +30848,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30877,7 +30877,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1052" t="n">
-        <v>8.76735782623291</v>
+        <v>8.76735687255859</v>
       </c>
       <c r="H1052" t="n">
         <v>700</v>
@@ -30935,7 +30935,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G1054" t="n">
-        <v>8.23321151733398</v>
+        <v>8.23321056365967</v>
       </c>
       <c r="H1054" t="n">
         <v>800</v>
@@ -30964,7 +30964,7 @@
         <v>9</v>
       </c>
       <c r="G1055" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1055" t="n">
         <v>3400</v>
@@ -30993,7 +30993,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41739845275879</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1056" t="n">
         <v>300</v>
@@ -31051,7 +31051,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1058" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1058" t="n">
         <v>1000</v>
@@ -31080,7 +31080,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1059" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31515,7 +31515,7 @@
         <v>9</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1074" t="n">
         <v>300</v>
@@ -31834,7 +31834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.85945129394531</v>
+        <v>8.859450340271</v>
       </c>
       <c r="H1085" t="n">
         <v>2600</v>
@@ -31863,7 +31863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1086" t="n">
         <v>200</v>
@@ -31892,7 +31892,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1087" t="n">
         <v>300</v>
@@ -31921,7 +31921,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1088" t="n">
         <v>100</v>
@@ -31950,7 +31950,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1090" t="n">
         <v>200</v>
@@ -32008,7 +32008,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1091" t="n">
         <v>1500</v>
@@ -32037,7 +32037,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1092" t="n">
-        <v>8.76735782623291</v>
+        <v>8.76735687255859</v>
       </c>
       <c r="H1092" t="n">
         <v>300</v>
@@ -32066,7 +32066,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1093" t="n">
-        <v>8.96996307373047</v>
+        <v>8.96996402740479</v>
       </c>
       <c r="H1093" t="n">
         <v>3000</v>
@@ -32095,7 +32095,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G1094" t="n">
-        <v>8.96996307373047</v>
+        <v>8.96996402740479</v>
       </c>
       <c r="H1094" t="n">
         <v>0</v>
@@ -32153,7 +32153,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1096" t="n">
         <v>1900</v>
@@ -32182,7 +32182,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1097" t="n">
         <v>3600</v>
@@ -32211,7 +32211,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1098" t="n">
         <v>1100</v>
@@ -32327,7 +32327,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G1102" t="n">
-        <v>8.54633140563965</v>
+        <v>8.54633045196533</v>
       </c>
       <c r="H1102" t="n">
         <v>14000</v>
@@ -32356,7 +32356,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1103" t="n">
         <v>11700</v>
@@ -32530,7 +32530,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1109" t="n">
         <v>2500</v>
@@ -32559,7 +32559,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1110" t="n">
         <v>22300</v>
@@ -32704,7 +32704,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1115" t="n">
         <v>5200</v>
@@ -32965,7 +32965,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1124" t="n">
         <v>7600</v>
@@ -33226,7 +33226,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1133" t="n">
         <v>700</v>
@@ -33255,7 +33255,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1134" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1134" t="n">
         <v>0</v>
@@ -33342,7 +33342,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1137" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1137" t="n">
         <v>200</v>
@@ -33429,7 +33429,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1140" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1140" t="n">
         <v>1000</v>
@@ -33574,7 +33574,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1145" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1145" t="n">
         <v>2300</v>
@@ -33661,7 +33661,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G1148" t="n">
-        <v>8.87787055969238</v>
+        <v>8.87786960601807</v>
       </c>
       <c r="H1148" t="n">
         <v>100</v>
@@ -33719,7 +33719,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1150" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1150" t="n">
         <v>2300</v>
@@ -33748,7 +33748,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1151" t="n">
         <v>2000</v>
@@ -33777,7 +33777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1152" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1152" t="n">
         <v>0</v>
@@ -33835,7 +33835,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H1154" t="n">
         <v>200</v>
@@ -33864,7 +33864,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1155" t="n">
         <v>100</v>
@@ -34183,7 +34183,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1166" t="n">
         <v>100</v>
@@ -34212,7 +34212,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1167" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1168" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>
@@ -34270,7 +34270,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1169" t="n">
         <v>0</v>
@@ -34299,7 +34299,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1170" t="n">
         <v>100</v>
@@ -34328,7 +34328,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1171" t="n">
         <v>0</v>
@@ -34357,7 +34357,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1172" t="n">
         <v>500</v>
@@ -34647,7 +34647,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1182" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1182" t="n">
         <v>1200</v>
@@ -34879,7 +34879,7 @@
         <v>9</v>
       </c>
       <c r="G1190" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1190" t="n">
         <v>2400</v>
@@ -34908,7 +34908,7 @@
         <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1191" t="n">
         <v>0</v>
@@ -34937,7 +34937,7 @@
         <v>9</v>
       </c>
       <c r="G1192" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1192" t="n">
         <v>800</v>
@@ -34966,7 +34966,7 @@
         <v>9</v>
       </c>
       <c r="G1193" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1193" t="n">
         <v>1600</v>
@@ -34995,7 +34995,7 @@
         <v>9</v>
       </c>
       <c r="G1194" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1194" t="n">
         <v>11800</v>
@@ -35024,7 +35024,7 @@
         <v>9</v>
       </c>
       <c r="G1195" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1195" t="n">
         <v>0</v>
@@ -35198,7 +35198,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.15953540802002</v>
+        <v>8.15953636169434</v>
       </c>
       <c r="H1201" t="n">
         <v>900</v>
@@ -35227,7 +35227,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.15953540802002</v>
+        <v>8.15953636169434</v>
       </c>
       <c r="H1202" t="n">
         <v>300</v>
@@ -35285,7 +35285,7 @@
         <v>9</v>
       </c>
       <c r="G1204" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1204" t="n">
         <v>500</v>
@@ -35314,7 +35314,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1205" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1205" t="n">
         <v>3300</v>
@@ -35343,7 +35343,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1206" t="n">
-        <v>8.10427856445312</v>
+        <v>8.10427951812744</v>
       </c>
       <c r="H1206" t="n">
         <v>800</v>
@@ -35372,7 +35372,7 @@
         <v>8.5</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.82799768447876</v>
+        <v>7.82799673080444</v>
       </c>
       <c r="H1207" t="n">
         <v>10600</v>
@@ -35401,7 +35401,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1208" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1208" t="n">
         <v>1300</v>
@@ -35430,7 +35430,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590278625488</v>
+        <v>7.73590326309204</v>
       </c>
       <c r="H1209" t="n">
         <v>2000</v>
@@ -35459,7 +35459,7 @@
         <v>8.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.82799768447876</v>
+        <v>7.82799673080444</v>
       </c>
       <c r="H1210" t="n">
         <v>3600</v>
@@ -35488,7 +35488,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1211" t="n">
         <v>1400</v>
@@ -35546,7 +35546,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.60697174072266</v>
+        <v>7.6069712638855</v>
       </c>
       <c r="H1213" t="n">
         <v>500</v>
@@ -35662,7 +35662,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1217" t="n">
-        <v>7.25701379776001</v>
+        <v>7.25701427459717</v>
       </c>
       <c r="H1217" t="n">
         <v>4400</v>
@@ -35749,7 +35749,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>7.18333864212036</v>
+        <v>7.1833381652832</v>
       </c>
       <c r="H1220" t="n">
         <v>200</v>
@@ -35836,7 +35836,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.25701379776001</v>
+        <v>7.25701427459717</v>
       </c>
       <c r="H1223" t="n">
         <v>5900</v>
@@ -35894,7 +35894,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.18333864212036</v>
+        <v>7.1833381652832</v>
       </c>
       <c r="H1225" t="n">
         <v>2600</v>
@@ -36039,7 +36039,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>7.60697174072266</v>
+        <v>7.6069712638855</v>
       </c>
       <c r="H1230" t="n">
         <v>9400</v>
@@ -36068,7 +36068,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1231" t="n">
-        <v>7.6806468963623</v>
+        <v>7.68064641952515</v>
       </c>
       <c r="H1231" t="n">
         <v>1300</v>
@@ -36097,7 +36097,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590278625488</v>
+        <v>7.73590326309204</v>
       </c>
       <c r="H1232" t="n">
         <v>200</v>
@@ -36242,7 +36242,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1237" t="n">
         <v>7900</v>
@@ -36271,7 +36271,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1238" t="n">
         <v>600</v>
@@ -36329,7 +36329,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1240" t="n">
         <v>1300</v>
@@ -36416,7 +36416,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1243" t="n">
         <v>1400</v>
@@ -36474,7 +36474,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1245" t="n">
         <v>1600</v>
@@ -36590,7 +36590,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.42175912857056</v>
+        <v>7.4217586517334</v>
       </c>
       <c r="H1249" t="n">
         <v>300</v>
@@ -36648,7 +36648,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.59347057342529</v>
+        <v>7.59347009658813</v>
       </c>
       <c r="H1251" t="n">
         <v>200</v>
@@ -36706,7 +36706,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.19280958175659</v>
+        <v>7.19281005859375</v>
       </c>
       <c r="H1253" t="n">
         <v>1200</v>
@@ -36735,7 +36735,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1254" t="n">
         <v>1200</v>
@@ -36764,7 +36764,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1255" t="n">
         <v>1300</v>
@@ -36793,7 +36793,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1256" t="n">
         <v>900</v>
@@ -36880,7 +36880,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1259" t="n">
         <v>3700</v>
@@ -36996,7 +36996,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.22307968139648</v>
+        <v>8.22307872772217</v>
       </c>
       <c r="H1263" t="n">
         <v>100</v>
@@ -37112,7 +37112,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1267" t="n">
         <v>2800</v>
@@ -37141,7 +37141,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1268" t="n">
         <v>1400</v>
@@ -37199,7 +37199,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.9178147315979</v>
+        <v>7.91781520843506</v>
       </c>
       <c r="H1270" t="n">
         <v>600</v>
@@ -37228,7 +37228,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1271" t="n">
         <v>400</v>
@@ -37518,7 +37518,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1281" t="n">
         <v>2100</v>
@@ -37547,7 +37547,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1282" t="n">
         <v>0</v>
@@ -37634,7 +37634,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1285" t="n">
         <v>300</v>
@@ -37663,7 +37663,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1286" t="n">
         <v>200</v>
@@ -37750,7 +37750,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.76518249511719</v>
+        <v>7.76518201828003</v>
       </c>
       <c r="H1289" t="n">
         <v>700</v>
@@ -37779,7 +37779,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1290" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1290" t="n">
         <v>100</v>
@@ -37837,7 +37837,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1292" t="n">
         <v>2700</v>
@@ -37866,7 +37866,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1293" t="n">
         <v>0</v>
@@ -37895,7 +37895,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1294" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1294" t="n">
         <v>800</v>
@@ -37924,7 +37924,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1295" t="n">
         <v>0</v>
@@ -38069,7 +38069,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1300" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1300" t="n">
         <v>1700</v>
@@ -38098,7 +38098,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1301" t="n">
         <v>1200</v>
@@ -38185,7 +38185,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1304" t="n">
         <v>700</v>
@@ -38272,7 +38272,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1307" t="n">
         <v>1000</v>
@@ -38475,7 +38475,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.25004720687866</v>
+        <v>7.2500467300415</v>
       </c>
       <c r="H1314" t="n">
         <v>200</v>
@@ -38678,7 +38678,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1321" t="n">
         <v>3700</v>
@@ -38881,7 +38881,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1328" t="n">
         <v>2100</v>
@@ -38968,7 +38968,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1331" t="n">
         <v>3300</v>
@@ -39084,7 +39084,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>6.18161916732788</v>
+        <v>6.18161869049072</v>
       </c>
       <c r="H1335" t="n">
         <v>1600</v>
@@ -39229,7 +39229,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>6.25793504714966</v>
+        <v>6.25793552398682</v>
       </c>
       <c r="H1340" t="n">
         <v>5900</v>
@@ -39345,7 +39345,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1344" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1344" t="n">
         <v>1600</v>
@@ -39403,7 +39403,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1346" t="n">
         <v>1100</v>
@@ -39490,7 +39490,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>6.73491191864014</v>
+        <v>6.73491239547729</v>
       </c>
       <c r="H1349" t="n">
         <v>4400</v>
@@ -39577,7 +39577,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1352" t="n">
         <v>400</v>
@@ -39867,7 +39867,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1362" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1362" t="n">
         <v>2600</v>
@@ -40041,7 +40041,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1368" t="n">
         <v>1300</v>
@@ -40099,7 +40099,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1370" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1370" t="n">
         <v>1000</v>
@@ -40128,7 +40128,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1371" t="n">
         <v>10600</v>
@@ -40157,7 +40157,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1372" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1372" t="n">
         <v>0</v>
@@ -40186,7 +40186,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1373" t="n">
         <v>0</v>
@@ -40215,7 +40215,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1374" t="n">
         <v>100</v>
@@ -40447,7 +40447,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1382" t="n">
-        <v>6.44872665405273</v>
+        <v>6.44872617721558</v>
       </c>
       <c r="H1382" t="n">
         <v>1000</v>
@@ -40563,7 +40563,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1386" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1386" t="n">
         <v>700</v>
@@ -40592,7 +40592,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1387" t="n">
         <v>700</v>
@@ -40621,7 +40621,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1388" t="n">
         <v>400</v>
@@ -40795,7 +40795,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1394" t="n">
-        <v>6.23885631561279</v>
+        <v>6.23885583877563</v>
       </c>
       <c r="H1394" t="n">
         <v>1100</v>
@@ -40853,7 +40853,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1396" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1396" t="n">
         <v>5300</v>
@@ -40911,7 +40911,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1398" t="n">
         <v>8500</v>
@@ -40969,7 +40969,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1400" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1400" t="n">
         <v>3800</v>
@@ -41056,7 +41056,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1403" t="n">
-        <v>5.85727500915527</v>
+        <v>5.85727453231812</v>
       </c>
       <c r="H1403" t="n">
         <v>3500</v>
@@ -41201,7 +41201,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1408" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1408" t="n">
         <v>100</v>
@@ -41375,7 +41375,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1414" t="n">
         <v>3900</v>
@@ -41462,7 +41462,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.12438201904297</v>
+        <v>6.12438154220581</v>
       </c>
       <c r="H1417" t="n">
         <v>1600</v>
@@ -41607,7 +41607,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1422" t="n">
-        <v>5.95266962051392</v>
+        <v>5.95267009735107</v>
       </c>
       <c r="H1422" t="n">
         <v>500</v>
@@ -41694,7 +41694,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>5.78095817565918</v>
+        <v>5.78095865249634</v>
       </c>
       <c r="H1425" t="n">
         <v>6300</v>
@@ -41868,7 +41868,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1431" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1431" t="n">
         <v>1000</v>
@@ -42071,7 +42071,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.32306051254272</v>
+        <v>5.32306098937988</v>
       </c>
       <c r="H1438" t="n">
         <v>8200</v>
@@ -42129,7 +42129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.53293085098267</v>
+        <v>5.53293037414551</v>
       </c>
       <c r="H1440" t="n">
         <v>4900</v>
@@ -42187,7 +42187,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1442" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1442" t="n">
         <v>5900</v>
@@ -42332,7 +42332,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1447" t="n">
         <v>400</v>
@@ -42361,7 +42361,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1448" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1448" t="n">
         <v>0</v>
@@ -42419,7 +42419,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1450" t="n">
         <v>7900</v>
@@ -42448,7 +42448,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.43753480911255</v>
+        <v>5.43753528594971</v>
       </c>
       <c r="H1451" t="n">
         <v>9800</v>
@@ -42593,7 +42593,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1456" t="n">
         <v>14200</v>
@@ -60869,6 +60869,35 @@
         <v>3200</v>
       </c>
       <c r="I2086" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2087" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="H2087" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2087" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -601,7 +601,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11247253417969</v>
+        <v>8.11247158050537</v>
       </c>
       <c r="H8" t="n">
         <v>7000</v>
@@ -630,7 +630,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549808502197</v>
       </c>
       <c r="H9" t="n">
         <v>3500</v>
@@ -659,7 +659,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549808502197</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549808502197</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549808502197</v>
       </c>
       <c r="H19" t="n">
         <v>9600</v>
@@ -949,7 +949,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549808502197</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10652923583984</v>
+        <v>8.10653209686279</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1094,7 +1094,7 @@
         <v>9.54199981689453</v>
       </c>
       <c r="G25" t="n">
-        <v>8.09719467163086</v>
+        <v>8.09719562530518</v>
       </c>
       <c r="H25" t="n">
         <v>4800</v>
@@ -1123,7 +1123,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G26" t="n">
-        <v>8.20666217803955</v>
+        <v>8.20666313171387</v>
       </c>
       <c r="H26" t="n">
         <v>200</v>
@@ -1152,7 +1152,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G27" t="n">
-        <v>8.20666217803955</v>
+        <v>8.20666313171387</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G29" t="n">
-        <v>8.08192157745361</v>
+        <v>8.08192253112793</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -1239,7 +1239,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H30" t="n">
         <v>7500</v>
@@ -1268,7 +1268,7 @@
         <v>9.50100040435791</v>
       </c>
       <c r="G31" t="n">
-        <v>8.06240272521973</v>
+        <v>8.06240367889404</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1326,7 +1326,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.0751314163208</v>
+        <v>8.07513236999512</v>
       </c>
       <c r="H33" t="n">
         <v>8000</v>
@@ -1384,7 +1384,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01063919067383</v>
+        <v>8.01064014434814</v>
       </c>
       <c r="H35" t="n">
         <v>7500</v>
@@ -1413,7 +1413,7 @@
         <v>9.44699954986572</v>
       </c>
       <c r="G36" t="n">
-        <v>8.01657962799072</v>
+        <v>8.01657867431641</v>
       </c>
       <c r="H36" t="n">
         <v>2900</v>
@@ -1529,7 +1529,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227121353149</v>
+        <v>7.96227025985718</v>
       </c>
       <c r="H40" t="n">
         <v>300</v>
@@ -1558,7 +1558,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227121353149</v>
+        <v>7.96227025985718</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.97924184799194</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H42" t="n">
         <v>300</v>
@@ -1616,7 +1616,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.97924184799194</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H43" t="n">
         <v>1700</v>
@@ -1645,7 +1645,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G44" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H44" t="n">
         <v>600</v>
@@ -1674,7 +1674,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G45" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H46" t="n">
         <v>8000</v>
@@ -1732,7 +1732,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1761,7 +1761,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G48" t="n">
-        <v>7.90881061553955</v>
+        <v>7.90880870819092</v>
       </c>
       <c r="H48" t="n">
         <v>3700</v>
@@ -1819,7 +1819,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619831085205</v>
+        <v>7.85619878768921</v>
       </c>
       <c r="H50" t="n">
         <v>8700</v>
@@ -1848,7 +1848,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940814971924</v>
       </c>
       <c r="H51" t="n">
         <v>16700</v>
@@ -1877,7 +1877,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G52" t="n">
-        <v>7.75097370147705</v>
+        <v>7.75097465515137</v>
       </c>
       <c r="H52" t="n">
         <v>5200</v>
@@ -1906,7 +1906,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.77473449707031</v>
+        <v>7.774733543396</v>
       </c>
       <c r="H53" t="n">
         <v>2300</v>
@@ -1993,7 +1993,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G56" t="n">
-        <v>7.76709604263306</v>
+        <v>7.76709699630737</v>
       </c>
       <c r="H56" t="n">
         <v>200</v>
@@ -2022,7 +2022,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940814971924</v>
       </c>
       <c r="H57" t="n">
         <v>12300</v>
@@ -2080,7 +2080,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H59" t="n">
         <v>13600</v>
@@ -2138,7 +2138,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940814971924</v>
       </c>
       <c r="H61" t="n">
         <v>4900</v>
@@ -2167,7 +2167,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H62" t="n">
         <v>8400</v>
@@ -2196,7 +2196,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H66" t="n">
         <v>2500</v>
@@ -2312,7 +2312,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>9.20699977874756</v>
       </c>
       <c r="G69" t="n">
-        <v>7.81291961669922</v>
+        <v>7.81291913986206</v>
       </c>
       <c r="H69" t="n">
         <v>200</v>
@@ -2399,7 +2399,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.80528211593628</v>
+        <v>7.8052830696106</v>
       </c>
       <c r="H70" t="n">
         <v>1000</v>
@@ -2457,7 +2457,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746271133423</v>
+        <v>7.78746128082275</v>
       </c>
       <c r="H72" t="n">
         <v>700</v>
@@ -2486,7 +2486,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746271133423</v>
+        <v>7.78746128082275</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>7.85534954071045</v>
+        <v>7.85534858703613</v>
       </c>
       <c r="H74" t="n">
         <v>10200</v>
@@ -2544,7 +2544,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G75" t="n">
-        <v>8.04882621765137</v>
+        <v>8.04882717132568</v>
       </c>
       <c r="H75" t="n">
         <v>100</v>
@@ -2573,7 +2573,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761173248291</v>
+        <v>8.02761077880859</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2602,7 +2602,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177160263062</v>
+        <v>7.84177255630493</v>
       </c>
       <c r="H77" t="n">
         <v>4000</v>
@@ -2660,7 +2660,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>7.84516668319702</v>
+        <v>7.84516525268555</v>
       </c>
       <c r="H79" t="n">
         <v>2400</v>
@@ -2689,7 +2689,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243703842163</v>
+        <v>7.83243656158447</v>
       </c>
       <c r="H80" t="n">
         <v>1600</v>
@@ -2718,7 +2718,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358505249023</v>
+        <v>7.80358600616455</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406810760498</v>
+        <v>7.7840690612793</v>
       </c>
       <c r="H82" t="n">
         <v>200</v>
@@ -2892,7 +2892,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G87" t="n">
-        <v>7.81037473678589</v>
+        <v>7.81037521362305</v>
       </c>
       <c r="H87" t="n">
         <v>2500</v>
@@ -2921,7 +2921,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89099025726318</v>
+        <v>7.89098834991455</v>
       </c>
       <c r="H88" t="n">
         <v>200</v>
@@ -2979,7 +2979,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.76879262924194</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.76879262924194</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H91" t="n">
         <v>700</v>
@@ -3124,7 +3124,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H95" t="n">
         <v>20300</v>
@@ -3153,7 +3153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G97" t="n">
-        <v>7.72212219238281</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H97" t="n">
         <v>7500</v>
@@ -3211,7 +3211,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.72212219238281</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70514965057373</v>
+        <v>7.70514917373657</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969226837158</v>
+        <v>7.67969274520874</v>
       </c>
       <c r="H100" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969226837158</v>
+        <v>7.67969274520874</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726282119751</v>
+        <v>7.63726186752319</v>
       </c>
       <c r="H102" t="n">
         <v>700</v>
@@ -3356,7 +3356,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423536300659</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423536300659</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904243469238</v>
+        <v>7.82904148101807</v>
       </c>
       <c r="H106" t="n">
         <v>300</v>
@@ -3472,7 +3472,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.72212219238281</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H107" t="n">
         <v>1100</v>
@@ -3501,7 +3501,7 @@
         <v>9.10099983215332</v>
       </c>
       <c r="G108" t="n">
-        <v>7.72296905517578</v>
+        <v>7.72296953201294</v>
       </c>
       <c r="H108" t="n">
         <v>2200</v>
@@ -3530,7 +3530,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72212219238281</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H109" t="n">
         <v>2200</v>
@@ -3559,7 +3559,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363496780396</v>
+        <v>7.71363544464111</v>
       </c>
       <c r="H110" t="n">
         <v>10000</v>
@@ -3588,7 +3588,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70514965057373</v>
+        <v>7.70514917373657</v>
       </c>
       <c r="H111" t="n">
         <v>25500</v>
@@ -3617,7 +3617,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70514965057373</v>
+        <v>7.70514917373657</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817758560181</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H113" t="n">
         <v>15900</v>
@@ -3675,7 +3675,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969226837158</v>
+        <v>7.67969274520874</v>
       </c>
       <c r="H114" t="n">
         <v>100</v>
@@ -3704,7 +3704,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902635574341</v>
+        <v>7.68902587890625</v>
       </c>
       <c r="H115" t="n">
         <v>1500</v>
@@ -3733,7 +3733,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110473632812</v>
+        <v>7.85110664367676</v>
       </c>
       <c r="H116" t="n">
         <v>800</v>
@@ -3762,7 +3762,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273675918579</v>
+        <v>7.80273580551147</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -3791,7 +3791,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308734893799</v>
+        <v>7.68308639526367</v>
       </c>
       <c r="H118" t="n">
         <v>2400</v>
@@ -3820,7 +3820,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G119" t="n">
-        <v>7.69666385650635</v>
+        <v>7.69666194915771</v>
       </c>
       <c r="H119" t="n">
         <v>2900</v>
@@ -3849,7 +3849,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G120" t="n">
-        <v>7.72212219238281</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H120" t="n">
         <v>2000</v>
@@ -3878,7 +3878,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G121" t="n">
-        <v>7.72212219238281</v>
+        <v>7.72212076187134</v>
       </c>
       <c r="H121" t="n">
         <v>5000</v>
@@ -3907,7 +3907,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817758560181</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H122" t="n">
         <v>3300</v>
@@ -3936,7 +3936,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.76879262924194</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H123" t="n">
         <v>100</v>
@@ -4023,7 +4023,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152179718018</v>
+        <v>7.78152275085449</v>
       </c>
       <c r="H126" t="n">
         <v>24300</v>
@@ -4052,7 +4052,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406810760498</v>
+        <v>7.7840690612793</v>
       </c>
       <c r="H127" t="n">
         <v>2000</v>
@@ -4081,7 +4081,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76455068588257</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H128" t="n">
         <v>100</v>
@@ -4110,7 +4110,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303552627563</v>
+        <v>7.77303647994995</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303552627563</v>
+        <v>7.77303647994995</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243703842163</v>
+        <v>7.83243656158447</v>
       </c>
       <c r="H131" t="n">
         <v>5900</v>
@@ -4197,7 +4197,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.79849481582642</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H132" t="n">
         <v>300</v>
@@ -4226,7 +4226,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940814971924</v>
       </c>
       <c r="H133" t="n">
         <v>13900</v>
@@ -4313,7 +4313,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445085525513</v>
+        <v>7.94445037841797</v>
       </c>
       <c r="H136" t="n">
         <v>2500</v>
@@ -4342,7 +4342,7 @@
         <v>9.5</v>
       </c>
       <c r="G137" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H137" t="n">
         <v>100</v>
@@ -4371,7 +4371,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.79849481582642</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H138" t="n">
         <v>800</v>
@@ -4458,7 +4458,7 @@
         <v>9.5</v>
       </c>
       <c r="G141" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H141" t="n">
         <v>300</v>
@@ -4661,7 +4661,7 @@
         <v>9.32100009918213</v>
       </c>
       <c r="G148" t="n">
-        <v>7.90965795516968</v>
+        <v>7.90965938568115</v>
       </c>
       <c r="H148" t="n">
         <v>700</v>
@@ -4690,7 +4690,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579780578613</v>
+        <v>8.06579875946045</v>
       </c>
       <c r="H149" t="n">
         <v>300</v>
@@ -4835,7 +4835,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.92832803726196</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H154" t="n">
         <v>1100</v>
@@ -4893,7 +4893,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G156" t="n">
-        <v>8.06664657592773</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H156" t="n">
         <v>100</v>
@@ -4922,7 +4922,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G157" t="n">
-        <v>8.06664657592773</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G158" t="n">
-        <v>8.06664657592773</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>9.34700012207031</v>
       </c>
       <c r="G159" t="n">
-        <v>7.93172121047974</v>
+        <v>7.93172168731689</v>
       </c>
       <c r="H159" t="n">
         <v>800</v>
@@ -5009,7 +5009,7 @@
         <v>9.44299983978271</v>
       </c>
       <c r="G160" t="n">
-        <v>8.01318645477295</v>
+        <v>8.01318550109863</v>
       </c>
       <c r="H160" t="n">
         <v>100</v>
@@ -5154,7 +5154,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>8.05306911468506</v>
+        <v>8.05307006835938</v>
       </c>
       <c r="H165" t="n">
         <v>300</v>
@@ -5183,7 +5183,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.92832803726196</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H166" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G167" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H167" t="n">
         <v>3300</v>
@@ -5241,7 +5241,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H168" t="n">
         <v>9400</v>
@@ -5270,7 +5270,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H169" t="n">
         <v>6900</v>
@@ -5299,7 +5299,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940814971924</v>
       </c>
       <c r="H170" t="n">
         <v>200</v>
@@ -5328,7 +5328,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940814971924</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H172" t="n">
         <v>3700</v>
@@ -5386,7 +5386,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940814971924</v>
       </c>
       <c r="H173" t="n">
         <v>200</v>
@@ -5415,7 +5415,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940814971924</v>
       </c>
       <c r="H174" t="n">
         <v>600</v>
@@ -5444,7 +5444,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H175" t="n">
         <v>300</v>
@@ -5473,7 +5473,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H176" t="n">
         <v>4900</v>
@@ -5502,7 +5502,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G177" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H177" t="n">
         <v>1900</v>
@@ -5531,7 +5531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H178" t="n">
         <v>300</v>
@@ -5560,7 +5560,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H179" t="n">
         <v>100</v>
@@ -5589,7 +5589,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G180" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H180" t="n">
         <v>3800</v>
@@ -5618,7 +5618,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H181" t="n">
         <v>5000</v>
@@ -5647,7 +5647,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>9.5</v>
       </c>
       <c r="G188" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H188" t="n">
         <v>500</v>
@@ -5879,7 +5879,7 @@
         <v>9.5</v>
       </c>
       <c r="G190" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H190" t="n">
         <v>1000</v>
@@ -5937,7 +5937,7 @@
         <v>9.5</v>
       </c>
       <c r="G192" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H192" t="n">
         <v>4100</v>
@@ -6024,7 +6024,7 @@
         <v>9.5</v>
       </c>
       <c r="G195" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H195" t="n">
         <v>4200</v>
@@ -6053,7 +6053,7 @@
         <v>9.5</v>
       </c>
       <c r="G196" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H196" t="n">
         <v>800</v>
@@ -6314,7 +6314,7 @@
         <v>9.5</v>
       </c>
       <c r="G205" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H205" t="n">
         <v>600</v>
@@ -6372,7 +6372,7 @@
         <v>9.5</v>
       </c>
       <c r="G207" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H207" t="n">
         <v>700</v>
@@ -6401,7 +6401,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6488,7 +6488,7 @@
         <v>9.5</v>
       </c>
       <c r="G211" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H211" t="n">
         <v>400</v>
@@ -6517,7 +6517,7 @@
         <v>9.5</v>
       </c>
       <c r="G212" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H212" t="n">
         <v>300</v>
@@ -7010,7 +7010,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H229" t="n">
         <v>100</v>
@@ -7039,7 +7039,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7068,7 +7068,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7097,7 +7097,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H232" t="n">
         <v>5200</v>
@@ -7184,7 +7184,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H235" t="n">
         <v>300</v>
@@ -7213,7 +7213,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H236" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H237" t="n">
         <v>100</v>
@@ -7271,7 +7271,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H238" t="n">
         <v>3200</v>
@@ -7300,7 +7300,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H239" t="n">
         <v>100</v>
@@ -7880,7 +7880,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H259" t="n">
         <v>25000</v>
@@ -7909,7 +7909,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8054,7 +8054,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G265" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H265" t="n">
         <v>100</v>
@@ -8083,7 +8083,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G266" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8112,7 +8112,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G267" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8199,7 +8199,7 @@
         <v>9.5</v>
       </c>
       <c r="G270" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H270" t="n">
         <v>600</v>
@@ -8344,7 +8344,7 @@
         <v>9.5</v>
       </c>
       <c r="G275" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H275" t="n">
         <v>400</v>
@@ -8402,7 +8402,7 @@
         <v>9.5</v>
       </c>
       <c r="G277" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H277" t="n">
         <v>7300</v>
@@ -8431,7 +8431,7 @@
         <v>9.5</v>
       </c>
       <c r="G278" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H278" t="n">
         <v>2000</v>
@@ -8460,7 +8460,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H279" t="n">
         <v>28000</v>
@@ -8518,7 +8518,7 @@
         <v>9.5</v>
       </c>
       <c r="G281" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H281" t="n">
         <v>2100</v>
@@ -8547,7 +8547,7 @@
         <v>9.5</v>
       </c>
       <c r="G282" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H282" t="n">
         <v>400</v>
@@ -8576,7 +8576,7 @@
         <v>9.5</v>
       </c>
       <c r="G283" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H283" t="n">
         <v>100</v>
@@ -8605,7 +8605,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H284" t="n">
         <v>6900</v>
@@ -8634,7 +8634,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H285" t="n">
         <v>200</v>
@@ -8779,7 +8779,7 @@
         <v>9.5</v>
       </c>
       <c r="G290" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H290" t="n">
         <v>5800</v>
@@ -8808,7 +8808,7 @@
         <v>9.5</v>
       </c>
       <c r="G291" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H291" t="n">
         <v>700</v>
@@ -8837,7 +8837,7 @@
         <v>9.5</v>
       </c>
       <c r="G292" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G293" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H293" t="n">
         <v>100</v>
@@ -8895,7 +8895,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G294" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G295" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>9.5</v>
       </c>
       <c r="G297" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9040,7 +9040,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9069,7 +9069,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H300" t="n">
         <v>100</v>
@@ -9098,7 +9098,7 @@
         <v>9.5</v>
       </c>
       <c r="G301" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H301" t="n">
         <v>19200</v>
@@ -9127,7 +9127,7 @@
         <v>9.5</v>
       </c>
       <c r="G302" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H302" t="n">
         <v>2300</v>
@@ -9156,7 +9156,7 @@
         <v>9.5</v>
       </c>
       <c r="G303" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H303" t="n">
         <v>4100</v>
@@ -9185,7 +9185,7 @@
         <v>9.5</v>
       </c>
       <c r="G304" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H304" t="n">
         <v>800</v>
@@ -9214,7 +9214,7 @@
         <v>9.5</v>
       </c>
       <c r="G305" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>9.5</v>
       </c>
       <c r="G308" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H308" t="n">
         <v>300</v>
@@ -9823,7 +9823,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G326" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H326" t="n">
         <v>100</v>
@@ -10055,7 +10055,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H334" t="n">
         <v>100</v>
@@ -10084,7 +10084,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H335" t="n">
         <v>2200</v>
@@ -10113,7 +10113,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G336" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H336" t="n">
         <v>100</v>
@@ -10142,7 +10142,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G337" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H337" t="n">
         <v>100</v>
@@ -10258,7 +10258,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H341" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H344" t="n">
         <v>1700</v>
@@ -10374,7 +10374,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G345" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G346" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H346" t="n">
         <v>3000</v>
@@ -10432,7 +10432,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G347" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G350" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H350" t="n">
         <v>4400</v>
@@ -10548,7 +10548,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H351" t="n">
         <v>1400</v>
@@ -10809,7 +10809,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H360" t="n">
         <v>5000</v>
@@ -10867,7 +10867,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H362" t="n">
         <v>300</v>
@@ -10896,7 +10896,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H363" t="n">
         <v>1100</v>
@@ -10925,7 +10925,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H365" t="n">
         <v>100</v>
@@ -10983,7 +10983,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H367" t="n">
         <v>900</v>
@@ -11041,7 +11041,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H368" t="n">
         <v>300</v>
@@ -11070,7 +11070,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H369" t="n">
         <v>100</v>
@@ -11099,7 +11099,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H371" t="n">
         <v>1700</v>
@@ -11157,7 +11157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H372" t="n">
         <v>1200</v>
@@ -11244,7 +11244,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H375" t="n">
         <v>5700</v>
@@ -11331,7 +11331,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H378" t="n">
         <v>30700</v>
@@ -11360,7 +11360,7 @@
         <v>9.75</v>
       </c>
       <c r="G379" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H379" t="n">
         <v>67200</v>
@@ -11389,7 +11389,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H380" t="n">
         <v>15200</v>
@@ -11476,7 +11476,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H383" t="n">
         <v>800</v>
@@ -11563,7 +11563,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H386" t="n">
         <v>300</v>
@@ -11621,7 +11621,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H388" t="n">
         <v>800</v>
@@ -11650,7 +11650,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H389" t="n">
         <v>4300</v>
@@ -11679,7 +11679,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H390" t="n">
         <v>300</v>
@@ -11795,7 +11795,7 @@
         <v>9.75</v>
       </c>
       <c r="G394" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H394" t="n">
         <v>23100</v>
@@ -11911,7 +11911,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H398" t="n">
         <v>1100</v>
@@ -11998,7 +11998,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H401" t="n">
         <v>7500</v>
@@ -12027,7 +12027,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H402" t="n">
         <v>700</v>
@@ -12056,7 +12056,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H403" t="n">
         <v>2200</v>
@@ -12085,7 +12085,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H404" t="n">
         <v>300</v>
@@ -12114,7 +12114,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H405" t="n">
         <v>100</v>
@@ -12172,7 +12172,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H407" t="n">
         <v>11800</v>
@@ -12201,7 +12201,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G409" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H409" t="n">
         <v>2800</v>
@@ -12259,7 +12259,7 @@
         <v>9.25</v>
       </c>
       <c r="G410" t="n">
-        <v>7.8494086265564</v>
+        <v>7.84940814971924</v>
       </c>
       <c r="H410" t="n">
         <v>13800</v>
@@ -12288,7 +12288,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12317,7 +12317,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H412" t="n">
         <v>13000</v>
@@ -12346,7 +12346,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H413" t="n">
         <v>1800</v>
@@ -12375,7 +12375,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G415" t="n">
-        <v>7.9766960144043</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H415" t="n">
         <v>200</v>
@@ -12433,7 +12433,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H416" t="n">
         <v>200</v>
@@ -12462,7 +12462,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H418" t="n">
         <v>10000</v>
@@ -12520,7 +12520,7 @@
         <v>9.5</v>
       </c>
       <c r="G419" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H419" t="n">
         <v>16300</v>
@@ -12636,7 +12636,7 @@
         <v>9.5</v>
       </c>
       <c r="G423" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H423" t="n">
         <v>15100</v>
@@ -12752,7 +12752,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G427" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H427" t="n">
         <v>2000</v>
@@ -12897,7 +12897,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H432" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G433" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H433" t="n">
         <v>800</v>
@@ -13129,7 +13129,7 @@
         <v>9.75</v>
       </c>
       <c r="G440" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H440" t="n">
         <v>300</v>
@@ -13216,7 +13216,7 @@
         <v>9.75</v>
       </c>
       <c r="G443" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H443" t="n">
         <v>100</v>
@@ -13245,7 +13245,7 @@
         <v>9.75</v>
       </c>
       <c r="G444" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H444" t="n">
         <v>500</v>
@@ -13274,7 +13274,7 @@
         <v>9.75</v>
       </c>
       <c r="G445" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>9.75</v>
       </c>
       <c r="G446" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13361,7 +13361,7 @@
         <v>9.75</v>
       </c>
       <c r="G448" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H448" t="n">
         <v>400</v>
@@ -13390,7 +13390,7 @@
         <v>9.75</v>
       </c>
       <c r="G449" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H449" t="n">
         <v>700</v>
@@ -13419,7 +13419,7 @@
         <v>9.75</v>
       </c>
       <c r="G450" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>9.75</v>
       </c>
       <c r="G451" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>9.75</v>
       </c>
       <c r="G452" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H452" t="n">
         <v>3100</v>
@@ -13506,7 +13506,7 @@
         <v>9.75</v>
       </c>
       <c r="G453" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H453" t="n">
         <v>100</v>
@@ -13535,7 +13535,7 @@
         <v>9.75</v>
       </c>
       <c r="G454" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H454" t="n">
         <v>100000</v>
@@ -13593,7 +13593,7 @@
         <v>9.75</v>
       </c>
       <c r="G456" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H456" t="n">
         <v>15500</v>
@@ -13622,7 +13622,7 @@
         <v>9.75</v>
       </c>
       <c r="G457" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H457" t="n">
         <v>50000</v>
@@ -13709,7 +13709,7 @@
         <v>9.75</v>
       </c>
       <c r="G460" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H460" t="n">
         <v>24400</v>
@@ -13738,7 +13738,7 @@
         <v>9.75</v>
       </c>
       <c r="G461" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>9.75</v>
       </c>
       <c r="G462" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H462" t="n">
         <v>10100</v>
@@ -13796,7 +13796,7 @@
         <v>9.75</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H463" t="n">
         <v>5900</v>
@@ -13825,7 +13825,7 @@
         <v>9.75</v>
       </c>
       <c r="G464" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H464" t="n">
         <v>18200</v>
@@ -13854,7 +13854,7 @@
         <v>9.75</v>
       </c>
       <c r="G465" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>9.75</v>
       </c>
       <c r="G466" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H466" t="n">
         <v>10100</v>
@@ -13912,7 +13912,7 @@
         <v>9.75</v>
       </c>
       <c r="G467" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H467" t="n">
         <v>8000</v>
@@ -13941,7 +13941,7 @@
         <v>9.75</v>
       </c>
       <c r="G468" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H468" t="n">
         <v>5800</v>
@@ -13999,7 +13999,7 @@
         <v>9.75</v>
       </c>
       <c r="G470" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H470" t="n">
         <v>5600</v>
@@ -14115,7 +14115,7 @@
         <v>9.75</v>
       </c>
       <c r="G474" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H474" t="n">
         <v>68300</v>
@@ -14144,7 +14144,7 @@
         <v>9.75</v>
       </c>
       <c r="G475" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H475" t="n">
         <v>88200</v>
@@ -14173,7 +14173,7 @@
         <v>9.75</v>
       </c>
       <c r="G476" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H476" t="n">
         <v>12000</v>
@@ -14260,7 +14260,7 @@
         <v>9.75</v>
       </c>
       <c r="G479" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H479" t="n">
         <v>36400</v>
@@ -14289,7 +14289,7 @@
         <v>9.75</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H480" t="n">
         <v>5300</v>
@@ -14318,7 +14318,7 @@
         <v>9.75</v>
       </c>
       <c r="G481" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H481" t="n">
         <v>22100</v>
@@ -14376,7 +14376,7 @@
         <v>9.75</v>
       </c>
       <c r="G483" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H483" t="n">
         <v>61200</v>
@@ -14405,7 +14405,7 @@
         <v>9.75</v>
       </c>
       <c r="G484" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H484" t="n">
         <v>17600</v>
@@ -14434,7 +14434,7 @@
         <v>9.75</v>
       </c>
       <c r="G485" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H485" t="n">
         <v>20000</v>
@@ -14463,7 +14463,7 @@
         <v>9.75</v>
       </c>
       <c r="G486" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H486" t="n">
         <v>34700</v>
@@ -14521,7 +14521,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H488" t="n">
         <v>140500</v>
@@ -14550,7 +14550,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H489" t="n">
         <v>134000</v>
@@ -14579,7 +14579,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H490" t="n">
         <v>5800</v>
@@ -14608,7 +14608,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35856151580811</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H491" t="n">
         <v>129300</v>
@@ -15043,7 +15043,7 @@
         <v>9.5</v>
       </c>
       <c r="G506" t="n">
-        <v>8.06155395507812</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H506" t="n">
         <v>100100</v>
@@ -15130,7 +15130,7 @@
         <v>9.75</v>
       </c>
       <c r="G509" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H509" t="n">
         <v>109100</v>
@@ -15333,7 +15333,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G516" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H516" t="n">
         <v>5700</v>
@@ -15362,7 +15362,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G518" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H531" t="n">
         <v>200</v>
@@ -16058,7 +16058,7 @@
         <v>9.75</v>
       </c>
       <c r="G541" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H541" t="n">
         <v>1500</v>
@@ -16087,7 +16087,7 @@
         <v>9.75</v>
       </c>
       <c r="G542" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>8.44341850280762</v>
+        <v>8.4434175491333</v>
       </c>
       <c r="H548" t="n">
         <v>21900</v>
@@ -16377,7 +16377,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>8.18884181976318</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H552" t="n">
         <v>1800</v>
@@ -16406,7 +16406,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H553" t="n">
         <v>1800</v>
@@ -16435,7 +16435,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H554" t="n">
         <v>2900</v>
@@ -16464,7 +16464,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>7.59483242034912</v>
+        <v>7.59483337402344</v>
       </c>
       <c r="H555" t="n">
         <v>5200</v>
@@ -16493,7 +16493,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G556" t="n">
-        <v>7.59483242034912</v>
+        <v>7.59483337402344</v>
       </c>
       <c r="H556" t="n">
         <v>2100</v>
@@ -16522,7 +16522,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782915115356</v>
+        <v>7.29782962799072</v>
       </c>
       <c r="H557" t="n">
         <v>1100</v>
@@ -16551,7 +16551,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G558" t="n">
-        <v>7.12811183929443</v>
+        <v>7.12811136245728</v>
       </c>
       <c r="H558" t="n">
         <v>13900</v>
@@ -16580,7 +16580,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66138982772827</v>
+        <v>6.66139030456543</v>
       </c>
       <c r="H559" t="n">
         <v>9300</v>
@@ -16667,7 +16667,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>6.49167394638062</v>
+        <v>6.4916729927063</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16696,7 +16696,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17054080963135</v>
+        <v>7.17054128646851</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16725,7 +16725,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>6.83110761642456</v>
+        <v>6.8311071395874</v>
       </c>
       <c r="H564" t="n">
         <v>8800</v>
@@ -16899,7 +16899,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>6.68633890151978</v>
+        <v>6.68633937835693</v>
       </c>
       <c r="H570" t="n">
         <v>900</v>
@@ -16928,7 +16928,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G571" t="n">
-        <v>6.94854831695557</v>
+        <v>6.94854879379272</v>
       </c>
       <c r="H571" t="n">
         <v>1400</v>
@@ -16986,7 +16986,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.46783113479614</v>
+        <v>6.4678316116333</v>
       </c>
       <c r="H573" t="n">
         <v>4700</v>
@@ -17218,7 +17218,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G581" t="n">
-        <v>7.34186315536499</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H581" t="n">
         <v>200</v>
@@ -17276,7 +17276,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G583" t="n">
-        <v>7.77887868881226</v>
+        <v>7.7788782119751</v>
       </c>
       <c r="H583" t="n">
         <v>4700</v>
@@ -17334,7 +17334,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>7.77887868881226</v>
+        <v>7.7788782119751</v>
       </c>
       <c r="H585" t="n">
         <v>24200</v>
@@ -17421,7 +17421,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G588" t="n">
-        <v>7.77887868881226</v>
+        <v>7.7788782119751</v>
       </c>
       <c r="H588" t="n">
         <v>1000</v>
@@ -17450,7 +17450,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H589" t="n">
         <v>1000</v>
@@ -17479,7 +17479,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H590" t="n">
         <v>600</v>
@@ -17508,7 +17508,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517608642578</v>
       </c>
       <c r="H591" t="n">
         <v>19400</v>
@@ -17537,7 +17537,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H592" t="n">
         <v>300</v>
@@ -17566,7 +17566,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G596" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H596" t="n">
         <v>400</v>
@@ -17682,7 +17682,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H597" t="n">
         <v>2000</v>
@@ -17711,7 +17711,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H598" t="n">
         <v>3300</v>
@@ -17740,7 +17740,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56036996841431</v>
+        <v>7.56037092208862</v>
       </c>
       <c r="H600" t="n">
         <v>100</v>
@@ -17798,7 +17798,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>7.47296667098999</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H601" t="n">
         <v>6300</v>
@@ -17827,7 +17827,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G602" t="n">
-        <v>7.47296667098999</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H602" t="n">
         <v>12100</v>
@@ -17856,7 +17856,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H603" t="n">
         <v>300</v>
@@ -17885,7 +17885,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517608642578</v>
       </c>
       <c r="H604" t="n">
         <v>700</v>
@@ -17914,7 +17914,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G605" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H605" t="n">
         <v>600</v>
@@ -17972,7 +17972,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H607" t="n">
         <v>300</v>
@@ -18030,7 +18030,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G609" t="n">
-        <v>7.77887868881226</v>
+        <v>7.7788782119751</v>
       </c>
       <c r="H609" t="n">
         <v>2600</v>
@@ -18059,7 +18059,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G610" t="n">
-        <v>7.77887868881226</v>
+        <v>7.7788782119751</v>
       </c>
       <c r="H610" t="n">
         <v>500</v>
@@ -18088,7 +18088,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H611" t="n">
         <v>800</v>
@@ -18117,7 +18117,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H612" t="n">
         <v>100</v>
@@ -18146,7 +18146,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95368480682373</v>
+        <v>7.95368432998657</v>
       </c>
       <c r="H613" t="n">
         <v>100</v>
@@ -18175,7 +18175,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H614" t="n">
         <v>600</v>
@@ -18204,7 +18204,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517608642578</v>
       </c>
       <c r="H615" t="n">
         <v>1200</v>
@@ -18233,7 +18233,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H616" t="n">
         <v>200</v>
@@ -18378,7 +18378,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H621" t="n">
         <v>100</v>
@@ -18407,7 +18407,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H622" t="n">
         <v>100</v>
@@ -18436,7 +18436,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>7.47296667098999</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H623" t="n">
         <v>2000</v>
@@ -18465,7 +18465,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G624" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H624" t="n">
         <v>3600</v>
@@ -18494,7 +18494,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H625" t="n">
         <v>1000</v>
@@ -18523,7 +18523,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G626" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H626" t="n">
         <v>6200</v>
@@ -18581,7 +18581,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>7.47296667098999</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H628" t="n">
         <v>5100</v>
@@ -18610,7 +18610,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G629" t="n">
-        <v>7.47296667098999</v>
+        <v>7.47296762466431</v>
       </c>
       <c r="H629" t="n">
         <v>1400</v>
@@ -18639,7 +18639,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34186315536499</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H630" t="n">
         <v>5900</v>
@@ -18668,7 +18668,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G631" t="n">
-        <v>7.34186315536499</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H631" t="n">
         <v>1200</v>
@@ -18697,7 +18697,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G632" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H632" t="n">
         <v>900</v>
@@ -18726,7 +18726,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34186315536499</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H633" t="n">
         <v>4200</v>
@@ -18755,7 +18755,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G634" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H634" t="n">
         <v>300</v>
@@ -18813,7 +18813,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G636" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H636" t="n">
         <v>2000</v>
@@ -19103,7 +19103,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G646" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H646" t="n">
         <v>2300</v>
@@ -19132,7 +19132,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G647" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H647" t="n">
         <v>5600</v>
@@ -19161,7 +19161,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G648" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H648" t="n">
         <v>2500</v>
@@ -19190,7 +19190,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G649" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H649" t="n">
         <v>1700</v>
@@ -19219,7 +19219,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G650" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H650" t="n">
         <v>800</v>
@@ -19248,7 +19248,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G651" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H651" t="n">
         <v>400</v>
@@ -19277,7 +19277,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484666824341</v>
+        <v>6.90484714508057</v>
       </c>
       <c r="H652" t="n">
         <v>2400</v>
@@ -19364,7 +19364,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G655" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H655" t="n">
         <v>1800</v>
@@ -19567,7 +19567,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H662" t="n">
         <v>7300</v>
@@ -19596,7 +19596,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G663" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H663" t="n">
         <v>11900</v>
@@ -19654,7 +19654,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H665" t="n">
         <v>18900</v>
@@ -19741,7 +19741,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G668" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H669" t="n">
         <v>6200</v>
@@ -19799,7 +19799,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H670" t="n">
         <v>2100</v>
@@ -19828,7 +19828,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G671" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H671" t="n">
         <v>1900</v>
@@ -19915,7 +19915,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H674" t="n">
         <v>2900</v>
@@ -19944,7 +19944,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H675" t="n">
         <v>1300</v>
@@ -19973,7 +19973,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H676" t="n">
         <v>2300</v>
@@ -20002,7 +20002,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H677" t="n">
         <v>1800</v>
@@ -20031,7 +20031,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>7.8225793838501</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H678" t="n">
         <v>1500</v>
@@ -20060,7 +20060,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G679" t="n">
-        <v>7.77887868881226</v>
+        <v>7.7788782119751</v>
       </c>
       <c r="H679" t="n">
         <v>700</v>
@@ -20089,7 +20089,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G680" t="n">
-        <v>7.77887868881226</v>
+        <v>7.7788782119751</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20147,7 +20147,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H682" t="n">
         <v>1900</v>
@@ -20176,7 +20176,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G683" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H683" t="n">
         <v>2100</v>
@@ -20205,7 +20205,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738645553589</v>
+        <v>7.99738597869873</v>
       </c>
       <c r="H684" t="n">
         <v>3100</v>
@@ -20234,7 +20234,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>7.77887868881226</v>
+        <v>7.7788782119751</v>
       </c>
       <c r="H685" t="n">
         <v>600</v>
@@ -20263,7 +20263,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G686" t="n">
-        <v>7.77887868881226</v>
+        <v>7.7788782119751</v>
       </c>
       <c r="H686" t="n">
         <v>500</v>
@@ -20292,7 +20292,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H687" t="n">
         <v>1500</v>
@@ -20350,7 +20350,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G689" t="n">
-        <v>7.51666879653931</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H689" t="n">
         <v>12600</v>
@@ -20437,7 +20437,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H692" t="n">
         <v>12900</v>
@@ -20466,7 +20466,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H693" t="n">
         <v>9100</v>
@@ -20524,7 +20524,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738645553589</v>
+        <v>7.99738597869873</v>
       </c>
       <c r="H695" t="n">
         <v>5300</v>
@@ -20640,7 +20640,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H699" t="n">
         <v>6500</v>
@@ -20669,7 +20669,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H700" t="n">
         <v>4100</v>
@@ -20698,7 +20698,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H701" t="n">
         <v>3600</v>
@@ -20727,7 +20727,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H702" t="n">
         <v>1900</v>
@@ -20756,7 +20756,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227088928223</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H703" t="n">
         <v>1400</v>
@@ -20785,7 +20785,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H704" t="n">
         <v>300</v>
@@ -20814,7 +20814,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G705" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H705" t="n">
         <v>900</v>
@@ -20843,7 +20843,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H706" t="n">
         <v>300</v>
@@ -20872,7 +20872,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G707" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H707" t="n">
         <v>5300</v>
@@ -20930,7 +20930,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G709" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H709" t="n">
         <v>5000</v>
@@ -20959,7 +20959,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H710" t="n">
         <v>1600</v>
@@ -20988,7 +20988,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G711" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H711" t="n">
         <v>900</v>
@@ -21162,7 +21162,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G717" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H717" t="n">
         <v>5900</v>
@@ -21191,7 +21191,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227088928223</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H718" t="n">
         <v>2600</v>
@@ -21220,7 +21220,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227088928223</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H719" t="n">
         <v>900</v>
@@ -21249,7 +21249,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H720" t="n">
         <v>1200</v>
@@ -21278,7 +21278,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H721" t="n">
         <v>6800</v>
@@ -21307,7 +21307,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H722" t="n">
         <v>55000</v>
@@ -21336,7 +21336,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227088928223</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H723" t="n">
         <v>26400</v>
@@ -21365,7 +21365,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227088928223</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H724" t="n">
         <v>21400</v>
@@ -21394,7 +21394,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227088928223</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H725" t="n">
         <v>70900</v>
@@ -21423,7 +21423,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H726" t="n">
         <v>38600</v>
@@ -21452,7 +21452,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H727" t="n">
         <v>100</v>
@@ -21481,7 +21481,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H728" t="n">
         <v>4500</v>
@@ -21510,7 +21510,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H729" t="n">
         <v>5100</v>
@@ -21539,7 +21539,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H730" t="n">
         <v>1200</v>
@@ -21568,7 +21568,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227088928223</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H731" t="n">
         <v>300</v>
@@ -21597,7 +21597,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H732" t="n">
         <v>2600</v>
@@ -21626,7 +21626,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G733" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H733" t="n">
         <v>6400</v>
@@ -21655,7 +21655,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H734" t="n">
         <v>12300</v>
@@ -21684,7 +21684,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H735" t="n">
         <v>6900</v>
@@ -21713,7 +21713,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H736" t="n">
         <v>3000</v>
@@ -21742,7 +21742,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G737" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G738" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H738" t="n">
         <v>100</v>
@@ -21800,7 +21800,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98813199996948</v>
+        <v>7.98813104629517</v>
       </c>
       <c r="H739" t="n">
         <v>18700</v>
@@ -21887,7 +21887,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H742" t="n">
         <v>7300</v>
@@ -21916,7 +21916,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G743" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H743" t="n">
         <v>300</v>
@@ -21945,7 +21945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G744" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H744" t="n">
         <v>7400</v>
@@ -21974,7 +21974,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G745" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H745" t="n">
         <v>400</v>
@@ -22003,7 +22003,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H746" t="n">
         <v>6800</v>
@@ -22032,7 +22032,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G747" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H747" t="n">
         <v>100</v>
@@ -22061,7 +22061,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H748" t="n">
         <v>700</v>
@@ -22119,7 +22119,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H750" t="n">
         <v>5400</v>
@@ -22148,7 +22148,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G751" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H751" t="n">
         <v>2100</v>
@@ -22177,7 +22177,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H752" t="n">
         <v>7900</v>
@@ -22206,7 +22206,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H753" t="n">
         <v>33700</v>
@@ -22235,7 +22235,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G754" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H754" t="n">
         <v>34600</v>
@@ -22264,7 +22264,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H755" t="n">
         <v>33100</v>
@@ -22322,7 +22322,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G757" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H757" t="n">
         <v>5400</v>
@@ -22351,7 +22351,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G758" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H758" t="n">
         <v>4100</v>
@@ -22525,7 +22525,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G764" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H764" t="n">
         <v>2200</v>
@@ -22757,7 +22757,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G772" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H772" t="n">
         <v>2900</v>
@@ -22873,7 +22873,7 @@
         <v>10.5</v>
       </c>
       <c r="G776" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H776" t="n">
         <v>25300</v>
@@ -22902,7 +22902,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>9.51395606994629</v>
+        <v>9.51395511627197</v>
       </c>
       <c r="H777" t="n">
         <v>16100</v>
@@ -22989,7 +22989,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>9.60371017456055</v>
+        <v>9.60370922088623</v>
       </c>
       <c r="H780" t="n">
         <v>22300</v>
@@ -23047,7 +23047,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>9.51395606994629</v>
+        <v>9.51395511627197</v>
       </c>
       <c r="H782" t="n">
         <v>15800</v>
@@ -23076,7 +23076,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>9.51395606994629</v>
+        <v>9.51395511627197</v>
       </c>
       <c r="H783" t="n">
         <v>10600</v>
@@ -23105,7 +23105,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>9.69346332550049</v>
+        <v>9.6934642791748</v>
       </c>
       <c r="H784" t="n">
         <v>22700</v>
@@ -23134,7 +23134,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G785" t="n">
-        <v>9.69346332550049</v>
+        <v>9.6934642791748</v>
       </c>
       <c r="H785" t="n">
         <v>6500</v>
@@ -23192,7 +23192,7 @@
         <v>10.5</v>
       </c>
       <c r="G787" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H787" t="n">
         <v>6800</v>
@@ -23221,7 +23221,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H788" t="n">
         <v>26400</v>
@@ -23250,7 +23250,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H789" t="n">
         <v>5100</v>
@@ -23424,7 +23424,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G795" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H795" t="n">
         <v>500</v>
@@ -23627,7 +23627,7 @@
         <v>9.75</v>
       </c>
       <c r="G802" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H802" t="n">
         <v>4400</v>
@@ -23743,7 +23743,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H806" t="n">
         <v>4300</v>
@@ -23772,7 +23772,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H807" t="n">
         <v>9500</v>
@@ -23801,7 +23801,7 @@
         <v>9.75</v>
       </c>
       <c r="G808" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H808" t="n">
         <v>2400</v>
@@ -23946,7 +23946,7 @@
         <v>9.75</v>
       </c>
       <c r="G813" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H813" t="n">
         <v>900</v>
@@ -24062,7 +24062,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G817" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H817" t="n">
         <v>8500</v>
@@ -24091,7 +24091,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G818" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H818" t="n">
         <v>2200</v>
@@ -24120,7 +24120,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H819" t="n">
         <v>1100</v>
@@ -24149,7 +24149,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G820" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H820" t="n">
         <v>4900</v>
@@ -24236,7 +24236,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H823" t="n">
         <v>2700</v>
@@ -24381,7 +24381,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H828" t="n">
         <v>9700</v>
@@ -24468,7 +24468,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H831" t="n">
         <v>4200</v>
@@ -24526,7 +24526,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H833" t="n">
         <v>1100</v>
@@ -24584,7 +24584,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H835" t="n">
         <v>1600</v>
@@ -24613,7 +24613,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G836" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H836" t="n">
         <v>2600</v>
@@ -24700,7 +24700,7 @@
         <v>9.75</v>
       </c>
       <c r="G839" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H839" t="n">
         <v>4200</v>
@@ -24758,7 +24758,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G841" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H841" t="n">
         <v>3500</v>
@@ -24787,7 +24787,7 @@
         <v>9.75</v>
       </c>
       <c r="G842" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H842" t="n">
         <v>700</v>
@@ -24816,7 +24816,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G843" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H843" t="n">
         <v>6000</v>
@@ -24845,7 +24845,7 @@
         <v>9.75</v>
       </c>
       <c r="G844" t="n">
-        <v>8.75104427337646</v>
+        <v>8.75104331970215</v>
       </c>
       <c r="H844" t="n">
         <v>700</v>
@@ -24874,7 +24874,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H845" t="n">
         <v>3000</v>
@@ -24932,7 +24932,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H847" t="n">
         <v>1100</v>
@@ -25048,7 +25048,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G851" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H851" t="n">
         <v>2400</v>
@@ -25077,7 +25077,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G852" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H852" t="n">
         <v>2600</v>
@@ -25135,7 +25135,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G854" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H854" t="n">
         <v>1100</v>
@@ -25193,7 +25193,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H856" t="n">
         <v>4000</v>
@@ -25280,7 +25280,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G859" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H859" t="n">
         <v>3300</v>
@@ -25425,7 +25425,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H864" t="n">
         <v>2300</v>
@@ -25541,7 +25541,7 @@
         <v>10.5</v>
       </c>
       <c r="G868" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H868" t="n">
         <v>2200</v>
@@ -25570,7 +25570,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H869" t="n">
         <v>13500</v>
@@ -25628,7 +25628,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H871" t="n">
         <v>1200</v>
@@ -25715,7 +25715,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G874" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H874" t="n">
         <v>4300</v>
@@ -25802,7 +25802,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G877" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H877" t="n">
         <v>1200</v>
@@ -25860,7 +25860,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H879" t="n">
         <v>26500</v>
@@ -25889,7 +25889,7 @@
         <v>10.5</v>
       </c>
       <c r="G880" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H880" t="n">
         <v>18700</v>
@@ -25918,7 +25918,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H881" t="n">
         <v>21200</v>
@@ -25947,7 +25947,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H882" t="n">
         <v>4500</v>
@@ -25976,7 +25976,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H883" t="n">
         <v>6700</v>
@@ -26005,7 +26005,7 @@
         <v>10.5</v>
       </c>
       <c r="G884" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H884" t="n">
         <v>11400</v>
@@ -26034,7 +26034,7 @@
         <v>10.5</v>
       </c>
       <c r="G885" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H885" t="n">
         <v>22400</v>
@@ -26063,7 +26063,7 @@
         <v>10.5</v>
       </c>
       <c r="G886" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H886" t="n">
         <v>19400</v>
@@ -26092,7 +26092,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H887" t="n">
         <v>10800</v>
@@ -26266,7 +26266,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H893" t="n">
         <v>2100</v>
@@ -26353,7 +26353,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H896" t="n">
         <v>1800</v>
@@ -26382,7 +26382,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H897" t="n">
         <v>900</v>
@@ -26411,7 +26411,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G898" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H898" t="n">
         <v>400</v>
@@ -26440,7 +26440,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H899" t="n">
         <v>500</v>
@@ -26498,7 +26498,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G901" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H901" t="n">
         <v>6700</v>
@@ -26527,7 +26527,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G902" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H902" t="n">
         <v>3900</v>
@@ -26556,7 +26556,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H903" t="n">
         <v>1300</v>
@@ -26585,7 +26585,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G904" t="n">
-        <v>8.2125186920166</v>
+        <v>8.21251773834229</v>
       </c>
       <c r="H904" t="n">
         <v>2900</v>
@@ -26672,7 +26672,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G907" t="n">
-        <v>7.98813199996948</v>
+        <v>7.98813104629517</v>
       </c>
       <c r="H907" t="n">
         <v>1400</v>
@@ -26788,7 +26788,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.35985231399536</v>
+        <v>7.3598518371582</v>
       </c>
       <c r="H911" t="n">
         <v>12900</v>
@@ -26817,7 +26817,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423709869385</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H912" t="n">
         <v>2900</v>
@@ -26846,7 +26846,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423709869385</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H913" t="n">
         <v>5400</v>
@@ -26875,7 +26875,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G914" t="n">
-        <v>7.98813199996948</v>
+        <v>7.98813104629517</v>
       </c>
       <c r="H914" t="n">
         <v>3400</v>
@@ -26904,7 +26904,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862283706665</v>
+        <v>7.80862426757812</v>
       </c>
       <c r="H915" t="n">
         <v>5300</v>
@@ -26933,7 +26933,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H916" t="n">
         <v>2500</v>
@@ -27078,7 +27078,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G921" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H921" t="n">
         <v>100</v>
@@ -27107,7 +27107,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H922" t="n">
         <v>2700</v>
@@ -27136,7 +27136,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G923" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H923" t="n">
         <v>1200</v>
@@ -27223,7 +27223,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G926" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H926" t="n">
         <v>1200</v>
@@ -27252,7 +27252,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G927" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H927" t="n">
         <v>1100</v>
@@ -27281,7 +27281,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G928" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H928" t="n">
         <v>300</v>
@@ -27339,7 +27339,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H930" t="n">
         <v>5000</v>
@@ -27426,7 +27426,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G933" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H933" t="n">
         <v>2200</v>
@@ -27455,7 +27455,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.54460906982422</v>
+        <v>8.54461002349854</v>
       </c>
       <c r="H934" t="n">
         <v>26000</v>
@@ -27513,7 +27513,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821716308594</v>
+        <v>8.68821620941162</v>
       </c>
       <c r="H936" t="n">
         <v>15100</v>
@@ -27542,7 +27542,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G937" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H937" t="n">
         <v>1600</v>
@@ -27571,7 +27571,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G938" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H938" t="n">
         <v>11000</v>
@@ -27658,7 +27658,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G941" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H941" t="n">
         <v>3000</v>
@@ -27716,7 +27716,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G943" t="n">
-        <v>8.84977245330811</v>
+        <v>8.84977340698242</v>
       </c>
       <c r="H943" t="n">
         <v>7100</v>
@@ -27919,7 +27919,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G950" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H950" t="n">
         <v>1300</v>
@@ -27948,7 +27948,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>9.3015022277832</v>
+        <v>9.30150318145752</v>
       </c>
       <c r="H951" t="n">
         <v>5000</v>
@@ -28006,7 +28006,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G953" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H953" t="n">
         <v>2400</v>
@@ -28093,7 +28093,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H956" t="n">
         <v>18400</v>
@@ -28354,7 +28354,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G965" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H965" t="n">
         <v>100</v>
@@ -28499,7 +28499,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>8.78577518463135</v>
+        <v>8.78577613830566</v>
       </c>
       <c r="H970" t="n">
         <v>5800</v>
@@ -28731,7 +28731,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G978" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H978" t="n">
         <v>18000</v>
@@ -28789,7 +28789,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H980" t="n">
         <v>5400</v>
@@ -28934,7 +28934,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H985" t="n">
         <v>1600</v>
@@ -28963,7 +28963,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -29108,7 +29108,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>8.14111614227295</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H991" t="n">
         <v>1100</v>
@@ -29137,7 +29137,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H992" t="n">
         <v>3200</v>
@@ -29253,7 +29253,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G996" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H996" t="n">
         <v>800</v>
@@ -29311,7 +29311,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G998" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H998" t="n">
         <v>600</v>
@@ -29340,7 +29340,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G999" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H999" t="n">
         <v>1100</v>
@@ -29398,7 +29398,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1001" t="n">
         <v>900</v>
@@ -29427,7 +29427,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1002" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1002" t="n">
         <v>2700</v>
@@ -29572,7 +29572,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423603057861</v>
+        <v>8.45423698425293</v>
       </c>
       <c r="H1007" t="n">
         <v>100</v>
@@ -29630,7 +29630,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1009" t="n">
         <v>2700</v>
@@ -29659,7 +29659,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29949,7 +29949,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1020" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1020" t="n">
         <v>1400</v>
@@ -29978,7 +29978,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1021" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -30007,7 +30007,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1022" t="n">
         <v>100</v>
@@ -30065,7 +30065,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1024" t="n">
         <v>1000</v>
@@ -30123,7 +30123,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1026" t="n">
         <v>300</v>
@@ -30239,7 +30239,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1030" t="n">
         <v>300</v>
@@ -30355,7 +30355,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1034" t="n">
         <v>3900</v>
@@ -30384,7 +30384,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.88325452804565</v>
+        <v>7.88325357437134</v>
       </c>
       <c r="H1035" t="n">
         <v>600</v>
@@ -30413,7 +30413,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.01218414306641</v>
+        <v>8.01218509674072</v>
       </c>
       <c r="H1036" t="n">
         <v>300</v>
@@ -30442,7 +30442,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.01218414306641</v>
+        <v>8.01218509674072</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -30587,7 +30587,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.14111614227295</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H1042" t="n">
         <v>7000</v>
@@ -30616,7 +30616,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1043" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1043" t="n">
         <v>2400</v>
@@ -30674,7 +30674,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1045" t="n">
         <v>2000</v>
@@ -30703,7 +30703,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1046" t="n">
         <v>900</v>
@@ -30732,7 +30732,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1047" t="n">
         <v>500</v>
@@ -30761,7 +30761,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1050" t="n">
         <v>11300</v>
@@ -30848,7 +30848,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30993,7 +30993,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1056" t="n">
         <v>300</v>
@@ -31138,7 +31138,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1061" t="n">
         <v>700</v>
@@ -31167,7 +31167,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1062" t="n">
         <v>800</v>
@@ -31312,7 +31312,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1067" t="n">
         <v>3400</v>
@@ -31341,7 +31341,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -31370,7 +31370,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1069" t="n">
         <v>1000</v>
@@ -31399,7 +31399,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1070" t="n">
         <v>2800</v>
@@ -31631,7 +31631,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1078" t="n">
         <v>800</v>
@@ -31834,7 +31834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.859450340271</v>
+        <v>8.85945129394531</v>
       </c>
       <c r="H1085" t="n">
         <v>2600</v>
@@ -31892,7 +31892,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1087" t="n">
         <v>300</v>
@@ -31921,7 +31921,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1088" t="n">
         <v>100</v>
@@ -31950,7 +31950,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1090" t="n">
         <v>200</v>
@@ -32153,7 +32153,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1096" t="n">
         <v>1900</v>
@@ -32385,7 +32385,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1104" t="n">
         <v>2200</v>
@@ -32559,7 +32559,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1110" t="n">
         <v>22300</v>
@@ -32675,7 +32675,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1114" t="n">
         <v>1100</v>
@@ -32704,7 +32704,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1115" t="n">
         <v>5200</v>
@@ -32965,7 +32965,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1124" t="n">
         <v>7600</v>
@@ -32994,7 +32994,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1125" t="n">
         <v>11000</v>
@@ -33226,7 +33226,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1133" t="n">
         <v>700</v>
@@ -33255,7 +33255,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1134" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1134" t="n">
         <v>0</v>
@@ -33284,7 +33284,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1135" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1135" t="n">
         <v>100</v>
@@ -33313,7 +33313,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1136" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1136" t="n">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1139" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1139" t="n">
         <v>3300</v>
@@ -33429,7 +33429,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1140" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1140" t="n">
         <v>1000</v>
@@ -33487,7 +33487,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1142" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1142" t="n">
         <v>300</v>
@@ -33574,7 +33574,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1145" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1145" t="n">
         <v>2300</v>
@@ -33603,7 +33603,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1146" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1146" t="n">
         <v>1600</v>
@@ -33719,7 +33719,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1150" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1150" t="n">
         <v>2300</v>
@@ -33864,7 +33864,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1155" t="n">
         <v>100</v>
@@ -33893,7 +33893,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H1156" t="n">
         <v>200</v>
@@ -33980,7 +33980,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1159" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1159" t="n">
         <v>4200</v>
@@ -34183,7 +34183,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1166" t="n">
         <v>100</v>
@@ -34212,7 +34212,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1167" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1168" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>
@@ -34270,7 +34270,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1169" t="n">
         <v>0</v>
@@ -34299,7 +34299,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1170" t="n">
         <v>100</v>
@@ -34328,7 +34328,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1171" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1174" t="n">
         <v>100</v>
@@ -34705,7 +34705,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1184" t="n">
         <v>900</v>
@@ -34792,7 +34792,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1187" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1187" t="n">
         <v>300</v>
@@ -34821,7 +34821,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1188" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1188" t="n">
         <v>0</v>
@@ -34850,7 +34850,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1189" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1189" t="n">
         <v>100</v>
@@ -35169,7 +35169,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1200" t="n">
         <v>100</v>
@@ -35198,7 +35198,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.15953636169434</v>
+        <v>8.15953540802002</v>
       </c>
       <c r="H1201" t="n">
         <v>900</v>
@@ -35227,7 +35227,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.15953636169434</v>
+        <v>8.15953540802002</v>
       </c>
       <c r="H1202" t="n">
         <v>300</v>
@@ -35256,7 +35256,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1203" t="n">
         <v>700</v>
@@ -35430,7 +35430,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590326309204</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1209" t="n">
         <v>2000</v>
@@ -35546,7 +35546,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.6069712638855</v>
+        <v>7.60697174072266</v>
       </c>
       <c r="H1213" t="n">
         <v>500</v>
@@ -35691,7 +35691,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1218" t="n">
-        <v>7.22017621994019</v>
+        <v>7.22017669677734</v>
       </c>
       <c r="H1218" t="n">
         <v>19000</v>
@@ -35720,7 +35720,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.05440664291382</v>
+        <v>7.05440616607666</v>
       </c>
       <c r="H1219" t="n">
         <v>4300</v>
@@ -35749,7 +35749,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>7.1833381652832</v>
+        <v>7.18333864212036</v>
       </c>
       <c r="H1220" t="n">
         <v>200</v>
@@ -35894,7 +35894,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.1833381652832</v>
+        <v>7.18333864212036</v>
       </c>
       <c r="H1225" t="n">
         <v>2600</v>
@@ -36039,7 +36039,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>7.6069712638855</v>
+        <v>7.60697174072266</v>
       </c>
       <c r="H1230" t="n">
         <v>9400</v>
@@ -36097,7 +36097,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590326309204</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1232" t="n">
         <v>200</v>
@@ -36155,7 +36155,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1234" t="n">
         <v>21900</v>
@@ -60898,6 +60898,35 @@
         <v>100</v>
       </c>
       <c r="I2087" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2088" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="G2088" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="H2088" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I2088" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -485,7 +485,7 @@
         <v>9.70100021362305</v>
       </c>
       <c r="G4" t="n">
-        <v>8.23212051391602</v>
+        <v>8.23212146759033</v>
       </c>
       <c r="H4" t="n">
         <v>4100</v>
@@ -862,7 +862,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10058975219727</v>
+        <v>8.10059070587158</v>
       </c>
       <c r="H17" t="n">
         <v>1300</v>
@@ -891,7 +891,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10058975219727</v>
+        <v>8.10059070587158</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10653209686279</v>
+        <v>8.10653018951416</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.13792896270752</v>
+        <v>8.1379280090332</v>
       </c>
       <c r="H22" t="n">
         <v>300</v>
@@ -1181,7 +1181,7 @@
         <v>9.52799987792969</v>
       </c>
       <c r="G28" t="n">
-        <v>8.08531475067139</v>
+        <v>8.0853157043457</v>
       </c>
       <c r="H28" t="n">
         <v>1500</v>
@@ -1210,7 +1210,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G29" t="n">
-        <v>8.08192253112793</v>
+        <v>8.08192157745361</v>
       </c>
       <c r="H29" t="n">
         <v>100</v>
@@ -1239,7 +1239,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H30" t="n">
         <v>7500</v>
@@ -1297,7 +1297,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10058975219727</v>
+        <v>8.10059070587158</v>
       </c>
       <c r="H32" t="n">
         <v>200</v>
@@ -1326,7 +1326,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.07513236999512</v>
+        <v>8.07513332366943</v>
       </c>
       <c r="H33" t="n">
         <v>8000</v>
@@ -1413,7 +1413,7 @@
         <v>9.44699954986572</v>
       </c>
       <c r="G36" t="n">
-        <v>8.01657867431641</v>
+        <v>8.01657962799072</v>
       </c>
       <c r="H36" t="n">
         <v>2900</v>
@@ -1442,7 +1442,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366760253906</v>
+        <v>7.99366855621338</v>
       </c>
       <c r="H37" t="n">
         <v>12300</v>
@@ -1471,7 +1471,7 @@
         <v>9.37100028991699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.95208835601807</v>
+        <v>7.95208787918091</v>
       </c>
       <c r="H38" t="n">
         <v>500</v>
@@ -1529,7 +1529,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227025985718</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H40" t="n">
         <v>300</v>
@@ -1558,7 +1558,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227025985718</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924137115479</v>
       </c>
       <c r="H42" t="n">
         <v>300</v>
@@ -1616,7 +1616,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924137115479</v>
       </c>
       <c r="H43" t="n">
         <v>1700</v>
@@ -1703,7 +1703,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.93426704406738</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H46" t="n">
         <v>8000</v>
@@ -1732,7 +1732,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1761,7 +1761,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G48" t="n">
-        <v>7.90880870819092</v>
+        <v>7.90880918502808</v>
       </c>
       <c r="H48" t="n">
         <v>3700</v>
@@ -1790,7 +1790,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729545593262</v>
+        <v>7.91729497909546</v>
       </c>
       <c r="H49" t="n">
         <v>9200</v>
@@ -1819,7 +1819,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619878768921</v>
+        <v>7.85619735717773</v>
       </c>
       <c r="H50" t="n">
         <v>8700</v>
@@ -1877,7 +1877,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G52" t="n">
-        <v>7.75097465515137</v>
+        <v>7.75097370147705</v>
       </c>
       <c r="H52" t="n">
         <v>5200</v>
@@ -1993,7 +1993,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G56" t="n">
-        <v>7.76709699630737</v>
+        <v>7.76709747314453</v>
       </c>
       <c r="H56" t="n">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697917938232</v>
       </c>
       <c r="H58" t="n">
         <v>4100</v>
@@ -2109,7 +2109,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697917938232</v>
       </c>
       <c r="H60" t="n">
         <v>24300</v>
@@ -2167,7 +2167,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H62" t="n">
         <v>8400</v>
@@ -2196,7 +2196,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H64" t="n">
         <v>1600</v>
@@ -2254,7 +2254,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697917938232</v>
       </c>
       <c r="H65" t="n">
         <v>7100</v>
@@ -2283,7 +2283,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H66" t="n">
         <v>2500</v>
@@ -2312,7 +2312,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>9.20699977874756</v>
       </c>
       <c r="G69" t="n">
-        <v>7.81291913986206</v>
+        <v>7.81291961669922</v>
       </c>
       <c r="H69" t="n">
         <v>200</v>
@@ -2399,7 +2399,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.8052830696106</v>
+        <v>7.80528259277344</v>
       </c>
       <c r="H70" t="n">
         <v>1000</v>
@@ -2428,7 +2428,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722993850708</v>
+        <v>7.86722898483276</v>
       </c>
       <c r="H71" t="n">
         <v>800</v>
@@ -2457,7 +2457,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746128082275</v>
+        <v>7.78746366500854</v>
       </c>
       <c r="H72" t="n">
         <v>700</v>
@@ -2486,7 +2486,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746128082275</v>
+        <v>7.78746366500854</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>9.25699996948242</v>
       </c>
       <c r="G74" t="n">
-        <v>7.85534858703613</v>
+        <v>7.85534954071045</v>
       </c>
       <c r="H74" t="n">
         <v>10200</v>
@@ -2544,7 +2544,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G75" t="n">
-        <v>8.04882717132568</v>
+        <v>8.04882621765137</v>
       </c>
       <c r="H75" t="n">
         <v>100</v>
@@ -2573,7 +2573,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761077880859</v>
+        <v>8.02761173248291</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2602,7 +2602,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177255630493</v>
+        <v>7.84177207946777</v>
       </c>
       <c r="H77" t="n">
         <v>4000</v>
@@ -2631,7 +2631,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.790855884552</v>
+        <v>7.79085731506348</v>
       </c>
       <c r="H78" t="n">
         <v>800</v>
@@ -2660,7 +2660,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>7.84516525268555</v>
+        <v>7.84516668319702</v>
       </c>
       <c r="H79" t="n">
         <v>2400</v>
@@ -2689,7 +2689,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243751525879</v>
       </c>
       <c r="H80" t="n">
         <v>1600</v>
@@ -2718,7 +2718,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358600616455</v>
+        <v>7.80358648300171</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.7840690612793</v>
+        <v>7.78406810760498</v>
       </c>
       <c r="H82" t="n">
         <v>200</v>
@@ -2776,7 +2776,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H83" t="n">
         <v>1100</v>
@@ -2805,7 +2805,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.80103921890259</v>
+        <v>7.8010401725769</v>
       </c>
       <c r="H86" t="n">
         <v>2900</v>
@@ -2892,7 +2892,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G87" t="n">
-        <v>7.81037521362305</v>
+        <v>7.81037473678589</v>
       </c>
       <c r="H87" t="n">
         <v>2500</v>
@@ -2921,7 +2921,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098834991455</v>
+        <v>7.89098882675171</v>
       </c>
       <c r="H88" t="n">
         <v>200</v>
@@ -2950,7 +2950,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782794952393</v>
+        <v>7.80782890319824</v>
       </c>
       <c r="H89" t="n">
         <v>5100</v>
@@ -2979,7 +2979,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H91" t="n">
         <v>700</v>
@@ -3037,7 +3037,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408466339111</v>
+        <v>7.92408514022827</v>
       </c>
       <c r="H92" t="n">
         <v>1200</v>
@@ -3066,7 +3066,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.77048969268799</v>
+        <v>7.77049016952515</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539993286133</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3269,7 +3269,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969274520874</v>
+        <v>7.67969226837158</v>
       </c>
       <c r="H100" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969274520874</v>
+        <v>7.67969226837158</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726186752319</v>
+        <v>7.63726234436035</v>
       </c>
       <c r="H102" t="n">
         <v>700</v>
@@ -3356,7 +3356,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423536300659</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423536300659</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904148101807</v>
+        <v>7.82904291152954</v>
       </c>
       <c r="H106" t="n">
         <v>300</v>
@@ -3501,7 +3501,7 @@
         <v>9.10099983215332</v>
       </c>
       <c r="G108" t="n">
-        <v>7.72296953201294</v>
+        <v>7.7229700088501</v>
       </c>
       <c r="H108" t="n">
         <v>2200</v>
@@ -3559,7 +3559,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363544464111</v>
+        <v>7.71363496780396</v>
       </c>
       <c r="H110" t="n">
         <v>10000</v>
@@ -3646,7 +3646,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817806243896</v>
       </c>
       <c r="H113" t="n">
         <v>15900</v>
@@ -3675,7 +3675,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969274520874</v>
+        <v>7.67969226837158</v>
       </c>
       <c r="H114" t="n">
         <v>100</v>
@@ -3704,7 +3704,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902587890625</v>
+        <v>7.68902635574341</v>
       </c>
       <c r="H115" t="n">
         <v>1500</v>
@@ -3733,7 +3733,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110664367676</v>
+        <v>7.8511061668396</v>
       </c>
       <c r="H116" t="n">
         <v>800</v>
@@ -3791,7 +3791,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308639526367</v>
+        <v>7.68308591842651</v>
       </c>
       <c r="H118" t="n">
         <v>2400</v>
@@ -3820,7 +3820,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G119" t="n">
-        <v>7.69666194915771</v>
+        <v>7.69666290283203</v>
       </c>
       <c r="H119" t="n">
         <v>2900</v>
@@ -3907,7 +3907,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817806243896</v>
       </c>
       <c r="H122" t="n">
         <v>3300</v>
@@ -3936,7 +3936,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879262924194</v>
       </c>
       <c r="H123" t="n">
         <v>100</v>
@@ -3965,7 +3965,7 @@
         <v>9.14900016784668</v>
       </c>
       <c r="G124" t="n">
-        <v>7.76370286941528</v>
+        <v>7.76370191574097</v>
       </c>
       <c r="H124" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.8655309677124</v>
+        <v>7.86553287506104</v>
       </c>
       <c r="H125" t="n">
         <v>300</v>
@@ -4023,7 +4023,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152275085449</v>
+        <v>7.78152179718018</v>
       </c>
       <c r="H126" t="n">
         <v>24300</v>
@@ -4052,7 +4052,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.7840690612793</v>
+        <v>7.78406810760498</v>
       </c>
       <c r="H127" t="n">
         <v>2000</v>
@@ -4110,7 +4110,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303647994995</v>
+        <v>7.77303600311279</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303647994995</v>
+        <v>7.77303600311279</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243751525879</v>
       </c>
       <c r="H131" t="n">
         <v>5900</v>
@@ -4197,7 +4197,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.7984938621521</v>
+        <v>7.79849338531494</v>
       </c>
       <c r="H132" t="n">
         <v>300</v>
@@ -4255,7 +4255,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000854492188</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000854492188</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445037841797</v>
+        <v>7.94445085525513</v>
       </c>
       <c r="H136" t="n">
         <v>2500</v>
@@ -4371,7 +4371,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.7984938621521</v>
+        <v>7.79849338531494</v>
       </c>
       <c r="H138" t="n">
         <v>800</v>
@@ -4400,7 +4400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.80697965621948</v>
+        <v>7.80697917938232</v>
       </c>
       <c r="H139" t="n">
         <v>1200</v>
@@ -4429,7 +4429,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G140" t="n">
-        <v>7.96311950683594</v>
+        <v>7.96311855316162</v>
       </c>
       <c r="H140" t="n">
         <v>500</v>
@@ -4661,7 +4661,7 @@
         <v>9.32100009918213</v>
       </c>
       <c r="G148" t="n">
-        <v>7.90965938568115</v>
+        <v>7.90965795516968</v>
       </c>
       <c r="H148" t="n">
         <v>700</v>
@@ -4690,7 +4690,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579875946045</v>
+        <v>8.06579780578613</v>
       </c>
       <c r="H149" t="n">
         <v>300</v>
@@ -4719,7 +4719,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153739929199</v>
       </c>
       <c r="H150" t="n">
         <v>100</v>
@@ -4748,7 +4748,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153739929199</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.92832708358765</v>
+        <v>7.9283275604248</v>
       </c>
       <c r="H154" t="n">
         <v>1100</v>
@@ -4893,7 +4893,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G156" t="n">
-        <v>8.06664562225342</v>
+        <v>8.06664657592773</v>
       </c>
       <c r="H156" t="n">
         <v>100</v>
@@ -4922,7 +4922,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G157" t="n">
-        <v>8.06664562225342</v>
+        <v>8.06664657592773</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G158" t="n">
-        <v>8.06664562225342</v>
+        <v>8.06664657592773</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G162" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153739929199</v>
       </c>
       <c r="H162" t="n">
         <v>2300</v>
@@ -5096,7 +5096,7 @@
         <v>9.4040002822876</v>
       </c>
       <c r="G163" t="n">
-        <v>7.98009157180786</v>
+        <v>7.9800910949707</v>
       </c>
       <c r="H163" t="n">
         <v>500</v>
@@ -5183,7 +5183,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.92832708358765</v>
+        <v>7.9283275604248</v>
       </c>
       <c r="H166" t="n">
         <v>1200</v>
@@ -5241,7 +5241,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.93426704406738</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H168" t="n">
         <v>9400</v>
@@ -5270,7 +5270,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.93426704406738</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H169" t="n">
         <v>6900</v>
@@ -5357,7 +5357,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H172" t="n">
         <v>3700</v>
@@ -5444,7 +5444,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.93426704406738</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H175" t="n">
         <v>300</v>
@@ -5473,7 +5473,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H176" t="n">
         <v>4900</v>
@@ -5531,7 +5531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H178" t="n">
         <v>300</v>
@@ -5560,7 +5560,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H179" t="n">
         <v>100</v>
@@ -5618,7 +5618,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.93426704406738</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H181" t="n">
         <v>5000</v>
@@ -5647,7 +5647,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.93426704406738</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H186" t="n">
         <v>700</v>
@@ -5908,7 +5908,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H191" t="n">
         <v>5600</v>
@@ -6082,7 +6082,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6256,7 +6256,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H203" t="n">
         <v>100</v>
@@ -6401,7 +6401,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6633,7 +6633,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H216" t="n">
         <v>100</v>
@@ -6749,7 +6749,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H220" t="n">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H221" t="n">
         <v>17700</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H224" t="n">
         <v>800</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H225" t="n">
         <v>600</v>
@@ -6981,7 +6981,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H228" t="n">
         <v>9100</v>
@@ -7010,7 +7010,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H229" t="n">
         <v>100</v>
@@ -7126,7 +7126,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H233" t="n">
         <v>5100</v>
@@ -7213,7 +7213,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H236" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H237" t="n">
         <v>100</v>
@@ -7271,7 +7271,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H238" t="n">
         <v>3200</v>
@@ -7300,7 +7300,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H239" t="n">
         <v>100</v>
@@ -7329,7 +7329,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H240" t="n">
         <v>100</v>
@@ -7358,7 +7358,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H241" t="n">
         <v>400</v>
@@ -7387,7 +7387,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H242" t="n">
         <v>7200</v>
@@ -7416,7 +7416,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H243" t="n">
         <v>100</v>
@@ -7445,7 +7445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H244" t="n">
         <v>1200</v>
@@ -7590,7 +7590,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H249" t="n">
         <v>600</v>
@@ -7648,7 +7648,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H251" t="n">
         <v>2100</v>
@@ -7880,7 +7880,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H259" t="n">
         <v>25000</v>
@@ -7909,7 +7909,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H263" t="n">
         <v>8000</v>
@@ -8141,7 +8141,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H268" t="n">
         <v>11200</v>
@@ -8170,7 +8170,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H269" t="n">
         <v>600</v>
@@ -8228,7 +8228,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H272" t="n">
         <v>100</v>
@@ -8286,7 +8286,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H273" t="n">
         <v>100</v>
@@ -8460,7 +8460,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H279" t="n">
         <v>28000</v>
@@ -8634,7 +8634,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H285" t="n">
         <v>200</v>
@@ -9011,7 +9011,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H298" t="n">
         <v>10700</v>
@@ -9243,7 +9243,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H311" t="n">
         <v>100</v>
@@ -9417,7 +9417,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H312" t="n">
         <v>100</v>
@@ -9446,7 +9446,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H313" t="n">
         <v>12700</v>
@@ -9475,7 +9475,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H314" t="n">
         <v>7100</v>
@@ -9504,7 +9504,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H318" t="n">
         <v>300</v>
@@ -9794,7 +9794,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H325" t="n">
         <v>20100</v>
@@ -9852,7 +9852,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -9997,7 +9997,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H332" t="n">
         <v>10000</v>
@@ -10026,7 +10026,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H338" t="n">
         <v>400</v>
@@ -10200,7 +10200,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H339" t="n">
         <v>6600</v>
@@ -10229,7 +10229,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H340" t="n">
         <v>400</v>
@@ -10809,7 +10809,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H360" t="n">
         <v>5000</v>
@@ -10867,7 +10867,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H362" t="n">
         <v>300</v>
@@ -10896,7 +10896,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H363" t="n">
         <v>1100</v>
@@ -10925,7 +10925,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H368" t="n">
         <v>300</v>
@@ -11360,7 +11360,7 @@
         <v>9.75</v>
       </c>
       <c r="G379" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H379" t="n">
         <v>67200</v>
@@ -11795,7 +11795,7 @@
         <v>9.75</v>
       </c>
       <c r="G394" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H394" t="n">
         <v>23100</v>
@@ -12143,7 +12143,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H406" t="n">
         <v>11100</v>
@@ -12288,7 +12288,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12317,7 +12317,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.93426704406738</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H412" t="n">
         <v>13000</v>
@@ -12433,7 +12433,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.93426704406738</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H416" t="n">
         <v>200</v>
@@ -12462,7 +12462,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.93426704406738</v>
+        <v>7.93426752090454</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H418" t="n">
         <v>10000</v>
@@ -12723,7 +12723,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H426" t="n">
         <v>300</v>
@@ -12868,7 +12868,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H431" t="n">
         <v>700</v>
@@ -13129,7 +13129,7 @@
         <v>9.75</v>
       </c>
       <c r="G440" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H440" t="n">
         <v>300</v>
@@ -13216,7 +13216,7 @@
         <v>9.75</v>
       </c>
       <c r="G443" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H443" t="n">
         <v>100</v>
@@ -13245,7 +13245,7 @@
         <v>9.75</v>
       </c>
       <c r="G444" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H444" t="n">
         <v>500</v>
@@ -13274,7 +13274,7 @@
         <v>9.75</v>
       </c>
       <c r="G445" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>9.75</v>
       </c>
       <c r="G446" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13361,7 +13361,7 @@
         <v>9.75</v>
       </c>
       <c r="G448" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H448" t="n">
         <v>400</v>
@@ -13390,7 +13390,7 @@
         <v>9.75</v>
       </c>
       <c r="G449" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H449" t="n">
         <v>700</v>
@@ -13419,7 +13419,7 @@
         <v>9.75</v>
       </c>
       <c r="G450" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>9.75</v>
       </c>
       <c r="G451" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>9.75</v>
       </c>
       <c r="G452" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H452" t="n">
         <v>3100</v>
@@ -13506,7 +13506,7 @@
         <v>9.75</v>
       </c>
       <c r="G453" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H453" t="n">
         <v>100</v>
@@ -13535,7 +13535,7 @@
         <v>9.75</v>
       </c>
       <c r="G454" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H454" t="n">
         <v>100000</v>
@@ -13593,7 +13593,7 @@
         <v>9.75</v>
       </c>
       <c r="G456" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H456" t="n">
         <v>15500</v>
@@ -13622,7 +13622,7 @@
         <v>9.75</v>
       </c>
       <c r="G457" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H457" t="n">
         <v>50000</v>
@@ -13709,7 +13709,7 @@
         <v>9.75</v>
       </c>
       <c r="G460" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H460" t="n">
         <v>24400</v>
@@ -13738,7 +13738,7 @@
         <v>9.75</v>
       </c>
       <c r="G461" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>9.75</v>
       </c>
       <c r="G462" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H462" t="n">
         <v>10100</v>
@@ -13796,7 +13796,7 @@
         <v>9.75</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H463" t="n">
         <v>5900</v>
@@ -13825,7 +13825,7 @@
         <v>9.75</v>
       </c>
       <c r="G464" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H464" t="n">
         <v>18200</v>
@@ -13854,7 +13854,7 @@
         <v>9.75</v>
       </c>
       <c r="G465" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>9.75</v>
       </c>
       <c r="G466" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H466" t="n">
         <v>10100</v>
@@ -13912,7 +13912,7 @@
         <v>9.75</v>
       </c>
       <c r="G467" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H467" t="n">
         <v>8000</v>
@@ -13941,7 +13941,7 @@
         <v>9.75</v>
       </c>
       <c r="G468" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H468" t="n">
         <v>5800</v>
@@ -13999,7 +13999,7 @@
         <v>9.75</v>
       </c>
       <c r="G470" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H470" t="n">
         <v>5600</v>
@@ -14115,7 +14115,7 @@
         <v>9.75</v>
       </c>
       <c r="G474" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H474" t="n">
         <v>68300</v>
@@ -14144,7 +14144,7 @@
         <v>9.75</v>
       </c>
       <c r="G475" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H475" t="n">
         <v>88200</v>
@@ -14173,7 +14173,7 @@
         <v>9.75</v>
       </c>
       <c r="G476" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H476" t="n">
         <v>12000</v>
@@ -14260,7 +14260,7 @@
         <v>9.75</v>
       </c>
       <c r="G479" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H479" t="n">
         <v>36400</v>
@@ -14289,7 +14289,7 @@
         <v>9.75</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H480" t="n">
         <v>5300</v>
@@ -14318,7 +14318,7 @@
         <v>9.75</v>
       </c>
       <c r="G481" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H481" t="n">
         <v>22100</v>
@@ -14376,7 +14376,7 @@
         <v>9.75</v>
       </c>
       <c r="G483" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H483" t="n">
         <v>61200</v>
@@ -14405,7 +14405,7 @@
         <v>9.75</v>
       </c>
       <c r="G484" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H484" t="n">
         <v>17600</v>
@@ -14434,7 +14434,7 @@
         <v>9.75</v>
       </c>
       <c r="G485" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H485" t="n">
         <v>20000</v>
@@ -14463,7 +14463,7 @@
         <v>9.75</v>
       </c>
       <c r="G486" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H486" t="n">
         <v>34700</v>
@@ -15014,7 +15014,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.14641284942627</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H505" t="n">
         <v>400</v>
@@ -15130,7 +15130,7 @@
         <v>9.75</v>
       </c>
       <c r="G509" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H509" t="n">
         <v>109100</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H531" t="n">
         <v>200</v>
@@ -16058,7 +16058,7 @@
         <v>9.75</v>
       </c>
       <c r="G541" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H541" t="n">
         <v>1500</v>
@@ -16087,7 +16087,7 @@
         <v>9.75</v>
       </c>
       <c r="G542" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>8.4434175491333</v>
+        <v>8.44341945648193</v>
       </c>
       <c r="H548" t="n">
         <v>21900</v>
@@ -16290,7 +16290,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>8.6555643081665</v>
+        <v>8.65556335449219</v>
       </c>
       <c r="H549" t="n">
         <v>900</v>
@@ -16319,7 +16319,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>8.6555643081665</v>
+        <v>8.65556335449219</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H553" t="n">
         <v>1800</v>
@@ -16435,7 +16435,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183950424194</v>
       </c>
       <c r="H554" t="n">
         <v>2900</v>
@@ -16522,7 +16522,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782962799072</v>
+        <v>7.29783010482788</v>
       </c>
       <c r="H557" t="n">
         <v>1100</v>
@@ -16609,7 +16609,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G560" t="n">
-        <v>6.10980987548828</v>
+        <v>6.10981035232544</v>
       </c>
       <c r="H560" t="n">
         <v>3900</v>
@@ -16638,7 +16638,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>6.10980987548828</v>
+        <v>6.10981035232544</v>
       </c>
       <c r="H561" t="n">
         <v>49300</v>
@@ -16667,7 +16667,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>6.4916729927063</v>
+        <v>6.49167394638062</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16696,7 +16696,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17054128646851</v>
+        <v>7.17054080963135</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16725,7 +16725,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>6.8311071395874</v>
+        <v>6.83110666275024</v>
       </c>
       <c r="H564" t="n">
         <v>8800</v>
@@ -16754,7 +16754,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867769241333</v>
+        <v>6.78867864608765</v>
       </c>
       <c r="H565" t="n">
         <v>3800</v>
@@ -16783,7 +16783,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867769241333</v>
+        <v>6.78867864608765</v>
       </c>
       <c r="H566" t="n">
         <v>3000</v>
@@ -16812,7 +16812,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867769241333</v>
+        <v>6.78867864608765</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>6.68633937835693</v>
+        <v>6.68633890151978</v>
       </c>
       <c r="H570" t="n">
         <v>900</v>
@@ -16986,7 +16986,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.4678316116333</v>
+        <v>6.46783113479614</v>
       </c>
       <c r="H573" t="n">
         <v>4700</v>
@@ -17102,7 +17102,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25445938110352</v>
       </c>
       <c r="H577" t="n">
         <v>1400</v>
@@ -17131,7 +17131,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25445938110352</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G579" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25445938110352</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G581" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H581" t="n">
         <v>200</v>
@@ -17247,7 +17247,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25445938110352</v>
       </c>
       <c r="H582" t="n">
         <v>100</v>
@@ -17276,7 +17276,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G583" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H583" t="n">
         <v>4700</v>
@@ -17305,7 +17305,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>7.69147491455078</v>
+        <v>7.6914758682251</v>
       </c>
       <c r="H584" t="n">
         <v>3700</v>
@@ -17334,7 +17334,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H585" t="n">
         <v>24200</v>
@@ -17363,7 +17363,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69147491455078</v>
+        <v>7.6914758682251</v>
       </c>
       <c r="H586" t="n">
         <v>1100</v>
@@ -17392,7 +17392,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G587" t="n">
-        <v>7.69147491455078</v>
+        <v>7.6914758682251</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G588" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H588" t="n">
         <v>1000</v>
@@ -17450,7 +17450,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H589" t="n">
         <v>1000</v>
@@ -17479,7 +17479,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H590" t="n">
         <v>600</v>
@@ -17508,7 +17508,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.73517608642578</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H591" t="n">
         <v>19400</v>
@@ -17537,7 +17537,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H592" t="n">
         <v>300</v>
@@ -17566,7 +17566,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G596" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H596" t="n">
         <v>400</v>
@@ -17711,7 +17711,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H598" t="n">
         <v>3300</v>
@@ -17740,7 +17740,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56037092208862</v>
+        <v>7.56036996841431</v>
       </c>
       <c r="H600" t="n">
         <v>100</v>
@@ -17885,7 +17885,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.73517608642578</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H604" t="n">
         <v>700</v>
@@ -17914,7 +17914,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G605" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H605" t="n">
         <v>600</v>
@@ -17972,7 +17972,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H607" t="n">
         <v>300</v>
@@ -18030,7 +18030,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G609" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H609" t="n">
         <v>2600</v>
@@ -18059,7 +18059,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G610" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H610" t="n">
         <v>500</v>
@@ -18204,7 +18204,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.73517608642578</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H615" t="n">
         <v>1200</v>
@@ -18291,7 +18291,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>7.69147491455078</v>
+        <v>7.6914758682251</v>
       </c>
       <c r="H618" t="n">
         <v>1600</v>
@@ -18465,7 +18465,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G624" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H624" t="n">
         <v>3600</v>
@@ -18523,7 +18523,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G626" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H626" t="n">
         <v>6200</v>
@@ -18639,7 +18639,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H630" t="n">
         <v>5900</v>
@@ -18668,7 +18668,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G631" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H631" t="n">
         <v>1200</v>
@@ -18697,7 +18697,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G632" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H632" t="n">
         <v>900</v>
@@ -18726,7 +18726,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H633" t="n">
         <v>4200</v>
@@ -18755,7 +18755,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G634" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H634" t="n">
         <v>300</v>
@@ -18813,7 +18813,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G636" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H636" t="n">
         <v>2000</v>
@@ -18842,7 +18842,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25445938110352</v>
       </c>
       <c r="H637" t="n">
         <v>5700</v>
@@ -18871,7 +18871,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25445938110352</v>
       </c>
       <c r="H638" t="n">
         <v>600</v>
@@ -19016,7 +19016,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25445938110352</v>
       </c>
       <c r="H643" t="n">
         <v>11600</v>
@@ -19103,7 +19103,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G646" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H646" t="n">
         <v>2300</v>
@@ -19132,7 +19132,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G647" t="n">
-        <v>7.1233549118042</v>
+        <v>7.12335395812988</v>
       </c>
       <c r="H647" t="n">
         <v>5600</v>
@@ -19161,7 +19161,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G648" t="n">
-        <v>7.1233549118042</v>
+        <v>7.12335395812988</v>
       </c>
       <c r="H648" t="n">
         <v>2500</v>
@@ -19190,7 +19190,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G649" t="n">
-        <v>7.1233549118042</v>
+        <v>7.12335395812988</v>
       </c>
       <c r="H649" t="n">
         <v>1700</v>
@@ -19219,7 +19219,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G650" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H650" t="n">
         <v>800</v>
@@ -19248,7 +19248,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G651" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H651" t="n">
         <v>400</v>
@@ -19277,7 +19277,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484714508057</v>
+        <v>6.90484666824341</v>
       </c>
       <c r="H652" t="n">
         <v>2400</v>
@@ -19364,7 +19364,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G655" t="n">
-        <v>7.07965326309204</v>
+        <v>7.0796537399292</v>
       </c>
       <c r="H655" t="n">
         <v>1800</v>
@@ -19509,7 +19509,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25445938110352</v>
       </c>
       <c r="H660" t="n">
         <v>8800</v>
@@ -19596,7 +19596,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G663" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H663" t="n">
         <v>11900</v>
@@ -19625,7 +19625,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G664" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25445938110352</v>
       </c>
       <c r="H664" t="n">
         <v>3400</v>
@@ -19712,7 +19712,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>7.69147491455078</v>
+        <v>7.6914758682251</v>
       </c>
       <c r="H667" t="n">
         <v>5600</v>
@@ -19828,7 +19828,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G671" t="n">
-        <v>7.90998268127441</v>
+        <v>7.90998315811157</v>
       </c>
       <c r="H671" t="n">
         <v>1900</v>
@@ -19857,7 +19857,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G672" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H672" t="n">
         <v>1900</v>
@@ -19886,7 +19886,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G673" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H673" t="n">
         <v>4100</v>
@@ -20060,7 +20060,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G679" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H679" t="n">
         <v>700</v>
@@ -20089,7 +20089,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G680" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20147,7 +20147,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H682" t="n">
         <v>1900</v>
@@ -20176,7 +20176,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G683" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H683" t="n">
         <v>2100</v>
@@ -20205,7 +20205,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738597869873</v>
+        <v>7.99738502502441</v>
       </c>
       <c r="H684" t="n">
         <v>3100</v>
@@ -20234,7 +20234,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H685" t="n">
         <v>600</v>
@@ -20263,7 +20263,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G686" t="n">
-        <v>7.7788782119751</v>
+        <v>7.77887868881226</v>
       </c>
       <c r="H686" t="n">
         <v>500</v>
@@ -20292,7 +20292,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H687" t="n">
         <v>1500</v>
@@ -20350,7 +20350,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G689" t="n">
-        <v>7.51666927337646</v>
+        <v>7.51666975021362</v>
       </c>
       <c r="H689" t="n">
         <v>12600</v>
@@ -20408,7 +20408,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G691" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H691" t="n">
         <v>6500</v>
@@ -20437,7 +20437,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>7.90998268127441</v>
+        <v>7.90998315811157</v>
       </c>
       <c r="H692" t="n">
         <v>12900</v>
@@ -20466,7 +20466,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>7.90998268127441</v>
+        <v>7.90998315811157</v>
       </c>
       <c r="H693" t="n">
         <v>9100</v>
@@ -20495,7 +20495,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H694" t="n">
         <v>5000</v>
@@ -20524,7 +20524,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738597869873</v>
+        <v>7.99738502502441</v>
       </c>
       <c r="H695" t="n">
         <v>5300</v>
@@ -20611,7 +20611,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G698" t="n">
-        <v>8.04108810424805</v>
+        <v>8.04108715057373</v>
       </c>
       <c r="H698" t="n">
         <v>10400</v>
@@ -20640,7 +20640,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H699" t="n">
         <v>6500</v>
@@ -20669,7 +20669,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H700" t="n">
         <v>4100</v>
@@ -20698,7 +20698,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H701" t="n">
         <v>3600</v>
@@ -20727,7 +20727,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H702" t="n">
         <v>1900</v>
@@ -20785,7 +20785,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H704" t="n">
         <v>300</v>
@@ -20814,7 +20814,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G705" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H705" t="n">
         <v>900</v>
@@ -20843,7 +20843,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H706" t="n">
         <v>300</v>
@@ -20959,7 +20959,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H710" t="n">
         <v>1600</v>
@@ -21017,7 +21017,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G712" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H712" t="n">
         <v>9300</v>
@@ -21046,7 +21046,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G713" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H713" t="n">
         <v>800</v>
@@ -21075,7 +21075,7 @@
         <v>9</v>
       </c>
       <c r="G714" t="n">
-        <v>8.07788753509521</v>
+        <v>8.0778865814209</v>
       </c>
       <c r="H714" t="n">
         <v>2100</v>
@@ -21104,7 +21104,7 @@
         <v>9</v>
       </c>
       <c r="G715" t="n">
-        <v>8.07788753509521</v>
+        <v>8.0778865814209</v>
       </c>
       <c r="H715" t="n">
         <v>1600</v>
@@ -21133,7 +21133,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G716" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H716" t="n">
         <v>1200</v>
@@ -21249,7 +21249,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H720" t="n">
         <v>1200</v>
@@ -21278,7 +21278,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H721" t="n">
         <v>6800</v>
@@ -21307,7 +21307,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H722" t="n">
         <v>55000</v>
@@ -21423,7 +21423,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H726" t="n">
         <v>38600</v>
@@ -21452,7 +21452,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H727" t="n">
         <v>100</v>
@@ -21481,7 +21481,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H728" t="n">
         <v>4500</v>
@@ -21510,7 +21510,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H729" t="n">
         <v>5100</v>
@@ -21539,7 +21539,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H730" t="n">
         <v>1200</v>
@@ -21597,7 +21597,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H732" t="n">
         <v>2600</v>
@@ -21626,7 +21626,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G733" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H733" t="n">
         <v>6400</v>
@@ -21655,7 +21655,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H734" t="n">
         <v>12300</v>
@@ -21684,7 +21684,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H735" t="n">
         <v>6900</v>
@@ -21713,7 +21713,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H736" t="n">
         <v>3000</v>
@@ -21742,7 +21742,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G737" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G738" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H738" t="n">
         <v>100</v>
@@ -21800,7 +21800,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98813104629517</v>
+        <v>7.98813247680664</v>
       </c>
       <c r="H739" t="n">
         <v>18700</v>
@@ -21858,7 +21858,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G741" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H741" t="n">
         <v>12400</v>
@@ -21887,7 +21887,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H742" t="n">
         <v>7300</v>
@@ -21945,7 +21945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G744" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H744" t="n">
         <v>7400</v>
@@ -22003,7 +22003,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H746" t="n">
         <v>6800</v>
@@ -22032,7 +22032,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G747" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H747" t="n">
         <v>100</v>
@@ -22061,7 +22061,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H748" t="n">
         <v>700</v>
@@ -22090,7 +22090,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G749" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H749" t="n">
         <v>2600</v>
@@ -22119,7 +22119,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H750" t="n">
         <v>5400</v>
@@ -22148,7 +22148,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G751" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H751" t="n">
         <v>2100</v>
@@ -22177,7 +22177,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H752" t="n">
         <v>7900</v>
@@ -22206,7 +22206,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H753" t="n">
         <v>33700</v>
@@ -22235,7 +22235,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G754" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H754" t="n">
         <v>34600</v>
@@ -22264,7 +22264,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H755" t="n">
         <v>33100</v>
@@ -22322,7 +22322,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G757" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H757" t="n">
         <v>5400</v>
@@ -22351,7 +22351,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G758" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H758" t="n">
         <v>4100</v>
@@ -22525,7 +22525,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G764" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H764" t="n">
         <v>2200</v>
@@ -22670,7 +22670,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H769" t="n">
         <v>1400</v>
@@ -22699,7 +22699,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H771" t="n">
         <v>300</v>
@@ -22757,7 +22757,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G772" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H772" t="n">
         <v>2900</v>
@@ -22815,7 +22815,7 @@
         <v>10</v>
       </c>
       <c r="G774" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H774" t="n">
         <v>23000</v>
@@ -22844,7 +22844,7 @@
         <v>10</v>
       </c>
       <c r="G775" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H775" t="n">
         <v>13400</v>
@@ -23221,7 +23221,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H788" t="n">
         <v>26400</v>
@@ -23308,7 +23308,7 @@
         <v>10</v>
       </c>
       <c r="G791" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H791" t="n">
         <v>7300</v>
@@ -23366,7 +23366,7 @@
         <v>10</v>
       </c>
       <c r="G793" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H793" t="n">
         <v>7200</v>
@@ -23424,7 +23424,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G795" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H795" t="n">
         <v>500</v>
@@ -23453,7 +23453,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H796" t="n">
         <v>1300</v>
@@ -23540,7 +23540,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H799" t="n">
         <v>2300</v>
@@ -23627,7 +23627,7 @@
         <v>9.75</v>
       </c>
       <c r="G802" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H802" t="n">
         <v>4400</v>
@@ -23743,7 +23743,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H806" t="n">
         <v>4300</v>
@@ -23801,7 +23801,7 @@
         <v>9.75</v>
       </c>
       <c r="G808" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H808" t="n">
         <v>2400</v>
@@ -23946,7 +23946,7 @@
         <v>9.75</v>
       </c>
       <c r="G813" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H813" t="n">
         <v>900</v>
@@ -24062,7 +24062,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G817" t="n">
-        <v>8.43690395355225</v>
+        <v>8.43690299987793</v>
       </c>
       <c r="H817" t="n">
         <v>8500</v>
@@ -24091,7 +24091,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G818" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H818" t="n">
         <v>2200</v>
@@ -24149,7 +24149,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G820" t="n">
-        <v>8.43690395355225</v>
+        <v>8.43690299987793</v>
       </c>
       <c r="H820" t="n">
         <v>4900</v>
@@ -24236,7 +24236,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>8.48178005218506</v>
+        <v>8.48178100585938</v>
       </c>
       <c r="H823" t="n">
         <v>2700</v>
@@ -24352,7 +24352,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H827" t="n">
         <v>49700</v>
@@ -24410,7 +24410,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H829" t="n">
         <v>12300</v>
@@ -24439,7 +24439,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H830" t="n">
         <v>1900</v>
@@ -24468,7 +24468,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H831" t="n">
         <v>4200</v>
@@ -24497,7 +24497,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H832" t="n">
         <v>1700</v>
@@ -24526,7 +24526,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H833" t="n">
         <v>1100</v>
@@ -24555,7 +24555,7 @@
         <v>10</v>
       </c>
       <c r="G834" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H834" t="n">
         <v>5900</v>
@@ -24584,7 +24584,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H835" t="n">
         <v>1600</v>
@@ -24613,7 +24613,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G836" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H836" t="n">
         <v>2600</v>
@@ -24700,7 +24700,7 @@
         <v>9.75</v>
       </c>
       <c r="G839" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H839" t="n">
         <v>4200</v>
@@ -24729,7 +24729,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G840" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H840" t="n">
         <v>500</v>
@@ -24758,7 +24758,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G841" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H841" t="n">
         <v>3500</v>
@@ -24787,7 +24787,7 @@
         <v>9.75</v>
       </c>
       <c r="G842" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H842" t="n">
         <v>700</v>
@@ -24816,7 +24816,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G843" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H843" t="n">
         <v>6000</v>
@@ -24845,7 +24845,7 @@
         <v>9.75</v>
       </c>
       <c r="G844" t="n">
-        <v>8.75104331970215</v>
+        <v>8.75104427337646</v>
       </c>
       <c r="H844" t="n">
         <v>700</v>
@@ -24874,7 +24874,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H845" t="n">
         <v>3000</v>
@@ -24990,7 +24990,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H849" t="n">
         <v>3700</v>
@@ -25019,7 +25019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H850" t="n">
         <v>1700</v>
@@ -25048,7 +25048,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G851" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H851" t="n">
         <v>2400</v>
@@ -25077,7 +25077,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G852" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H852" t="n">
         <v>2600</v>
@@ -25135,7 +25135,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G854" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H854" t="n">
         <v>1100</v>
@@ -25251,7 +25251,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H858" t="n">
         <v>3300</v>
@@ -25280,7 +25280,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G859" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H859" t="n">
         <v>3300</v>
@@ -25425,7 +25425,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H864" t="n">
         <v>2300</v>
@@ -25483,7 +25483,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H866" t="n">
         <v>200</v>
@@ -25628,7 +25628,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H871" t="n">
         <v>1200</v>
@@ -25657,7 +25657,7 @@
         <v>10</v>
       </c>
       <c r="G872" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H872" t="n">
         <v>1500</v>
@@ -25686,7 +25686,7 @@
         <v>10</v>
       </c>
       <c r="G873" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H873" t="n">
         <v>3200</v>
@@ -25715,7 +25715,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G874" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H874" t="n">
         <v>4300</v>
@@ -25744,7 +25744,7 @@
         <v>10</v>
       </c>
       <c r="G875" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H875" t="n">
         <v>7800</v>
@@ -25773,7 +25773,7 @@
         <v>10</v>
       </c>
       <c r="G876" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G877" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H877" t="n">
         <v>1200</v>
@@ -25831,7 +25831,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H878" t="n">
         <v>23100</v>
@@ -25860,7 +25860,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H879" t="n">
         <v>26500</v>
@@ -25947,7 +25947,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H882" t="n">
         <v>4500</v>
@@ -26150,7 +26150,7 @@
         <v>10</v>
       </c>
       <c r="G889" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H889" t="n">
         <v>15100</v>
@@ -26179,7 +26179,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H890" t="n">
         <v>2500</v>
@@ -26208,7 +26208,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H891" t="n">
         <v>5500</v>
@@ -26237,7 +26237,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H892" t="n">
         <v>1200</v>
@@ -26266,7 +26266,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H893" t="n">
         <v>2100</v>
@@ -26295,7 +26295,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H894" t="n">
         <v>500</v>
@@ -26353,7 +26353,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H896" t="n">
         <v>1800</v>
@@ -26382,7 +26382,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H897" t="n">
         <v>900</v>
@@ -26411,7 +26411,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G898" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H898" t="n">
         <v>400</v>
@@ -26440,7 +26440,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H899" t="n">
         <v>500</v>
@@ -26498,7 +26498,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G901" t="n">
-        <v>8.43690395355225</v>
+        <v>8.43690299987793</v>
       </c>
       <c r="H901" t="n">
         <v>6700</v>
@@ -26527,7 +26527,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G902" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H902" t="n">
         <v>3900</v>
@@ -26556,7 +26556,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H903" t="n">
         <v>1300</v>
@@ -26614,7 +26614,7 @@
         <v>9</v>
       </c>
       <c r="G905" t="n">
-        <v>8.07788753509521</v>
+        <v>8.0778865814209</v>
       </c>
       <c r="H905" t="n">
         <v>2300</v>
@@ -26672,7 +26672,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G907" t="n">
-        <v>7.98813104629517</v>
+        <v>7.98813247680664</v>
       </c>
       <c r="H907" t="n">
         <v>1400</v>
@@ -26759,7 +26759,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G910" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H910" t="n">
         <v>1300</v>
@@ -26875,7 +26875,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G914" t="n">
-        <v>7.98813104629517</v>
+        <v>7.98813247680664</v>
       </c>
       <c r="H914" t="n">
         <v>3400</v>
@@ -26904,7 +26904,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862426757812</v>
+        <v>7.80862331390381</v>
       </c>
       <c r="H915" t="n">
         <v>5300</v>
@@ -26933,7 +26933,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H916" t="n">
         <v>2500</v>
@@ -26962,7 +26962,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G917" t="n">
-        <v>8.16764163970947</v>
+        <v>8.16764068603516</v>
       </c>
       <c r="H917" t="n">
         <v>2900</v>
@@ -27078,7 +27078,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G921" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H921" t="n">
         <v>100</v>
@@ -27136,7 +27136,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G923" t="n">
-        <v>8.48178005218506</v>
+        <v>8.48178100585938</v>
       </c>
       <c r="H923" t="n">
         <v>1200</v>
@@ -27165,7 +27165,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G924" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H924" t="n">
         <v>500</v>
@@ -27194,7 +27194,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -27223,7 +27223,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G926" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H926" t="n">
         <v>1200</v>
@@ -27252,7 +27252,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G927" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H927" t="n">
         <v>1100</v>
@@ -27281,7 +27281,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G928" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H928" t="n">
         <v>300</v>
@@ -27339,7 +27339,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88567447662354</v>
+        <v>8.88567543029785</v>
       </c>
       <c r="H930" t="n">
         <v>5000</v>
@@ -27368,7 +27368,7 @@
         <v>10</v>
       </c>
       <c r="G931" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H931" t="n">
         <v>600</v>
@@ -27397,7 +27397,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231418609619</v>
+        <v>8.65231513977051</v>
       </c>
       <c r="H932" t="n">
         <v>500</v>
@@ -27426,7 +27426,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G933" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H933" t="n">
         <v>2200</v>
@@ -27455,7 +27455,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.54461002349854</v>
+        <v>8.54460906982422</v>
       </c>
       <c r="H934" t="n">
         <v>26000</v>
@@ -27484,7 +27484,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27542,7 +27542,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G937" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H937" t="n">
         <v>1600</v>
@@ -27571,7 +27571,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G938" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H938" t="n">
         <v>11000</v>
@@ -27658,7 +27658,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G941" t="n">
-        <v>8.25739479064941</v>
+        <v>8.25739574432373</v>
       </c>
       <c r="H941" t="n">
         <v>3000</v>
@@ -27745,7 +27745,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G944" t="n">
-        <v>8.83182239532471</v>
+        <v>8.83182334899902</v>
       </c>
       <c r="H944" t="n">
         <v>4800</v>
@@ -27774,7 +27774,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G945" t="n">
-        <v>9.06205749511719</v>
+        <v>9.0620584487915</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G946" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H946" t="n">
         <v>1200</v>
@@ -27832,7 +27832,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H947" t="n">
         <v>4900</v>
@@ -27919,7 +27919,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G950" t="n">
-        <v>9.11731338500977</v>
+        <v>9.11731433868408</v>
       </c>
       <c r="H950" t="n">
         <v>1300</v>
@@ -27948,7 +27948,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>9.30150318145752</v>
+        <v>9.3015022277832</v>
       </c>
       <c r="H951" t="n">
         <v>5000</v>
@@ -28006,7 +28006,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G953" t="n">
-        <v>9.11731338500977</v>
+        <v>9.11731433868408</v>
       </c>
       <c r="H953" t="n">
         <v>2400</v>
@@ -28093,7 +28093,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H956" t="n">
         <v>18400</v>
@@ -28151,7 +28151,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>9.06205749511719</v>
+        <v>9.0620584487915</v>
       </c>
       <c r="H958" t="n">
         <v>1400</v>
@@ -28180,7 +28180,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G959" t="n">
-        <v>9.00680160522461</v>
+        <v>9.00680065155029</v>
       </c>
       <c r="H959" t="n">
         <v>1600</v>
@@ -28296,7 +28296,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G963" t="n">
-        <v>9.04363918304443</v>
+        <v>9.04363822937012</v>
       </c>
       <c r="H963" t="n">
         <v>1100</v>
@@ -28325,7 +28325,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G964" t="n">
-        <v>9.00680160522461</v>
+        <v>9.00680065155029</v>
       </c>
       <c r="H964" t="n">
         <v>7900</v>
@@ -28354,7 +28354,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G965" t="n">
-        <v>8.84103202819824</v>
+        <v>8.84103298187256</v>
       </c>
       <c r="H965" t="n">
         <v>100</v>
@@ -28412,7 +28412,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G967" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H967" t="n">
         <v>6400</v>
@@ -28615,7 +28615,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H974" t="n">
         <v>500</v>
@@ -28644,7 +28644,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H975" t="n">
         <v>1900</v>
@@ -28673,7 +28673,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H976" t="n">
         <v>5400</v>
@@ -28731,7 +28731,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G978" t="n">
-        <v>8.84103202819824</v>
+        <v>8.84103298187256</v>
       </c>
       <c r="H978" t="n">
         <v>18000</v>
@@ -28789,7 +28789,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H980" t="n">
         <v>5400</v>
@@ -28818,7 +28818,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H981" t="n">
         <v>200</v>
@@ -28847,7 +28847,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G982" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H982" t="n">
         <v>2200</v>
@@ -28934,7 +28934,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H985" t="n">
         <v>1600</v>
@@ -28963,7 +28963,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -29050,7 +29050,7 @@
         <v>9</v>
       </c>
       <c r="G989" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H989" t="n">
         <v>2200</v>
@@ -29137,7 +29137,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H992" t="n">
         <v>3200</v>
@@ -29166,7 +29166,7 @@
         <v>9</v>
       </c>
       <c r="G993" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H993" t="n">
         <v>5000</v>
@@ -29311,7 +29311,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G998" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H998" t="n">
         <v>600</v>
@@ -29340,7 +29340,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G999" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H999" t="n">
         <v>1100</v>
@@ -29398,7 +29398,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1001" t="n">
         <v>900</v>
@@ -29572,7 +29572,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423698425293</v>
+        <v>8.45423793792725</v>
       </c>
       <c r="H1007" t="n">
         <v>100</v>
@@ -29630,7 +29630,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1009" t="n">
         <v>2700</v>
@@ -29659,7 +29659,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29717,7 +29717,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1012" t="n">
-        <v>8.17795467376709</v>
+        <v>8.17795562744141</v>
       </c>
       <c r="H1012" t="n">
         <v>200</v>
@@ -30036,7 +30036,7 @@
         <v>9</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1023" t="n">
         <v>100</v>
@@ -30065,7 +30065,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1024" t="n">
         <v>1000</v>
@@ -30094,7 +30094,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1025" t="n">
         <v>200</v>
@@ -30123,7 +30123,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1026" t="n">
         <v>300</v>
@@ -30152,7 +30152,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1027" t="n">
         <v>100</v>
@@ -30181,7 +30181,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -30239,7 +30239,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1030" t="n">
         <v>300</v>
@@ -30268,7 +30268,7 @@
         <v>9</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1031" t="n">
         <v>1000</v>
@@ -30297,7 +30297,7 @@
         <v>9</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -30326,7 +30326,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>7.9753475189209</v>
+        <v>7.97534799575806</v>
       </c>
       <c r="H1033" t="n">
         <v>1200</v>
@@ -30355,7 +30355,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>7.71748447418213</v>
+        <v>7.71748399734497</v>
       </c>
       <c r="H1034" t="n">
         <v>3900</v>
@@ -30384,7 +30384,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.88325357437134</v>
+        <v>7.8832540512085</v>
       </c>
       <c r="H1035" t="n">
         <v>600</v>
@@ -30645,7 +30645,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H1044" t="n">
         <v>3800</v>
@@ -30674,7 +30674,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1045" t="n">
         <v>2000</v>
@@ -30790,7 +30790,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.73051929473877</v>
+        <v>8.73051834106445</v>
       </c>
       <c r="H1049" t="n">
         <v>1100</v>
@@ -30819,7 +30819,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1050" t="n">
         <v>11300</v>
@@ -30848,7 +30848,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30964,7 +30964,7 @@
         <v>9</v>
       </c>
       <c r="G1055" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1055" t="n">
         <v>3400</v>
@@ -30993,7 +30993,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1056" t="n">
         <v>300</v>
@@ -31051,7 +31051,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1058" t="n">
-        <v>8.73051929473877</v>
+        <v>8.73051834106445</v>
       </c>
       <c r="H1058" t="n">
         <v>1000</v>
@@ -31080,7 +31080,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1059" t="n">
-        <v>8.73051929473877</v>
+        <v>8.73051834106445</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31138,7 +31138,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1061" t="n">
         <v>700</v>
@@ -31167,7 +31167,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1062" t="n">
         <v>800</v>
@@ -31312,7 +31312,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1067" t="n">
         <v>3400</v>
@@ -31341,7 +31341,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -31370,7 +31370,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1069" t="n">
         <v>1000</v>
@@ -31399,7 +31399,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1070" t="n">
         <v>2800</v>
@@ -31515,7 +31515,7 @@
         <v>9</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1074" t="n">
         <v>300</v>
@@ -31573,7 +31573,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.17795467376709</v>
+        <v>8.17795562744141</v>
       </c>
       <c r="H1076" t="n">
         <v>14700</v>
@@ -31631,7 +31631,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1078" t="n">
         <v>800</v>
@@ -31863,7 +31863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H1086" t="n">
         <v>200</v>
@@ -31892,7 +31892,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1087" t="n">
         <v>300</v>
@@ -31921,7 +31921,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1088" t="n">
         <v>100</v>
@@ -31950,7 +31950,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1090" t="n">
         <v>200</v>
@@ -32008,7 +32008,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H1091" t="n">
         <v>1500</v>
@@ -32153,7 +32153,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1096" t="n">
         <v>1900</v>
@@ -32182,7 +32182,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>8.63842487335205</v>
+        <v>8.63842582702637</v>
       </c>
       <c r="H1097" t="n">
         <v>3600</v>
@@ -32211,7 +32211,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H1098" t="n">
         <v>1100</v>
@@ -32356,7 +32356,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.49107551574707</v>
+        <v>8.49107456207275</v>
       </c>
       <c r="H1103" t="n">
         <v>11700</v>
@@ -32385,7 +32385,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1104" t="n">
         <v>2200</v>
@@ -32530,7 +32530,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H1109" t="n">
         <v>2500</v>
@@ -32559,7 +32559,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1110" t="n">
         <v>22300</v>
@@ -32675,7 +32675,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1114" t="n">
         <v>1100</v>
@@ -32704,7 +32704,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1115" t="n">
         <v>5200</v>
@@ -32994,7 +32994,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1125" t="n">
         <v>11000</v>
@@ -33139,7 +33139,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1130" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1130" t="n">
         <v>100</v>
@@ -33168,7 +33168,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1131" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1131" t="n">
         <v>0</v>
@@ -33197,7 +33197,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1132" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1132" t="n">
         <v>1500</v>
@@ -33284,7 +33284,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1135" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1135" t="n">
         <v>100</v>
@@ -33313,7 +33313,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1136" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1136" t="n">
         <v>0</v>
@@ -33342,7 +33342,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1137" t="n">
-        <v>8.73051929473877</v>
+        <v>8.73051834106445</v>
       </c>
       <c r="H1137" t="n">
         <v>200</v>
@@ -33400,7 +33400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1139" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1139" t="n">
         <v>3300</v>
@@ -33487,7 +33487,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1142" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1142" t="n">
         <v>300</v>
@@ -33603,7 +33603,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1146" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1146" t="n">
         <v>1600</v>
@@ -33719,7 +33719,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1150" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1150" t="n">
         <v>2300</v>
@@ -33748,7 +33748,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H1151" t="n">
         <v>2000</v>
@@ -33777,7 +33777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1152" t="n">
-        <v>8.93312644958496</v>
+        <v>8.93312549591064</v>
       </c>
       <c r="H1152" t="n">
         <v>0</v>
@@ -33835,7 +33835,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.00680160522461</v>
+        <v>9.00680065155029</v>
       </c>
       <c r="H1154" t="n">
         <v>200</v>
@@ -33864,7 +33864,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1155" t="n">
         <v>100</v>
@@ -33893,7 +33893,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.84103202819824</v>
+        <v>8.84103298187256</v>
       </c>
       <c r="H1156" t="n">
         <v>200</v>
@@ -33980,7 +33980,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1159" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1159" t="n">
         <v>4200</v>
@@ -34154,7 +34154,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1165" t="n">
-        <v>8.58316802978516</v>
+        <v>8.58316898345947</v>
       </c>
       <c r="H1165" t="n">
         <v>100</v>
@@ -34357,7 +34357,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.71210098266602</v>
+        <v>8.7121000289917</v>
       </c>
       <c r="H1172" t="n">
         <v>500</v>
@@ -34415,7 +34415,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1174" t="n">
         <v>100</v>
@@ -34531,7 +34531,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1178" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1178" t="n">
         <v>100</v>
@@ -34560,7 +34560,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1179" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1179" t="n">
         <v>0</v>
@@ -34589,7 +34589,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1180" t="n">
-        <v>8.58316802978516</v>
+        <v>8.58316898345947</v>
       </c>
       <c r="H1180" t="n">
         <v>3700</v>
@@ -34647,7 +34647,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1182" t="n">
-        <v>8.49107551574707</v>
+        <v>8.49107456207275</v>
       </c>
       <c r="H1182" t="n">
         <v>1200</v>
@@ -34705,7 +34705,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1184" t="n">
         <v>900</v>
@@ -34792,7 +34792,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1187" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1187" t="n">
         <v>300</v>
@@ -34821,7 +34821,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1188" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1188" t="n">
         <v>0</v>
@@ -34850,7 +34850,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1189" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1189" t="n">
         <v>100</v>
@@ -34879,7 +34879,7 @@
         <v>9</v>
       </c>
       <c r="G1190" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1190" t="n">
         <v>2400</v>
@@ -34908,7 +34908,7 @@
         <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1191" t="n">
         <v>0</v>
@@ -34937,7 +34937,7 @@
         <v>9</v>
       </c>
       <c r="G1192" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1192" t="n">
         <v>800</v>
@@ -34966,7 +34966,7 @@
         <v>9</v>
       </c>
       <c r="G1193" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1193" t="n">
         <v>1600</v>
@@ -34995,7 +34995,7 @@
         <v>9</v>
       </c>
       <c r="G1194" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1194" t="n">
         <v>11800</v>
@@ -35024,7 +35024,7 @@
         <v>9</v>
       </c>
       <c r="G1195" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1195" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1197" t="n">
-        <v>8.50949287414551</v>
+        <v>8.50949382781982</v>
       </c>
       <c r="H1197" t="n">
         <v>300</v>
@@ -35169,7 +35169,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1200" t="n">
         <v>100</v>
@@ -35256,7 +35256,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1203" t="n">
         <v>700</v>
@@ -35285,7 +35285,7 @@
         <v>9</v>
       </c>
       <c r="G1204" t="n">
-        <v>8.28846836090088</v>
+        <v>8.28846740722656</v>
       </c>
       <c r="H1204" t="n">
         <v>500</v>
@@ -35372,7 +35372,7 @@
         <v>8.5</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.82799673080444</v>
+        <v>7.8279972076416</v>
       </c>
       <c r="H1207" t="n">
         <v>10600</v>
@@ -35401,7 +35401,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1208" t="n">
-        <v>7.80957794189453</v>
+        <v>7.80957746505737</v>
       </c>
       <c r="H1208" t="n">
         <v>1300</v>
@@ -35430,7 +35430,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590278625488</v>
+        <v>7.73590230941772</v>
       </c>
       <c r="H1209" t="n">
         <v>2000</v>
@@ -35459,7 +35459,7 @@
         <v>8.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.82799673080444</v>
+        <v>7.8279972076416</v>
       </c>
       <c r="H1210" t="n">
         <v>3600</v>
@@ -35488,7 +35488,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.80957794189453</v>
+        <v>7.80957746505737</v>
       </c>
       <c r="H1211" t="n">
         <v>1400</v>
@@ -35575,7 +35575,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.49645853042603</v>
+        <v>7.49645900726318</v>
       </c>
       <c r="H1214" t="n">
         <v>3700</v>
@@ -35662,7 +35662,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1217" t="n">
-        <v>7.25701427459717</v>
+        <v>7.25701379776001</v>
       </c>
       <c r="H1217" t="n">
         <v>4400</v>
@@ -35720,7 +35720,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.05440616607666</v>
+        <v>7.05440664291382</v>
       </c>
       <c r="H1219" t="n">
         <v>4300</v>
@@ -35836,7 +35836,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.25701427459717</v>
+        <v>7.25701379776001</v>
       </c>
       <c r="H1223" t="n">
         <v>5900</v>
@@ -36097,7 +36097,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590278625488</v>
+        <v>7.73590230941772</v>
       </c>
       <c r="H1232" t="n">
         <v>200</v>
@@ -36155,7 +36155,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.71748447418213</v>
+        <v>7.71748399734497</v>
       </c>
       <c r="H1234" t="n">
         <v>21900</v>
@@ -36242,7 +36242,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1237" t="n">
         <v>7900</v>
@@ -36271,7 +36271,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1238" t="n">
         <v>600</v>
@@ -36329,7 +36329,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1240" t="n">
         <v>1300</v>
@@ -36416,7 +36416,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.49807548522949</v>
+        <v>7.49807500839233</v>
       </c>
       <c r="H1243" t="n">
         <v>1400</v>
@@ -36474,7 +36474,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.30728387832642</v>
+        <v>7.30728435516357</v>
       </c>
       <c r="H1245" t="n">
         <v>1600</v>
@@ -36590,7 +36590,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.4217586517334</v>
+        <v>7.42175912857056</v>
       </c>
       <c r="H1249" t="n">
         <v>300</v>
@@ -36648,7 +36648,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.59347009658813</v>
+        <v>7.59347057342529</v>
       </c>
       <c r="H1251" t="n">
         <v>200</v>
@@ -36706,7 +36706,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.19281005859375</v>
+        <v>7.19280958175659</v>
       </c>
       <c r="H1253" t="n">
         <v>1200</v>
@@ -36735,7 +36735,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.61254978179932</v>
+        <v>7.61254930496216</v>
       </c>
       <c r="H1254" t="n">
         <v>1200</v>
@@ -36764,7 +36764,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1255" t="n">
         <v>1300</v>
@@ -36793,7 +36793,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1256" t="n">
         <v>900</v>
@@ -36880,7 +36880,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1259" t="n">
         <v>3700</v>
@@ -36996,7 +36996,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.22307872772217</v>
+        <v>8.22307968139648</v>
       </c>
       <c r="H1263" t="n">
         <v>100</v>
@@ -37112,7 +37112,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.80334091186523</v>
+        <v>7.80334043502808</v>
       </c>
       <c r="H1267" t="n">
         <v>2800</v>
@@ -37141,7 +37141,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1268" t="n">
         <v>1400</v>
@@ -37199,7 +37199,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.91781520843506</v>
+        <v>7.9178147315979</v>
       </c>
       <c r="H1270" t="n">
         <v>600</v>
@@ -37228,7 +37228,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1271" t="n">
         <v>400</v>
@@ -37518,7 +37518,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.30728387832642</v>
+        <v>7.30728435516357</v>
       </c>
       <c r="H1281" t="n">
         <v>2100</v>
@@ -37547,7 +37547,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.30728387832642</v>
+        <v>7.30728435516357</v>
       </c>
       <c r="H1282" t="n">
         <v>0</v>
@@ -37634,7 +37634,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.61254978179932</v>
+        <v>7.61254930496216</v>
       </c>
       <c r="H1285" t="n">
         <v>300</v>
@@ -37663,7 +37663,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1286" t="n">
         <v>200</v>
@@ -37750,7 +37750,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.76518201828003</v>
+        <v>7.76518249511719</v>
       </c>
       <c r="H1289" t="n">
         <v>700</v>
@@ -37779,7 +37779,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1290" t="n">
-        <v>7.80334091186523</v>
+        <v>7.80334043502808</v>
       </c>
       <c r="H1290" t="n">
         <v>100</v>
@@ -37837,7 +37837,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.86057710647583</v>
+        <v>7.86057758331299</v>
       </c>
       <c r="H1292" t="n">
         <v>2700</v>
@@ -37866,7 +37866,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.86057710647583</v>
+        <v>7.86057758331299</v>
       </c>
       <c r="H1293" t="n">
         <v>0</v>
@@ -37895,7 +37895,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1294" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1294" t="n">
         <v>800</v>
@@ -37924,7 +37924,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1295" t="n">
         <v>0</v>
@@ -38069,7 +38069,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1300" t="n">
-        <v>7.82241916656494</v>
+        <v>7.82241868972778</v>
       </c>
       <c r="H1300" t="n">
         <v>1700</v>
@@ -38098,7 +38098,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1301" t="n">
         <v>1200</v>
@@ -38185,7 +38185,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>7.66978693008423</v>
+        <v>7.66978645324707</v>
       </c>
       <c r="H1304" t="n">
         <v>700</v>
@@ -38272,7 +38272,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.49807548522949</v>
+        <v>7.49807500839233</v>
       </c>
       <c r="H1307" t="n">
         <v>1000</v>
@@ -38475,7 +38475,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.2500467300415</v>
+        <v>7.25004720687866</v>
       </c>
       <c r="H1314" t="n">
         <v>200</v>
@@ -38678,7 +38678,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.08622407913208</v>
+        <v>6.08622360229492</v>
       </c>
       <c r="H1321" t="n">
         <v>3700</v>
@@ -38881,7 +38881,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.42964696884155</v>
+        <v>6.42964649200439</v>
       </c>
       <c r="H1328" t="n">
         <v>2100</v>
@@ -38968,7 +38968,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.42964696884155</v>
+        <v>6.42964649200439</v>
       </c>
       <c r="H1331" t="n">
         <v>3300</v>
@@ -39084,7 +39084,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>6.18161869049072</v>
+        <v>6.18161916732788</v>
       </c>
       <c r="H1335" t="n">
         <v>1600</v>
@@ -39229,7 +39229,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>6.25793552398682</v>
+        <v>6.25793504714966</v>
       </c>
       <c r="H1340" t="n">
         <v>5900</v>
@@ -39345,7 +39345,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1344" t="n">
-        <v>6.37240982055664</v>
+        <v>6.37240934371948</v>
       </c>
       <c r="H1344" t="n">
         <v>1600</v>
@@ -39403,7 +39403,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1346" t="n">
         <v>1100</v>
@@ -39490,7 +39490,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>6.73491239547729</v>
+        <v>6.73491191864014</v>
       </c>
       <c r="H1349" t="n">
         <v>4400</v>
@@ -39577,7 +39577,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.42964696884155</v>
+        <v>6.42964649200439</v>
       </c>
       <c r="H1352" t="n">
         <v>400</v>
@@ -39867,7 +39867,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1362" t="n">
-        <v>6.62043762207031</v>
+        <v>6.62043809890747</v>
       </c>
       <c r="H1362" t="n">
         <v>2600</v>
@@ -40041,7 +40041,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1368" t="n">
         <v>1300</v>
@@ -40099,7 +40099,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1370" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1370" t="n">
         <v>1000</v>
@@ -40128,7 +40128,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.62043762207031</v>
+        <v>6.62043809890747</v>
       </c>
       <c r="H1371" t="n">
         <v>10600</v>
@@ -40157,7 +40157,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1372" t="n">
-        <v>6.62043762207031</v>
+        <v>6.62043809890747</v>
       </c>
       <c r="H1372" t="n">
         <v>0</v>
@@ -40186,7 +40186,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.62043762207031</v>
+        <v>6.62043809890747</v>
       </c>
       <c r="H1373" t="n">
         <v>0</v>
@@ -40215,7 +40215,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1374" t="n">
         <v>100</v>
@@ -40447,7 +40447,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1382" t="n">
-        <v>6.44872617721558</v>
+        <v>6.44872665405273</v>
       </c>
       <c r="H1382" t="n">
         <v>1000</v>
@@ -40563,7 +40563,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1386" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1386" t="n">
         <v>700</v>
@@ -40592,7 +40592,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.42964696884155</v>
+        <v>6.42964649200439</v>
       </c>
       <c r="H1387" t="n">
         <v>700</v>
@@ -40621,7 +40621,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.54412174224854</v>
+        <v>6.54412126541138</v>
       </c>
       <c r="H1388" t="n">
         <v>400</v>
@@ -40795,7 +40795,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1394" t="n">
-        <v>6.23885583877563</v>
+        <v>6.23885631561279</v>
       </c>
       <c r="H1394" t="n">
         <v>1100</v>
@@ -40853,7 +40853,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1396" t="n">
-        <v>6.37240982055664</v>
+        <v>6.37240934371948</v>
       </c>
       <c r="H1396" t="n">
         <v>5300</v>
@@ -40911,7 +40911,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>6.08622407913208</v>
+        <v>6.08622360229492</v>
       </c>
       <c r="H1398" t="n">
         <v>8500</v>
@@ -40969,7 +40969,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1400" t="n">
-        <v>6.08622407913208</v>
+        <v>6.08622360229492</v>
       </c>
       <c r="H1400" t="n">
         <v>3800</v>
@@ -41056,7 +41056,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1403" t="n">
-        <v>5.85727453231812</v>
+        <v>5.85727500915527</v>
       </c>
       <c r="H1403" t="n">
         <v>3500</v>
@@ -41201,7 +41201,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1408" t="n">
-        <v>5.91451215744019</v>
+        <v>5.91451168060303</v>
       </c>
       <c r="H1408" t="n">
         <v>100</v>
@@ -41375,7 +41375,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.08622407913208</v>
+        <v>6.08622360229492</v>
       </c>
       <c r="H1414" t="n">
         <v>3900</v>
@@ -41462,7 +41462,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.12438154220581</v>
+        <v>6.12438201904297</v>
       </c>
       <c r="H1417" t="n">
         <v>1600</v>
@@ -41607,7 +41607,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1422" t="n">
-        <v>5.95267009735107</v>
+        <v>5.95266962051392</v>
       </c>
       <c r="H1422" t="n">
         <v>500</v>
@@ -41694,7 +41694,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>5.78095865249634</v>
+        <v>5.78095817565918</v>
       </c>
       <c r="H1425" t="n">
         <v>6300</v>
@@ -41868,7 +41868,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1431" t="n">
-        <v>5.91451215744019</v>
+        <v>5.91451168060303</v>
       </c>
       <c r="H1431" t="n">
         <v>1000</v>
@@ -42071,7 +42071,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.32306098937988</v>
+        <v>5.32306051254272</v>
       </c>
       <c r="H1438" t="n">
         <v>8200</v>
@@ -42129,7 +42129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.53293037414551</v>
+        <v>5.53293085098267</v>
       </c>
       <c r="H1440" t="n">
         <v>4900</v>
@@ -42187,7 +42187,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1442" t="n">
-        <v>5.58062791824341</v>
+        <v>5.58062839508057</v>
       </c>
       <c r="H1442" t="n">
         <v>5900</v>
@@ -42332,7 +42332,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>5.34213972091675</v>
+        <v>5.34214019775391</v>
       </c>
       <c r="H1447" t="n">
         <v>400</v>
@@ -42361,7 +42361,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1448" t="n">
-        <v>5.34213972091675</v>
+        <v>5.34214019775391</v>
       </c>
       <c r="H1448" t="n">
         <v>0</v>
@@ -42419,7 +42419,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>5.34213972091675</v>
+        <v>5.34214019775391</v>
       </c>
       <c r="H1450" t="n">
         <v>7900</v>
@@ -42448,7 +42448,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.43753528594971</v>
+        <v>5.43753480911255</v>
       </c>
       <c r="H1451" t="n">
         <v>9800</v>
@@ -42593,7 +42593,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.58062791824341</v>
+        <v>5.58062839508057</v>
       </c>
       <c r="H1456" t="n">
         <v>14200</v>
@@ -60927,6 +60927,35 @@
         <v>2700</v>
       </c>
       <c r="I2088" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2089" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>2.95000004768372</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>2.95000004768372</v>
+      </c>
+      <c r="G2089" t="n">
+        <v>2.95000004768372</v>
+      </c>
+      <c r="H2089" t="n">
+        <v>1900</v>
+      </c>
+      <c r="I2089" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -601,7 +601,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11247158050537</v>
+        <v>8.11247062683105</v>
       </c>
       <c r="H8" t="n">
         <v>7000</v>
@@ -717,7 +717,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -746,7 +746,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -804,7 +804,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -833,7 +833,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10059070587158</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H17" t="n">
         <v>1300</v>
@@ -891,7 +891,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10059070587158</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10653018951416</v>
+        <v>8.10653209686279</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.1379280090332</v>
+        <v>8.13792896270752</v>
       </c>
       <c r="H22" t="n">
         <v>300</v>
@@ -1065,7 +1065,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852745056152</v>
+        <v>8.07852649688721</v>
       </c>
       <c r="H24" t="n">
         <v>2800</v>
@@ -1239,7 +1239,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H30" t="n">
         <v>7500</v>
@@ -1297,7 +1297,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10059070587158</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H32" t="n">
         <v>200</v>
@@ -1326,7 +1326,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.07513332366943</v>
+        <v>8.07513236999512</v>
       </c>
       <c r="H33" t="n">
         <v>8000</v>
@@ -1384,7 +1384,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01064014434814</v>
+        <v>8.01063919067383</v>
       </c>
       <c r="H35" t="n">
         <v>7500</v>
@@ -1471,7 +1471,7 @@
         <v>9.37100028991699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.95208787918091</v>
+        <v>7.95208740234375</v>
       </c>
       <c r="H38" t="n">
         <v>500</v>
@@ -1500,7 +1500,7 @@
         <v>9.33100032806396</v>
       </c>
       <c r="G39" t="n">
-        <v>7.91814374923706</v>
+        <v>7.91814470291138</v>
       </c>
       <c r="H39" t="n">
         <v>400</v>
@@ -1529,7 +1529,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227073669434</v>
+        <v>7.96227216720581</v>
       </c>
       <c r="H40" t="n">
         <v>300</v>
@@ -1558,7 +1558,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227073669434</v>
+        <v>7.96227216720581</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.97924137115479</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H42" t="n">
         <v>300</v>
@@ -1616,7 +1616,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.97924137115479</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H43" t="n">
         <v>1700</v>
@@ -1703,7 +1703,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H46" t="n">
         <v>8000</v>
@@ -1732,7 +1732,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1761,7 +1761,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G48" t="n">
-        <v>7.90880918502808</v>
+        <v>7.90880966186523</v>
       </c>
       <c r="H48" t="n">
         <v>3700</v>
@@ -1790,7 +1790,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729497909546</v>
+        <v>7.91729545593262</v>
       </c>
       <c r="H49" t="n">
         <v>9200</v>
@@ -1819,7 +1819,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619735717773</v>
+        <v>7.85619878768921</v>
       </c>
       <c r="H50" t="n">
         <v>8700</v>
@@ -1848,7 +1848,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H51" t="n">
         <v>16700</v>
@@ -1877,7 +1877,7 @@
         <v>9.13399982452393</v>
       </c>
       <c r="G52" t="n">
-        <v>7.75097370147705</v>
+        <v>7.75097274780273</v>
       </c>
       <c r="H52" t="n">
         <v>5200</v>
@@ -1993,7 +1993,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G56" t="n">
-        <v>7.76709747314453</v>
+        <v>7.76709604263306</v>
       </c>
       <c r="H56" t="n">
         <v>200</v>
@@ -2022,7 +2022,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H57" t="n">
         <v>12300</v>
@@ -2051,7 +2051,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.80697917938232</v>
+        <v>7.80697870254517</v>
       </c>
       <c r="H58" t="n">
         <v>4100</v>
@@ -2109,7 +2109,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.80697917938232</v>
+        <v>7.80697870254517</v>
       </c>
       <c r="H60" t="n">
         <v>24300</v>
@@ -2138,7 +2138,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H61" t="n">
         <v>4900</v>
@@ -2167,7 +2167,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H62" t="n">
         <v>8400</v>
@@ -2196,7 +2196,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H64" t="n">
         <v>1600</v>
@@ -2254,7 +2254,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.80697917938232</v>
+        <v>7.80697870254517</v>
       </c>
       <c r="H65" t="n">
         <v>7100</v>
@@ -2283,7 +2283,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H66" t="n">
         <v>2500</v>
@@ -2312,7 +2312,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>9.20699977874756</v>
       </c>
       <c r="G69" t="n">
-        <v>7.81291961669922</v>
+        <v>7.81291913986206</v>
       </c>
       <c r="H69" t="n">
         <v>200</v>
@@ -2399,7 +2399,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.80528259277344</v>
+        <v>7.80528211593628</v>
       </c>
       <c r="H70" t="n">
         <v>1000</v>
@@ -2428,7 +2428,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722898483276</v>
+        <v>7.86722993850708</v>
       </c>
       <c r="H71" t="n">
         <v>800</v>
@@ -2457,7 +2457,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746366500854</v>
+        <v>7.78746223449707</v>
       </c>
       <c r="H72" t="n">
         <v>700</v>
@@ -2486,7 +2486,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746366500854</v>
+        <v>7.78746223449707</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761173248291</v>
+        <v>8.02761077880859</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2602,7 +2602,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177207946777</v>
+        <v>7.84177255630493</v>
       </c>
       <c r="H77" t="n">
         <v>4000</v>
@@ -2631,7 +2631,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.79085731506348</v>
+        <v>7.790855884552</v>
       </c>
       <c r="H78" t="n">
         <v>800</v>
@@ -2660,7 +2660,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>7.84516668319702</v>
+        <v>7.84516525268555</v>
       </c>
       <c r="H79" t="n">
         <v>2400</v>
@@ -2689,7 +2689,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243751525879</v>
+        <v>7.83243656158447</v>
       </c>
       <c r="H80" t="n">
         <v>1600</v>
@@ -2718,7 +2718,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358648300171</v>
+        <v>7.80358505249023</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2776,7 +2776,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H83" t="n">
         <v>1100</v>
@@ -2805,7 +2805,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G87" t="n">
-        <v>7.81037473678589</v>
+        <v>7.81037425994873</v>
       </c>
       <c r="H87" t="n">
         <v>2500</v>
@@ -2921,7 +2921,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098882675171</v>
+        <v>7.89098930358887</v>
       </c>
       <c r="H88" t="n">
         <v>200</v>
@@ -2950,7 +2950,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782890319824</v>
+        <v>7.80782794952393</v>
       </c>
       <c r="H89" t="n">
         <v>5100</v>
@@ -2979,7 +2979,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.76879262924194</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.76879262924194</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H91" t="n">
         <v>700</v>
@@ -3037,7 +3037,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408514022827</v>
+        <v>7.92408561706543</v>
       </c>
       <c r="H92" t="n">
         <v>1200</v>
@@ -3066,7 +3066,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.77049016952515</v>
+        <v>7.77048969268799</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539993286133</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3182,7 +3182,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G97" t="n">
-        <v>7.72212076187134</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H97" t="n">
         <v>7500</v>
@@ -3211,7 +3211,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G98" t="n">
-        <v>7.72212076187134</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969226837158</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H100" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969226837158</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726234436035</v>
+        <v>7.63726186752319</v>
       </c>
       <c r="H102" t="n">
         <v>700</v>
@@ -3356,7 +3356,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423440933228</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423440933228</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904291152954</v>
+        <v>7.82904148101807</v>
       </c>
       <c r="H106" t="n">
         <v>300</v>
@@ -3472,7 +3472,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G107" t="n">
-        <v>7.72212076187134</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H107" t="n">
         <v>1100</v>
@@ -3501,7 +3501,7 @@
         <v>9.10099983215332</v>
       </c>
       <c r="G108" t="n">
-        <v>7.7229700088501</v>
+        <v>7.72297048568726</v>
       </c>
       <c r="H108" t="n">
         <v>2200</v>
@@ -3530,7 +3530,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G109" t="n">
-        <v>7.72212076187134</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H109" t="n">
         <v>2200</v>
@@ -3559,7 +3559,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363496780396</v>
+        <v>7.71363544464111</v>
       </c>
       <c r="H110" t="n">
         <v>10000</v>
@@ -3646,7 +3646,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817806243896</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H113" t="n">
         <v>15900</v>
@@ -3675,7 +3675,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969226837158</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H114" t="n">
         <v>100</v>
@@ -3704,7 +3704,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902635574341</v>
+        <v>7.68902587890625</v>
       </c>
       <c r="H115" t="n">
         <v>1500</v>
@@ -3733,7 +3733,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.8511061668396</v>
+        <v>7.85110664367676</v>
       </c>
       <c r="H116" t="n">
         <v>800</v>
@@ -3762,7 +3762,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273580551147</v>
+        <v>7.80273675918579</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -3791,7 +3791,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308591842651</v>
+        <v>7.68308734893799</v>
       </c>
       <c r="H118" t="n">
         <v>2400</v>
@@ -3849,7 +3849,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G120" t="n">
-        <v>7.72212076187134</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H120" t="n">
         <v>2000</v>
@@ -3878,7 +3878,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G121" t="n">
-        <v>7.72212076187134</v>
+        <v>7.72212171554565</v>
       </c>
       <c r="H121" t="n">
         <v>5000</v>
@@ -3907,7 +3907,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817806243896</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H122" t="n">
         <v>3300</v>
@@ -3936,7 +3936,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.76879262924194</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H123" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.86553287506104</v>
+        <v>7.86553192138672</v>
       </c>
       <c r="H125" t="n">
         <v>300</v>
@@ -4023,7 +4023,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152179718018</v>
+        <v>7.78152132034302</v>
       </c>
       <c r="H126" t="n">
         <v>24300</v>
@@ -4110,7 +4110,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303647994995</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303647994995</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243751525879</v>
+        <v>7.83243656158447</v>
       </c>
       <c r="H131" t="n">
         <v>5900</v>
@@ -4197,7 +4197,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.79849338531494</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H132" t="n">
         <v>300</v>
@@ -4226,7 +4226,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H133" t="n">
         <v>13900</v>
@@ -4255,7 +4255,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000759124756</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000759124756</v>
+        <v>7.79000854492188</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445085525513</v>
+        <v>7.94445037841797</v>
       </c>
       <c r="H136" t="n">
         <v>2500</v>
@@ -4342,7 +4342,7 @@
         <v>9.5</v>
       </c>
       <c r="G137" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H137" t="n">
         <v>100</v>
@@ -4371,7 +4371,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.79849338531494</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H138" t="n">
         <v>800</v>
@@ -4400,7 +4400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.80697917938232</v>
+        <v>7.80697870254517</v>
       </c>
       <c r="H139" t="n">
         <v>1200</v>
@@ -4429,7 +4429,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G140" t="n">
-        <v>7.96311855316162</v>
+        <v>7.96311950683594</v>
       </c>
       <c r="H140" t="n">
         <v>500</v>
@@ -4458,7 +4458,7 @@
         <v>9.5</v>
       </c>
       <c r="G141" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H141" t="n">
         <v>300</v>
@@ -4632,7 +4632,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G147" t="n">
-        <v>8.06919193267822</v>
+        <v>8.06919288635254</v>
       </c>
       <c r="H147" t="n">
         <v>100</v>
@@ -4661,7 +4661,7 @@
         <v>9.32100009918213</v>
       </c>
       <c r="G148" t="n">
-        <v>7.90965795516968</v>
+        <v>7.90965843200684</v>
       </c>
       <c r="H148" t="n">
         <v>700</v>
@@ -4719,7 +4719,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>7.92153739929199</v>
+        <v>7.92153835296631</v>
       </c>
       <c r="H150" t="n">
         <v>100</v>
@@ -4748,7 +4748,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.92153739929199</v>
+        <v>7.92153835296631</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G152" t="n">
-        <v>8.06919193267822</v>
+        <v>8.06919288635254</v>
       </c>
       <c r="H152" t="n">
         <v>700</v>
@@ -4806,7 +4806,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G153" t="n">
-        <v>8.06919193267822</v>
+        <v>8.06919288635254</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.9283275604248</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H154" t="n">
         <v>1100</v>
@@ -4893,7 +4893,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G156" t="n">
-        <v>8.06664657592773</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H156" t="n">
         <v>100</v>
@@ -4922,7 +4922,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G157" t="n">
-        <v>8.06664657592773</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G158" t="n">
-        <v>8.06664657592773</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>9.44299983978271</v>
       </c>
       <c r="G160" t="n">
-        <v>8.01318550109863</v>
+        <v>8.01318645477295</v>
       </c>
       <c r="H160" t="n">
         <v>100</v>
@@ -5067,7 +5067,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G162" t="n">
-        <v>7.92153739929199</v>
+        <v>7.92153835296631</v>
       </c>
       <c r="H162" t="n">
         <v>2300</v>
@@ -5096,7 +5096,7 @@
         <v>9.4040002822876</v>
       </c>
       <c r="G163" t="n">
-        <v>7.9800910949707</v>
+        <v>7.98009157180786</v>
       </c>
       <c r="H163" t="n">
         <v>500</v>
@@ -5154,7 +5154,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>8.05307006835938</v>
+        <v>8.05306911468506</v>
       </c>
       <c r="H165" t="n">
         <v>300</v>
@@ -5183,7 +5183,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.9283275604248</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H166" t="n">
         <v>1200</v>
@@ -5241,7 +5241,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H168" t="n">
         <v>9400</v>
@@ -5270,7 +5270,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H169" t="n">
         <v>6900</v>
@@ -5299,7 +5299,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H170" t="n">
         <v>200</v>
@@ -5328,7 +5328,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H172" t="n">
         <v>3700</v>
@@ -5386,7 +5386,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H173" t="n">
         <v>200</v>
@@ -5415,7 +5415,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H174" t="n">
         <v>600</v>
@@ -5444,7 +5444,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H175" t="n">
         <v>300</v>
@@ -5473,7 +5473,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H176" t="n">
         <v>4900</v>
@@ -5531,7 +5531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H178" t="n">
         <v>300</v>
@@ -5560,7 +5560,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H179" t="n">
         <v>100</v>
@@ -5618,7 +5618,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H181" t="n">
         <v>5000</v>
@@ -5647,7 +5647,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H184" t="n">
         <v>300</v>
@@ -5734,7 +5734,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H185" t="n">
         <v>200</v>
@@ -5792,7 +5792,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H187" t="n">
         <v>900</v>
@@ -5821,7 +5821,7 @@
         <v>9.5</v>
       </c>
       <c r="G188" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H188" t="n">
         <v>500</v>
@@ -5850,7 +5850,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H189" t="n">
         <v>1900</v>
@@ -5879,7 +5879,7 @@
         <v>9.5</v>
       </c>
       <c r="G190" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H190" t="n">
         <v>1000</v>
@@ -5937,7 +5937,7 @@
         <v>9.5</v>
       </c>
       <c r="G192" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H192" t="n">
         <v>4100</v>
@@ -5966,7 +5966,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H193" t="n">
         <v>3200</v>
@@ -5995,7 +5995,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H194" t="n">
         <v>300</v>
@@ -6024,7 +6024,7 @@
         <v>9.5</v>
       </c>
       <c r="G195" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H195" t="n">
         <v>4200</v>
@@ -6053,7 +6053,7 @@
         <v>9.5</v>
       </c>
       <c r="G196" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H196" t="n">
         <v>800</v>
@@ -6111,7 +6111,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H198" t="n">
         <v>4700</v>
@@ -6140,7 +6140,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H200" t="n">
         <v>2000</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H201" t="n">
         <v>1500</v>
@@ -6227,7 +6227,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H202" t="n">
         <v>800</v>
@@ -6285,7 +6285,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H204" t="n">
         <v>5900</v>
@@ -6314,7 +6314,7 @@
         <v>9.5</v>
       </c>
       <c r="G205" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H205" t="n">
         <v>600</v>
@@ -6343,7 +6343,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H206" t="n">
         <v>300</v>
@@ -6372,7 +6372,7 @@
         <v>9.5</v>
       </c>
       <c r="G207" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H207" t="n">
         <v>700</v>
@@ -6401,7 +6401,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6430,7 +6430,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G209" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6459,7 +6459,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H210" t="n">
         <v>600</v>
@@ -6488,7 +6488,7 @@
         <v>9.5</v>
       </c>
       <c r="G211" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H211" t="n">
         <v>400</v>
@@ -6517,7 +6517,7 @@
         <v>9.5</v>
       </c>
       <c r="G212" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H212" t="n">
         <v>300</v>
@@ -6546,7 +6546,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H213" t="n">
         <v>2600</v>
@@ -6575,7 +6575,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H214" t="n">
         <v>200</v>
@@ -6604,7 +6604,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H215" t="n">
         <v>6600</v>
@@ -6662,7 +6662,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6691,7 +6691,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H218" t="n">
         <v>900</v>
@@ -6720,7 +6720,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6807,7 +6807,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H222" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H226" t="n">
         <v>100</v>
@@ -6952,7 +6952,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H227" t="n">
         <v>100</v>
@@ -7010,7 +7010,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H229" t="n">
         <v>100</v>
@@ -7039,7 +7039,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7068,7 +7068,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7097,7 +7097,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H232" t="n">
         <v>5200</v>
@@ -7155,7 +7155,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H234" t="n">
         <v>100</v>
@@ -7184,7 +7184,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H235" t="n">
         <v>300</v>
@@ -7213,7 +7213,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H236" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H237" t="n">
         <v>100</v>
@@ -7271,7 +7271,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H238" t="n">
         <v>3200</v>
@@ -7300,7 +7300,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H239" t="n">
         <v>100</v>
@@ -7474,7 +7474,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H245" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H248" t="n">
         <v>700</v>
@@ -7619,7 +7619,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G250" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H250" t="n">
         <v>300</v>
@@ -7677,7 +7677,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H252" t="n">
         <v>1800</v>
@@ -7706,7 +7706,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H253" t="n">
         <v>1700</v>
@@ -7735,7 +7735,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H254" t="n">
         <v>1800</v>
@@ -7764,7 +7764,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G255" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H255" t="n">
         <v>7900</v>
@@ -7793,7 +7793,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G256" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H256" t="n">
         <v>2300</v>
@@ -7822,7 +7822,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H257" t="n">
         <v>100</v>
@@ -7851,7 +7851,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H258" t="n">
         <v>1200</v>
@@ -7880,7 +7880,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H259" t="n">
         <v>25000</v>
@@ -7909,7 +7909,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8054,7 +8054,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G265" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H265" t="n">
         <v>100</v>
@@ -8083,7 +8083,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G266" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8112,7 +8112,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G267" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8199,7 +8199,7 @@
         <v>9.5</v>
       </c>
       <c r="G270" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H270" t="n">
         <v>600</v>
@@ -8315,7 +8315,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H274" t="n">
         <v>200</v>
@@ -8344,7 +8344,7 @@
         <v>9.5</v>
       </c>
       <c r="G275" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H275" t="n">
         <v>400</v>
@@ -8373,7 +8373,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H276" t="n">
         <v>100</v>
@@ -8402,7 +8402,7 @@
         <v>9.5</v>
       </c>
       <c r="G277" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H277" t="n">
         <v>7300</v>
@@ -8431,7 +8431,7 @@
         <v>9.5</v>
       </c>
       <c r="G278" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H278" t="n">
         <v>2000</v>
@@ -8460,7 +8460,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H279" t="n">
         <v>28000</v>
@@ -8489,7 +8489,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H280" t="n">
         <v>100</v>
@@ -8518,7 +8518,7 @@
         <v>9.5</v>
       </c>
       <c r="G281" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H281" t="n">
         <v>2100</v>
@@ -8547,7 +8547,7 @@
         <v>9.5</v>
       </c>
       <c r="G282" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H282" t="n">
         <v>400</v>
@@ -8576,7 +8576,7 @@
         <v>9.5</v>
       </c>
       <c r="G283" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H283" t="n">
         <v>100</v>
@@ -8605,7 +8605,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H284" t="n">
         <v>6900</v>
@@ -8634,7 +8634,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H285" t="n">
         <v>200</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H286" t="n">
         <v>1900</v>
@@ -8692,7 +8692,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8721,7 +8721,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H289" t="n">
         <v>800</v>
@@ -8779,7 +8779,7 @@
         <v>9.5</v>
       </c>
       <c r="G290" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H290" t="n">
         <v>5800</v>
@@ -8808,7 +8808,7 @@
         <v>9.5</v>
       </c>
       <c r="G291" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H291" t="n">
         <v>700</v>
@@ -8837,7 +8837,7 @@
         <v>9.5</v>
       </c>
       <c r="G292" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G293" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H293" t="n">
         <v>100</v>
@@ -8895,7 +8895,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G294" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G295" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G296" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H296" t="n">
         <v>200</v>
@@ -8982,7 +8982,7 @@
         <v>9.5</v>
       </c>
       <c r="G297" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9040,7 +9040,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9069,7 +9069,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H300" t="n">
         <v>100</v>
@@ -9098,7 +9098,7 @@
         <v>9.5</v>
       </c>
       <c r="G301" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H301" t="n">
         <v>19200</v>
@@ -9127,7 +9127,7 @@
         <v>9.5</v>
       </c>
       <c r="G302" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H302" t="n">
         <v>2300</v>
@@ -9156,7 +9156,7 @@
         <v>9.5</v>
       </c>
       <c r="G303" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H303" t="n">
         <v>4100</v>
@@ -9185,7 +9185,7 @@
         <v>9.5</v>
       </c>
       <c r="G304" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H304" t="n">
         <v>800</v>
@@ -9214,7 +9214,7 @@
         <v>9.5</v>
       </c>
       <c r="G305" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>9.5</v>
       </c>
       <c r="G308" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H308" t="n">
         <v>300</v>
@@ -9330,7 +9330,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H309" t="n">
         <v>500</v>
@@ -9359,7 +9359,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H310" t="n">
         <v>3300</v>
@@ -9620,7 +9620,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H319" t="n">
         <v>200</v>
@@ -9649,7 +9649,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G320" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H320" t="n">
         <v>100</v>
@@ -9678,7 +9678,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H321" t="n">
         <v>100</v>
@@ -9707,7 +9707,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H322" t="n">
         <v>4600</v>
@@ -9736,7 +9736,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H323" t="n">
         <v>26700</v>
@@ -9765,7 +9765,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H324" t="n">
         <v>100</v>
@@ -9823,7 +9823,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G326" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H326" t="n">
         <v>100</v>
@@ -9881,7 +9881,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H328" t="n">
         <v>52800</v>
@@ -9910,7 +9910,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H329" t="n">
         <v>10000</v>
@@ -9939,7 +9939,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H330" t="n">
         <v>200</v>
@@ -9968,7 +9968,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H331" t="n">
         <v>900</v>
@@ -10055,7 +10055,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H334" t="n">
         <v>100</v>
@@ -10084,7 +10084,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H335" t="n">
         <v>2200</v>
@@ -10113,7 +10113,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G336" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H336" t="n">
         <v>100</v>
@@ -10142,7 +10142,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G337" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H337" t="n">
         <v>100</v>
@@ -10258,7 +10258,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H341" t="n">
         <v>300</v>
@@ -10287,7 +10287,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H342" t="n">
         <v>100</v>
@@ -10316,7 +10316,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H344" t="n">
         <v>1700</v>
@@ -10374,7 +10374,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G345" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G346" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H346" t="n">
         <v>3000</v>
@@ -10432,7 +10432,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G347" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G350" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H350" t="n">
         <v>4400</v>
@@ -10548,7 +10548,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H351" t="n">
         <v>1400</v>
@@ -10577,7 +10577,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G352" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H352" t="n">
         <v>100</v>
@@ -10606,7 +10606,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G353" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H360" t="n">
         <v>5000</v>
@@ -10867,7 +10867,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H362" t="n">
         <v>300</v>
@@ -10896,7 +10896,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H363" t="n">
         <v>1100</v>
@@ -10925,7 +10925,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H365" t="n">
         <v>100</v>
@@ -10983,7 +10983,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H367" t="n">
         <v>900</v>
@@ -11041,7 +11041,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H368" t="n">
         <v>300</v>
@@ -11070,7 +11070,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H369" t="n">
         <v>100</v>
@@ -11099,7 +11099,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H371" t="n">
         <v>1700</v>
@@ -11157,7 +11157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H372" t="n">
         <v>1200</v>
@@ -11244,7 +11244,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H375" t="n">
         <v>5700</v>
@@ -11331,7 +11331,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H378" t="n">
         <v>30700</v>
@@ -11360,7 +11360,7 @@
         <v>9.75</v>
       </c>
       <c r="G379" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H379" t="n">
         <v>67200</v>
@@ -11389,7 +11389,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H380" t="n">
         <v>15200</v>
@@ -11476,7 +11476,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H383" t="n">
         <v>800</v>
@@ -11563,7 +11563,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H386" t="n">
         <v>300</v>
@@ -11621,7 +11621,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H388" t="n">
         <v>800</v>
@@ -11650,7 +11650,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H389" t="n">
         <v>4300</v>
@@ -11679,7 +11679,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H390" t="n">
         <v>300</v>
@@ -11795,7 +11795,7 @@
         <v>9.75</v>
       </c>
       <c r="G394" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H394" t="n">
         <v>23100</v>
@@ -11853,7 +11853,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H396" t="n">
         <v>1100</v>
@@ -11882,7 +11882,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H397" t="n">
         <v>69000</v>
@@ -11911,7 +11911,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H398" t="n">
         <v>1100</v>
@@ -11940,7 +11940,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H399" t="n">
         <v>300</v>
@@ -11969,7 +11969,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H400" t="n">
         <v>900</v>
@@ -11998,7 +11998,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H401" t="n">
         <v>7500</v>
@@ -12027,7 +12027,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H402" t="n">
         <v>700</v>
@@ -12056,7 +12056,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H403" t="n">
         <v>2200</v>
@@ -12085,7 +12085,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H404" t="n">
         <v>300</v>
@@ -12114,7 +12114,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H405" t="n">
         <v>100</v>
@@ -12259,7 +12259,7 @@
         <v>9.25</v>
       </c>
       <c r="G410" t="n">
-        <v>7.84940814971924</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H410" t="n">
         <v>13800</v>
@@ -12288,7 +12288,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12317,7 +12317,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H412" t="n">
         <v>13000</v>
@@ -12433,7 +12433,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H416" t="n">
         <v>200</v>
@@ -12462,7 +12462,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.93426752090454</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H418" t="n">
         <v>10000</v>
@@ -12520,7 +12520,7 @@
         <v>9.5</v>
       </c>
       <c r="G419" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H419" t="n">
         <v>16300</v>
@@ -12549,7 +12549,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G420" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H420" t="n">
         <v>12500</v>
@@ -12578,7 +12578,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G421" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H421" t="n">
         <v>10000</v>
@@ -12607,7 +12607,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>9.5</v>
       </c>
       <c r="G423" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H423" t="n">
         <v>15100</v>
@@ -12665,7 +12665,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G424" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H424" t="n">
         <v>8900</v>
@@ -12694,7 +12694,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398387908936</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12752,7 +12752,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G427" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H427" t="n">
         <v>2000</v>
@@ -12781,7 +12781,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H428" t="n">
         <v>800</v>
@@ -12810,7 +12810,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H429" t="n">
         <v>400</v>
@@ -12839,7 +12839,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H432" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G433" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H433" t="n">
         <v>800</v>
@@ -12955,7 +12955,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H434" t="n">
         <v>4300</v>
@@ -12984,7 +12984,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H435" t="n">
         <v>5200</v>
@@ -13013,7 +13013,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H436" t="n">
         <v>400</v>
@@ -13042,7 +13042,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H438" t="n">
         <v>9200</v>
@@ -13100,7 +13100,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H439" t="n">
         <v>1000</v>
@@ -13129,7 +13129,7 @@
         <v>9.75</v>
       </c>
       <c r="G440" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H440" t="n">
         <v>300</v>
@@ -13158,7 +13158,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H441" t="n">
         <v>1700</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H442" t="n">
         <v>1200</v>
@@ -13216,7 +13216,7 @@
         <v>9.75</v>
       </c>
       <c r="G443" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H443" t="n">
         <v>100</v>
@@ -13245,7 +13245,7 @@
         <v>9.75</v>
       </c>
       <c r="G444" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H444" t="n">
         <v>500</v>
@@ -13274,7 +13274,7 @@
         <v>9.75</v>
       </c>
       <c r="G445" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>9.75</v>
       </c>
       <c r="G446" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H447" t="n">
         <v>300</v>
@@ -13361,7 +13361,7 @@
         <v>9.75</v>
       </c>
       <c r="G448" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H448" t="n">
         <v>400</v>
@@ -13390,7 +13390,7 @@
         <v>9.75</v>
       </c>
       <c r="G449" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H449" t="n">
         <v>700</v>
@@ -13419,7 +13419,7 @@
         <v>9.75</v>
       </c>
       <c r="G450" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>9.75</v>
       </c>
       <c r="G451" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>9.75</v>
       </c>
       <c r="G452" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H452" t="n">
         <v>3100</v>
@@ -13506,7 +13506,7 @@
         <v>9.75</v>
       </c>
       <c r="G453" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H453" t="n">
         <v>100</v>
@@ -13535,7 +13535,7 @@
         <v>9.75</v>
       </c>
       <c r="G454" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H454" t="n">
         <v>100000</v>
@@ -13564,7 +13564,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H455" t="n">
         <v>60600</v>
@@ -13593,7 +13593,7 @@
         <v>9.75</v>
       </c>
       <c r="G456" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H456" t="n">
         <v>15500</v>
@@ -13622,7 +13622,7 @@
         <v>9.75</v>
       </c>
       <c r="G457" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H457" t="n">
         <v>50000</v>
@@ -13651,7 +13651,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H458" t="n">
         <v>53200</v>
@@ -13680,7 +13680,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H459" t="n">
         <v>5700</v>
@@ -13709,7 +13709,7 @@
         <v>9.75</v>
       </c>
       <c r="G460" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H460" t="n">
         <v>24400</v>
@@ -13738,7 +13738,7 @@
         <v>9.75</v>
       </c>
       <c r="G461" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>9.75</v>
       </c>
       <c r="G462" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H462" t="n">
         <v>10100</v>
@@ -13796,7 +13796,7 @@
         <v>9.75</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H463" t="n">
         <v>5900</v>
@@ -13825,7 +13825,7 @@
         <v>9.75</v>
       </c>
       <c r="G464" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H464" t="n">
         <v>18200</v>
@@ -13854,7 +13854,7 @@
         <v>9.75</v>
       </c>
       <c r="G465" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>9.75</v>
       </c>
       <c r="G466" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H466" t="n">
         <v>10100</v>
@@ -13912,7 +13912,7 @@
         <v>9.75</v>
       </c>
       <c r="G467" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H467" t="n">
         <v>8000</v>
@@ -13941,7 +13941,7 @@
         <v>9.75</v>
       </c>
       <c r="G468" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H468" t="n">
         <v>5800</v>
@@ -13970,7 +13970,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H469" t="n">
         <v>200</v>
@@ -13999,7 +13999,7 @@
         <v>9.75</v>
       </c>
       <c r="G470" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H470" t="n">
         <v>5600</v>
@@ -14115,7 +14115,7 @@
         <v>9.75</v>
       </c>
       <c r="G474" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H474" t="n">
         <v>68300</v>
@@ -14144,7 +14144,7 @@
         <v>9.75</v>
       </c>
       <c r="G475" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H475" t="n">
         <v>88200</v>
@@ -14173,7 +14173,7 @@
         <v>9.75</v>
       </c>
       <c r="G476" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H476" t="n">
         <v>12000</v>
@@ -14260,7 +14260,7 @@
         <v>9.75</v>
       </c>
       <c r="G479" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H479" t="n">
         <v>36400</v>
@@ -14289,7 +14289,7 @@
         <v>9.75</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H480" t="n">
         <v>5300</v>
@@ -14318,7 +14318,7 @@
         <v>9.75</v>
       </c>
       <c r="G481" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H481" t="n">
         <v>22100</v>
@@ -14347,7 +14347,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G482" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H482" t="n">
         <v>80100</v>
@@ -14376,7 +14376,7 @@
         <v>9.75</v>
       </c>
       <c r="G483" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H483" t="n">
         <v>61200</v>
@@ -14405,7 +14405,7 @@
         <v>9.75</v>
       </c>
       <c r="G484" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H484" t="n">
         <v>17600</v>
@@ -14434,7 +14434,7 @@
         <v>9.75</v>
       </c>
       <c r="G485" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H485" t="n">
         <v>20000</v>
@@ -14463,7 +14463,7 @@
         <v>9.75</v>
       </c>
       <c r="G486" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H486" t="n">
         <v>34700</v>
@@ -14521,7 +14521,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H488" t="n">
         <v>140500</v>
@@ -14550,7 +14550,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H489" t="n">
         <v>134000</v>
@@ -14579,7 +14579,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H490" t="n">
         <v>5800</v>
@@ -14608,7 +14608,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H491" t="n">
         <v>129300</v>
@@ -15043,7 +15043,7 @@
         <v>9.5</v>
       </c>
       <c r="G506" t="n">
-        <v>8.06155490875244</v>
+        <v>8.06155586242676</v>
       </c>
       <c r="H506" t="n">
         <v>100100</v>
@@ -15130,7 +15130,7 @@
         <v>9.75</v>
       </c>
       <c r="G509" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H509" t="n">
         <v>109100</v>
@@ -15333,7 +15333,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G516" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H516" t="n">
         <v>5700</v>
@@ -15362,7 +15362,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G518" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H523" t="n">
         <v>1000</v>
@@ -15565,7 +15565,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H531" t="n">
         <v>200</v>
@@ -16058,7 +16058,7 @@
         <v>9.75</v>
       </c>
       <c r="G541" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H541" t="n">
         <v>1500</v>
@@ -16087,7 +16087,7 @@
         <v>9.75</v>
       </c>
       <c r="G542" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>8.44341945648193</v>
+        <v>8.4434175491333</v>
       </c>
       <c r="H548" t="n">
         <v>21900</v>
@@ -16290,7 +16290,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>8.65556335449219</v>
+        <v>8.65556526184082</v>
       </c>
       <c r="H549" t="n">
         <v>900</v>
@@ -16319,7 +16319,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>8.65556335449219</v>
+        <v>8.65556526184082</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H552" t="n">
         <v>1800</v>
@@ -16406,7 +16406,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912593841553</v>
       </c>
       <c r="H553" t="n">
         <v>1800</v>
@@ -16435,7 +16435,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183950424194</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H554" t="n">
         <v>2900</v>
@@ -16464,7 +16464,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>7.59483337402344</v>
+        <v>7.59483242034912</v>
       </c>
       <c r="H555" t="n">
         <v>5200</v>
@@ -16493,7 +16493,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G556" t="n">
-        <v>7.59483337402344</v>
+        <v>7.59483242034912</v>
       </c>
       <c r="H556" t="n">
         <v>2100</v>
@@ -16522,7 +16522,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29783010482788</v>
+        <v>7.29782867431641</v>
       </c>
       <c r="H557" t="n">
         <v>1100</v>
@@ -16580,7 +16580,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66139030456543</v>
+        <v>6.66139078140259</v>
       </c>
       <c r="H559" t="n">
         <v>9300</v>
@@ -16609,7 +16609,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G560" t="n">
-        <v>6.10981035232544</v>
+        <v>6.10980987548828</v>
       </c>
       <c r="H560" t="n">
         <v>3900</v>
@@ -16638,7 +16638,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>6.10981035232544</v>
+        <v>6.10980987548828</v>
       </c>
       <c r="H561" t="n">
         <v>49300</v>
@@ -16667,7 +16667,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>6.49167394638062</v>
+        <v>6.49167346954346</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16696,7 +16696,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17054080963135</v>
+        <v>7.17054033279419</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16725,7 +16725,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>6.83110666275024</v>
+        <v>6.83110761642456</v>
       </c>
       <c r="H564" t="n">
         <v>8800</v>
@@ -16754,7 +16754,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867864608765</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H565" t="n">
         <v>3800</v>
@@ -16783,7 +16783,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867864608765</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H566" t="n">
         <v>3000</v>
@@ -16812,7 +16812,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867864608765</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>6.68633890151978</v>
+        <v>6.68633937835693</v>
       </c>
       <c r="H570" t="n">
         <v>900</v>
@@ -16928,7 +16928,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G571" t="n">
-        <v>6.94854879379272</v>
+        <v>6.94854831695557</v>
       </c>
       <c r="H571" t="n">
         <v>1400</v>
@@ -16986,7 +16986,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.46783113479614</v>
+        <v>6.4678316116333</v>
       </c>
       <c r="H573" t="n">
         <v>4700</v>
@@ -17044,7 +17044,7 @@
         <v>8.25</v>
       </c>
       <c r="G575" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H575" t="n">
         <v>6200</v>
@@ -17102,7 +17102,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>7.25445938110352</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H577" t="n">
         <v>1400</v>
@@ -17131,7 +17131,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25445938110352</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G579" t="n">
-        <v>7.25445938110352</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>7.25445938110352</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H582" t="n">
         <v>100</v>
@@ -17276,7 +17276,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G583" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H583" t="n">
         <v>4700</v>
@@ -17305,7 +17305,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>7.6914758682251</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H584" t="n">
         <v>3700</v>
@@ -17334,7 +17334,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G585" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H585" t="n">
         <v>24200</v>
@@ -17363,7 +17363,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>7.6914758682251</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H586" t="n">
         <v>1100</v>
@@ -17392,7 +17392,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G587" t="n">
-        <v>7.6914758682251</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G588" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H588" t="n">
         <v>1000</v>
@@ -17450,7 +17450,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H589" t="n">
         <v>1000</v>
@@ -17479,7 +17479,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H590" t="n">
         <v>600</v>
@@ -17508,7 +17508,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517608642578</v>
       </c>
       <c r="H591" t="n">
         <v>19400</v>
@@ -17537,7 +17537,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H592" t="n">
         <v>300</v>
@@ -17566,7 +17566,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G596" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666831970215</v>
       </c>
       <c r="H596" t="n">
         <v>400</v>
@@ -17682,7 +17682,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H597" t="n">
         <v>2000</v>
@@ -17711,7 +17711,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H598" t="n">
         <v>3300</v>
@@ -17740,7 +17740,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H603" t="n">
         <v>300</v>
@@ -17885,7 +17885,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517608642578</v>
       </c>
       <c r="H604" t="n">
         <v>700</v>
@@ -17914,7 +17914,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G605" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666831970215</v>
       </c>
       <c r="H605" t="n">
         <v>600</v>
@@ -17972,7 +17972,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666831970215</v>
       </c>
       <c r="H607" t="n">
         <v>300</v>
@@ -18030,7 +18030,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G609" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H609" t="n">
         <v>2600</v>
@@ -18059,7 +18059,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G610" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H610" t="n">
         <v>500</v>
@@ -18088,7 +18088,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H611" t="n">
         <v>800</v>
@@ -18117,7 +18117,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H612" t="n">
         <v>100</v>
@@ -18175,7 +18175,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H614" t="n">
         <v>600</v>
@@ -18204,7 +18204,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517608642578</v>
       </c>
       <c r="H615" t="n">
         <v>1200</v>
@@ -18233,7 +18233,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H616" t="n">
         <v>200</v>
@@ -18291,7 +18291,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>7.6914758682251</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H618" t="n">
         <v>1600</v>
@@ -18378,7 +18378,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H621" t="n">
         <v>100</v>
@@ -18407,7 +18407,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H622" t="n">
         <v>100</v>
@@ -18465,7 +18465,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G624" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666831970215</v>
       </c>
       <c r="H624" t="n">
         <v>3600</v>
@@ -18494,7 +18494,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H625" t="n">
         <v>1000</v>
@@ -18523,7 +18523,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G626" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666831970215</v>
       </c>
       <c r="H626" t="n">
         <v>6200</v>
@@ -18552,7 +18552,7 @@
         <v>8.25</v>
       </c>
       <c r="G627" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H627" t="n">
         <v>2600</v>
@@ -18697,7 +18697,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G632" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H632" t="n">
         <v>900</v>
@@ -18755,7 +18755,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G634" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H634" t="n">
         <v>300</v>
@@ -18784,7 +18784,7 @@
         <v>8.25</v>
       </c>
       <c r="G635" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H635" t="n">
         <v>3900</v>
@@ -18813,7 +18813,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G636" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H636" t="n">
         <v>2000</v>
@@ -18842,7 +18842,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>7.25445938110352</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H637" t="n">
         <v>5700</v>
@@ -18871,7 +18871,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>7.25445938110352</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H638" t="n">
         <v>600</v>
@@ -19016,7 +19016,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>7.25445938110352</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H643" t="n">
         <v>11600</v>
@@ -19103,7 +19103,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G646" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H646" t="n">
         <v>2300</v>
@@ -19132,7 +19132,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G647" t="n">
-        <v>7.12335395812988</v>
+        <v>7.12335443496704</v>
       </c>
       <c r="H647" t="n">
         <v>5600</v>
@@ -19161,7 +19161,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G648" t="n">
-        <v>7.12335395812988</v>
+        <v>7.12335443496704</v>
       </c>
       <c r="H648" t="n">
         <v>2500</v>
@@ -19190,7 +19190,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G649" t="n">
-        <v>7.12335395812988</v>
+        <v>7.12335443496704</v>
       </c>
       <c r="H649" t="n">
         <v>1700</v>
@@ -19219,7 +19219,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G650" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H650" t="n">
         <v>800</v>
@@ -19248,7 +19248,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G651" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H651" t="n">
         <v>400</v>
@@ -19277,7 +19277,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484666824341</v>
+        <v>6.90484714508057</v>
       </c>
       <c r="H652" t="n">
         <v>2400</v>
@@ -19364,7 +19364,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G655" t="n">
-        <v>7.0796537399292</v>
+        <v>7.07965326309204</v>
       </c>
       <c r="H655" t="n">
         <v>1800</v>
@@ -19422,7 +19422,7 @@
         <v>8.25</v>
       </c>
       <c r="G657" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H657" t="n">
         <v>8600</v>
@@ -19451,7 +19451,7 @@
         <v>8.25</v>
       </c>
       <c r="G658" t="n">
-        <v>7.21075820922852</v>
+        <v>7.21075773239136</v>
       </c>
       <c r="H658" t="n">
         <v>1100</v>
@@ -19509,7 +19509,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>7.25445938110352</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H660" t="n">
         <v>8800</v>
@@ -19567,7 +19567,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H662" t="n">
         <v>7300</v>
@@ -19596,7 +19596,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G663" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H663" t="n">
         <v>11900</v>
@@ -19625,7 +19625,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G664" t="n">
-        <v>7.25445938110352</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H664" t="n">
         <v>3400</v>
@@ -19654,7 +19654,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556337356567</v>
       </c>
       <c r="H665" t="n">
         <v>18900</v>
@@ -19712,7 +19712,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>7.6914758682251</v>
+        <v>7.69147491455078</v>
       </c>
       <c r="H667" t="n">
         <v>5600</v>
@@ -19741,7 +19741,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G668" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H669" t="n">
         <v>6200</v>
@@ -19799,7 +19799,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H670" t="n">
         <v>2100</v>
@@ -19828,7 +19828,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G671" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H671" t="n">
         <v>1900</v>
@@ -19915,7 +19915,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H674" t="n">
         <v>2900</v>
@@ -19944,7 +19944,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H675" t="n">
         <v>1300</v>
@@ -19973,7 +19973,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H676" t="n">
         <v>2300</v>
@@ -20002,7 +20002,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.86628150939941</v>
+        <v>7.8662805557251</v>
       </c>
       <c r="H677" t="n">
         <v>1800</v>
@@ -20031,7 +20031,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H678" t="n">
         <v>1500</v>
@@ -20060,7 +20060,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G679" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H679" t="n">
         <v>700</v>
@@ -20089,7 +20089,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G680" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20147,7 +20147,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H682" t="n">
         <v>1900</v>
@@ -20176,7 +20176,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G683" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666831970215</v>
       </c>
       <c r="H683" t="n">
         <v>2100</v>
@@ -20205,7 +20205,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738597869873</v>
       </c>
       <c r="H684" t="n">
         <v>3100</v>
@@ -20234,7 +20234,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G685" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H685" t="n">
         <v>600</v>
@@ -20263,7 +20263,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G686" t="n">
-        <v>7.77887868881226</v>
+        <v>7.77887773513794</v>
       </c>
       <c r="H686" t="n">
         <v>500</v>
@@ -20292,7 +20292,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777374267578</v>
       </c>
       <c r="H687" t="n">
         <v>1500</v>
@@ -20350,7 +20350,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G689" t="n">
-        <v>7.51666975021362</v>
+        <v>7.51666831970215</v>
       </c>
       <c r="H689" t="n">
         <v>12600</v>
@@ -20437,7 +20437,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G692" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H692" t="n">
         <v>12900</v>
@@ -20466,7 +20466,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G693" t="n">
-        <v>7.90998315811157</v>
+        <v>7.90998268127441</v>
       </c>
       <c r="H693" t="n">
         <v>9100</v>
@@ -20524,7 +20524,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738597869873</v>
       </c>
       <c r="H695" t="n">
         <v>5300</v>
@@ -20640,7 +20640,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H699" t="n">
         <v>6500</v>
@@ -20756,7 +20756,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H703" t="n">
         <v>1400</v>
@@ -20785,7 +20785,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H704" t="n">
         <v>300</v>
@@ -20901,7 +20901,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G708" t="n">
-        <v>8.12276363372803</v>
+        <v>8.12276458740234</v>
       </c>
       <c r="H708" t="n">
         <v>1500</v>
@@ -20959,7 +20959,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H710" t="n">
         <v>1600</v>
@@ -21017,7 +21017,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G712" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H712" t="n">
         <v>9300</v>
@@ -21046,7 +21046,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G713" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H713" t="n">
         <v>800</v>
@@ -21075,7 +21075,7 @@
         <v>9</v>
       </c>
       <c r="G714" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H714" t="n">
         <v>2100</v>
@@ -21104,7 +21104,7 @@
         <v>9</v>
       </c>
       <c r="G715" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H715" t="n">
         <v>1600</v>
@@ -21133,7 +21133,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G716" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H716" t="n">
         <v>1200</v>
@@ -21191,7 +21191,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H718" t="n">
         <v>2600</v>
@@ -21220,7 +21220,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H719" t="n">
         <v>900</v>
@@ -21278,7 +21278,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H721" t="n">
         <v>6800</v>
@@ -21336,7 +21336,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H723" t="n">
         <v>26400</v>
@@ -21365,7 +21365,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H724" t="n">
         <v>21400</v>
@@ -21394,7 +21394,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H725" t="n">
         <v>70900</v>
@@ -21423,7 +21423,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H726" t="n">
         <v>38600</v>
@@ -21452,7 +21452,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H727" t="n">
         <v>100</v>
@@ -21481,7 +21481,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H728" t="n">
         <v>4500</v>
@@ -21510,7 +21510,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H729" t="n">
         <v>5100</v>
@@ -21539,7 +21539,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H730" t="n">
         <v>1200</v>
@@ -21568,7 +21568,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H731" t="n">
         <v>300</v>
@@ -21597,7 +21597,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H732" t="n">
         <v>2600</v>
@@ -21626,7 +21626,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G733" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H733" t="n">
         <v>6400</v>
@@ -21655,7 +21655,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H734" t="n">
         <v>12300</v>
@@ -21684,7 +21684,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H735" t="n">
         <v>6900</v>
@@ -21713,7 +21713,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H736" t="n">
         <v>3000</v>
@@ -21742,7 +21742,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G737" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G738" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H738" t="n">
         <v>100</v>
@@ -21800,7 +21800,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H739" t="n">
         <v>18700</v>
@@ -21829,7 +21829,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G740" t="n">
-        <v>8.12276363372803</v>
+        <v>8.12276458740234</v>
       </c>
       <c r="H740" t="n">
         <v>3700</v>
@@ -21858,7 +21858,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G741" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H741" t="n">
         <v>12400</v>
@@ -21887,7 +21887,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H742" t="n">
         <v>7300</v>
@@ -21945,7 +21945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G744" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H744" t="n">
         <v>7400</v>
@@ -22003,7 +22003,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H746" t="n">
         <v>6800</v>
@@ -22061,7 +22061,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H748" t="n">
         <v>700</v>
@@ -22090,7 +22090,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G749" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H749" t="n">
         <v>2600</v>
@@ -22119,7 +22119,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H750" t="n">
         <v>5400</v>
@@ -22148,7 +22148,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G751" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H751" t="n">
         <v>2100</v>
@@ -22177,7 +22177,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H752" t="n">
         <v>7900</v>
@@ -22206,7 +22206,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H753" t="n">
         <v>33700</v>
@@ -22235,7 +22235,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G754" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H754" t="n">
         <v>34600</v>
@@ -22264,7 +22264,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H755" t="n">
         <v>33100</v>
@@ -22670,7 +22670,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H769" t="n">
         <v>1400</v>
@@ -22699,7 +22699,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H771" t="n">
         <v>300</v>
@@ -22757,7 +22757,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G772" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H772" t="n">
         <v>2900</v>
@@ -22815,7 +22815,7 @@
         <v>10</v>
       </c>
       <c r="G774" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H774" t="n">
         <v>23000</v>
@@ -22844,7 +22844,7 @@
         <v>10</v>
       </c>
       <c r="G775" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H775" t="n">
         <v>13400</v>
@@ -22902,7 +22902,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G777" t="n">
-        <v>9.51395511627197</v>
+        <v>9.51395606994629</v>
       </c>
       <c r="H777" t="n">
         <v>16100</v>
@@ -22960,7 +22960,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>9.96272754669189</v>
+        <v>9.96272659301758</v>
       </c>
       <c r="H779" t="n">
         <v>29900</v>
@@ -22989,7 +22989,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>9.60370922088623</v>
+        <v>9.60371017456055</v>
       </c>
       <c r="H780" t="n">
         <v>22300</v>
@@ -23047,7 +23047,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>9.51395511627197</v>
+        <v>9.51395606994629</v>
       </c>
       <c r="H782" t="n">
         <v>15800</v>
@@ -23076,7 +23076,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>9.51395511627197</v>
+        <v>9.51395606994629</v>
       </c>
       <c r="H783" t="n">
         <v>10600</v>
@@ -23105,7 +23105,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>9.6934642791748</v>
+        <v>9.69346332550049</v>
       </c>
       <c r="H784" t="n">
         <v>22700</v>
@@ -23134,7 +23134,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G785" t="n">
-        <v>9.6934642791748</v>
+        <v>9.69346332550049</v>
       </c>
       <c r="H785" t="n">
         <v>6500</v>
@@ -23250,7 +23250,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H789" t="n">
         <v>5100</v>
@@ -23308,7 +23308,7 @@
         <v>10</v>
       </c>
       <c r="G791" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H791" t="n">
         <v>7300</v>
@@ -23366,7 +23366,7 @@
         <v>10</v>
       </c>
       <c r="G793" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H793" t="n">
         <v>7200</v>
@@ -23453,7 +23453,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H796" t="n">
         <v>1300</v>
@@ -23540,7 +23540,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H799" t="n">
         <v>2300</v>
@@ -23772,7 +23772,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H807" t="n">
         <v>9500</v>
@@ -24120,7 +24120,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H819" t="n">
         <v>1100</v>
@@ -24352,7 +24352,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H827" t="n">
         <v>49700</v>
@@ -24381,7 +24381,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H828" t="n">
         <v>9700</v>
@@ -24410,7 +24410,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H829" t="n">
         <v>12300</v>
@@ -24439,7 +24439,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H830" t="n">
         <v>1900</v>
@@ -24497,7 +24497,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H832" t="n">
         <v>1700</v>
@@ -24555,7 +24555,7 @@
         <v>10</v>
       </c>
       <c r="G834" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H834" t="n">
         <v>5900</v>
@@ -24729,7 +24729,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G840" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H840" t="n">
         <v>500</v>
@@ -24932,7 +24932,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H847" t="n">
         <v>1100</v>
@@ -24990,7 +24990,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H849" t="n">
         <v>3700</v>
@@ -25019,7 +25019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H850" t="n">
         <v>1700</v>
@@ -25193,7 +25193,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H856" t="n">
         <v>4000</v>
@@ -25251,7 +25251,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H858" t="n">
         <v>3300</v>
@@ -25483,7 +25483,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H866" t="n">
         <v>200</v>
@@ -25570,7 +25570,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H869" t="n">
         <v>13500</v>
@@ -25657,7 +25657,7 @@
         <v>10</v>
       </c>
       <c r="G872" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H872" t="n">
         <v>1500</v>
@@ -25686,7 +25686,7 @@
         <v>10</v>
       </c>
       <c r="G873" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H873" t="n">
         <v>3200</v>
@@ -25744,7 +25744,7 @@
         <v>10</v>
       </c>
       <c r="G875" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H875" t="n">
         <v>7800</v>
@@ -25773,7 +25773,7 @@
         <v>10</v>
       </c>
       <c r="G876" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25831,7 +25831,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H878" t="n">
         <v>23100</v>
@@ -25918,7 +25918,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H881" t="n">
         <v>21200</v>
@@ -26092,7 +26092,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>9.33444690704346</v>
+        <v>9.33444595336914</v>
       </c>
       <c r="H887" t="n">
         <v>10800</v>
@@ -26150,7 +26150,7 @@
         <v>10</v>
       </c>
       <c r="G889" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H889" t="n">
         <v>15100</v>
@@ -26179,7 +26179,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H890" t="n">
         <v>2500</v>
@@ -26208,7 +26208,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H891" t="n">
         <v>5500</v>
@@ -26237,7 +26237,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H892" t="n">
         <v>1200</v>
@@ -26295,7 +26295,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H894" t="n">
         <v>500</v>
@@ -26614,7 +26614,7 @@
         <v>9</v>
       </c>
       <c r="G905" t="n">
-        <v>8.0778865814209</v>
+        <v>8.07788753509521</v>
       </c>
       <c r="H905" t="n">
         <v>2300</v>
@@ -26643,7 +26643,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>8.12276363372803</v>
+        <v>8.12276458740234</v>
       </c>
       <c r="H906" t="n">
         <v>5400</v>
@@ -26672,7 +26672,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G907" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H907" t="n">
         <v>1400</v>
@@ -26759,7 +26759,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G910" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H910" t="n">
         <v>1300</v>
@@ -26788,7 +26788,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.3598518371582</v>
+        <v>7.35985231399536</v>
       </c>
       <c r="H911" t="n">
         <v>12900</v>
@@ -26817,7 +26817,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423805236816</v>
+        <v>7.58423709869385</v>
       </c>
       <c r="H912" t="n">
         <v>2900</v>
@@ -26846,7 +26846,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423805236816</v>
+        <v>7.58423709869385</v>
       </c>
       <c r="H913" t="n">
         <v>5400</v>
@@ -26875,7 +26875,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G914" t="n">
-        <v>7.98813247680664</v>
+        <v>7.98813199996948</v>
       </c>
       <c r="H914" t="n">
         <v>3400</v>
@@ -26962,7 +26962,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G917" t="n">
-        <v>8.16764068603516</v>
+        <v>8.16764163970947</v>
       </c>
       <c r="H917" t="n">
         <v>2900</v>
@@ -27107,7 +27107,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153606414795</v>
+        <v>8.57153511047363</v>
       </c>
       <c r="H922" t="n">
         <v>2700</v>
@@ -27165,7 +27165,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G924" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H924" t="n">
         <v>500</v>
@@ -27194,7 +27194,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -27368,7 +27368,7 @@
         <v>10</v>
       </c>
       <c r="G931" t="n">
-        <v>8.97542953491211</v>
+        <v>8.97543048858643</v>
       </c>
       <c r="H931" t="n">
         <v>600</v>
@@ -27397,7 +27397,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231513977051</v>
+        <v>8.65231418609619</v>
       </c>
       <c r="H932" t="n">
         <v>500</v>
@@ -27455,7 +27455,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.54460906982422</v>
+        <v>8.54461002349854</v>
       </c>
       <c r="H934" t="n">
         <v>26000</v>
@@ -27484,7 +27484,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27513,7 +27513,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821620941162</v>
+        <v>8.68821716308594</v>
       </c>
       <c r="H936" t="n">
         <v>15100</v>
@@ -27745,7 +27745,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G944" t="n">
-        <v>8.83182334899902</v>
+        <v>8.83182239532471</v>
       </c>
       <c r="H944" t="n">
         <v>4800</v>
@@ -27774,7 +27774,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G945" t="n">
-        <v>9.0620584487915</v>
+        <v>9.06205749511719</v>
       </c>
       <c r="H945" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G946" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H946" t="n">
         <v>1200</v>
@@ -27832,7 +27832,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G947" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H947" t="n">
         <v>4900</v>
@@ -28151,7 +28151,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>9.0620584487915</v>
+        <v>9.06205749511719</v>
       </c>
       <c r="H958" t="n">
         <v>1400</v>
@@ -28180,7 +28180,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G959" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H959" t="n">
         <v>1600</v>
@@ -28296,7 +28296,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G963" t="n">
-        <v>9.04363822937012</v>
+        <v>9.04363918304443</v>
       </c>
       <c r="H963" t="n">
         <v>1100</v>
@@ -28325,7 +28325,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G964" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H964" t="n">
         <v>7900</v>
@@ -28412,7 +28412,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G967" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H967" t="n">
         <v>6400</v>
@@ -28499,7 +28499,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>8.78577613830566</v>
+        <v>8.78577518463135</v>
       </c>
       <c r="H970" t="n">
         <v>5800</v>
@@ -28615,7 +28615,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G974" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H974" t="n">
         <v>500</v>
@@ -28644,7 +28644,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H975" t="n">
         <v>1900</v>
@@ -28673,7 +28673,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G976" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H976" t="n">
         <v>5400</v>
@@ -28818,7 +28818,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G981" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H981" t="n">
         <v>200</v>
@@ -28847,7 +28847,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G982" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H982" t="n">
         <v>2200</v>
@@ -29050,7 +29050,7 @@
         <v>9</v>
       </c>
       <c r="G989" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H989" t="n">
         <v>2200</v>
@@ -29108,7 +29108,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>8.14111709594727</v>
+        <v>8.14111614227295</v>
       </c>
       <c r="H991" t="n">
         <v>1100</v>
@@ -29166,7 +29166,7 @@
         <v>9</v>
       </c>
       <c r="G993" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H993" t="n">
         <v>5000</v>
@@ -29253,7 +29253,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G996" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H996" t="n">
         <v>800</v>
@@ -29427,7 +29427,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1002" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1002" t="n">
         <v>2700</v>
@@ -29572,7 +29572,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423793792725</v>
+        <v>8.45423603057861</v>
       </c>
       <c r="H1007" t="n">
         <v>100</v>
@@ -29717,7 +29717,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1012" t="n">
-        <v>8.17795562744141</v>
+        <v>8.17795467376709</v>
       </c>
       <c r="H1012" t="n">
         <v>200</v>
@@ -29949,7 +29949,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1020" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1020" t="n">
         <v>1400</v>
@@ -29978,7 +29978,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1021" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -30007,7 +30007,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1022" t="n">
         <v>100</v>
@@ -30036,7 +30036,7 @@
         <v>9</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1023" t="n">
         <v>100</v>
@@ -30094,7 +30094,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1025" t="n">
         <v>200</v>
@@ -30152,7 +30152,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1027" t="n">
         <v>100</v>
@@ -30181,7 +30181,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1028" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1028" t="n">
         <v>0</v>
@@ -30210,7 +30210,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -30268,7 +30268,7 @@
         <v>9</v>
       </c>
       <c r="G1031" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1031" t="n">
         <v>1000</v>
@@ -30297,7 +30297,7 @@
         <v>9</v>
       </c>
       <c r="G1032" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1032" t="n">
         <v>0</v>
@@ -30326,7 +30326,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G1033" t="n">
-        <v>7.97534799575806</v>
+        <v>7.9753475189209</v>
       </c>
       <c r="H1033" t="n">
         <v>1200</v>
@@ -30384,7 +30384,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.8832540512085</v>
+        <v>7.88325452804565</v>
       </c>
       <c r="H1035" t="n">
         <v>600</v>
@@ -30413,7 +30413,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.01218509674072</v>
+        <v>8.01218414306641</v>
       </c>
       <c r="H1036" t="n">
         <v>300</v>
@@ -30442,7 +30442,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.01218509674072</v>
+        <v>8.01218414306641</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -30587,7 +30587,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.14111709594727</v>
+        <v>8.14111614227295</v>
       </c>
       <c r="H1042" t="n">
         <v>7000</v>
@@ -30616,7 +30616,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1043" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1043" t="n">
         <v>2400</v>
@@ -30645,7 +30645,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1044" t="n">
         <v>3800</v>
@@ -30703,7 +30703,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1046" t="n">
         <v>900</v>
@@ -30732,7 +30732,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1047" t="n">
         <v>500</v>
@@ -30761,7 +30761,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -30790,7 +30790,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1049" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1049" t="n">
         <v>1100</v>
@@ -30964,7 +30964,7 @@
         <v>9</v>
       </c>
       <c r="G1055" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1055" t="n">
         <v>3400</v>
@@ -31051,7 +31051,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1058" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1058" t="n">
         <v>1000</v>
@@ -31080,7 +31080,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1059" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1059" t="n">
         <v>400</v>
@@ -31515,7 +31515,7 @@
         <v>9</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1074" t="n">
         <v>300</v>
@@ -31573,7 +31573,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.17795562744141</v>
+        <v>8.17795467376709</v>
       </c>
       <c r="H1076" t="n">
         <v>14700</v>
@@ -31834,7 +31834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.85945129394531</v>
+        <v>8.859450340271</v>
       </c>
       <c r="H1085" t="n">
         <v>2600</v>
@@ -31863,7 +31863,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1086" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1086" t="n">
         <v>200</v>
@@ -32008,7 +32008,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1091" t="n">
         <v>1500</v>
@@ -32182,7 +32182,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G1097" t="n">
-        <v>8.63842582702637</v>
+        <v>8.63842487335205</v>
       </c>
       <c r="H1097" t="n">
         <v>3600</v>
@@ -32211,7 +32211,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1098" t="n">
         <v>1100</v>
@@ -32356,7 +32356,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1103" t="n">
         <v>11700</v>
@@ -32530,7 +32530,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1109" t="n">
         <v>2500</v>
@@ -32965,7 +32965,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1124" t="n">
         <v>7600</v>
@@ -33139,7 +33139,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1130" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1130" t="n">
         <v>100</v>
@@ -33168,7 +33168,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1131" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1131" t="n">
         <v>0</v>
@@ -33197,7 +33197,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1132" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1132" t="n">
         <v>1500</v>
@@ -33226,7 +33226,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1133" t="n">
         <v>700</v>
@@ -33255,7 +33255,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1134" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1134" t="n">
         <v>0</v>
@@ -33342,7 +33342,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1137" t="n">
-        <v>8.73051834106445</v>
+        <v>8.73051929473877</v>
       </c>
       <c r="H1137" t="n">
         <v>200</v>
@@ -33429,7 +33429,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1140" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1140" t="n">
         <v>1000</v>
@@ -33574,7 +33574,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1145" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1145" t="n">
         <v>2300</v>
@@ -33748,7 +33748,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1151" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1151" t="n">
         <v>2000</v>
@@ -33777,7 +33777,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1152" t="n">
-        <v>8.93312549591064</v>
+        <v>8.93312644958496</v>
       </c>
       <c r="H1152" t="n">
         <v>0</v>
@@ -33835,7 +33835,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.00680065155029</v>
+        <v>9.00680160522461</v>
       </c>
       <c r="H1154" t="n">
         <v>200</v>
@@ -34154,7 +34154,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1165" t="n">
-        <v>8.58316898345947</v>
+        <v>8.58316802978516</v>
       </c>
       <c r="H1165" t="n">
         <v>100</v>
@@ -34183,7 +34183,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1166" t="n">
         <v>100</v>
@@ -34212,7 +34212,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1167" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1168" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>
@@ -34270,7 +34270,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1169" t="n">
         <v>0</v>
@@ -34299,7 +34299,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1170" t="n">
         <v>100</v>
@@ -34328,7 +34328,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1171" t="n">
         <v>0</v>
@@ -34357,7 +34357,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1172" t="n">
-        <v>8.7121000289917</v>
+        <v>8.71210098266602</v>
       </c>
       <c r="H1172" t="n">
         <v>500</v>
@@ -34531,7 +34531,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1178" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1178" t="n">
         <v>100</v>
@@ -34560,7 +34560,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1179" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1179" t="n">
         <v>0</v>
@@ -34589,7 +34589,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1180" t="n">
-        <v>8.58316898345947</v>
+        <v>8.58316802978516</v>
       </c>
       <c r="H1180" t="n">
         <v>3700</v>
@@ -34647,7 +34647,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1182" t="n">
-        <v>8.49107456207275</v>
+        <v>8.49107551574707</v>
       </c>
       <c r="H1182" t="n">
         <v>1200</v>
@@ -34879,7 +34879,7 @@
         <v>9</v>
       </c>
       <c r="G1190" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1190" t="n">
         <v>2400</v>
@@ -34908,7 +34908,7 @@
         <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1191" t="n">
         <v>0</v>
@@ -34937,7 +34937,7 @@
         <v>9</v>
       </c>
       <c r="G1192" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1192" t="n">
         <v>800</v>
@@ -34966,7 +34966,7 @@
         <v>9</v>
       </c>
       <c r="G1193" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1193" t="n">
         <v>1600</v>
@@ -34995,7 +34995,7 @@
         <v>9</v>
       </c>
       <c r="G1194" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1194" t="n">
         <v>11800</v>
@@ -35024,7 +35024,7 @@
         <v>9</v>
       </c>
       <c r="G1195" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1195" t="n">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1197" t="n">
-        <v>8.50949382781982</v>
+        <v>8.50949287414551</v>
       </c>
       <c r="H1197" t="n">
         <v>300</v>
@@ -35198,7 +35198,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.15953540802002</v>
+        <v>8.15953636169434</v>
       </c>
       <c r="H1201" t="n">
         <v>900</v>
@@ -35227,7 +35227,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.15953540802002</v>
+        <v>8.15953636169434</v>
       </c>
       <c r="H1202" t="n">
         <v>300</v>
@@ -35285,7 +35285,7 @@
         <v>9</v>
       </c>
       <c r="G1204" t="n">
-        <v>8.28846740722656</v>
+        <v>8.28846836090088</v>
       </c>
       <c r="H1204" t="n">
         <v>500</v>
@@ -35372,7 +35372,7 @@
         <v>8.5</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.8279972076416</v>
+        <v>7.82799673080444</v>
       </c>
       <c r="H1207" t="n">
         <v>10600</v>
@@ -35401,7 +35401,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1208" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1208" t="n">
         <v>1300</v>
@@ -35430,7 +35430,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590230941772</v>
+        <v>7.73590326309204</v>
       </c>
       <c r="H1209" t="n">
         <v>2000</v>
@@ -35459,7 +35459,7 @@
         <v>8.5</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.8279972076416</v>
+        <v>7.82799673080444</v>
       </c>
       <c r="H1210" t="n">
         <v>3600</v>
@@ -35488,7 +35488,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.80957746505737</v>
+        <v>7.80957794189453</v>
       </c>
       <c r="H1211" t="n">
         <v>1400</v>
@@ -35546,7 +35546,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.60697174072266</v>
+        <v>7.6069712638855</v>
       </c>
       <c r="H1213" t="n">
         <v>500</v>
@@ -35575,7 +35575,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1214" t="n">
-        <v>7.49645900726318</v>
+        <v>7.49645853042603</v>
       </c>
       <c r="H1214" t="n">
         <v>3700</v>
@@ -35662,7 +35662,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1217" t="n">
-        <v>7.25701379776001</v>
+        <v>7.25701427459717</v>
       </c>
       <c r="H1217" t="n">
         <v>4400</v>
@@ -35691,7 +35691,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1218" t="n">
-        <v>7.22017669677734</v>
+        <v>7.22017621994019</v>
       </c>
       <c r="H1218" t="n">
         <v>19000</v>
@@ -35749,7 +35749,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>7.18333864212036</v>
+        <v>7.1833381652832</v>
       </c>
       <c r="H1220" t="n">
         <v>200</v>
@@ -35836,7 +35836,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.25701379776001</v>
+        <v>7.25701427459717</v>
       </c>
       <c r="H1223" t="n">
         <v>5900</v>
@@ -35894,7 +35894,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.18333864212036</v>
+        <v>7.1833381652832</v>
       </c>
       <c r="H1225" t="n">
         <v>2600</v>
@@ -36039,7 +36039,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>7.60697174072266</v>
+        <v>7.6069712638855</v>
       </c>
       <c r="H1230" t="n">
         <v>9400</v>
@@ -36097,7 +36097,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590230941772</v>
+        <v>7.73590326309204</v>
       </c>
       <c r="H1232" t="n">
         <v>200</v>
@@ -36242,7 +36242,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1237" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1237" t="n">
         <v>7900</v>
@@ -36271,7 +36271,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1238" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1238" t="n">
         <v>600</v>
@@ -36329,7 +36329,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1240" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1240" t="n">
         <v>1300</v>
@@ -36416,7 +36416,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1243" t="n">
         <v>1400</v>
@@ -36474,7 +36474,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1245" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1245" t="n">
         <v>1600</v>
@@ -36590,7 +36590,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1249" t="n">
-        <v>7.42175912857056</v>
+        <v>7.4217586517334</v>
       </c>
       <c r="H1249" t="n">
         <v>300</v>
@@ -36648,7 +36648,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1251" t="n">
-        <v>7.59347057342529</v>
+        <v>7.59347009658813</v>
       </c>
       <c r="H1251" t="n">
         <v>200</v>
@@ -36706,7 +36706,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G1253" t="n">
-        <v>7.19280958175659</v>
+        <v>7.19281005859375</v>
       </c>
       <c r="H1253" t="n">
         <v>1200</v>
@@ -36735,7 +36735,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1254" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1254" t="n">
         <v>1200</v>
@@ -36764,7 +36764,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1255" t="n">
         <v>1300</v>
@@ -36793,7 +36793,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1256" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1256" t="n">
         <v>900</v>
@@ -36880,7 +36880,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1259" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1259" t="n">
         <v>3700</v>
@@ -36996,7 +36996,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G1263" t="n">
-        <v>8.22307968139648</v>
+        <v>8.22307872772217</v>
       </c>
       <c r="H1263" t="n">
         <v>100</v>
@@ -37112,7 +37112,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1267" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1267" t="n">
         <v>2800</v>
@@ -37141,7 +37141,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1268" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1268" t="n">
         <v>1400</v>
@@ -37199,7 +37199,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1270" t="n">
-        <v>7.9178147315979</v>
+        <v>7.91781520843506</v>
       </c>
       <c r="H1270" t="n">
         <v>600</v>
@@ -37228,7 +37228,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1271" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1271" t="n">
         <v>400</v>
@@ -37518,7 +37518,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1281" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1281" t="n">
         <v>2100</v>
@@ -37547,7 +37547,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1282" t="n">
-        <v>7.30728435516357</v>
+        <v>7.30728387832642</v>
       </c>
       <c r="H1282" t="n">
         <v>0</v>
@@ -37634,7 +37634,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1285" t="n">
-        <v>7.61254930496216</v>
+        <v>7.61254978179932</v>
       </c>
       <c r="H1285" t="n">
         <v>300</v>
@@ -37663,7 +37663,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1286" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1286" t="n">
         <v>200</v>
@@ -37750,7 +37750,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1289" t="n">
-        <v>7.76518249511719</v>
+        <v>7.76518201828003</v>
       </c>
       <c r="H1289" t="n">
         <v>700</v>
@@ -37779,7 +37779,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1290" t="n">
-        <v>7.80334043502808</v>
+        <v>7.80334091186523</v>
       </c>
       <c r="H1290" t="n">
         <v>100</v>
@@ -37837,7 +37837,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1292" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1292" t="n">
         <v>2700</v>
@@ -37866,7 +37866,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G1293" t="n">
-        <v>7.86057758331299</v>
+        <v>7.86057710647583</v>
       </c>
       <c r="H1293" t="n">
         <v>0</v>
@@ -37895,7 +37895,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1294" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1294" t="n">
         <v>800</v>
@@ -37924,7 +37924,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1295" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1295" t="n">
         <v>0</v>
@@ -38069,7 +38069,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1300" t="n">
-        <v>7.82241868972778</v>
+        <v>7.82241916656494</v>
       </c>
       <c r="H1300" t="n">
         <v>1700</v>
@@ -38098,7 +38098,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1301" t="n">
         <v>1200</v>
@@ -38185,7 +38185,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1304" t="n">
-        <v>7.66978645324707</v>
+        <v>7.66978693008423</v>
       </c>
       <c r="H1304" t="n">
         <v>700</v>
@@ -38272,7 +38272,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.49807500839233</v>
+        <v>7.49807548522949</v>
       </c>
       <c r="H1307" t="n">
         <v>1000</v>
@@ -38475,7 +38475,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.25004720687866</v>
+        <v>7.2500467300415</v>
       </c>
       <c r="H1314" t="n">
         <v>200</v>
@@ -38678,7 +38678,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1321" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1321" t="n">
         <v>3700</v>
@@ -38881,7 +38881,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1328" t="n">
         <v>2100</v>
@@ -38968,7 +38968,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1331" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1331" t="n">
         <v>3300</v>
@@ -39084,7 +39084,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1335" t="n">
-        <v>6.18161916732788</v>
+        <v>6.18161869049072</v>
       </c>
       <c r="H1335" t="n">
         <v>1600</v>
@@ -39229,7 +39229,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1340" t="n">
-        <v>6.25793504714966</v>
+        <v>6.25793552398682</v>
       </c>
       <c r="H1340" t="n">
         <v>5900</v>
@@ -39345,7 +39345,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1344" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1344" t="n">
         <v>1600</v>
@@ -39403,7 +39403,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1346" t="n">
         <v>1100</v>
@@ -39490,7 +39490,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1349" t="n">
-        <v>6.73491191864014</v>
+        <v>6.73491239547729</v>
       </c>
       <c r="H1349" t="n">
         <v>4400</v>
@@ -39577,7 +39577,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1352" t="n">
         <v>400</v>
@@ -39867,7 +39867,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1362" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1362" t="n">
         <v>2600</v>
@@ -40041,7 +40041,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1368" t="n">
         <v>1300</v>
@@ -40099,7 +40099,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1370" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1370" t="n">
         <v>1000</v>
@@ -40128,7 +40128,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1371" t="n">
         <v>10600</v>
@@ -40157,7 +40157,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1372" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1372" t="n">
         <v>0</v>
@@ -40186,7 +40186,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.62043809890747</v>
+        <v>6.62043762207031</v>
       </c>
       <c r="H1373" t="n">
         <v>0</v>
@@ -40215,7 +40215,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1374" t="n">
         <v>100</v>
@@ -40447,7 +40447,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1382" t="n">
-        <v>6.44872665405273</v>
+        <v>6.44872617721558</v>
       </c>
       <c r="H1382" t="n">
         <v>1000</v>
@@ -40563,7 +40563,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1386" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1386" t="n">
         <v>700</v>
@@ -40592,7 +40592,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.42964649200439</v>
+        <v>6.42964696884155</v>
       </c>
       <c r="H1387" t="n">
         <v>700</v>
@@ -40621,7 +40621,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1388" t="n">
-        <v>6.54412126541138</v>
+        <v>6.54412174224854</v>
       </c>
       <c r="H1388" t="n">
         <v>400</v>
@@ -40795,7 +40795,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1394" t="n">
-        <v>6.23885631561279</v>
+        <v>6.23885583877563</v>
       </c>
       <c r="H1394" t="n">
         <v>1100</v>
@@ -40853,7 +40853,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1396" t="n">
-        <v>6.37240934371948</v>
+        <v>6.37240982055664</v>
       </c>
       <c r="H1396" t="n">
         <v>5300</v>
@@ -40911,7 +40911,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1398" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1398" t="n">
         <v>8500</v>
@@ -40969,7 +40969,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1400" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1400" t="n">
         <v>3800</v>
@@ -41056,7 +41056,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1403" t="n">
-        <v>5.85727500915527</v>
+        <v>5.85727453231812</v>
       </c>
       <c r="H1403" t="n">
         <v>3500</v>
@@ -41201,7 +41201,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1408" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1408" t="n">
         <v>100</v>
@@ -41375,7 +41375,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1414" t="n">
-        <v>6.08622360229492</v>
+        <v>6.08622407913208</v>
       </c>
       <c r="H1414" t="n">
         <v>3900</v>
@@ -41462,7 +41462,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.12438201904297</v>
+        <v>6.12438154220581</v>
       </c>
       <c r="H1417" t="n">
         <v>1600</v>
@@ -41607,7 +41607,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1422" t="n">
-        <v>5.95266962051392</v>
+        <v>5.95267009735107</v>
       </c>
       <c r="H1422" t="n">
         <v>500</v>
@@ -41694,7 +41694,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>5.78095817565918</v>
+        <v>5.78095865249634</v>
       </c>
       <c r="H1425" t="n">
         <v>6300</v>
@@ -41868,7 +41868,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1431" t="n">
-        <v>5.91451168060303</v>
+        <v>5.91451215744019</v>
       </c>
       <c r="H1431" t="n">
         <v>1000</v>
@@ -42071,7 +42071,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1438" t="n">
-        <v>5.32306051254272</v>
+        <v>5.32306098937988</v>
       </c>
       <c r="H1438" t="n">
         <v>8200</v>
@@ -42129,7 +42129,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1440" t="n">
-        <v>5.53293085098267</v>
+        <v>5.53293037414551</v>
       </c>
       <c r="H1440" t="n">
         <v>4900</v>
@@ -42187,7 +42187,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1442" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1442" t="n">
         <v>5900</v>
@@ -42332,7 +42332,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1447" t="n">
         <v>400</v>
@@ -42361,7 +42361,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1448" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1448" t="n">
         <v>0</v>
@@ -42419,7 +42419,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1450" t="n">
-        <v>5.34214019775391</v>
+        <v>5.34213972091675</v>
       </c>
       <c r="H1450" t="n">
         <v>7900</v>
@@ -42448,7 +42448,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1451" t="n">
-        <v>5.43753480911255</v>
+        <v>5.43753528594971</v>
       </c>
       <c r="H1451" t="n">
         <v>9800</v>
@@ -42593,7 +42593,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1456" t="n">
-        <v>5.58062839508057</v>
+        <v>5.58062791824341</v>
       </c>
       <c r="H1456" t="n">
         <v>14200</v>
@@ -60956,6 +60956,35 @@
         <v>1900</v>
       </c>
       <c r="I2089" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2090" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>2.95000004768372</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>2.95000004768372</v>
+      </c>
+      <c r="G2090" t="n">
+        <v>2.95000004768372</v>
+      </c>
+      <c r="H2090" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I2090" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G2" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H2" t="n">
         <v>3600</v>
@@ -456,7 +456,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G3" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H3" t="n">
         <v>300</v>
@@ -485,7 +485,7 @@
         <v>9.70100021362305</v>
       </c>
       <c r="G4" t="n">
-        <v>8.23212146759033</v>
+        <v>8.2321195602417</v>
       </c>
       <c r="H4" t="n">
         <v>4100</v>
@@ -572,7 +572,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G7" t="n">
-        <v>8.18035697937012</v>
+        <v>8.18035793304443</v>
       </c>
       <c r="H7" t="n">
         <v>6500</v>
@@ -601,7 +601,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11247062683105</v>
+        <v>8.11246967315674</v>
       </c>
       <c r="H8" t="n">
         <v>7000</v>
@@ -630,7 +630,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H9" t="n">
         <v>3500</v>
@@ -659,7 +659,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -746,7 +746,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -804,7 +804,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -833,7 +833,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H19" t="n">
         <v>9600</v>
@@ -949,7 +949,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549808502197</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10653209686279</v>
+        <v>8.10653018951416</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.13792896270752</v>
+        <v>8.1379280090332</v>
       </c>
       <c r="H22" t="n">
         <v>300</v>
@@ -1065,7 +1065,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852649688721</v>
+        <v>8.07852745056152</v>
       </c>
       <c r="H24" t="n">
         <v>2800</v>
@@ -1181,7 +1181,7 @@
         <v>9.52799987792969</v>
       </c>
       <c r="G28" t="n">
-        <v>8.0853157043457</v>
+        <v>8.08531475067139</v>
       </c>
       <c r="H28" t="n">
         <v>1500</v>
@@ -1239,7 +1239,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H30" t="n">
         <v>7500</v>
@@ -1268,7 +1268,7 @@
         <v>9.50100040435791</v>
       </c>
       <c r="G31" t="n">
-        <v>8.06240367889404</v>
+        <v>8.06240463256836</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1326,7 +1326,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.07513236999512</v>
+        <v>8.07513332366943</v>
       </c>
       <c r="H33" t="n">
         <v>8000</v>
@@ -1384,7 +1384,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G35" t="n">
-        <v>8.01063919067383</v>
+        <v>8.01064014434814</v>
       </c>
       <c r="H35" t="n">
         <v>7500</v>
@@ -1442,7 +1442,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366855621338</v>
+        <v>7.99366903305054</v>
       </c>
       <c r="H37" t="n">
         <v>12300</v>
@@ -1471,7 +1471,7 @@
         <v>9.37100028991699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.95208740234375</v>
+        <v>7.95208787918091</v>
       </c>
       <c r="H38" t="n">
         <v>500</v>
@@ -1529,7 +1529,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227216720581</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H40" t="n">
         <v>300</v>
@@ -1558,7 +1558,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227216720581</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924280166626</v>
       </c>
       <c r="H42" t="n">
         <v>300</v>
@@ -1616,7 +1616,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924280166626</v>
       </c>
       <c r="H43" t="n">
         <v>1700</v>
@@ -1645,7 +1645,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G44" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H44" t="n">
         <v>600</v>
@@ -1674,7 +1674,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G45" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1790,7 +1790,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729545593262</v>
+        <v>7.91729593276978</v>
       </c>
       <c r="H49" t="n">
         <v>9200</v>
@@ -1819,7 +1819,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619878768921</v>
+        <v>7.85619831085205</v>
       </c>
       <c r="H50" t="n">
         <v>8700</v>
@@ -1848,7 +1848,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H51" t="n">
         <v>16700</v>
@@ -1906,7 +1906,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.774733543396</v>
+        <v>7.77473258972168</v>
       </c>
       <c r="H53" t="n">
         <v>2300</v>
@@ -1993,7 +1993,7 @@
         <v>9.15299987792969</v>
       </c>
       <c r="G56" t="n">
-        <v>7.76709604263306</v>
+        <v>7.76709651947021</v>
       </c>
       <c r="H56" t="n">
         <v>200</v>
@@ -2022,7 +2022,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H57" t="n">
         <v>12300</v>
@@ -2051,7 +2051,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G58" t="n">
-        <v>7.80697870254517</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H58" t="n">
         <v>4100</v>
@@ -2080,7 +2080,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H59" t="n">
         <v>13600</v>
@@ -2109,7 +2109,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>7.80697870254517</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H60" t="n">
         <v>24300</v>
@@ -2138,7 +2138,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H61" t="n">
         <v>4900</v>
@@ -2167,7 +2167,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H62" t="n">
         <v>8400</v>
@@ -2196,7 +2196,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>7.80697870254517</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H65" t="n">
         <v>7100</v>
@@ -2283,7 +2283,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H66" t="n">
         <v>2500</v>
@@ -2312,7 +2312,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>9.20699977874756</v>
       </c>
       <c r="G69" t="n">
-        <v>7.81291913986206</v>
+        <v>7.81291961669922</v>
       </c>
       <c r="H69" t="n">
         <v>200</v>
@@ -2399,7 +2399,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.80528211593628</v>
+        <v>7.80528163909912</v>
       </c>
       <c r="H70" t="n">
         <v>1000</v>
@@ -2428,7 +2428,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722993850708</v>
+        <v>7.86722946166992</v>
       </c>
       <c r="H71" t="n">
         <v>800</v>
@@ -2457,7 +2457,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G72" t="n">
-        <v>7.78746223449707</v>
+        <v>7.78746318817139</v>
       </c>
       <c r="H72" t="n">
         <v>700</v>
@@ -2486,7 +2486,7 @@
         <v>9.17700004577637</v>
       </c>
       <c r="G73" t="n">
-        <v>7.78746223449707</v>
+        <v>7.78746318817139</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761077880859</v>
+        <v>8.02761268615723</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2602,7 +2602,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177255630493</v>
+        <v>7.84177303314209</v>
       </c>
       <c r="H77" t="n">
         <v>4000</v>
@@ -2631,7 +2631,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.790855884552</v>
+        <v>7.79085636138916</v>
       </c>
       <c r="H78" t="n">
         <v>800</v>
@@ -2660,7 +2660,7 @@
         <v>9.24499988555908</v>
       </c>
       <c r="G79" t="n">
-        <v>7.84516525268555</v>
+        <v>7.84516620635986</v>
       </c>
       <c r="H79" t="n">
         <v>2400</v>
@@ -2747,7 +2747,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406810760498</v>
+        <v>7.78406715393066</v>
       </c>
       <c r="H82" t="n">
         <v>200</v>
@@ -2863,7 +2863,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.8010401725769</v>
+        <v>7.80103969573975</v>
       </c>
       <c r="H86" t="n">
         <v>2900</v>
@@ -2892,7 +2892,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G87" t="n">
-        <v>7.81037425994873</v>
+        <v>7.81037378311157</v>
       </c>
       <c r="H87" t="n">
         <v>2500</v>
@@ -2921,7 +2921,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098930358887</v>
+        <v>7.89098882675171</v>
       </c>
       <c r="H88" t="n">
         <v>200</v>
@@ -2950,7 +2950,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782794952393</v>
+        <v>7.80782747268677</v>
       </c>
       <c r="H89" t="n">
         <v>5100</v>
@@ -2979,7 +2979,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879215240479</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879215240479</v>
       </c>
       <c r="H91" t="n">
         <v>700</v>
@@ -3037,7 +3037,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408561706543</v>
+        <v>7.92408466339111</v>
       </c>
       <c r="H92" t="n">
         <v>1200</v>
@@ -3066,7 +3066,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.77048969268799</v>
+        <v>7.77049016952515</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3124,7 +3124,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H95" t="n">
         <v>20300</v>
@@ -3153,7 +3153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969179153442</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H100" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969179153442</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726186752319</v>
+        <v>7.63726329803467</v>
       </c>
       <c r="H102" t="n">
         <v>700</v>
@@ -3356,7 +3356,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423440933228</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423440933228</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>9.22599983215332</v>
       </c>
       <c r="G106" t="n">
-        <v>7.82904148101807</v>
+        <v>7.82904243469238</v>
       </c>
       <c r="H106" t="n">
         <v>300</v>
@@ -3588,7 +3588,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H111" t="n">
         <v>25500</v>
@@ -3617,7 +3617,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817806243896</v>
       </c>
       <c r="H113" t="n">
         <v>15900</v>
@@ -3675,7 +3675,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969179153442</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H114" t="n">
         <v>100</v>
@@ -3733,7 +3733,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110664367676</v>
+        <v>7.8511061668396</v>
       </c>
       <c r="H116" t="n">
         <v>800</v>
@@ -3762,7 +3762,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273675918579</v>
+        <v>7.80273723602295</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -3791,7 +3791,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308734893799</v>
+        <v>7.68308544158936</v>
       </c>
       <c r="H118" t="n">
         <v>2400</v>
@@ -3820,7 +3820,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G119" t="n">
-        <v>7.69666290283203</v>
+        <v>7.69666337966919</v>
       </c>
       <c r="H119" t="n">
         <v>2900</v>
@@ -3907,7 +3907,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817806243896</v>
       </c>
       <c r="H122" t="n">
         <v>3300</v>
@@ -3936,7 +3936,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879215240479</v>
       </c>
       <c r="H123" t="n">
         <v>100</v>
@@ -3965,7 +3965,7 @@
         <v>9.14900016784668</v>
       </c>
       <c r="G124" t="n">
-        <v>7.76370191574097</v>
+        <v>7.76370239257812</v>
       </c>
       <c r="H124" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.86553192138672</v>
+        <v>7.86553144454956</v>
       </c>
       <c r="H125" t="n">
         <v>300</v>
@@ -4023,7 +4023,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G126" t="n">
-        <v>7.78152132034302</v>
+        <v>7.78152275085449</v>
       </c>
       <c r="H126" t="n">
         <v>24300</v>
@@ -4052,7 +4052,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406810760498</v>
+        <v>7.78406715393066</v>
       </c>
       <c r="H127" t="n">
         <v>2000</v>
@@ -4081,7 +4081,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H128" t="n">
         <v>100</v>
@@ -4197,7 +4197,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.7984938621521</v>
+        <v>7.79849290847778</v>
       </c>
       <c r="H132" t="n">
         <v>300</v>
@@ -4226,7 +4226,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H133" t="n">
         <v>13900</v>
@@ -4255,7 +4255,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000854492188</v>
+        <v>7.7900071144104</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000854492188</v>
+        <v>7.7900071144104</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445037841797</v>
+        <v>7.94445180892944</v>
       </c>
       <c r="H136" t="n">
         <v>2500</v>
@@ -4342,7 +4342,7 @@
         <v>9.5</v>
       </c>
       <c r="G137" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H137" t="n">
         <v>100</v>
@@ -4371,7 +4371,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.7984938621521</v>
+        <v>7.79849290847778</v>
       </c>
       <c r="H138" t="n">
         <v>800</v>
@@ -4400,7 +4400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>7.80697870254517</v>
+        <v>7.80697965621948</v>
       </c>
       <c r="H139" t="n">
         <v>1200</v>
@@ -4458,7 +4458,7 @@
         <v>9.5</v>
       </c>
       <c r="G141" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H141" t="n">
         <v>300</v>
@@ -4690,7 +4690,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579780578613</v>
+        <v>8.06579971313477</v>
       </c>
       <c r="H149" t="n">
         <v>300</v>
@@ -4719,7 +4719,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H150" t="n">
         <v>100</v>
@@ -4748,7 +4748,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>9.34700012207031</v>
       </c>
       <c r="G159" t="n">
-        <v>7.93172168731689</v>
+        <v>7.93172121047974</v>
       </c>
       <c r="H159" t="n">
         <v>800</v>
@@ -5009,7 +5009,7 @@
         <v>9.44299983978271</v>
       </c>
       <c r="G160" t="n">
-        <v>8.01318645477295</v>
+        <v>8.01318550109863</v>
       </c>
       <c r="H160" t="n">
         <v>100</v>
@@ -5067,7 +5067,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G162" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H162" t="n">
         <v>2300</v>
@@ -5154,7 +5154,7 @@
         <v>9.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>8.05306911468506</v>
+        <v>8.05307006835938</v>
       </c>
       <c r="H165" t="n">
         <v>300</v>
@@ -5212,7 +5212,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H167" t="n">
         <v>3300</v>
@@ -5299,7 +5299,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H170" t="n">
         <v>200</v>
@@ -5328,7 +5328,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H172" t="n">
         <v>3700</v>
@@ -5386,7 +5386,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H173" t="n">
         <v>200</v>
@@ -5415,7 +5415,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H174" t="n">
         <v>600</v>
@@ -5473,7 +5473,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H176" t="n">
         <v>4900</v>
@@ -5502,7 +5502,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G177" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H177" t="n">
         <v>1900</v>
@@ -5531,7 +5531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H178" t="n">
         <v>300</v>
@@ -5560,7 +5560,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H179" t="n">
         <v>100</v>
@@ -5589,7 +5589,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G180" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H180" t="n">
         <v>3800</v>
@@ -5676,7 +5676,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H184" t="n">
         <v>300</v>
@@ -5734,7 +5734,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H185" t="n">
         <v>200</v>
@@ -5763,7 +5763,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H186" t="n">
         <v>700</v>
@@ -5792,7 +5792,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H187" t="n">
         <v>900</v>
@@ -5821,7 +5821,7 @@
         <v>9.5</v>
       </c>
       <c r="G188" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H188" t="n">
         <v>500</v>
@@ -5850,7 +5850,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H189" t="n">
         <v>1900</v>
@@ -5879,7 +5879,7 @@
         <v>9.5</v>
       </c>
       <c r="G190" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H190" t="n">
         <v>1000</v>
@@ -5908,7 +5908,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H191" t="n">
         <v>5600</v>
@@ -5937,7 +5937,7 @@
         <v>9.5</v>
       </c>
       <c r="G192" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H192" t="n">
         <v>4100</v>
@@ -5966,7 +5966,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H193" t="n">
         <v>3200</v>
@@ -5995,7 +5995,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H194" t="n">
         <v>300</v>
@@ -6024,7 +6024,7 @@
         <v>9.5</v>
       </c>
       <c r="G195" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H195" t="n">
         <v>4200</v>
@@ -6053,7 +6053,7 @@
         <v>9.5</v>
       </c>
       <c r="G196" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H196" t="n">
         <v>800</v>
@@ -6082,7 +6082,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6111,7 +6111,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H198" t="n">
         <v>4700</v>
@@ -6140,7 +6140,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H200" t="n">
         <v>2000</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H201" t="n">
         <v>1500</v>
@@ -6227,7 +6227,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H202" t="n">
         <v>800</v>
@@ -6256,7 +6256,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H203" t="n">
         <v>100</v>
@@ -6285,7 +6285,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H204" t="n">
         <v>5900</v>
@@ -6314,7 +6314,7 @@
         <v>9.5</v>
       </c>
       <c r="G205" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H205" t="n">
         <v>600</v>
@@ -6343,7 +6343,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H206" t="n">
         <v>300</v>
@@ -6372,7 +6372,7 @@
         <v>9.5</v>
       </c>
       <c r="G207" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H207" t="n">
         <v>700</v>
@@ -6401,7 +6401,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6430,7 +6430,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G209" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6459,7 +6459,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H210" t="n">
         <v>600</v>
@@ -6488,7 +6488,7 @@
         <v>9.5</v>
       </c>
       <c r="G211" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H211" t="n">
         <v>400</v>
@@ -6517,7 +6517,7 @@
         <v>9.5</v>
       </c>
       <c r="G212" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H212" t="n">
         <v>300</v>
@@ -6546,7 +6546,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H213" t="n">
         <v>2600</v>
@@ -6575,7 +6575,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H214" t="n">
         <v>200</v>
@@ -6604,7 +6604,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H215" t="n">
         <v>6600</v>
@@ -6633,7 +6633,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H216" t="n">
         <v>100</v>
@@ -6662,7 +6662,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6691,7 +6691,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H218" t="n">
         <v>900</v>
@@ -6720,7 +6720,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6749,7 +6749,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H220" t="n">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H221" t="n">
         <v>17700</v>
@@ -6807,7 +6807,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H222" t="n">
         <v>300</v>
@@ -6836,7 +6836,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G223" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H223" t="n">
         <v>300</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H224" t="n">
         <v>800</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H225" t="n">
         <v>600</v>
@@ -6923,7 +6923,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H226" t="n">
         <v>100</v>
@@ -6952,7 +6952,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H227" t="n">
         <v>100</v>
@@ -6981,7 +6981,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H228" t="n">
         <v>9100</v>
@@ -7010,7 +7010,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H229" t="n">
         <v>100</v>
@@ -7039,7 +7039,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7068,7 +7068,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7126,7 +7126,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H233" t="n">
         <v>5100</v>
@@ -7155,7 +7155,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H234" t="n">
         <v>100</v>
@@ -7213,7 +7213,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H236" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H237" t="n">
         <v>100</v>
@@ -7271,7 +7271,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H238" t="n">
         <v>3200</v>
@@ -7300,7 +7300,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H239" t="n">
         <v>100</v>
@@ -7329,7 +7329,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H240" t="n">
         <v>100</v>
@@ -7358,7 +7358,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H241" t="n">
         <v>400</v>
@@ -7387,7 +7387,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H242" t="n">
         <v>7200</v>
@@ -7416,7 +7416,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H243" t="n">
         <v>100</v>
@@ -7445,7 +7445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H244" t="n">
         <v>1200</v>
@@ -7474,7 +7474,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H245" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H248" t="n">
         <v>700</v>
@@ -7590,7 +7590,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H249" t="n">
         <v>600</v>
@@ -7619,7 +7619,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G250" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H250" t="n">
         <v>300</v>
@@ -7648,7 +7648,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H251" t="n">
         <v>2100</v>
@@ -7677,7 +7677,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H252" t="n">
         <v>1800</v>
@@ -7706,7 +7706,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H253" t="n">
         <v>1700</v>
@@ -7735,7 +7735,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H254" t="n">
         <v>1800</v>
@@ -7764,7 +7764,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G255" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H255" t="n">
         <v>7900</v>
@@ -7793,7 +7793,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G256" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H256" t="n">
         <v>2300</v>
@@ -7822,7 +7822,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H257" t="n">
         <v>100</v>
@@ -7851,7 +7851,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H258" t="n">
         <v>1200</v>
@@ -7880,7 +7880,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H259" t="n">
         <v>25000</v>
@@ -7909,7 +7909,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H263" t="n">
         <v>8000</v>
@@ -8141,7 +8141,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H268" t="n">
         <v>11200</v>
@@ -8170,7 +8170,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H269" t="n">
         <v>600</v>
@@ -8199,7 +8199,7 @@
         <v>9.5</v>
       </c>
       <c r="G270" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H270" t="n">
         <v>600</v>
@@ -8228,7 +8228,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H272" t="n">
         <v>100</v>
@@ -8286,7 +8286,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H273" t="n">
         <v>100</v>
@@ -8315,7 +8315,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H274" t="n">
         <v>200</v>
@@ -8344,7 +8344,7 @@
         <v>9.5</v>
       </c>
       <c r="G275" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H275" t="n">
         <v>400</v>
@@ -8373,7 +8373,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H276" t="n">
         <v>100</v>
@@ -8402,7 +8402,7 @@
         <v>9.5</v>
       </c>
       <c r="G277" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H277" t="n">
         <v>7300</v>
@@ -8431,7 +8431,7 @@
         <v>9.5</v>
       </c>
       <c r="G278" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H278" t="n">
         <v>2000</v>
@@ -8460,7 +8460,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H279" t="n">
         <v>28000</v>
@@ -8489,7 +8489,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H280" t="n">
         <v>100</v>
@@ -8518,7 +8518,7 @@
         <v>9.5</v>
       </c>
       <c r="G281" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H281" t="n">
         <v>2100</v>
@@ -8547,7 +8547,7 @@
         <v>9.5</v>
       </c>
       <c r="G282" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H282" t="n">
         <v>400</v>
@@ -8576,7 +8576,7 @@
         <v>9.5</v>
       </c>
       <c r="G283" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H283" t="n">
         <v>100</v>
@@ -8634,7 +8634,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H285" t="n">
         <v>200</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H286" t="n">
         <v>1900</v>
@@ -8692,7 +8692,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8721,7 +8721,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H289" t="n">
         <v>800</v>
@@ -8779,7 +8779,7 @@
         <v>9.5</v>
       </c>
       <c r="G290" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H290" t="n">
         <v>5800</v>
@@ -8808,7 +8808,7 @@
         <v>9.5</v>
       </c>
       <c r="G291" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H291" t="n">
         <v>700</v>
@@ -8837,7 +8837,7 @@
         <v>9.5</v>
       </c>
       <c r="G292" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G296" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H296" t="n">
         <v>200</v>
@@ -8982,7 +8982,7 @@
         <v>9.5</v>
       </c>
       <c r="G297" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H297" t="n">
         <v>500</v>
@@ -9011,7 +9011,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H298" t="n">
         <v>10700</v>
@@ -9098,7 +9098,7 @@
         <v>9.5</v>
       </c>
       <c r="G301" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H301" t="n">
         <v>19200</v>
@@ -9127,7 +9127,7 @@
         <v>9.5</v>
       </c>
       <c r="G302" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H302" t="n">
         <v>2300</v>
@@ -9156,7 +9156,7 @@
         <v>9.5</v>
       </c>
       <c r="G303" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H303" t="n">
         <v>4100</v>
@@ -9185,7 +9185,7 @@
         <v>9.5</v>
       </c>
       <c r="G304" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H304" t="n">
         <v>800</v>
@@ -9214,7 +9214,7 @@
         <v>9.5</v>
       </c>
       <c r="G305" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>9.5</v>
       </c>
       <c r="G308" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H308" t="n">
         <v>300</v>
@@ -9330,7 +9330,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H309" t="n">
         <v>500</v>
@@ -9359,7 +9359,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H310" t="n">
         <v>3300</v>
@@ -9388,7 +9388,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H311" t="n">
         <v>100</v>
@@ -9417,7 +9417,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H312" t="n">
         <v>100</v>
@@ -9446,7 +9446,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H313" t="n">
         <v>12700</v>
@@ -9475,7 +9475,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H314" t="n">
         <v>7100</v>
@@ -9504,7 +9504,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H318" t="n">
         <v>300</v>
@@ -9620,7 +9620,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H319" t="n">
         <v>200</v>
@@ -9649,7 +9649,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G320" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H320" t="n">
         <v>100</v>
@@ -9678,7 +9678,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H321" t="n">
         <v>100</v>
@@ -9707,7 +9707,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H322" t="n">
         <v>4600</v>
@@ -9736,7 +9736,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H323" t="n">
         <v>26700</v>
@@ -9765,7 +9765,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H324" t="n">
         <v>100</v>
@@ -9794,7 +9794,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H325" t="n">
         <v>20100</v>
@@ -9852,7 +9852,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -9881,7 +9881,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H328" t="n">
         <v>52800</v>
@@ -9910,7 +9910,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H329" t="n">
         <v>10000</v>
@@ -9939,7 +9939,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H330" t="n">
         <v>200</v>
@@ -9968,7 +9968,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H331" t="n">
         <v>900</v>
@@ -9997,7 +9997,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H332" t="n">
         <v>10000</v>
@@ -10026,7 +10026,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H338" t="n">
         <v>400</v>
@@ -10200,7 +10200,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H339" t="n">
         <v>6600</v>
@@ -10229,7 +10229,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H340" t="n">
         <v>400</v>
@@ -10287,7 +10287,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H342" t="n">
         <v>100</v>
@@ -10461,7 +10461,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G352" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H352" t="n">
         <v>100</v>
@@ -10606,7 +10606,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G353" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H356" t="n">
         <v>100</v>
@@ -10722,7 +10722,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G357" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H357" t="n">
         <v>2700</v>
@@ -10751,7 +10751,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G358" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H360" t="n">
         <v>5000</v>
@@ -10838,7 +10838,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G361" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H361" t="n">
         <v>4700</v>
@@ -10867,7 +10867,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H362" t="n">
         <v>300</v>
@@ -10896,7 +10896,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H363" t="n">
         <v>1100</v>
@@ -10925,7 +10925,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H365" t="n">
         <v>100</v>
@@ -10983,7 +10983,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H367" t="n">
         <v>900</v>
@@ -11041,7 +11041,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H368" t="n">
         <v>300</v>
@@ -11070,7 +11070,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H369" t="n">
         <v>100</v>
@@ -11099,7 +11099,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H371" t="n">
         <v>1700</v>
@@ -11157,7 +11157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H372" t="n">
         <v>1200</v>
@@ -11186,7 +11186,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H373" t="n">
         <v>5000</v>
@@ -11215,7 +11215,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H374" t="n">
         <v>11400</v>
@@ -11244,7 +11244,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H375" t="n">
         <v>5700</v>
@@ -11273,7 +11273,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H376" t="n">
         <v>13700</v>
@@ -11302,7 +11302,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H377" t="n">
         <v>5900</v>
@@ -11331,7 +11331,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H378" t="n">
         <v>30700</v>
@@ -11360,7 +11360,7 @@
         <v>9.75</v>
       </c>
       <c r="G379" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H379" t="n">
         <v>67200</v>
@@ -11389,7 +11389,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H380" t="n">
         <v>15200</v>
@@ -11418,7 +11418,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H381" t="n">
         <v>25400</v>
@@ -11447,7 +11447,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G382" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H382" t="n">
         <v>5600</v>
@@ -11476,7 +11476,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H383" t="n">
         <v>800</v>
@@ -11505,7 +11505,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G384" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H384" t="n">
         <v>55500</v>
@@ -11534,7 +11534,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G385" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H385" t="n">
         <v>1700</v>
@@ -11563,7 +11563,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H386" t="n">
         <v>300</v>
@@ -11592,7 +11592,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G387" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H387" t="n">
         <v>800</v>
@@ -11621,7 +11621,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H388" t="n">
         <v>800</v>
@@ -11650,7 +11650,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H389" t="n">
         <v>4300</v>
@@ -11679,7 +11679,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H390" t="n">
         <v>300</v>
@@ -11708,7 +11708,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G391" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H391" t="n">
         <v>400</v>
@@ -11737,7 +11737,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G392" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H392" t="n">
         <v>10300</v>
@@ -11766,7 +11766,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H393" t="n">
         <v>33000</v>
@@ -11795,7 +11795,7 @@
         <v>9.75</v>
       </c>
       <c r="G394" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H394" t="n">
         <v>23100</v>
@@ -11824,7 +11824,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G395" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H395" t="n">
         <v>100</v>
@@ -11853,7 +11853,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H396" t="n">
         <v>1100</v>
@@ -11882,7 +11882,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H397" t="n">
         <v>69000</v>
@@ -11940,7 +11940,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H399" t="n">
         <v>300</v>
@@ -11969,7 +11969,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H400" t="n">
         <v>900</v>
@@ -12143,7 +12143,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H406" t="n">
         <v>11100</v>
@@ -12172,7 +12172,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H407" t="n">
         <v>11800</v>
@@ -12201,7 +12201,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G409" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H409" t="n">
         <v>2800</v>
@@ -12259,7 +12259,7 @@
         <v>9.25</v>
       </c>
       <c r="G410" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H410" t="n">
         <v>13800</v>
@@ -12288,7 +12288,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12346,7 +12346,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H413" t="n">
         <v>1800</v>
@@ -12375,7 +12375,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G415" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H415" t="n">
         <v>200</v>
@@ -12491,7 +12491,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H418" t="n">
         <v>10000</v>
@@ -12520,7 +12520,7 @@
         <v>9.5</v>
       </c>
       <c r="G419" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H419" t="n">
         <v>16300</v>
@@ -12549,7 +12549,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G420" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H420" t="n">
         <v>12500</v>
@@ -12578,7 +12578,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G421" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H421" t="n">
         <v>10000</v>
@@ -12607,7 +12607,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12636,7 +12636,7 @@
         <v>9.5</v>
       </c>
       <c r="G423" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H423" t="n">
         <v>15100</v>
@@ -12665,7 +12665,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G424" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H424" t="n">
         <v>8900</v>
@@ -12694,7 +12694,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>8.10398387908936</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H426" t="n">
         <v>300</v>
@@ -12781,7 +12781,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H428" t="n">
         <v>800</v>
@@ -12810,7 +12810,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H429" t="n">
         <v>400</v>
@@ -12839,7 +12839,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H431" t="n">
         <v>700</v>
@@ -12955,7 +12955,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H434" t="n">
         <v>4300</v>
@@ -12984,7 +12984,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H435" t="n">
         <v>5200</v>
@@ -13013,7 +13013,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H436" t="n">
         <v>400</v>
@@ -13042,7 +13042,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H438" t="n">
         <v>9200</v>
@@ -13100,7 +13100,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H439" t="n">
         <v>1000</v>
@@ -13129,7 +13129,7 @@
         <v>9.75</v>
       </c>
       <c r="G440" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H440" t="n">
         <v>300</v>
@@ -13158,7 +13158,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H441" t="n">
         <v>1700</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H442" t="n">
         <v>1200</v>
@@ -13216,7 +13216,7 @@
         <v>9.75</v>
       </c>
       <c r="G443" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H443" t="n">
         <v>100</v>
@@ -13245,7 +13245,7 @@
         <v>9.75</v>
       </c>
       <c r="G444" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H444" t="n">
         <v>500</v>
@@ -13274,7 +13274,7 @@
         <v>9.75</v>
       </c>
       <c r="G445" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>9.75</v>
       </c>
       <c r="G446" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H447" t="n">
         <v>300</v>
@@ -13361,7 +13361,7 @@
         <v>9.75</v>
       </c>
       <c r="G448" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H448" t="n">
         <v>400</v>
@@ -13390,7 +13390,7 @@
         <v>9.75</v>
       </c>
       <c r="G449" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H449" t="n">
         <v>700</v>
@@ -13419,7 +13419,7 @@
         <v>9.75</v>
       </c>
       <c r="G450" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>9.75</v>
       </c>
       <c r="G451" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>9.75</v>
       </c>
       <c r="G452" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H452" t="n">
         <v>3100</v>
@@ -13506,7 +13506,7 @@
         <v>9.75</v>
       </c>
       <c r="G453" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H453" t="n">
         <v>100</v>
@@ -13535,7 +13535,7 @@
         <v>9.75</v>
       </c>
       <c r="G454" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H454" t="n">
         <v>100000</v>
@@ -13564,7 +13564,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H455" t="n">
         <v>60600</v>
@@ -13593,7 +13593,7 @@
         <v>9.75</v>
       </c>
       <c r="G456" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H456" t="n">
         <v>15500</v>
@@ -13622,7 +13622,7 @@
         <v>9.75</v>
       </c>
       <c r="G457" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H457" t="n">
         <v>50000</v>
@@ -13651,7 +13651,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H458" t="n">
         <v>53200</v>
@@ -13680,7 +13680,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H459" t="n">
         <v>5700</v>
@@ -13709,7 +13709,7 @@
         <v>9.75</v>
       </c>
       <c r="G460" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H460" t="n">
         <v>24400</v>
@@ -13738,7 +13738,7 @@
         <v>9.75</v>
       </c>
       <c r="G461" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>9.75</v>
       </c>
       <c r="G462" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H462" t="n">
         <v>10100</v>
@@ -13796,7 +13796,7 @@
         <v>9.75</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H463" t="n">
         <v>5900</v>
@@ -13825,7 +13825,7 @@
         <v>9.75</v>
       </c>
       <c r="G464" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H464" t="n">
         <v>18200</v>
@@ -13854,7 +13854,7 @@
         <v>9.75</v>
       </c>
       <c r="G465" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>9.75</v>
       </c>
       <c r="G466" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H466" t="n">
         <v>10100</v>
@@ -13912,7 +13912,7 @@
         <v>9.75</v>
       </c>
       <c r="G467" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H467" t="n">
         <v>8000</v>
@@ -13941,7 +13941,7 @@
         <v>9.75</v>
       </c>
       <c r="G468" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H468" t="n">
         <v>5800</v>
@@ -13970,7 +13970,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H469" t="n">
         <v>200</v>
@@ -13999,7 +13999,7 @@
         <v>9.75</v>
       </c>
       <c r="G470" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H470" t="n">
         <v>5600</v>
@@ -14028,7 +14028,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G471" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H471" t="n">
         <v>7300</v>
@@ -14057,7 +14057,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G472" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H472" t="n">
         <v>600</v>
@@ -14086,7 +14086,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G473" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H473" t="n">
         <v>6100</v>
@@ -14115,7 +14115,7 @@
         <v>9.75</v>
       </c>
       <c r="G474" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H474" t="n">
         <v>68300</v>
@@ -14144,7 +14144,7 @@
         <v>9.75</v>
       </c>
       <c r="G475" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H475" t="n">
         <v>88200</v>
@@ -14173,7 +14173,7 @@
         <v>9.75</v>
       </c>
       <c r="G476" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H476" t="n">
         <v>12000</v>
@@ -14202,7 +14202,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H477" t="n">
         <v>100</v>
@@ -14231,7 +14231,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G478" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H478" t="n">
         <v>400</v>
@@ -14260,7 +14260,7 @@
         <v>9.75</v>
       </c>
       <c r="G479" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H479" t="n">
         <v>36400</v>
@@ -14289,7 +14289,7 @@
         <v>9.75</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H480" t="n">
         <v>5300</v>
@@ -14318,7 +14318,7 @@
         <v>9.75</v>
       </c>
       <c r="G481" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H481" t="n">
         <v>22100</v>
@@ -14347,7 +14347,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G482" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H482" t="n">
         <v>80100</v>
@@ -14376,7 +14376,7 @@
         <v>9.75</v>
       </c>
       <c r="G483" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H483" t="n">
         <v>61200</v>
@@ -14405,7 +14405,7 @@
         <v>9.75</v>
       </c>
       <c r="G484" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H484" t="n">
         <v>17600</v>
@@ -14434,7 +14434,7 @@
         <v>9.75</v>
       </c>
       <c r="G485" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H485" t="n">
         <v>20000</v>
@@ -14463,7 +14463,7 @@
         <v>9.75</v>
       </c>
       <c r="G486" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H486" t="n">
         <v>34700</v>
@@ -14492,7 +14492,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G487" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H487" t="n">
         <v>77000</v>
@@ -14521,7 +14521,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H488" t="n">
         <v>140500</v>
@@ -14550,7 +14550,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H489" t="n">
         <v>134000</v>
@@ -14579,7 +14579,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H490" t="n">
         <v>5800</v>
@@ -14608,7 +14608,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H491" t="n">
         <v>129300</v>
@@ -14637,7 +14637,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G492" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H492" t="n">
         <v>135100</v>
@@ -14666,7 +14666,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G493" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H493" t="n">
         <v>60500</v>
@@ -14695,7 +14695,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H494" t="n">
         <v>300</v>
@@ -14724,7 +14724,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G496" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H496" t="n">
         <v>25000</v>
@@ -14782,7 +14782,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H497" t="n">
         <v>72200</v>
@@ -14811,7 +14811,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H498" t="n">
         <v>0</v>
@@ -14840,7 +14840,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H500" t="n">
         <v>100</v>
@@ -14898,7 +14898,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G501" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H501" t="n">
         <v>20200</v>
@@ -14927,7 +14927,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G502" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H502" t="n">
         <v>2900</v>
@@ -14956,7 +14956,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G503" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H503" t="n">
         <v>0</v>
@@ -14985,7 +14985,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G504" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H504" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H505" t="n">
         <v>400</v>
@@ -15043,7 +15043,7 @@
         <v>9.5</v>
       </c>
       <c r="G506" t="n">
-        <v>8.06155586242676</v>
+        <v>8.06155490875244</v>
       </c>
       <c r="H506" t="n">
         <v>100100</v>
@@ -15072,7 +15072,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H507" t="n">
         <v>3500</v>
@@ -15101,7 +15101,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H508" t="n">
         <v>6000</v>
@@ -15130,7 +15130,7 @@
         <v>9.75</v>
       </c>
       <c r="G509" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H509" t="n">
         <v>109100</v>
@@ -15159,7 +15159,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H510" t="n">
         <v>101000</v>
@@ -15188,7 +15188,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G511" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G512" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15246,7 +15246,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G513" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H513" t="n">
         <v>290000</v>
@@ -15275,7 +15275,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G514" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H514" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G515" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -15449,7 +15449,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G520" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H520" t="n">
         <v>7600</v>
@@ -15478,7 +15478,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G521" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H521" t="n">
         <v>1500</v>
@@ -15507,7 +15507,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G522" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H522" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H523" t="n">
         <v>1000</v>
@@ -15565,7 +15565,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G526" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H526" t="n">
         <v>6800</v>
@@ -15652,7 +15652,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G527" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G528" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G529" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H529" t="n">
         <v>600</v>
@@ -15739,7 +15739,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G530" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H531" t="n">
         <v>200</v>
@@ -15797,7 +15797,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G532" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H532" t="n">
         <v>300</v>
@@ -15826,7 +15826,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G533" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G534" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H534" t="n">
         <v>100</v>
@@ -15884,7 +15884,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G535" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H535" t="n">
         <v>200</v>
@@ -15913,7 +15913,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G536" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H536" t="n">
         <v>100</v>
@@ -15942,7 +15942,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G537" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H537" t="n">
         <v>500</v>
@@ -15971,7 +15971,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G538" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H538" t="n">
         <v>0</v>
@@ -16000,7 +16000,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G539" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H539" t="n">
         <v>0</v>
@@ -16029,7 +16029,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G540" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H540" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>9.75</v>
       </c>
       <c r="G541" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H541" t="n">
         <v>1500</v>
@@ -16087,7 +16087,7 @@
         <v>9.75</v>
       </c>
       <c r="G542" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G543" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H543" t="n">
         <v>400</v>
@@ -16145,7 +16145,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G544" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H544" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G545" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H545" t="n">
         <v>0</v>
@@ -16203,7 +16203,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G546" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H546" t="n">
         <v>30300</v>
@@ -16232,7 +16232,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G547" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>8.65556526184082</v>
+        <v>8.65556335449219</v>
       </c>
       <c r="H549" t="n">
         <v>900</v>
@@ -16319,7 +16319,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>8.65556526184082</v>
+        <v>8.65556335449219</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16348,7 +16348,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G551" t="n">
-        <v>8.31613063812256</v>
+        <v>8.31613159179688</v>
       </c>
       <c r="H551" t="n">
         <v>8600</v>
@@ -16406,7 +16406,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>8.01912593841553</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H553" t="n">
         <v>1800</v>
@@ -16435,7 +16435,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H554" t="n">
         <v>2900</v>
@@ -16464,7 +16464,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>7.59483242034912</v>
+        <v>7.5948338508606</v>
       </c>
       <c r="H555" t="n">
         <v>5200</v>
@@ -16493,7 +16493,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G556" t="n">
-        <v>7.59483242034912</v>
+        <v>7.5948338508606</v>
       </c>
       <c r="H556" t="n">
         <v>2100</v>
@@ -16522,7 +16522,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782867431641</v>
+        <v>7.29782962799072</v>
       </c>
       <c r="H557" t="n">
         <v>1100</v>
@@ -16580,7 +16580,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66139078140259</v>
+        <v>6.66139030456543</v>
       </c>
       <c r="H559" t="n">
         <v>9300</v>
@@ -16609,7 +16609,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G560" t="n">
-        <v>6.10980987548828</v>
+        <v>6.10981035232544</v>
       </c>
       <c r="H560" t="n">
         <v>3900</v>
@@ -16638,7 +16638,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>6.10980987548828</v>
+        <v>6.10981035232544</v>
       </c>
       <c r="H561" t="n">
         <v>49300</v>
@@ -16667,7 +16667,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>6.49167346954346</v>
+        <v>6.4916729927063</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16696,7 +16696,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17054033279419</v>
+        <v>7.17054128646851</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16725,7 +16725,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G564" t="n">
-        <v>6.83110761642456</v>
+        <v>6.8311071395874</v>
       </c>
       <c r="H564" t="n">
         <v>8800</v>
@@ -16841,7 +16841,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>6.7038197517395</v>
+        <v>6.70381927490234</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -16870,7 +16870,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>6.7038197517395</v>
+        <v>6.70381927490234</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16957,7 +16957,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G572" t="n">
-        <v>6.73004055023193</v>
+        <v>6.73004007339478</v>
       </c>
       <c r="H572" t="n">
         <v>900</v>
@@ -16986,7 +16986,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.4678316116333</v>
+        <v>6.46783113479614</v>
       </c>
       <c r="H573" t="n">
         <v>4700</v>
@@ -17015,7 +17015,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G574" t="n">
-        <v>6.73004055023193</v>
+        <v>6.73004007339478</v>
       </c>
       <c r="H574" t="n">
         <v>3700</v>
@@ -17073,7 +17073,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H576" t="n">
         <v>24700</v>
@@ -17102,7 +17102,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25446033477783</v>
       </c>
       <c r="H577" t="n">
         <v>1400</v>
@@ -17131,7 +17131,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25446033477783</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G579" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25446033477783</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17247,7 +17247,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25446033477783</v>
       </c>
       <c r="H582" t="n">
         <v>100</v>
@@ -17305,7 +17305,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G584" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H584" t="n">
         <v>3700</v>
@@ -17363,7 +17363,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H586" t="n">
         <v>1100</v>
@@ -17392,7 +17392,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G587" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H587" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H589" t="n">
         <v>1000</v>
@@ -17479,7 +17479,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H590" t="n">
         <v>600</v>
@@ -17508,7 +17508,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.73517608642578</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H591" t="n">
         <v>19400</v>
@@ -17537,7 +17537,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H592" t="n">
         <v>300</v>
@@ -17566,7 +17566,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G596" t="n">
-        <v>7.51666831970215</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H596" t="n">
         <v>400</v>
@@ -17682,7 +17682,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H597" t="n">
         <v>2000</v>
@@ -17711,7 +17711,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H598" t="n">
         <v>3300</v>
@@ -17740,7 +17740,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56036996841431</v>
+        <v>7.56036949157715</v>
       </c>
       <c r="H600" t="n">
         <v>100</v>
@@ -17856,7 +17856,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H603" t="n">
         <v>300</v>
@@ -17885,7 +17885,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.73517608642578</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H604" t="n">
         <v>700</v>
@@ -17914,7 +17914,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G605" t="n">
-        <v>7.51666831970215</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H605" t="n">
         <v>600</v>
@@ -17972,7 +17972,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G607" t="n">
-        <v>7.51666831970215</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H607" t="n">
         <v>300</v>
@@ -18088,7 +18088,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H611" t="n">
         <v>800</v>
@@ -18117,7 +18117,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H612" t="n">
         <v>100</v>
@@ -18146,7 +18146,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95368432998657</v>
+        <v>7.95368480682373</v>
       </c>
       <c r="H613" t="n">
         <v>100</v>
@@ -18175,7 +18175,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H614" t="n">
         <v>600</v>
@@ -18204,7 +18204,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.73517608642578</v>
+        <v>7.7351770401001</v>
       </c>
       <c r="H615" t="n">
         <v>1200</v>
@@ -18233,7 +18233,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H616" t="n">
         <v>200</v>
@@ -18291,7 +18291,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G618" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H618" t="n">
         <v>1600</v>
@@ -18378,7 +18378,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H621" t="n">
         <v>100</v>
@@ -18407,7 +18407,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H622" t="n">
         <v>100</v>
@@ -18465,7 +18465,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G624" t="n">
-        <v>7.51666831970215</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H624" t="n">
         <v>3600</v>
@@ -18494,7 +18494,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H625" t="n">
         <v>1000</v>
@@ -18523,7 +18523,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G626" t="n">
-        <v>7.51666831970215</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H626" t="n">
         <v>6200</v>
@@ -18842,7 +18842,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25446033477783</v>
       </c>
       <c r="H637" t="n">
         <v>5700</v>
@@ -18871,7 +18871,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25446033477783</v>
       </c>
       <c r="H638" t="n">
         <v>600</v>
@@ -18900,7 +18900,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H639" t="n">
         <v>1100</v>
@@ -19016,7 +19016,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25446033477783</v>
       </c>
       <c r="H643" t="n">
         <v>11600</v>
@@ -19393,7 +19393,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G656" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H656" t="n">
         <v>1100</v>
@@ -19480,7 +19480,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H659" t="n">
         <v>5400</v>
@@ -19509,7 +19509,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25446033477783</v>
       </c>
       <c r="H660" t="n">
         <v>8800</v>
@@ -19538,7 +19538,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G661" t="n">
-        <v>7.03595161437988</v>
+        <v>7.03595113754272</v>
       </c>
       <c r="H661" t="n">
         <v>11500</v>
@@ -19567,7 +19567,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H662" t="n">
         <v>7300</v>
@@ -19625,7 +19625,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G664" t="n">
-        <v>7.25445985794067</v>
+        <v>7.25446033477783</v>
       </c>
       <c r="H664" t="n">
         <v>3400</v>
@@ -19654,7 +19654,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556337356567</v>
+        <v>7.38556385040283</v>
       </c>
       <c r="H665" t="n">
         <v>18900</v>
@@ -19712,7 +19712,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>7.69147491455078</v>
+        <v>7.69147443771362</v>
       </c>
       <c r="H667" t="n">
         <v>5600</v>
@@ -19741,7 +19741,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G668" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H669" t="n">
         <v>6200</v>
@@ -19799,7 +19799,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H670" t="n">
         <v>2100</v>
@@ -19915,7 +19915,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H674" t="n">
         <v>2900</v>
@@ -19944,7 +19944,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H675" t="n">
         <v>1300</v>
@@ -19973,7 +19973,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H676" t="n">
         <v>2300</v>
@@ -20002,7 +20002,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.8662805557251</v>
+        <v>7.86628198623657</v>
       </c>
       <c r="H677" t="n">
         <v>1800</v>
@@ -20031,7 +20031,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H678" t="n">
         <v>1500</v>
@@ -20147,7 +20147,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H682" t="n">
         <v>1900</v>
@@ -20176,7 +20176,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G683" t="n">
-        <v>7.51666831970215</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H683" t="n">
         <v>2100</v>
@@ -20205,7 +20205,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738597869873</v>
+        <v>7.99738550186157</v>
       </c>
       <c r="H684" t="n">
         <v>3100</v>
@@ -20292,7 +20292,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777374267578</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H687" t="n">
         <v>1500</v>
@@ -20350,7 +20350,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G689" t="n">
-        <v>7.51666831970215</v>
+        <v>7.51666927337646</v>
       </c>
       <c r="H689" t="n">
         <v>12600</v>
@@ -20524,7 +20524,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738597869873</v>
+        <v>7.99738550186157</v>
       </c>
       <c r="H695" t="n">
         <v>5300</v>
@@ -20640,7 +20640,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H699" t="n">
         <v>6500</v>
@@ -20669,7 +20669,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G700" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H700" t="n">
         <v>4100</v>
@@ -20698,7 +20698,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H701" t="n">
         <v>3600</v>
@@ -20727,7 +20727,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H702" t="n">
         <v>1900</v>
@@ -20756,7 +20756,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H703" t="n">
         <v>1400</v>
@@ -20785,7 +20785,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H704" t="n">
         <v>300</v>
@@ -20814,7 +20814,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G705" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H705" t="n">
         <v>900</v>
@@ -20843,7 +20843,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H706" t="n">
         <v>300</v>
@@ -20901,7 +20901,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G708" t="n">
-        <v>8.12276458740234</v>
+        <v>8.12276363372803</v>
       </c>
       <c r="H708" t="n">
         <v>1500</v>
@@ -20959,7 +20959,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H710" t="n">
         <v>1600</v>
@@ -21191,7 +21191,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H718" t="n">
         <v>2600</v>
@@ -21220,7 +21220,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H719" t="n">
         <v>900</v>
@@ -21249,7 +21249,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G720" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H720" t="n">
         <v>1200</v>
@@ -21278,7 +21278,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H721" t="n">
         <v>6800</v>
@@ -21307,7 +21307,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H722" t="n">
         <v>55000</v>
@@ -21336,7 +21336,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H723" t="n">
         <v>26400</v>
@@ -21365,7 +21365,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H724" t="n">
         <v>21400</v>
@@ -21394,7 +21394,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H725" t="n">
         <v>70900</v>
@@ -21423,7 +21423,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H726" t="n">
         <v>38600</v>
@@ -21452,7 +21452,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H727" t="n">
         <v>100</v>
@@ -21481,7 +21481,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H728" t="n">
         <v>4500</v>
@@ -21510,7 +21510,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H729" t="n">
         <v>5100</v>
@@ -21539,7 +21539,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H730" t="n">
         <v>1200</v>
@@ -21568,7 +21568,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H731" t="n">
         <v>300</v>
@@ -21597,7 +21597,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H732" t="n">
         <v>2600</v>
@@ -21626,7 +21626,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G733" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H733" t="n">
         <v>6400</v>
@@ -21655,7 +21655,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H734" t="n">
         <v>12300</v>
@@ -21684,7 +21684,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H735" t="n">
         <v>6900</v>
@@ -21713,7 +21713,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H736" t="n">
         <v>3000</v>
@@ -21742,7 +21742,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G737" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G738" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H738" t="n">
         <v>100</v>
@@ -21829,7 +21829,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G740" t="n">
-        <v>8.12276458740234</v>
+        <v>8.12276363372803</v>
       </c>
       <c r="H740" t="n">
         <v>3700</v>
@@ -21887,7 +21887,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H742" t="n">
         <v>7300</v>
@@ -21945,7 +21945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G744" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H744" t="n">
         <v>7400</v>
@@ -22003,7 +22003,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H746" t="n">
         <v>6800</v>
@@ -22032,7 +22032,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G747" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H747" t="n">
         <v>100</v>
@@ -22061,7 +22061,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H748" t="n">
         <v>700</v>
@@ -22119,7 +22119,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H750" t="n">
         <v>5400</v>
@@ -22148,7 +22148,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G751" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H751" t="n">
         <v>2100</v>
@@ -22177,7 +22177,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H752" t="n">
         <v>7900</v>
@@ -22206,7 +22206,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H753" t="n">
         <v>33700</v>
@@ -22235,7 +22235,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G754" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H754" t="n">
         <v>34600</v>
@@ -22264,7 +22264,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H755" t="n">
         <v>33100</v>
@@ -22380,7 +22380,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G759" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H759" t="n">
         <v>2600</v>
@@ -22409,7 +22409,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G760" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H760" t="n">
         <v>900</v>
@@ -22438,7 +22438,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G761" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H761" t="n">
         <v>3200</v>
@@ -22467,7 +22467,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G762" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G763" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H763" t="n">
         <v>1000</v>
@@ -22525,7 +22525,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G764" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H764" t="n">
         <v>2200</v>
@@ -22554,7 +22554,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G765" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H765" t="n">
         <v>2400</v>
@@ -22583,7 +22583,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G766" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H766" t="n">
         <v>8900</v>
@@ -22612,7 +22612,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G767" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H767" t="n">
         <v>600</v>
@@ -22641,7 +22641,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G768" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H768" t="n">
         <v>1100</v>
@@ -22757,7 +22757,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G772" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H772" t="n">
         <v>2900</v>
@@ -22786,7 +22786,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G773" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H773" t="n">
         <v>11900</v>
@@ -22815,7 +22815,7 @@
         <v>10</v>
       </c>
       <c r="G774" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H774" t="n">
         <v>23000</v>
@@ -22844,7 +22844,7 @@
         <v>10</v>
       </c>
       <c r="G775" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H775" t="n">
         <v>13400</v>
@@ -22960,7 +22960,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>9.96272659301758</v>
+        <v>9.96272754669189</v>
       </c>
       <c r="H779" t="n">
         <v>29900</v>
@@ -22989,7 +22989,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G780" t="n">
-        <v>9.60371017456055</v>
+        <v>9.60370922088623</v>
       </c>
       <c r="H780" t="n">
         <v>22300</v>
@@ -23105,7 +23105,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>9.69346332550049</v>
+        <v>9.6934642791748</v>
       </c>
       <c r="H784" t="n">
         <v>22700</v>
@@ -23134,7 +23134,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G785" t="n">
-        <v>9.69346332550049</v>
+        <v>9.6934642791748</v>
       </c>
       <c r="H785" t="n">
         <v>6500</v>
@@ -23163,7 +23163,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G786" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H786" t="n">
         <v>12700</v>
@@ -23250,7 +23250,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G789" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H789" t="n">
         <v>5100</v>
@@ -23279,7 +23279,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H790" t="n">
         <v>4700</v>
@@ -23308,7 +23308,7 @@
         <v>10</v>
       </c>
       <c r="G791" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H791" t="n">
         <v>7300</v>
@@ -23337,7 +23337,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G792" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H792" t="n">
         <v>18900</v>
@@ -23366,7 +23366,7 @@
         <v>10</v>
       </c>
       <c r="G793" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H793" t="n">
         <v>7200</v>
@@ -23395,7 +23395,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H794" t="n">
         <v>3700</v>
@@ -23424,7 +23424,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G795" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H795" t="n">
         <v>500</v>
@@ -23482,7 +23482,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G797" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H797" t="n">
         <v>1700</v>
@@ -23569,7 +23569,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G800" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H800" t="n">
         <v>1400</v>
@@ -23598,7 +23598,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G801" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H801" t="n">
         <v>0</v>
@@ -23656,7 +23656,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G803" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H803" t="n">
         <v>5800</v>
@@ -23714,7 +23714,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G805" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H805" t="n">
         <v>1100</v>
@@ -23743,7 +23743,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G806" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H806" t="n">
         <v>4300</v>
@@ -23772,7 +23772,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G807" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H807" t="n">
         <v>9500</v>
@@ -23830,7 +23830,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G809" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H809" t="n">
         <v>7800</v>
@@ -23859,7 +23859,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G810" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G811" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H811" t="n">
         <v>1800</v>
@@ -23917,7 +23917,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G812" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H812" t="n">
         <v>600</v>
@@ -23975,7 +23975,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G814" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H814" t="n">
         <v>200</v>
@@ -24004,7 +24004,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H815" t="n">
         <v>1400</v>
@@ -24033,7 +24033,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G816" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H816" t="n">
         <v>200</v>
@@ -24062,7 +24062,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G817" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H817" t="n">
         <v>8500</v>
@@ -24120,7 +24120,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G819" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H819" t="n">
         <v>1100</v>
@@ -24149,7 +24149,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G820" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H820" t="n">
         <v>4900</v>
@@ -24178,7 +24178,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G821" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H821" t="n">
         <v>2900</v>
@@ -24236,7 +24236,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H823" t="n">
         <v>2700</v>
@@ -24265,7 +24265,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H824" t="n">
         <v>1900</v>
@@ -24294,7 +24294,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H825" t="n">
         <v>14600</v>
@@ -24323,7 +24323,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H826" t="n">
         <v>44000</v>
@@ -24381,7 +24381,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G828" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H828" t="n">
         <v>9700</v>
@@ -24555,7 +24555,7 @@
         <v>10</v>
       </c>
       <c r="G834" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H834" t="n">
         <v>5900</v>
@@ -24613,7 +24613,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G836" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H836" t="n">
         <v>2600</v>
@@ -24642,7 +24642,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H837" t="n">
         <v>3000</v>
@@ -24671,7 +24671,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G838" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H838" t="n">
         <v>11100</v>
@@ -24758,7 +24758,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G841" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H841" t="n">
         <v>3500</v>
@@ -24903,7 +24903,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H846" t="n">
         <v>2100</v>
@@ -24932,7 +24932,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G847" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H847" t="n">
         <v>1100</v>
@@ -24961,7 +24961,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G848" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H848" t="n">
         <v>2000</v>
@@ -25106,7 +25106,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H853" t="n">
         <v>1200</v>
@@ -25135,7 +25135,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G854" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H854" t="n">
         <v>1100</v>
@@ -25164,7 +25164,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G855" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H855" t="n">
         <v>1800</v>
@@ -25193,7 +25193,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G856" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H856" t="n">
         <v>4000</v>
@@ -25280,7 +25280,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G859" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H859" t="n">
         <v>3300</v>
@@ -25309,7 +25309,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H860" t="n">
         <v>8600</v>
@@ -25338,7 +25338,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G861" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H861" t="n">
         <v>3500</v>
@@ -25367,7 +25367,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G862" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H862" t="n">
         <v>1000</v>
@@ -25396,7 +25396,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G863" t="n">
-        <v>8.84079933166504</v>
+        <v>8.84079837799072</v>
       </c>
       <c r="H863" t="n">
         <v>6800</v>
@@ -25454,7 +25454,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H865" t="n">
         <v>3700</v>
@@ -25512,7 +25512,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H867" t="n">
         <v>20600</v>
@@ -25570,7 +25570,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G869" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H869" t="n">
         <v>13500</v>
@@ -25599,7 +25599,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>9.2446928024292</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H870" t="n">
         <v>25600</v>
@@ -25657,7 +25657,7 @@
         <v>10</v>
       </c>
       <c r="G872" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H872" t="n">
         <v>1500</v>
@@ -25686,7 +25686,7 @@
         <v>10</v>
       </c>
       <c r="G873" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H873" t="n">
         <v>3200</v>
@@ -25715,7 +25715,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G874" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H874" t="n">
         <v>4300</v>
@@ -25744,7 +25744,7 @@
         <v>10</v>
       </c>
       <c r="G875" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H875" t="n">
         <v>7800</v>
@@ -25773,7 +25773,7 @@
         <v>10</v>
       </c>
       <c r="G876" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H876" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G877" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H877" t="n">
         <v>1200</v>
@@ -25918,7 +25918,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H881" t="n">
         <v>21200</v>
@@ -26092,7 +26092,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>9.33444595336914</v>
+        <v>9.33444690704346</v>
       </c>
       <c r="H887" t="n">
         <v>10800</v>
@@ -26150,7 +26150,7 @@
         <v>10</v>
       </c>
       <c r="G889" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H889" t="n">
         <v>15100</v>
@@ -26411,7 +26411,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G898" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H898" t="n">
         <v>400</v>
@@ -26469,7 +26469,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H900" t="n">
         <v>3000</v>
@@ -26498,7 +26498,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G901" t="n">
-        <v>8.43690299987793</v>
+        <v>8.43690395355225</v>
       </c>
       <c r="H901" t="n">
         <v>6700</v>
@@ -26527,7 +26527,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G902" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H902" t="n">
         <v>3900</v>
@@ -26556,7 +26556,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H903" t="n">
         <v>1300</v>
@@ -26643,7 +26643,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>8.12276458740234</v>
+        <v>8.12276363372803</v>
       </c>
       <c r="H906" t="n">
         <v>5400</v>
@@ -26788,7 +26788,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.35985231399536</v>
+        <v>7.3598518371582</v>
       </c>
       <c r="H911" t="n">
         <v>12900</v>
@@ -26817,7 +26817,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G912" t="n">
-        <v>7.58423709869385</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H912" t="n">
         <v>2900</v>
@@ -26846,7 +26846,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G913" t="n">
-        <v>7.58423709869385</v>
+        <v>7.58423805236816</v>
       </c>
       <c r="H913" t="n">
         <v>5400</v>
@@ -26933,7 +26933,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H916" t="n">
         <v>2500</v>
@@ -27107,7 +27107,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G922" t="n">
-        <v>8.57153511047363</v>
+        <v>8.57153606414795</v>
       </c>
       <c r="H922" t="n">
         <v>2700</v>
@@ -27136,7 +27136,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G923" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H923" t="n">
         <v>1200</v>
@@ -27223,7 +27223,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G926" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H926" t="n">
         <v>1200</v>
@@ -27252,7 +27252,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G927" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H927" t="n">
         <v>1100</v>
@@ -27281,7 +27281,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G928" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H928" t="n">
         <v>300</v>
@@ -27310,7 +27310,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G929" t="n">
-        <v>8.66128921508789</v>
+        <v>8.66129016876221</v>
       </c>
       <c r="H929" t="n">
         <v>2500</v>
@@ -27339,7 +27339,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G930" t="n">
-        <v>8.88567543029785</v>
+        <v>8.88567447662354</v>
       </c>
       <c r="H930" t="n">
         <v>5000</v>
@@ -27368,7 +27368,7 @@
         <v>10</v>
       </c>
       <c r="G931" t="n">
-        <v>8.97543048858643</v>
+        <v>8.97542953491211</v>
       </c>
       <c r="H931" t="n">
         <v>600</v>
@@ -27397,7 +27397,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231418609619</v>
+        <v>8.65231513977051</v>
       </c>
       <c r="H932" t="n">
         <v>500</v>
@@ -27455,7 +27455,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.54461002349854</v>
+        <v>8.54460906982422</v>
       </c>
       <c r="H934" t="n">
         <v>26000</v>
@@ -27513,7 +27513,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821716308594</v>
+        <v>8.68821620941162</v>
       </c>
       <c r="H936" t="n">
         <v>15100</v>
@@ -27658,7 +27658,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G941" t="n">
-        <v>8.25739574432373</v>
+        <v>8.25739479064941</v>
       </c>
       <c r="H941" t="n">
         <v>3000</v>
@@ -27919,7 +27919,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G950" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H950" t="n">
         <v>1300</v>
@@ -27948,7 +27948,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>9.3015022277832</v>
+        <v>9.30150318145752</v>
       </c>
       <c r="H951" t="n">
         <v>5000</v>
@@ -28006,7 +28006,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G953" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H953" t="n">
         <v>2400</v>
@@ -28093,7 +28093,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H956" t="n">
         <v>18400</v>
@@ -28354,7 +28354,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G965" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H965" t="n">
         <v>100</v>
@@ -28499,7 +28499,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>8.78577518463135</v>
+        <v>8.78577613830566</v>
       </c>
       <c r="H970" t="n">
         <v>5800</v>
@@ -28731,7 +28731,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G978" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H978" t="n">
         <v>18000</v>
@@ -28789,7 +28789,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H980" t="n">
         <v>5400</v>
@@ -28934,7 +28934,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H985" t="n">
         <v>1600</v>
@@ -28963,7 +28963,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -29108,7 +29108,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>8.14111614227295</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H991" t="n">
         <v>1100</v>
@@ -29137,7 +29137,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H992" t="n">
         <v>3200</v>
@@ -29253,7 +29253,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G996" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H996" t="n">
         <v>800</v>
@@ -29311,7 +29311,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G998" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H998" t="n">
         <v>600</v>
@@ -29340,7 +29340,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G999" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H999" t="n">
         <v>1100</v>
@@ -29398,7 +29398,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1001" t="n">
         <v>900</v>
@@ -29427,7 +29427,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1002" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1002" t="n">
         <v>2700</v>
@@ -29572,7 +29572,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423603057861</v>
+        <v>8.45423698425293</v>
       </c>
       <c r="H1007" t="n">
         <v>100</v>
@@ -29630,7 +29630,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1009" t="n">
         <v>2700</v>
@@ -29659,7 +29659,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29949,7 +29949,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1020" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1020" t="n">
         <v>1400</v>
@@ -29978,7 +29978,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1021" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -30007,7 +30007,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1022" t="n">
         <v>100</v>
@@ -30065,7 +30065,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1024" t="n">
         <v>1000</v>
@@ -30123,7 +30123,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1026" t="n">
         <v>300</v>
@@ -30239,7 +30239,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1030" t="n">
         <v>300</v>
@@ -30355,7 +30355,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1034" t="n">
         <v>3900</v>
@@ -30384,7 +30384,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.88325452804565</v>
+        <v>7.88325357437134</v>
       </c>
       <c r="H1035" t="n">
         <v>600</v>
@@ -30413,7 +30413,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.01218414306641</v>
+        <v>8.01218509674072</v>
       </c>
       <c r="H1036" t="n">
         <v>300</v>
@@ -30442,7 +30442,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.01218414306641</v>
+        <v>8.01218509674072</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -30587,7 +30587,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.14111614227295</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H1042" t="n">
         <v>7000</v>
@@ -30616,7 +30616,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1043" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1043" t="n">
         <v>2400</v>
@@ -30674,7 +30674,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1045" t="n">
         <v>2000</v>
@@ -30703,7 +30703,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1046" t="n">
         <v>900</v>
@@ -30732,7 +30732,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1047" t="n">
         <v>500</v>
@@ -30761,7 +30761,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1050" t="n">
         <v>11300</v>
@@ -30848,7 +30848,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30993,7 +30993,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1056" t="n">
         <v>300</v>
@@ -31138,7 +31138,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1061" t="n">
         <v>700</v>
@@ -31167,7 +31167,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1062" t="n">
         <v>800</v>
@@ -31312,7 +31312,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1067" t="n">
         <v>3400</v>
@@ -31341,7 +31341,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -31370,7 +31370,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1069" t="n">
         <v>1000</v>
@@ -31399,7 +31399,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1070" t="n">
         <v>2800</v>
@@ -31631,7 +31631,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1078" t="n">
         <v>800</v>
@@ -31834,7 +31834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.859450340271</v>
+        <v>8.85945129394531</v>
       </c>
       <c r="H1085" t="n">
         <v>2600</v>
@@ -31892,7 +31892,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1087" t="n">
         <v>300</v>
@@ -31921,7 +31921,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1088" t="n">
         <v>100</v>
@@ -31950,7 +31950,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1090" t="n">
         <v>200</v>
@@ -32153,7 +32153,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1096" t="n">
         <v>1900</v>
@@ -32385,7 +32385,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1104" t="n">
         <v>2200</v>
@@ -32559,7 +32559,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1110" t="n">
         <v>22300</v>
@@ -32675,7 +32675,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1114" t="n">
         <v>1100</v>
@@ -32704,7 +32704,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1115" t="n">
         <v>5200</v>
@@ -32965,7 +32965,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1124" t="n">
         <v>7600</v>
@@ -32994,7 +32994,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1125" t="n">
         <v>11000</v>
@@ -33226,7 +33226,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1133" t="n">
         <v>700</v>
@@ -33255,7 +33255,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1134" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1134" t="n">
         <v>0</v>
@@ -33284,7 +33284,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1135" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1135" t="n">
         <v>100</v>
@@ -33313,7 +33313,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1136" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1136" t="n">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1139" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1139" t="n">
         <v>3300</v>
@@ -33429,7 +33429,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1140" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1140" t="n">
         <v>1000</v>
@@ -33487,7 +33487,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1142" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1142" t="n">
         <v>300</v>
@@ -33574,7 +33574,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1145" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1145" t="n">
         <v>2300</v>
@@ -33603,7 +33603,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1146" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1146" t="n">
         <v>1600</v>
@@ -33719,7 +33719,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1150" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1150" t="n">
         <v>2300</v>
@@ -33864,7 +33864,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1155" t="n">
         <v>100</v>
@@ -33893,7 +33893,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H1156" t="n">
         <v>200</v>
@@ -33980,7 +33980,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1159" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1159" t="n">
         <v>4200</v>
@@ -34183,7 +34183,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1166" t="n">
         <v>100</v>
@@ -34212,7 +34212,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1167" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1168" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>
@@ -34270,7 +34270,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1169" t="n">
         <v>0</v>
@@ -34299,7 +34299,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1170" t="n">
         <v>100</v>
@@ -34328,7 +34328,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1171" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1174" t="n">
         <v>100</v>
@@ -34705,7 +34705,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1184" t="n">
         <v>900</v>
@@ -34792,7 +34792,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1187" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1187" t="n">
         <v>300</v>
@@ -34821,7 +34821,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1188" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1188" t="n">
         <v>0</v>
@@ -34850,7 +34850,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1189" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1189" t="n">
         <v>100</v>
@@ -35169,7 +35169,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1200" t="n">
         <v>100</v>
@@ -35198,7 +35198,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.15953636169434</v>
+        <v>8.15953540802002</v>
       </c>
       <c r="H1201" t="n">
         <v>900</v>
@@ -35227,7 +35227,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.15953636169434</v>
+        <v>8.15953540802002</v>
       </c>
       <c r="H1202" t="n">
         <v>300</v>
@@ -35256,7 +35256,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1203" t="n">
         <v>700</v>
@@ -35430,7 +35430,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590326309204</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1209" t="n">
         <v>2000</v>
@@ -35546,7 +35546,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.6069712638855</v>
+        <v>7.60697174072266</v>
       </c>
       <c r="H1213" t="n">
         <v>500</v>
@@ -35691,7 +35691,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1218" t="n">
-        <v>7.22017621994019</v>
+        <v>7.22017669677734</v>
       </c>
       <c r="H1218" t="n">
         <v>19000</v>
@@ -35720,7 +35720,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.05440664291382</v>
+        <v>7.05440616607666</v>
       </c>
       <c r="H1219" t="n">
         <v>4300</v>
@@ -35749,7 +35749,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>7.1833381652832</v>
+        <v>7.18333864212036</v>
       </c>
       <c r="H1220" t="n">
         <v>200</v>
@@ -35894,7 +35894,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.1833381652832</v>
+        <v>7.18333864212036</v>
       </c>
       <c r="H1225" t="n">
         <v>2600</v>
@@ -36039,7 +36039,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>7.6069712638855</v>
+        <v>7.60697174072266</v>
       </c>
       <c r="H1230" t="n">
         <v>9400</v>
@@ -36097,7 +36097,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590326309204</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1232" t="n">
         <v>200</v>
@@ -36155,7 +36155,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1234" t="n">
         <v>21900</v>
@@ -60985,6 +60985,35 @@
         <v>2200</v>
       </c>
       <c r="I2090" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2091" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="G2091" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="H2091" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2091" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -485,7 +485,7 @@
         <v>9.70100021362305</v>
       </c>
       <c r="G4" t="n">
-        <v>8.2321195602417</v>
+        <v>8.23212051391602</v>
       </c>
       <c r="H4" t="n">
         <v>4100</v>
@@ -543,7 +543,7 @@
         <v>9.61100006103516</v>
       </c>
       <c r="G6" t="n">
-        <v>8.15574836730957</v>
+        <v>8.15574741363525</v>
       </c>
       <c r="H6" t="n">
         <v>14900</v>
@@ -572,7 +572,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G7" t="n">
-        <v>8.18035793304443</v>
+        <v>8.18035697937012</v>
       </c>
       <c r="H7" t="n">
         <v>6500</v>
@@ -601,7 +601,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11246967315674</v>
+        <v>8.11247062683105</v>
       </c>
       <c r="H8" t="n">
         <v>7000</v>
@@ -630,7 +630,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H9" t="n">
         <v>3500</v>
@@ -659,7 +659,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -746,7 +746,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -804,7 +804,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -833,7 +833,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10059070587158</v>
       </c>
       <c r="H17" t="n">
         <v>1300</v>
@@ -891,7 +891,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10059070587158</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H19" t="n">
         <v>9600</v>
@@ -949,7 +949,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549999237061</v>
+        <v>8.09549903869629</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10653018951416</v>
+        <v>8.10653114318848</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.1379280090332</v>
+        <v>8.13792896270752</v>
       </c>
       <c r="H22" t="n">
         <v>300</v>
@@ -1123,7 +1123,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G26" t="n">
-        <v>8.20666313171387</v>
+        <v>8.20666217803955</v>
       </c>
       <c r="H26" t="n">
         <v>200</v>
@@ -1152,7 +1152,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G27" t="n">
-        <v>8.20666313171387</v>
+        <v>8.20666217803955</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H30" t="n">
         <v>7500</v>
@@ -1297,7 +1297,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10058879852295</v>
+        <v>8.10059070587158</v>
       </c>
       <c r="H32" t="n">
         <v>200</v>
@@ -1326,7 +1326,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.07513332366943</v>
+        <v>8.07513236999512</v>
       </c>
       <c r="H33" t="n">
         <v>8000</v>
@@ -1413,7 +1413,7 @@
         <v>9.44699954986572</v>
       </c>
       <c r="G36" t="n">
-        <v>8.01657962799072</v>
+        <v>8.01657867431641</v>
       </c>
       <c r="H36" t="n">
         <v>2900</v>
@@ -1442,7 +1442,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366903305054</v>
+        <v>7.9936695098877</v>
       </c>
       <c r="H37" t="n">
         <v>12300</v>
@@ -1471,7 +1471,7 @@
         <v>9.37100028991699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.95208787918091</v>
+        <v>7.95208835601807</v>
       </c>
       <c r="H38" t="n">
         <v>500</v>
@@ -1529,7 +1529,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227073669434</v>
+        <v>7.96227121353149</v>
       </c>
       <c r="H40" t="n">
         <v>300</v>
@@ -1558,7 +1558,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227073669434</v>
+        <v>7.96227121353149</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.97924280166626</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H42" t="n">
         <v>300</v>
@@ -1616,7 +1616,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.97924280166626</v>
+        <v>7.9792423248291</v>
       </c>
       <c r="H43" t="n">
         <v>1700</v>
@@ -1645,7 +1645,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G44" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H44" t="n">
         <v>600</v>
@@ -1674,7 +1674,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G45" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H46" t="n">
         <v>8000</v>
@@ -1732,7 +1732,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1790,7 +1790,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729593276978</v>
+        <v>7.9172945022583</v>
       </c>
       <c r="H49" t="n">
         <v>9200</v>
@@ -1819,7 +1819,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619831085205</v>
+        <v>7.85619878768921</v>
       </c>
       <c r="H50" t="n">
         <v>8700</v>
@@ -1848,7 +1848,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H51" t="n">
         <v>16700</v>
@@ -1906,7 +1906,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.77473258972168</v>
+        <v>7.77473402023315</v>
       </c>
       <c r="H53" t="n">
         <v>2300</v>
@@ -2022,7 +2022,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H57" t="n">
         <v>12300</v>
@@ -2080,7 +2080,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76454973220825</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H59" t="n">
         <v>13600</v>
@@ -2138,7 +2138,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H61" t="n">
         <v>4900</v>
@@ -2167,7 +2167,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H62" t="n">
         <v>8400</v>
@@ -2196,7 +2196,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539897918701</v>
       </c>
       <c r="H64" t="n">
         <v>1600</v>
@@ -2283,7 +2283,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H66" t="n">
         <v>2500</v>
@@ -2312,7 +2312,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>9.20699977874756</v>
       </c>
       <c r="G69" t="n">
-        <v>7.81291961669922</v>
+        <v>7.81292009353638</v>
       </c>
       <c r="H69" t="n">
         <v>200</v>
@@ -2399,7 +2399,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.80528163909912</v>
+        <v>7.80528211593628</v>
       </c>
       <c r="H70" t="n">
         <v>1000</v>
@@ -2428,7 +2428,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722946166992</v>
+        <v>7.86722898483276</v>
       </c>
       <c r="H71" t="n">
         <v>800</v>
@@ -2573,7 +2573,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761268615723</v>
+        <v>8.02761077880859</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2602,7 +2602,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177303314209</v>
+        <v>7.84177255630493</v>
       </c>
       <c r="H77" t="n">
         <v>4000</v>
@@ -2631,7 +2631,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.79085636138916</v>
+        <v>7.790855884552</v>
       </c>
       <c r="H78" t="n">
         <v>800</v>
@@ -2689,7 +2689,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243751525879</v>
       </c>
       <c r="H80" t="n">
         <v>1600</v>
@@ -2718,7 +2718,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358505249023</v>
+        <v>7.80358600616455</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406715393066</v>
+        <v>7.78406858444214</v>
       </c>
       <c r="H82" t="n">
         <v>200</v>
@@ -2776,7 +2776,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539897918701</v>
       </c>
       <c r="H83" t="n">
         <v>1100</v>
@@ -2805,7 +2805,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539897918701</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539897918701</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.80103969573975</v>
+        <v>7.80103921890259</v>
       </c>
       <c r="H86" t="n">
         <v>2900</v>
@@ -2892,7 +2892,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G87" t="n">
-        <v>7.81037378311157</v>
+        <v>7.81037425994873</v>
       </c>
       <c r="H87" t="n">
         <v>2500</v>
@@ -2921,7 +2921,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098882675171</v>
+        <v>7.89098930358887</v>
       </c>
       <c r="H88" t="n">
         <v>200</v>
@@ -2950,7 +2950,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782747268677</v>
+        <v>7.80782794952393</v>
       </c>
       <c r="H89" t="n">
         <v>5100</v>
@@ -2979,7 +2979,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.76879215240479</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.76879215240479</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H91" t="n">
         <v>700</v>
@@ -3037,7 +3037,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408466339111</v>
+        <v>7.92408561706543</v>
       </c>
       <c r="H92" t="n">
         <v>1200</v>
@@ -3066,7 +3066,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.77049016952515</v>
+        <v>7.77048969268799</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3095,7 +3095,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539850234985</v>
+        <v>7.76539897918701</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3124,7 +3124,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76454973220825</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H95" t="n">
         <v>20300</v>
@@ -3153,7 +3153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76454973220825</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70514869689941</v>
+        <v>7.70514917373657</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969131469727</v>
+        <v>7.67969274520874</v>
       </c>
       <c r="H100" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969131469727</v>
+        <v>7.67969274520874</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726329803467</v>
+        <v>7.63726282119751</v>
       </c>
       <c r="H102" t="n">
         <v>700</v>
@@ -3356,7 +3356,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423583984375</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423488616943</v>
+        <v>7.65423583984375</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>9.10099983215332</v>
       </c>
       <c r="G108" t="n">
-        <v>7.72297048568726</v>
+        <v>7.72296953201294</v>
       </c>
       <c r="H108" t="n">
         <v>2200</v>
@@ -3559,7 +3559,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363544464111</v>
+        <v>7.71363496780396</v>
       </c>
       <c r="H110" t="n">
         <v>10000</v>
@@ -3588,7 +3588,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70514869689941</v>
+        <v>7.70514917373657</v>
       </c>
       <c r="H111" t="n">
         <v>25500</v>
@@ -3617,7 +3617,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70514869689941</v>
+        <v>7.70514917373657</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817806243896</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H113" t="n">
         <v>15900</v>
@@ -3675,7 +3675,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969131469727</v>
+        <v>7.67969274520874</v>
       </c>
       <c r="H114" t="n">
         <v>100</v>
@@ -3704,7 +3704,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902587890625</v>
+        <v>7.68902635574341</v>
       </c>
       <c r="H115" t="n">
         <v>1500</v>
@@ -3733,7 +3733,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.8511061668396</v>
+        <v>7.85110664367676</v>
       </c>
       <c r="H116" t="n">
         <v>800</v>
@@ -3762,7 +3762,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273723602295</v>
+        <v>7.80273580551147</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -3791,7 +3791,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308544158936</v>
+        <v>7.68308639526367</v>
       </c>
       <c r="H118" t="n">
         <v>2400</v>
@@ -3907,7 +3907,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817806243896</v>
+        <v>7.68817853927612</v>
       </c>
       <c r="H122" t="n">
         <v>3300</v>
@@ -3936,7 +3936,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.76879215240479</v>
+        <v>7.7687931060791</v>
       </c>
       <c r="H123" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.86553144454956</v>
+        <v>7.86553192138672</v>
       </c>
       <c r="H125" t="n">
         <v>300</v>
@@ -4052,7 +4052,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406715393066</v>
+        <v>7.78406858444214</v>
       </c>
       <c r="H127" t="n">
         <v>2000</v>
@@ -4081,7 +4081,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76454973220825</v>
+        <v>7.76455020904541</v>
       </c>
       <c r="H128" t="n">
         <v>100</v>
@@ -4110,7 +4110,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303647994995</v>
+        <v>7.77303600311279</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303647994995</v>
+        <v>7.77303600311279</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243656158447</v>
+        <v>7.83243751525879</v>
       </c>
       <c r="H131" t="n">
         <v>5900</v>
@@ -4197,7 +4197,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.79849290847778</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H132" t="n">
         <v>300</v>
@@ -4226,7 +4226,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H133" t="n">
         <v>13900</v>
@@ -4255,7 +4255,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.7900071144104</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.7900071144104</v>
+        <v>7.79000759124756</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445180892944</v>
+        <v>7.94445037841797</v>
       </c>
       <c r="H136" t="n">
         <v>2500</v>
@@ -4371,7 +4371,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.79849290847778</v>
+        <v>7.7984938621521</v>
       </c>
       <c r="H138" t="n">
         <v>800</v>
@@ -4429,7 +4429,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G140" t="n">
-        <v>7.96311950683594</v>
+        <v>7.96311855316162</v>
       </c>
       <c r="H140" t="n">
         <v>500</v>
@@ -4632,7 +4632,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G147" t="n">
-        <v>8.06919288635254</v>
+        <v>8.06919193267822</v>
       </c>
       <c r="H147" t="n">
         <v>100</v>
@@ -4690,7 +4690,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579971313477</v>
+        <v>8.06579875946045</v>
       </c>
       <c r="H149" t="n">
         <v>300</v>
@@ -4719,7 +4719,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>7.92153930664062</v>
+        <v>7.92153835296631</v>
       </c>
       <c r="H150" t="n">
         <v>100</v>
@@ -4748,7 +4748,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.92153930664062</v>
+        <v>7.92153835296631</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G152" t="n">
-        <v>8.06919288635254</v>
+        <v>8.06919193267822</v>
       </c>
       <c r="H152" t="n">
         <v>700</v>
@@ -4806,7 +4806,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G153" t="n">
-        <v>8.06919288635254</v>
+        <v>8.06919193267822</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.92832708358765</v>
+        <v>7.92832803726196</v>
       </c>
       <c r="H154" t="n">
         <v>1100</v>
@@ -4980,7 +4980,7 @@
         <v>9.34700012207031</v>
       </c>
       <c r="G159" t="n">
-        <v>7.93172121047974</v>
+        <v>7.93172168731689</v>
       </c>
       <c r="H159" t="n">
         <v>800</v>
@@ -5067,7 +5067,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G162" t="n">
-        <v>7.92153930664062</v>
+        <v>7.92153835296631</v>
       </c>
       <c r="H162" t="n">
         <v>2300</v>
@@ -5096,7 +5096,7 @@
         <v>9.4040002822876</v>
       </c>
       <c r="G163" t="n">
-        <v>7.98009157180786</v>
+        <v>7.98009061813354</v>
       </c>
       <c r="H163" t="n">
         <v>500</v>
@@ -5183,7 +5183,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.92832708358765</v>
+        <v>7.92832803726196</v>
       </c>
       <c r="H166" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H167" t="n">
         <v>3300</v>
@@ -5241,7 +5241,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H168" t="n">
         <v>9400</v>
@@ -5270,7 +5270,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H169" t="n">
         <v>6900</v>
@@ -5299,7 +5299,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H170" t="n">
         <v>200</v>
@@ -5328,7 +5328,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H172" t="n">
         <v>3700</v>
@@ -5386,7 +5386,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H173" t="n">
         <v>200</v>
@@ -5415,7 +5415,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H174" t="n">
         <v>600</v>
@@ -5444,7 +5444,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H175" t="n">
         <v>300</v>
@@ -5473,7 +5473,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H176" t="n">
         <v>4900</v>
@@ -5502,7 +5502,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G177" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H177" t="n">
         <v>1900</v>
@@ -5531,7 +5531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H178" t="n">
         <v>300</v>
@@ -5560,7 +5560,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H179" t="n">
         <v>100</v>
@@ -5589,7 +5589,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G180" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H180" t="n">
         <v>3800</v>
@@ -5618,7 +5618,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H181" t="n">
         <v>5000</v>
@@ -5647,7 +5647,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H184" t="n">
         <v>300</v>
@@ -5734,7 +5734,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H185" t="n">
         <v>200</v>
@@ -5763,7 +5763,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H186" t="n">
         <v>700</v>
@@ -5792,7 +5792,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H187" t="n">
         <v>900</v>
@@ -5850,7 +5850,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H189" t="n">
         <v>1900</v>
@@ -5908,7 +5908,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H191" t="n">
         <v>5600</v>
@@ -5966,7 +5966,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H193" t="n">
         <v>3200</v>
@@ -5995,7 +5995,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H194" t="n">
         <v>300</v>
@@ -6082,7 +6082,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6111,7 +6111,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H198" t="n">
         <v>4700</v>
@@ -6140,7 +6140,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H200" t="n">
         <v>2000</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H201" t="n">
         <v>1500</v>
@@ -6227,7 +6227,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H202" t="n">
         <v>800</v>
@@ -6256,7 +6256,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H203" t="n">
         <v>100</v>
@@ -6285,7 +6285,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H204" t="n">
         <v>5900</v>
@@ -6343,7 +6343,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H206" t="n">
         <v>300</v>
@@ -6401,7 +6401,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6430,7 +6430,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G209" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6459,7 +6459,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H210" t="n">
         <v>600</v>
@@ -6546,7 +6546,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H213" t="n">
         <v>2600</v>
@@ -6575,7 +6575,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H214" t="n">
         <v>200</v>
@@ -6604,7 +6604,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H215" t="n">
         <v>6600</v>
@@ -6633,7 +6633,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H216" t="n">
         <v>100</v>
@@ -6662,7 +6662,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6691,7 +6691,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H218" t="n">
         <v>900</v>
@@ -6720,7 +6720,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6749,7 +6749,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H220" t="n">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H221" t="n">
         <v>17700</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H224" t="n">
         <v>800</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H225" t="n">
         <v>600</v>
@@ -6923,7 +6923,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H226" t="n">
         <v>100</v>
@@ -6952,7 +6952,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H227" t="n">
         <v>100</v>
@@ -6981,7 +6981,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H228" t="n">
         <v>9100</v>
@@ -7039,7 +7039,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7068,7 +7068,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7097,7 +7097,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H232" t="n">
         <v>5200</v>
@@ -7126,7 +7126,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H233" t="n">
         <v>5100</v>
@@ -7184,7 +7184,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H235" t="n">
         <v>300</v>
@@ -7329,7 +7329,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H240" t="n">
         <v>100</v>
@@ -7358,7 +7358,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H241" t="n">
         <v>400</v>
@@ -7387,7 +7387,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H242" t="n">
         <v>7200</v>
@@ -7416,7 +7416,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H243" t="n">
         <v>100</v>
@@ -7445,7 +7445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H244" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H248" t="n">
         <v>700</v>
@@ -7590,7 +7590,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H249" t="n">
         <v>600</v>
@@ -7619,7 +7619,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G250" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H250" t="n">
         <v>300</v>
@@ -7648,7 +7648,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H251" t="n">
         <v>2100</v>
@@ -7677,7 +7677,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H252" t="n">
         <v>1800</v>
@@ -7706,7 +7706,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H253" t="n">
         <v>1700</v>
@@ -7735,7 +7735,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H254" t="n">
         <v>1800</v>
@@ -7793,7 +7793,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G256" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H256" t="n">
         <v>2300</v>
@@ -7822,7 +7822,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H257" t="n">
         <v>100</v>
@@ -7851,7 +7851,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H258" t="n">
         <v>1200</v>
@@ -7880,7 +7880,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H259" t="n">
         <v>25000</v>
@@ -7909,7 +7909,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H263" t="n">
         <v>8000</v>
@@ -8025,7 +8025,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8054,7 +8054,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G265" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H265" t="n">
         <v>100</v>
@@ -8083,7 +8083,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G266" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8112,7 +8112,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G267" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H268" t="n">
         <v>11200</v>
@@ -8170,7 +8170,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H269" t="n">
         <v>600</v>
@@ -8228,7 +8228,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H272" t="n">
         <v>100</v>
@@ -8286,7 +8286,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H273" t="n">
         <v>100</v>
@@ -8315,7 +8315,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H274" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H276" t="n">
         <v>100</v>
@@ -8605,7 +8605,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H284" t="n">
         <v>6900</v>
@@ -8866,7 +8866,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G293" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H293" t="n">
         <v>100</v>
@@ -8895,7 +8895,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G294" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G295" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G296" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H296" t="n">
         <v>200</v>
@@ -9011,7 +9011,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H298" t="n">
         <v>10700</v>
@@ -9040,7 +9040,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9069,7 +9069,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H300" t="n">
         <v>100</v>
@@ -9243,7 +9243,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H309" t="n">
         <v>500</v>
@@ -9359,7 +9359,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H310" t="n">
         <v>3300</v>
@@ -9388,7 +9388,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H311" t="n">
         <v>100</v>
@@ -9417,7 +9417,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H312" t="n">
         <v>100</v>
@@ -9446,7 +9446,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H313" t="n">
         <v>12700</v>
@@ -9475,7 +9475,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H314" t="n">
         <v>7100</v>
@@ -9504,7 +9504,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H318" t="n">
         <v>300</v>
@@ -9736,7 +9736,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H323" t="n">
         <v>26700</v>
@@ -9765,7 +9765,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H324" t="n">
         <v>100</v>
@@ -9794,7 +9794,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H325" t="n">
         <v>20100</v>
@@ -9823,7 +9823,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G326" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H326" t="n">
         <v>100</v>
@@ -9852,7 +9852,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -9881,7 +9881,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H328" t="n">
         <v>52800</v>
@@ -9910,7 +9910,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H329" t="n">
         <v>10000</v>
@@ -9939,7 +9939,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H330" t="n">
         <v>200</v>
@@ -9968,7 +9968,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H331" t="n">
         <v>900</v>
@@ -9997,7 +9997,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H332" t="n">
         <v>10000</v>
@@ -10026,7 +10026,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H334" t="n">
         <v>100</v>
@@ -10084,7 +10084,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H335" t="n">
         <v>2200</v>
@@ -10113,7 +10113,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G336" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H336" t="n">
         <v>100</v>
@@ -10142,7 +10142,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G337" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H337" t="n">
         <v>100</v>
@@ -10171,7 +10171,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H338" t="n">
         <v>400</v>
@@ -10200,7 +10200,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H339" t="n">
         <v>6600</v>
@@ -10229,7 +10229,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H340" t="n">
         <v>400</v>
@@ -10258,7 +10258,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H341" t="n">
         <v>300</v>
@@ -10316,7 +10316,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H344" t="n">
         <v>1700</v>
@@ -10374,7 +10374,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G345" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G346" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H346" t="n">
         <v>3000</v>
@@ -10432,7 +10432,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G347" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G350" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H350" t="n">
         <v>4400</v>
@@ -10548,7 +10548,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H351" t="n">
         <v>1400</v>
@@ -10954,7 +10954,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H365" t="n">
         <v>100</v>
@@ -10983,7 +10983,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H367" t="n">
         <v>900</v>
@@ -11070,7 +11070,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H369" t="n">
         <v>100</v>
@@ -11099,7 +11099,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H371" t="n">
         <v>1700</v>
@@ -11157,7 +11157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H372" t="n">
         <v>1200</v>
@@ -11244,7 +11244,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H375" t="n">
         <v>5700</v>
@@ -11331,7 +11331,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H378" t="n">
         <v>30700</v>
@@ -11389,7 +11389,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G380" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H380" t="n">
         <v>15200</v>
@@ -11476,7 +11476,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G383" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H383" t="n">
         <v>800</v>
@@ -11563,7 +11563,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H386" t="n">
         <v>300</v>
@@ -11621,7 +11621,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H388" t="n">
         <v>800</v>
@@ -11650,7 +11650,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G389" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H389" t="n">
         <v>4300</v>
@@ -11679,7 +11679,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G390" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H390" t="n">
         <v>300</v>
@@ -11911,7 +11911,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H398" t="n">
         <v>1100</v>
@@ -11998,7 +11998,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H401" t="n">
         <v>7500</v>
@@ -12027,7 +12027,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H402" t="n">
         <v>700</v>
@@ -12056,7 +12056,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H403" t="n">
         <v>2200</v>
@@ -12085,7 +12085,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H404" t="n">
         <v>300</v>
@@ -12114,7 +12114,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H405" t="n">
         <v>100</v>
@@ -12143,7 +12143,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H406" t="n">
         <v>11100</v>
@@ -12172,7 +12172,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G407" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H407" t="n">
         <v>11800</v>
@@ -12201,7 +12201,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G408" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H408" t="n">
         <v>1000</v>
@@ -12230,7 +12230,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G409" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H409" t="n">
         <v>2800</v>
@@ -12259,7 +12259,7 @@
         <v>9.25</v>
       </c>
       <c r="G410" t="n">
-        <v>7.84940958023071</v>
+        <v>7.84940910339355</v>
       </c>
       <c r="H410" t="n">
         <v>13800</v>
@@ -12288,7 +12288,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12317,7 +12317,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G412" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H412" t="n">
         <v>13000</v>
@@ -12346,7 +12346,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H413" t="n">
         <v>1800</v>
@@ -12375,7 +12375,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G414" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G415" t="n">
-        <v>7.97669696807861</v>
+        <v>7.97669649124146</v>
       </c>
       <c r="H415" t="n">
         <v>200</v>
@@ -12433,7 +12433,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G416" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H416" t="n">
         <v>200</v>
@@ -12462,7 +12462,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G417" t="n">
-        <v>7.9342679977417</v>
+        <v>7.93426704406738</v>
       </c>
       <c r="H417" t="n">
         <v>0</v>
@@ -12491,7 +12491,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H418" t="n">
         <v>10000</v>
@@ -12549,7 +12549,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G420" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H420" t="n">
         <v>12500</v>
@@ -12578,7 +12578,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G421" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H421" t="n">
         <v>10000</v>
@@ -12607,7 +12607,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G424" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H424" t="n">
         <v>8900</v>
@@ -12694,7 +12694,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>8.10398578643799</v>
+        <v>8.10398483276367</v>
       </c>
       <c r="H425" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H426" t="n">
         <v>300</v>
@@ -12752,7 +12752,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G427" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H427" t="n">
         <v>2000</v>
@@ -12868,7 +12868,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H431" t="n">
         <v>700</v>
@@ -12897,7 +12897,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H432" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G433" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H433" t="n">
         <v>800</v>
@@ -14521,7 +14521,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G488" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H488" t="n">
         <v>140500</v>
@@ -14550,7 +14550,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G489" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H489" t="n">
         <v>134000</v>
@@ -14579,7 +14579,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H490" t="n">
         <v>5800</v>
@@ -14608,7 +14608,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G491" t="n">
-        <v>8.35855960845947</v>
+        <v>8.35856056213379</v>
       </c>
       <c r="H491" t="n">
         <v>129300</v>
@@ -15014,7 +15014,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.1464147567749</v>
+        <v>8.14641380310059</v>
       </c>
       <c r="H505" t="n">
         <v>400</v>
@@ -15333,7 +15333,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G516" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H516" t="n">
         <v>5700</v>
@@ -15362,7 +15362,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G518" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G526" t="n">
-        <v>8.40098762512207</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H526" t="n">
         <v>6800</v>
@@ -15652,7 +15652,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G527" t="n">
-        <v>8.40098762512207</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G528" t="n">
-        <v>8.40098762512207</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G529" t="n">
-        <v>8.40098762512207</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H529" t="n">
         <v>600</v>
@@ -15739,7 +15739,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G530" t="n">
-        <v>8.40098762512207</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15797,7 +15797,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G532" t="n">
-        <v>8.40098762512207</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H532" t="n">
         <v>300</v>
@@ -15826,7 +15826,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G533" t="n">
-        <v>8.40098762512207</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G534" t="n">
-        <v>8.40098762512207</v>
+        <v>8.40098857879639</v>
       </c>
       <c r="H534" t="n">
         <v>100</v>
@@ -16261,7 +16261,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>8.4434175491333</v>
+        <v>8.44341850280762</v>
       </c>
       <c r="H548" t="n">
         <v>21900</v>
@@ -16290,7 +16290,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G549" t="n">
-        <v>8.65556335449219</v>
+        <v>8.6555643081665</v>
       </c>
       <c r="H549" t="n">
         <v>900</v>
@@ -16319,7 +16319,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>8.65556335449219</v>
+        <v>8.6555643081665</v>
       </c>
       <c r="H550" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>8.18884372711182</v>
+        <v>8.1888427734375</v>
       </c>
       <c r="H552" t="n">
         <v>1800</v>
@@ -16406,7 +16406,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>8.01912498474121</v>
+        <v>8.01912689208984</v>
       </c>
       <c r="H553" t="n">
         <v>1800</v>
@@ -16435,7 +16435,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183855056763</v>
+        <v>7.89183759689331</v>
       </c>
       <c r="H554" t="n">
         <v>2900</v>
@@ -16464,7 +16464,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G555" t="n">
-        <v>7.5948338508606</v>
+        <v>7.59483337402344</v>
       </c>
       <c r="H555" t="n">
         <v>5200</v>
@@ -16493,7 +16493,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G556" t="n">
-        <v>7.5948338508606</v>
+        <v>7.59483337402344</v>
       </c>
       <c r="H556" t="n">
         <v>2100</v>
@@ -16522,7 +16522,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G557" t="n">
-        <v>7.29782962799072</v>
+        <v>7.29782915115356</v>
       </c>
       <c r="H557" t="n">
         <v>1100</v>
@@ -16580,7 +16580,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66139030456543</v>
+        <v>6.66138982772827</v>
       </c>
       <c r="H559" t="n">
         <v>9300</v>
@@ -16609,7 +16609,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G560" t="n">
-        <v>6.10981035232544</v>
+        <v>6.10980987548828</v>
       </c>
       <c r="H560" t="n">
         <v>3900</v>
@@ -16638,7 +16638,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G561" t="n">
-        <v>6.10981035232544</v>
+        <v>6.10980987548828</v>
       </c>
       <c r="H561" t="n">
         <v>49300</v>
@@ -16696,7 +16696,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17054128646851</v>
+        <v>7.17054080963135</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16754,7 +16754,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867769241333</v>
+        <v>6.78867816925049</v>
       </c>
       <c r="H565" t="n">
         <v>3800</v>
@@ -16783,7 +16783,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867769241333</v>
+        <v>6.78867816925049</v>
       </c>
       <c r="H566" t="n">
         <v>3000</v>
@@ -16812,7 +16812,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867769241333</v>
+        <v>6.78867816925049</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16841,7 +16841,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>6.70381927490234</v>
+        <v>6.70382022857666</v>
       </c>
       <c r="H568" t="n">
         <v>2000</v>
@@ -16870,7 +16870,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>6.70381927490234</v>
+        <v>6.70382022857666</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.46783113479614</v>
+        <v>6.4678316116333</v>
       </c>
       <c r="H573" t="n">
         <v>4700</v>
@@ -17073,7 +17073,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>7.16705560684204</v>
+        <v>7.1670560836792</v>
       </c>
       <c r="H576" t="n">
         <v>24700</v>
@@ -17102,7 +17102,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>7.25446033477783</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H577" t="n">
         <v>1400</v>
@@ -17131,7 +17131,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>7.25446033477783</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H578" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G579" t="n">
-        <v>7.25446033477783</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H579" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G581" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H581" t="n">
         <v>200</v>
@@ -17247,7 +17247,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>7.25446033477783</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H582" t="n">
         <v>100</v>
@@ -17450,7 +17450,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H589" t="n">
         <v>1000</v>
@@ -17479,7 +17479,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H590" t="n">
         <v>600</v>
@@ -17508,7 +17508,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517656326294</v>
       </c>
       <c r="H591" t="n">
         <v>19400</v>
@@ -17537,7 +17537,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H592" t="n">
         <v>300</v>
@@ -17566,7 +17566,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H597" t="n">
         <v>2000</v>
@@ -17711,7 +17711,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H598" t="n">
         <v>3300</v>
@@ -17740,7 +17740,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56036949157715</v>
+        <v>7.56037044525146</v>
       </c>
       <c r="H600" t="n">
         <v>100</v>
@@ -17856,7 +17856,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H603" t="n">
         <v>300</v>
@@ -17885,7 +17885,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517656326294</v>
       </c>
       <c r="H604" t="n">
         <v>700</v>
@@ -18001,7 +18001,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>7.60407161712646</v>
+        <v>7.60407209396362</v>
       </c>
       <c r="H608" t="n">
         <v>200</v>
@@ -18088,7 +18088,7 @@
         <v>9</v>
       </c>
       <c r="G611" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H611" t="n">
         <v>800</v>
@@ -18117,7 +18117,7 @@
         <v>9</v>
       </c>
       <c r="G612" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H612" t="n">
         <v>100</v>
@@ -18146,7 +18146,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G613" t="n">
-        <v>7.95368480682373</v>
+        <v>7.95368528366089</v>
       </c>
       <c r="H613" t="n">
         <v>100</v>
@@ -18175,7 +18175,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H614" t="n">
         <v>600</v>
@@ -18204,7 +18204,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.7351770401001</v>
+        <v>7.73517656326294</v>
       </c>
       <c r="H615" t="n">
         <v>1200</v>
@@ -18233,7 +18233,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H616" t="n">
         <v>200</v>
@@ -18378,7 +18378,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G621" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H621" t="n">
         <v>100</v>
@@ -18407,7 +18407,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G622" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H622" t="n">
         <v>100</v>
@@ -18494,7 +18494,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G625" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H625" t="n">
         <v>1000</v>
@@ -18639,7 +18639,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H630" t="n">
         <v>5900</v>
@@ -18668,7 +18668,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G631" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H631" t="n">
         <v>1200</v>
@@ -18697,7 +18697,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G632" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H632" t="n">
         <v>900</v>
@@ -18726,7 +18726,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34186220169067</v>
+        <v>7.34186267852783</v>
       </c>
       <c r="H633" t="n">
         <v>4200</v>
@@ -18755,7 +18755,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G634" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H634" t="n">
         <v>300</v>
@@ -18813,7 +18813,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G636" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H636" t="n">
         <v>2000</v>
@@ -18842,7 +18842,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G637" t="n">
-        <v>7.25446033477783</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H637" t="n">
         <v>5700</v>
@@ -18871,7 +18871,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G638" t="n">
-        <v>7.25446033477783</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H638" t="n">
         <v>600</v>
@@ -18900,7 +18900,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.16705560684204</v>
+        <v>7.1670560836792</v>
       </c>
       <c r="H639" t="n">
         <v>1100</v>
@@ -19016,7 +19016,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G643" t="n">
-        <v>7.25446033477783</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H643" t="n">
         <v>11600</v>
@@ -19132,7 +19132,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G647" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H647" t="n">
         <v>5600</v>
@@ -19161,7 +19161,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G648" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H648" t="n">
         <v>2500</v>
@@ -19190,7 +19190,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G649" t="n">
-        <v>7.12335443496704</v>
+        <v>7.1233549118042</v>
       </c>
       <c r="H649" t="n">
         <v>1700</v>
@@ -19277,7 +19277,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484714508057</v>
+        <v>6.90484666824341</v>
       </c>
       <c r="H652" t="n">
         <v>2400</v>
@@ -19393,7 +19393,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G656" t="n">
-        <v>7.16705560684204</v>
+        <v>7.1670560836792</v>
       </c>
       <c r="H656" t="n">
         <v>1100</v>
@@ -19480,7 +19480,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>7.16705560684204</v>
+        <v>7.1670560836792</v>
       </c>
       <c r="H659" t="n">
         <v>5400</v>
@@ -19509,7 +19509,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G660" t="n">
-        <v>7.25446033477783</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H660" t="n">
         <v>8800</v>
@@ -19538,7 +19538,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G661" t="n">
-        <v>7.03595113754272</v>
+        <v>7.03595209121704</v>
       </c>
       <c r="H661" t="n">
         <v>11500</v>
@@ -19567,7 +19567,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G662" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H662" t="n">
         <v>7300</v>
@@ -19596,7 +19596,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G663" t="n">
-        <v>7.29816102981567</v>
+        <v>7.29816150665283</v>
       </c>
       <c r="H663" t="n">
         <v>11900</v>
@@ -19625,7 +19625,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G664" t="n">
-        <v>7.25446033477783</v>
+        <v>7.25445985794067</v>
       </c>
       <c r="H664" t="n">
         <v>3400</v>
@@ -19654,7 +19654,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G665" t="n">
-        <v>7.38556385040283</v>
+        <v>7.38556432723999</v>
       </c>
       <c r="H665" t="n">
         <v>18900</v>
@@ -19741,7 +19741,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G668" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -19770,7 +19770,7 @@
         <v>9</v>
       </c>
       <c r="G669" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H669" t="n">
         <v>6200</v>
@@ -19799,7 +19799,7 @@
         <v>9</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H670" t="n">
         <v>2100</v>
@@ -19915,7 +19915,7 @@
         <v>9</v>
       </c>
       <c r="G674" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H674" t="n">
         <v>2900</v>
@@ -19944,7 +19944,7 @@
         <v>9</v>
       </c>
       <c r="G675" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H675" t="n">
         <v>1300</v>
@@ -19973,7 +19973,7 @@
         <v>9</v>
       </c>
       <c r="G676" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H676" t="n">
         <v>2300</v>
@@ -20002,7 +20002,7 @@
         <v>9</v>
       </c>
       <c r="G677" t="n">
-        <v>7.86628198623657</v>
+        <v>7.86628150939941</v>
       </c>
       <c r="H677" t="n">
         <v>1800</v>
@@ -20031,7 +20031,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>7.82257986068726</v>
+        <v>7.82257890701294</v>
       </c>
       <c r="H678" t="n">
         <v>1500</v>
@@ -20118,7 +20118,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60407161712646</v>
+        <v>7.60407209396362</v>
       </c>
       <c r="H681" t="n">
         <v>1400</v>
@@ -20147,7 +20147,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H682" t="n">
         <v>1900</v>
@@ -20205,7 +20205,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738550186157</v>
+        <v>7.99738502502441</v>
       </c>
       <c r="H684" t="n">
         <v>3100</v>
@@ -20292,7 +20292,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777326583862</v>
+        <v>7.64777421951294</v>
       </c>
       <c r="H687" t="n">
         <v>1500</v>
@@ -20321,7 +20321,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>7.60407161712646</v>
+        <v>7.60407209396362</v>
       </c>
       <c r="H688" t="n">
         <v>1500</v>
@@ -20524,7 +20524,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738550186157</v>
+        <v>7.99738502502441</v>
       </c>
       <c r="H695" t="n">
         <v>5300</v>
@@ -20640,7 +20640,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H699" t="n">
         <v>6500</v>
@@ -20756,7 +20756,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H703" t="n">
         <v>1400</v>
@@ -20785,7 +20785,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H704" t="n">
         <v>300</v>
@@ -20959,7 +20959,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H710" t="n">
         <v>1600</v>
@@ -21191,7 +21191,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H718" t="n">
         <v>2600</v>
@@ -21220,7 +21220,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H719" t="n">
         <v>900</v>
@@ -21278,7 +21278,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H721" t="n">
         <v>6800</v>
@@ -21336,7 +21336,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H723" t="n">
         <v>26400</v>
@@ -21365,7 +21365,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H724" t="n">
         <v>21400</v>
@@ -21394,7 +21394,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H725" t="n">
         <v>70900</v>
@@ -21423,7 +21423,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H726" t="n">
         <v>38600</v>
@@ -21452,7 +21452,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H727" t="n">
         <v>100</v>
@@ -21481,7 +21481,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H728" t="n">
         <v>4500</v>
@@ -21510,7 +21510,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H729" t="n">
         <v>5100</v>
@@ -21539,7 +21539,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H730" t="n">
         <v>1200</v>
@@ -21568,7 +21568,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227279663086</v>
+        <v>8.30227184295654</v>
       </c>
       <c r="H731" t="n">
         <v>300</v>
@@ -21597,7 +21597,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H732" t="n">
         <v>2600</v>
@@ -21626,7 +21626,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G733" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H733" t="n">
         <v>6400</v>
@@ -21655,7 +21655,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H734" t="n">
         <v>12300</v>
@@ -21684,7 +21684,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H735" t="n">
         <v>6900</v>
@@ -21713,7 +21713,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H736" t="n">
         <v>3000</v>
@@ -21742,7 +21742,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G737" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G738" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H738" t="n">
         <v>100</v>
@@ -21887,7 +21887,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H742" t="n">
         <v>7300</v>
@@ -21945,7 +21945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G744" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H744" t="n">
         <v>7400</v>
@@ -22003,7 +22003,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H746" t="n">
         <v>6800</v>
@@ -22061,7 +22061,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H748" t="n">
         <v>700</v>
@@ -22119,7 +22119,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H750" t="n">
         <v>5400</v>
@@ -22148,7 +22148,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G751" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H751" t="n">
         <v>2100</v>
@@ -22177,7 +22177,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H752" t="n">
         <v>7900</v>
@@ -22206,7 +22206,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H753" t="n">
         <v>33700</v>
@@ -22235,7 +22235,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G754" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H754" t="n">
         <v>34600</v>
@@ -22264,7 +22264,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H755" t="n">
         <v>33100</v>
@@ -22322,7 +22322,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G757" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H757" t="n">
         <v>5400</v>
@@ -22351,7 +22351,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G758" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H758" t="n">
         <v>4100</v>
@@ -22438,7 +22438,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G761" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H761" t="n">
         <v>3200</v>
@@ -22467,7 +22467,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G762" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G763" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H763" t="n">
         <v>1000</v>
@@ -22612,7 +22612,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G767" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H767" t="n">
         <v>600</v>
@@ -22641,7 +22641,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G768" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H768" t="n">
         <v>1100</v>
@@ -22670,7 +22670,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H769" t="n">
         <v>1400</v>
@@ -22699,7 +22699,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H771" t="n">
         <v>300</v>
@@ -22757,7 +22757,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G772" t="n">
-        <v>8.34714984893799</v>
+        <v>8.34714889526367</v>
       </c>
       <c r="H772" t="n">
         <v>2900</v>
@@ -22873,7 +22873,7 @@
         <v>10.5</v>
       </c>
       <c r="G776" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H776" t="n">
         <v>25300</v>
@@ -22960,7 +22960,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>9.96272754669189</v>
+        <v>9.96272659301758</v>
       </c>
       <c r="H779" t="n">
         <v>29900</v>
@@ -23105,7 +23105,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>9.6934642791748</v>
+        <v>9.69346332550049</v>
       </c>
       <c r="H784" t="n">
         <v>22700</v>
@@ -23134,7 +23134,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G785" t="n">
-        <v>9.6934642791748</v>
+        <v>9.69346332550049</v>
       </c>
       <c r="H785" t="n">
         <v>6500</v>
@@ -23163,7 +23163,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G786" t="n">
-        <v>9.24469184875488</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H786" t="n">
         <v>12700</v>
@@ -23192,7 +23192,7 @@
         <v>10.5</v>
       </c>
       <c r="G787" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H787" t="n">
         <v>6800</v>
@@ -23221,7 +23221,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H788" t="n">
         <v>26400</v>
@@ -23279,7 +23279,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>9.24469184875488</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H790" t="n">
         <v>4700</v>
@@ -23337,7 +23337,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G792" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H792" t="n">
         <v>18900</v>
@@ -23395,7 +23395,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H794" t="n">
         <v>3700</v>
@@ -23453,7 +23453,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H796" t="n">
         <v>1300</v>
@@ -23511,7 +23511,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G798" t="n">
-        <v>8.93055248260498</v>
+        <v>8.9305534362793</v>
       </c>
       <c r="H798" t="n">
         <v>700</v>
@@ -23540,7 +23540,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H799" t="n">
         <v>2300</v>
@@ -24004,7 +24004,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H815" t="n">
         <v>1400</v>
@@ -24091,7 +24091,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G818" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H818" t="n">
         <v>2200</v>
@@ -24236,7 +24236,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>8.48178005218506</v>
+        <v>8.48178100585938</v>
       </c>
       <c r="H823" t="n">
         <v>2700</v>
@@ -24265,7 +24265,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H824" t="n">
         <v>1900</v>
@@ -24294,7 +24294,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>9.24469184875488</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H825" t="n">
         <v>14600</v>
@@ -24323,7 +24323,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>9.24469184875488</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H826" t="n">
         <v>44000</v>
@@ -24352,7 +24352,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H827" t="n">
         <v>49700</v>
@@ -24410,7 +24410,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H829" t="n">
         <v>12300</v>
@@ -24439,7 +24439,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H830" t="n">
         <v>1900</v>
@@ -24468,7 +24468,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H831" t="n">
         <v>4200</v>
@@ -24497,7 +24497,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H832" t="n">
         <v>1700</v>
@@ -24526,7 +24526,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H833" t="n">
         <v>1100</v>
@@ -24584,7 +24584,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H835" t="n">
         <v>1600</v>
@@ -24642,7 +24642,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H837" t="n">
         <v>3000</v>
@@ -24729,7 +24729,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G840" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H840" t="n">
         <v>500</v>
@@ -24816,7 +24816,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G843" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H843" t="n">
         <v>6000</v>
@@ -24874,7 +24874,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H845" t="n">
         <v>3000</v>
@@ -24903,7 +24903,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H846" t="n">
         <v>2100</v>
@@ -24990,7 +24990,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H849" t="n">
         <v>3700</v>
@@ -25019,7 +25019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H850" t="n">
         <v>1700</v>
@@ -25048,7 +25048,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G851" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H851" t="n">
         <v>2400</v>
@@ -25077,7 +25077,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G852" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H852" t="n">
         <v>2600</v>
@@ -25106,7 +25106,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H853" t="n">
         <v>1200</v>
@@ -25164,7 +25164,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G855" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H855" t="n">
         <v>1800</v>
@@ -25251,7 +25251,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H858" t="n">
         <v>3300</v>
@@ -25309,7 +25309,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H860" t="n">
         <v>8600</v>
@@ -25425,7 +25425,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H864" t="n">
         <v>2300</v>
@@ -25454,7 +25454,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>9.24469184875488</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H865" t="n">
         <v>3700</v>
@@ -25483,7 +25483,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H866" t="n">
         <v>200</v>
@@ -25512,7 +25512,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>9.24469184875488</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H867" t="n">
         <v>20600</v>
@@ -25541,7 +25541,7 @@
         <v>10.5</v>
       </c>
       <c r="G868" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H868" t="n">
         <v>2200</v>
@@ -25599,7 +25599,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>9.24469184875488</v>
+        <v>9.24469375610352</v>
       </c>
       <c r="H870" t="n">
         <v>25600</v>
@@ -25628,7 +25628,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H871" t="n">
         <v>1200</v>
@@ -25831,7 +25831,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H878" t="n">
         <v>23100</v>
@@ -25860,7 +25860,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H879" t="n">
         <v>26500</v>
@@ -25889,7 +25889,7 @@
         <v>10.5</v>
       </c>
       <c r="G880" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H880" t="n">
         <v>18700</v>
@@ -25947,7 +25947,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H882" t="n">
         <v>4500</v>
@@ -25976,7 +25976,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H883" t="n">
         <v>6700</v>
@@ -26005,7 +26005,7 @@
         <v>10.5</v>
       </c>
       <c r="G884" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H884" t="n">
         <v>11400</v>
@@ -26034,7 +26034,7 @@
         <v>10.5</v>
       </c>
       <c r="G885" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H885" t="n">
         <v>22400</v>
@@ -26063,7 +26063,7 @@
         <v>10.5</v>
       </c>
       <c r="G886" t="n">
-        <v>9.42420196533203</v>
+        <v>9.42420101165771</v>
       </c>
       <c r="H886" t="n">
         <v>19400</v>
@@ -26121,7 +26121,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G888" t="n">
-        <v>8.93055248260498</v>
+        <v>8.9305534362793</v>
       </c>
       <c r="H888" t="n">
         <v>21000</v>
@@ -26179,7 +26179,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H890" t="n">
         <v>2500</v>
@@ -26208,7 +26208,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H891" t="n">
         <v>5500</v>
@@ -26237,7 +26237,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H892" t="n">
         <v>1200</v>
@@ -26266,7 +26266,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H893" t="n">
         <v>2100</v>
@@ -26295,7 +26295,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.15493774414062</v>
+        <v>9.15493869781494</v>
       </c>
       <c r="H894" t="n">
         <v>500</v>
@@ -26324,7 +26324,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G895" t="n">
-        <v>8.93055248260498</v>
+        <v>8.9305534362793</v>
       </c>
       <c r="H895" t="n">
         <v>2200</v>
@@ -26353,7 +26353,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H896" t="n">
         <v>1800</v>
@@ -26382,7 +26382,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H897" t="n">
         <v>900</v>
@@ -26440,7 +26440,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518363952637</v>
+        <v>9.06518459320068</v>
       </c>
       <c r="H899" t="n">
         <v>500</v>
@@ -26469,7 +26469,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>8.79592227935791</v>
+        <v>8.79592132568359</v>
       </c>
       <c r="H900" t="n">
         <v>3000</v>
@@ -26701,7 +26701,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G908" t="n">
-        <v>8.03300952911377</v>
+        <v>8.03300857543945</v>
       </c>
       <c r="H908" t="n">
         <v>400</v>
@@ -26730,7 +26730,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G909" t="n">
-        <v>8.03300952911377</v>
+        <v>8.03300857543945</v>
       </c>
       <c r="H909" t="n">
         <v>1800</v>
@@ -26788,7 +26788,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.3598518371582</v>
+        <v>7.35985231399536</v>
       </c>
       <c r="H911" t="n">
         <v>12900</v>
@@ -26904,7 +26904,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862331390381</v>
+        <v>7.80862426757812</v>
       </c>
       <c r="H915" t="n">
         <v>5300</v>
@@ -27078,7 +27078,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G921" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H921" t="n">
         <v>100</v>
@@ -27136,7 +27136,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G923" t="n">
-        <v>8.48178005218506</v>
+        <v>8.48178100585938</v>
       </c>
       <c r="H923" t="n">
         <v>1200</v>
@@ -27165,7 +27165,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G924" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H924" t="n">
         <v>500</v>
@@ -27194,7 +27194,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -27397,7 +27397,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231513977051</v>
+        <v>8.65231418609619</v>
       </c>
       <c r="H932" t="n">
         <v>500</v>
@@ -27426,7 +27426,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G933" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H933" t="n">
         <v>2200</v>
@@ -27455,7 +27455,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.54460906982422</v>
+        <v>8.54461002349854</v>
       </c>
       <c r="H934" t="n">
         <v>26000</v>
@@ -27484,7 +27484,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>8.70616722106934</v>
+        <v>8.70616626739502</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27513,7 +27513,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821620941162</v>
+        <v>8.68821716308594</v>
       </c>
       <c r="H936" t="n">
         <v>15100</v>
@@ -27542,7 +27542,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G937" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H937" t="n">
         <v>1600</v>
@@ -27571,7 +27571,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G938" t="n">
-        <v>8.61641311645508</v>
+        <v>8.61641216278076</v>
       </c>
       <c r="H938" t="n">
         <v>11000</v>
@@ -27716,7 +27716,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G943" t="n">
-        <v>8.84977340698242</v>
+        <v>8.84977245330811</v>
       </c>
       <c r="H943" t="n">
         <v>7100</v>
@@ -27919,7 +27919,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G950" t="n">
-        <v>9.11731338500977</v>
+        <v>9.11731433868408</v>
       </c>
       <c r="H950" t="n">
         <v>1300</v>
@@ -27948,7 +27948,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>9.30150318145752</v>
+        <v>9.3015022277832</v>
       </c>
       <c r="H951" t="n">
         <v>5000</v>
@@ -28006,7 +28006,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G953" t="n">
-        <v>9.11731338500977</v>
+        <v>9.11731433868408</v>
       </c>
       <c r="H953" t="n">
         <v>2400</v>
@@ -28093,7 +28093,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H956" t="n">
         <v>18400</v>
@@ -28354,7 +28354,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G965" t="n">
-        <v>8.84103202819824</v>
+        <v>8.84103298187256</v>
       </c>
       <c r="H965" t="n">
         <v>100</v>
@@ -28499,7 +28499,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>8.78577613830566</v>
+        <v>8.78577518463135</v>
       </c>
       <c r="H970" t="n">
         <v>5800</v>
@@ -28731,7 +28731,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G978" t="n">
-        <v>8.84103202819824</v>
+        <v>8.84103298187256</v>
       </c>
       <c r="H978" t="n">
         <v>18000</v>
@@ -28789,7 +28789,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H980" t="n">
         <v>5400</v>
@@ -28934,7 +28934,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H985" t="n">
         <v>1600</v>
@@ -28963,7 +28963,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -29108,7 +29108,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>8.14111709594727</v>
+        <v>8.14111614227295</v>
       </c>
       <c r="H991" t="n">
         <v>1100</v>
@@ -29137,7 +29137,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H992" t="n">
         <v>3200</v>
@@ -29253,7 +29253,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G996" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H996" t="n">
         <v>800</v>
@@ -29311,7 +29311,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G998" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H998" t="n">
         <v>600</v>
@@ -29340,7 +29340,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G999" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H999" t="n">
         <v>1100</v>
@@ -29398,7 +29398,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1001" t="n">
         <v>900</v>
@@ -29427,7 +29427,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1002" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1002" t="n">
         <v>2700</v>
@@ -29572,7 +29572,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423698425293</v>
+        <v>8.45423603057861</v>
       </c>
       <c r="H1007" t="n">
         <v>100</v>
@@ -29630,7 +29630,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1009" t="n">
         <v>2700</v>
@@ -29659,7 +29659,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29949,7 +29949,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1020" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1020" t="n">
         <v>1400</v>
@@ -29978,7 +29978,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1021" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -30007,7 +30007,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1022" t="n">
         <v>100</v>
@@ -30065,7 +30065,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1024" t="n">
         <v>1000</v>
@@ -30123,7 +30123,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1026" t="n">
         <v>300</v>
@@ -30239,7 +30239,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1030" t="n">
         <v>300</v>
@@ -30355,7 +30355,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>7.71748447418213</v>
+        <v>7.71748399734497</v>
       </c>
       <c r="H1034" t="n">
         <v>3900</v>
@@ -30384,7 +30384,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.88325357437134</v>
+        <v>7.88325452804565</v>
       </c>
       <c r="H1035" t="n">
         <v>600</v>
@@ -30413,7 +30413,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.01218509674072</v>
+        <v>8.01218414306641</v>
       </c>
       <c r="H1036" t="n">
         <v>300</v>
@@ -30442,7 +30442,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.01218509674072</v>
+        <v>8.01218414306641</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -30587,7 +30587,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.14111709594727</v>
+        <v>8.14111614227295</v>
       </c>
       <c r="H1042" t="n">
         <v>7000</v>
@@ -30616,7 +30616,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1043" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1043" t="n">
         <v>2400</v>
@@ -30674,7 +30674,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1045" t="n">
         <v>2000</v>
@@ -30703,7 +30703,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1046" t="n">
         <v>900</v>
@@ -30732,7 +30732,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1047" t="n">
         <v>500</v>
@@ -30761,7 +30761,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1050" t="n">
         <v>11300</v>
@@ -30848,7 +30848,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30993,7 +30993,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41740036010742</v>
+        <v>8.41739940643311</v>
       </c>
       <c r="H1056" t="n">
         <v>300</v>
@@ -31138,7 +31138,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1061" t="n">
         <v>700</v>
@@ -31167,7 +31167,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1062" t="n">
         <v>800</v>
@@ -31312,7 +31312,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1067" t="n">
         <v>3400</v>
@@ -31341,7 +31341,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -31370,7 +31370,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1069" t="n">
         <v>1000</v>
@@ -31399,7 +31399,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1070" t="n">
         <v>2800</v>
@@ -31631,7 +31631,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1078" t="n">
         <v>800</v>
@@ -31834,7 +31834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.85945129394531</v>
+        <v>8.859450340271</v>
       </c>
       <c r="H1085" t="n">
         <v>2600</v>
@@ -31892,7 +31892,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1087" t="n">
         <v>300</v>
@@ -31921,7 +31921,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1088" t="n">
         <v>100</v>
@@ -31950,7 +31950,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1090" t="n">
         <v>200</v>
@@ -32153,7 +32153,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1096" t="n">
         <v>1900</v>
@@ -32385,7 +32385,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1104" t="n">
         <v>2200</v>
@@ -32559,7 +32559,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1110" t="n">
         <v>22300</v>
@@ -32675,7 +32675,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1114" t="n">
         <v>1100</v>
@@ -32704,7 +32704,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.80419445037842</v>
+        <v>8.80419540405273</v>
       </c>
       <c r="H1115" t="n">
         <v>5200</v>
@@ -32965,7 +32965,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1124" t="n">
         <v>7600</v>
@@ -32994,7 +32994,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1125" t="n">
         <v>11000</v>
@@ -33226,7 +33226,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1133" t="n">
         <v>700</v>
@@ -33255,7 +33255,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1134" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1134" t="n">
         <v>0</v>
@@ -33284,7 +33284,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1135" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1135" t="n">
         <v>100</v>
@@ -33313,7 +33313,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1136" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1136" t="n">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1139" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1139" t="n">
         <v>3300</v>
@@ -33429,7 +33429,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1140" t="n">
-        <v>8.39898014068604</v>
+        <v>8.39898109436035</v>
       </c>
       <c r="H1140" t="n">
         <v>1000</v>
@@ -33487,7 +33487,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1142" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1142" t="n">
         <v>300</v>
@@ -33574,7 +33574,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1145" t="n">
-        <v>8.60158729553223</v>
+        <v>8.60158824920654</v>
       </c>
       <c r="H1145" t="n">
         <v>2300</v>
@@ -33603,7 +33603,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1146" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1146" t="n">
         <v>1600</v>
@@ -33719,7 +33719,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1150" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1150" t="n">
         <v>2300</v>
@@ -33864,7 +33864,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>8.91470718383789</v>
+        <v>8.91470813751221</v>
       </c>
       <c r="H1155" t="n">
         <v>100</v>
@@ -33893,7 +33893,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.84103202819824</v>
+        <v>8.84103298187256</v>
       </c>
       <c r="H1156" t="n">
         <v>200</v>
@@ -33980,7 +33980,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1159" t="n">
-        <v>8.65684413909912</v>
+        <v>8.6568431854248</v>
       </c>
       <c r="H1159" t="n">
         <v>4200</v>
@@ -34183,7 +34183,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1166" t="n">
         <v>100</v>
@@ -34212,7 +34212,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1167" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1168" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>
@@ -34270,7 +34270,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1169" t="n">
         <v>0</v>
@@ -34299,7 +34299,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1170" t="n">
         <v>100</v>
@@ -34328,7 +34328,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.69368076324463</v>
+        <v>8.69368171691895</v>
       </c>
       <c r="H1171" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1174" t="n">
         <v>100</v>
@@ -34705,7 +34705,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.47265529632568</v>
+        <v>8.47265625</v>
       </c>
       <c r="H1184" t="n">
         <v>900</v>
@@ -34792,7 +34792,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1187" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1187" t="n">
         <v>300</v>
@@ -34821,7 +34821,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1188" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1188" t="n">
         <v>0</v>
@@ -34850,7 +34850,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1189" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1189" t="n">
         <v>100</v>
@@ -35169,7 +35169,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1200" t="n">
         <v>100</v>
@@ -35198,7 +35198,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.15953540802002</v>
+        <v>8.15953636169434</v>
       </c>
       <c r="H1201" t="n">
         <v>900</v>
@@ -35227,7 +35227,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.15953540802002</v>
+        <v>8.15953636169434</v>
       </c>
       <c r="H1202" t="n">
         <v>300</v>
@@ -35256,7 +35256,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.19637203216553</v>
+        <v>8.19637298583984</v>
       </c>
       <c r="H1203" t="n">
         <v>700</v>
@@ -35430,7 +35430,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590278625488</v>
+        <v>7.73590326309204</v>
       </c>
       <c r="H1209" t="n">
         <v>2000</v>
@@ -35546,7 +35546,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.60697174072266</v>
+        <v>7.6069712638855</v>
       </c>
       <c r="H1213" t="n">
         <v>500</v>
@@ -35691,7 +35691,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1218" t="n">
-        <v>7.22017669677734</v>
+        <v>7.22017621994019</v>
       </c>
       <c r="H1218" t="n">
         <v>19000</v>
@@ -35720,7 +35720,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.05440616607666</v>
+        <v>7.05440664291382</v>
       </c>
       <c r="H1219" t="n">
         <v>4300</v>
@@ -35749,7 +35749,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>7.18333864212036</v>
+        <v>7.1833381652832</v>
       </c>
       <c r="H1220" t="n">
         <v>200</v>
@@ -35894,7 +35894,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.18333864212036</v>
+        <v>7.1833381652832</v>
       </c>
       <c r="H1225" t="n">
         <v>2600</v>
@@ -36039,7 +36039,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>7.60697174072266</v>
+        <v>7.6069712638855</v>
       </c>
       <c r="H1230" t="n">
         <v>9400</v>
@@ -36097,7 +36097,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590278625488</v>
+        <v>7.73590326309204</v>
       </c>
       <c r="H1232" t="n">
         <v>200</v>
@@ -36155,7 +36155,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.71748447418213</v>
+        <v>7.71748399734497</v>
       </c>
       <c r="H1234" t="n">
         <v>21900</v>
@@ -61014,6 +61014,35 @@
         <v>1000</v>
       </c>
       <c r="I2091" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2092" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2092" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="D2092" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="G2092" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="H2092" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I2092" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -862,7 +862,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G17" t="n">
-        <v>8.10059070587158</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H17" t="n">
         <v>1300</v>
@@ -891,7 +891,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G18" t="n">
-        <v>8.10059070587158</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>9.55300045013428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.10653114318848</v>
+        <v>8.10653018951416</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>9.59000015258789</v>
       </c>
       <c r="G22" t="n">
-        <v>8.13792896270752</v>
+        <v>8.1379280090332</v>
       </c>
       <c r="H22" t="n">
         <v>300</v>
@@ -1065,7 +1065,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852745056152</v>
+        <v>8.07852649688721</v>
       </c>
       <c r="H24" t="n">
         <v>2800</v>
@@ -1123,7 +1123,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G26" t="n">
-        <v>8.20666217803955</v>
+        <v>8.20666313171387</v>
       </c>
       <c r="H26" t="n">
         <v>200</v>
@@ -1152,7 +1152,7 @@
         <v>9.67099952697754</v>
       </c>
       <c r="G27" t="n">
-        <v>8.20666217803955</v>
+        <v>8.20666313171387</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G30" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H30" t="n">
         <v>7500</v>
@@ -1268,7 +1268,7 @@
         <v>9.50100040435791</v>
       </c>
       <c r="G31" t="n">
-        <v>8.06240463256836</v>
+        <v>8.06240367889404</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1297,7 +1297,7 @@
         <v>9.54599952697754</v>
       </c>
       <c r="G32" t="n">
-        <v>8.10059070587158</v>
+        <v>8.10058879852295</v>
       </c>
       <c r="H32" t="n">
         <v>200</v>
@@ -1413,7 +1413,7 @@
         <v>9.44699954986572</v>
       </c>
       <c r="G36" t="n">
-        <v>8.01657867431641</v>
+        <v>8.01657962799072</v>
       </c>
       <c r="H36" t="n">
         <v>2900</v>
@@ -1442,7 +1442,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.9936695098877</v>
+        <v>7.99366855621338</v>
       </c>
       <c r="H37" t="n">
         <v>12300</v>
@@ -1500,7 +1500,7 @@
         <v>9.33100032806396</v>
       </c>
       <c r="G39" t="n">
-        <v>7.91814470291138</v>
+        <v>7.91814565658569</v>
       </c>
       <c r="H39" t="n">
         <v>400</v>
@@ -1587,7 +1587,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924327850342</v>
       </c>
       <c r="H42" t="n">
         <v>300</v>
@@ -1616,7 +1616,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.9792423248291</v>
+        <v>7.97924327850342</v>
       </c>
       <c r="H43" t="n">
         <v>1700</v>
@@ -1732,7 +1732,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H47" t="n">
         <v>7500</v>
@@ -1790,7 +1790,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.9172945022583</v>
+        <v>7.91729545593262</v>
       </c>
       <c r="H49" t="n">
         <v>9200</v>
@@ -1819,7 +1819,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619878768921</v>
+        <v>7.85619783401489</v>
       </c>
       <c r="H50" t="n">
         <v>8700</v>
@@ -1906,7 +1906,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.77473402023315</v>
+        <v>7.77473306655884</v>
       </c>
       <c r="H53" t="n">
         <v>2300</v>
@@ -2080,7 +2080,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76455116271973</v>
       </c>
       <c r="H59" t="n">
         <v>13600</v>
@@ -2167,7 +2167,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G62" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H62" t="n">
         <v>8400</v>
@@ -2196,7 +2196,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G63" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G66" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H66" t="n">
         <v>2500</v>
@@ -2312,7 +2312,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G67" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G68" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>8.02761077880859</v>
+        <v>8.02761268615723</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
@@ -2631,7 +2631,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.790855884552</v>
+        <v>7.79085683822632</v>
       </c>
       <c r="H78" t="n">
         <v>800</v>
@@ -2689,7 +2689,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G80" t="n">
-        <v>7.83243751525879</v>
+        <v>7.83243656158447</v>
       </c>
       <c r="H80" t="n">
         <v>1600</v>
@@ -2718,7 +2718,7 @@
         <v>9.19600009918213</v>
       </c>
       <c r="G81" t="n">
-        <v>7.80358600616455</v>
+        <v>7.80358505249023</v>
       </c>
       <c r="H81" t="n">
         <v>400</v>
@@ -2747,7 +2747,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406858444214</v>
+        <v>7.78406763076782</v>
       </c>
       <c r="H82" t="n">
         <v>200</v>
@@ -3066,7 +3066,7 @@
         <v>9.1569995880127</v>
       </c>
       <c r="G93" t="n">
-        <v>7.77048969268799</v>
+        <v>7.77049016952515</v>
       </c>
       <c r="H93" t="n">
         <v>200</v>
@@ -3124,7 +3124,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76455116271973</v>
       </c>
       <c r="H95" t="n">
         <v>20300</v>
@@ -3153,7 +3153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76455116271973</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969274520874</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H100" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969274520874</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G103" t="n">
-        <v>7.65423583984375</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H103" t="n">
         <v>100</v>
@@ -3385,7 +3385,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G104" t="n">
-        <v>7.65423583984375</v>
+        <v>7.65423488616943</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969274520874</v>
+        <v>7.67969179153442</v>
       </c>
       <c r="H114" t="n">
         <v>100</v>
@@ -3733,7 +3733,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110664367676</v>
+        <v>7.85110569000244</v>
       </c>
       <c r="H116" t="n">
         <v>800</v>
@@ -3762,7 +3762,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273580551147</v>
+        <v>7.80273675918579</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -4052,7 +4052,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406858444214</v>
+        <v>7.78406763076782</v>
       </c>
       <c r="H127" t="n">
         <v>2000</v>
@@ -4081,7 +4081,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76455020904541</v>
+        <v>7.76455116271973</v>
       </c>
       <c r="H128" t="n">
         <v>100</v>
@@ -4110,7 +4110,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303695678711</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303600311279</v>
+        <v>7.77303695678711</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G131" t="n">
-        <v>7.83243751525879</v>
+        <v>7.83243656158447</v>
       </c>
       <c r="H131" t="n">
         <v>5900</v>
@@ -4197,7 +4197,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>7.7984938621521</v>
+        <v>7.79849290847778</v>
       </c>
       <c r="H132" t="n">
         <v>300</v>
@@ -4313,7 +4313,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445037841797</v>
+        <v>7.94445133209229</v>
       </c>
       <c r="H136" t="n">
         <v>2500</v>
@@ -4371,7 +4371,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G138" t="n">
-        <v>7.7984938621521</v>
+        <v>7.79849290847778</v>
       </c>
       <c r="H138" t="n">
         <v>800</v>
@@ -4429,7 +4429,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G140" t="n">
-        <v>7.96311855316162</v>
+        <v>7.96311950683594</v>
       </c>
       <c r="H140" t="n">
         <v>500</v>
@@ -4632,7 +4632,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G147" t="n">
-        <v>8.06919193267822</v>
+        <v>8.06919288635254</v>
       </c>
       <c r="H147" t="n">
         <v>100</v>
@@ -4661,7 +4661,7 @@
         <v>9.32100009918213</v>
       </c>
       <c r="G148" t="n">
-        <v>7.90965843200684</v>
+        <v>7.90965938568115</v>
       </c>
       <c r="H148" t="n">
         <v>700</v>
@@ -4690,7 +4690,7 @@
         <v>9.50500011444092</v>
       </c>
       <c r="G149" t="n">
-        <v>8.06579875946045</v>
+        <v>8.06579971313477</v>
       </c>
       <c r="H149" t="n">
         <v>300</v>
@@ -4777,7 +4777,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G152" t="n">
-        <v>8.06919193267822</v>
+        <v>8.06919288635254</v>
       </c>
       <c r="H152" t="n">
         <v>700</v>
@@ -4806,7 +4806,7 @@
         <v>9.50899982452393</v>
       </c>
       <c r="G153" t="n">
-        <v>8.06919193267822</v>
+        <v>8.06919288635254</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G156" t="n">
-        <v>8.06664562225342</v>
+        <v>8.0666446685791</v>
       </c>
       <c r="H156" t="n">
         <v>100</v>
@@ -4922,7 +4922,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G157" t="n">
-        <v>8.06664562225342</v>
+        <v>8.0666446685791</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G158" t="n">
-        <v>8.06664562225342</v>
+        <v>8.0666446685791</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>9.4040002822876</v>
       </c>
       <c r="G163" t="n">
-        <v>7.98009061813354</v>
+        <v>7.98009157180786</v>
       </c>
       <c r="H163" t="n">
         <v>500</v>
@@ -5357,7 +5357,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G172" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H172" t="n">
         <v>3700</v>
@@ -5473,7 +5473,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G176" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H176" t="n">
         <v>4900</v>
@@ -5531,7 +5531,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G178" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H178" t="n">
         <v>300</v>
@@ -5560,7 +5560,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G179" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H179" t="n">
         <v>100</v>
@@ -5763,7 +5763,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G186" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H186" t="n">
         <v>700</v>
@@ -5908,7 +5908,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G191" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H191" t="n">
         <v>5600</v>
@@ -6082,7 +6082,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G197" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H197" t="n">
         <v>300</v>
@@ -6256,7 +6256,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G203" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H203" t="n">
         <v>100</v>
@@ -6401,7 +6401,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G208" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H208" t="n">
         <v>4500</v>
@@ -6633,7 +6633,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G216" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H216" t="n">
         <v>100</v>
@@ -6749,7 +6749,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G220" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H220" t="n">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G221" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H221" t="n">
         <v>17700</v>
@@ -6807,7 +6807,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H222" t="n">
         <v>300</v>
@@ -6865,7 +6865,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G224" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H224" t="n">
         <v>800</v>
@@ -6894,7 +6894,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G225" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H225" t="n">
         <v>600</v>
@@ -6981,7 +6981,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G228" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H228" t="n">
         <v>9100</v>
@@ -7010,7 +7010,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H229" t="n">
         <v>100</v>
@@ -7097,7 +7097,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G232" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H232" t="n">
         <v>5200</v>
@@ -7126,7 +7126,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G233" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H233" t="n">
         <v>5100</v>
@@ -7155,7 +7155,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H234" t="n">
         <v>100</v>
@@ -7184,7 +7184,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G235" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H235" t="n">
         <v>300</v>
@@ -7213,7 +7213,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H236" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H237" t="n">
         <v>100</v>
@@ -7271,7 +7271,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H238" t="n">
         <v>3200</v>
@@ -7300,7 +7300,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H239" t="n">
         <v>100</v>
@@ -7329,7 +7329,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G240" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H240" t="n">
         <v>100</v>
@@ -7358,7 +7358,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G241" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H241" t="n">
         <v>400</v>
@@ -7387,7 +7387,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G242" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H242" t="n">
         <v>7200</v>
@@ -7416,7 +7416,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G243" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H243" t="n">
         <v>100</v>
@@ -7445,7 +7445,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G244" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H244" t="n">
         <v>1200</v>
@@ -7474,7 +7474,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H245" t="n">
         <v>1200</v>
@@ -7590,7 +7590,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G249" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H249" t="n">
         <v>600</v>
@@ -7648,7 +7648,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G251" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H251" t="n">
         <v>2100</v>
@@ -7764,7 +7764,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G255" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H255" t="n">
         <v>7900</v>
@@ -7880,7 +7880,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H259" t="n">
         <v>25000</v>
@@ -7909,7 +7909,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G260" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G261" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G262" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G263" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H263" t="n">
         <v>8000</v>
@@ -8025,7 +8025,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G264" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H264" t="n">
         <v>100</v>
@@ -8054,7 +8054,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G265" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H265" t="n">
         <v>100</v>
@@ -8083,7 +8083,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G266" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H266" t="n">
         <v>600</v>
@@ -8112,7 +8112,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G267" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H267" t="n">
         <v>300</v>
@@ -8141,7 +8141,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G268" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H268" t="n">
         <v>11200</v>
@@ -8170,7 +8170,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G269" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H269" t="n">
         <v>600</v>
@@ -8228,7 +8228,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G271" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H271" t="n">
         <v>100</v>
@@ -8257,7 +8257,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G272" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H272" t="n">
         <v>100</v>
@@ -8286,7 +8286,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G273" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H273" t="n">
         <v>100</v>
@@ -8460,7 +8460,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H279" t="n">
         <v>28000</v>
@@ -8489,7 +8489,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H280" t="n">
         <v>100</v>
@@ -8605,7 +8605,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G284" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H284" t="n">
         <v>6900</v>
@@ -8634,7 +8634,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H285" t="n">
         <v>200</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H286" t="n">
         <v>1900</v>
@@ -8692,7 +8692,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8721,7 +8721,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H289" t="n">
         <v>800</v>
@@ -8866,7 +8866,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G293" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H293" t="n">
         <v>100</v>
@@ -8895,7 +8895,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G294" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G295" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G298" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H298" t="n">
         <v>10700</v>
@@ -9040,7 +9040,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G299" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H299" t="n">
         <v>700</v>
@@ -9069,7 +9069,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G300" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H300" t="n">
         <v>100</v>
@@ -9243,7 +9243,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G306" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H306" t="n">
         <v>100</v>
@@ -9272,7 +9272,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G307" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G311" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H311" t="n">
         <v>100</v>
@@ -9417,7 +9417,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H312" t="n">
         <v>100</v>
@@ -9446,7 +9446,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G313" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H313" t="n">
         <v>12700</v>
@@ -9475,7 +9475,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G314" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H314" t="n">
         <v>7100</v>
@@ -9504,7 +9504,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G316" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H318" t="n">
         <v>300</v>
@@ -9620,7 +9620,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H319" t="n">
         <v>200</v>
@@ -9649,7 +9649,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G320" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H320" t="n">
         <v>100</v>
@@ -9678,7 +9678,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H321" t="n">
         <v>100</v>
@@ -9707,7 +9707,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H322" t="n">
         <v>4600</v>
@@ -9794,7 +9794,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G325" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H325" t="n">
         <v>20100</v>
@@ -9823,7 +9823,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G326" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H326" t="n">
         <v>100</v>
@@ -9852,7 +9852,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G327" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H327" t="n">
         <v>500</v>
@@ -9997,7 +9997,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G332" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H332" t="n">
         <v>10000</v>
@@ -10026,7 +10026,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G333" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H334" t="n">
         <v>100</v>
@@ -10084,7 +10084,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H335" t="n">
         <v>2200</v>
@@ -10113,7 +10113,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G336" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H336" t="n">
         <v>100</v>
@@ -10142,7 +10142,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G337" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H337" t="n">
         <v>100</v>
@@ -10171,7 +10171,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G338" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H338" t="n">
         <v>400</v>
@@ -10200,7 +10200,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H339" t="n">
         <v>6600</v>
@@ -10229,7 +10229,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G340" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H340" t="n">
         <v>400</v>
@@ -10258,7 +10258,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G341" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H341" t="n">
         <v>300</v>
@@ -10287,7 +10287,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H342" t="n">
         <v>100</v>
@@ -10316,7 +10316,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H343" t="n">
         <v>100</v>
@@ -10345,7 +10345,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G344" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H344" t="n">
         <v>1700</v>
@@ -10374,7 +10374,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G345" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G346" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H346" t="n">
         <v>3000</v>
@@ -10432,7 +10432,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G347" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G350" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H350" t="n">
         <v>4400</v>
@@ -10548,7 +10548,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G351" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H351" t="n">
         <v>1400</v>
@@ -10577,7 +10577,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G352" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H352" t="n">
         <v>100</v>
@@ -10606,7 +10606,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G353" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H360" t="n">
         <v>5000</v>
@@ -10867,7 +10867,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H362" t="n">
         <v>300</v>
@@ -10896,7 +10896,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H363" t="n">
         <v>1100</v>
@@ -10925,7 +10925,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H368" t="n">
         <v>300</v>
@@ -11360,7 +11360,7 @@
         <v>9.75</v>
       </c>
       <c r="G379" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H379" t="n">
         <v>67200</v>
@@ -11795,7 +11795,7 @@
         <v>9.75</v>
       </c>
       <c r="G394" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H394" t="n">
         <v>23100</v>
@@ -11853,7 +11853,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H396" t="n">
         <v>1100</v>
@@ -11882,7 +11882,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G397" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H397" t="n">
         <v>69000</v>
@@ -11911,7 +11911,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G398" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H398" t="n">
         <v>1100</v>
@@ -11940,7 +11940,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G399" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H399" t="n">
         <v>300</v>
@@ -11969,7 +11969,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G400" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H400" t="n">
         <v>900</v>
@@ -11998,7 +11998,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G401" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H401" t="n">
         <v>7500</v>
@@ -12027,7 +12027,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G402" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H402" t="n">
         <v>700</v>
@@ -12056,7 +12056,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G403" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H403" t="n">
         <v>2200</v>
@@ -12085,7 +12085,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G404" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H404" t="n">
         <v>300</v>
@@ -12114,7 +12114,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G405" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H405" t="n">
         <v>100</v>
@@ -12143,7 +12143,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G406" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H406" t="n">
         <v>11100</v>
@@ -12288,7 +12288,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12491,7 +12491,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G418" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H418" t="n">
         <v>10000</v>
@@ -12723,7 +12723,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G426" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H426" t="n">
         <v>300</v>
@@ -12752,7 +12752,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G427" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H427" t="n">
         <v>2000</v>
@@ -12781,7 +12781,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G428" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H428" t="n">
         <v>800</v>
@@ -12810,7 +12810,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G429" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H429" t="n">
         <v>400</v>
@@ -12839,7 +12839,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H430" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G431" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H431" t="n">
         <v>700</v>
@@ -12897,7 +12897,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G432" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H432" t="n">
         <v>500</v>
@@ -12926,7 +12926,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G433" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H433" t="n">
         <v>800</v>
@@ -12955,7 +12955,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H434" t="n">
         <v>4300</v>
@@ -12984,7 +12984,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H435" t="n">
         <v>5200</v>
@@ -13013,7 +13013,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H436" t="n">
         <v>400</v>
@@ -13042,7 +13042,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H437" t="n">
         <v>0</v>
@@ -13071,7 +13071,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H438" t="n">
         <v>9200</v>
@@ -13100,7 +13100,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G439" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H439" t="n">
         <v>1000</v>
@@ -13129,7 +13129,7 @@
         <v>9.75</v>
       </c>
       <c r="G440" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H440" t="n">
         <v>300</v>
@@ -13158,7 +13158,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H441" t="n">
         <v>1700</v>
@@ -13187,7 +13187,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H442" t="n">
         <v>1200</v>
@@ -13216,7 +13216,7 @@
         <v>9.75</v>
       </c>
       <c r="G443" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H443" t="n">
         <v>100</v>
@@ -13245,7 +13245,7 @@
         <v>9.75</v>
       </c>
       <c r="G444" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H444" t="n">
         <v>500</v>
@@ -13274,7 +13274,7 @@
         <v>9.75</v>
       </c>
       <c r="G445" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H445" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>9.75</v>
       </c>
       <c r="G446" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H447" t="n">
         <v>300</v>
@@ -13361,7 +13361,7 @@
         <v>9.75</v>
       </c>
       <c r="G448" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H448" t="n">
         <v>400</v>
@@ -13390,7 +13390,7 @@
         <v>9.75</v>
       </c>
       <c r="G449" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H449" t="n">
         <v>700</v>
@@ -13419,7 +13419,7 @@
         <v>9.75</v>
       </c>
       <c r="G450" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H450" t="n">
         <v>0</v>
@@ -13448,7 +13448,7 @@
         <v>9.75</v>
       </c>
       <c r="G451" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H451" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>9.75</v>
       </c>
       <c r="G452" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H452" t="n">
         <v>3100</v>
@@ -13506,7 +13506,7 @@
         <v>9.75</v>
       </c>
       <c r="G453" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H453" t="n">
         <v>100</v>
@@ -13535,7 +13535,7 @@
         <v>9.75</v>
       </c>
       <c r="G454" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H454" t="n">
         <v>100000</v>
@@ -13564,7 +13564,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G455" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H455" t="n">
         <v>60600</v>
@@ -13593,7 +13593,7 @@
         <v>9.75</v>
       </c>
       <c r="G456" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H456" t="n">
         <v>15500</v>
@@ -13622,7 +13622,7 @@
         <v>9.75</v>
       </c>
       <c r="G457" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H457" t="n">
         <v>50000</v>
@@ -13651,7 +13651,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G458" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H458" t="n">
         <v>53200</v>
@@ -13680,7 +13680,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H459" t="n">
         <v>5700</v>
@@ -13709,7 +13709,7 @@
         <v>9.75</v>
       </c>
       <c r="G460" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H460" t="n">
         <v>24400</v>
@@ -13738,7 +13738,7 @@
         <v>9.75</v>
       </c>
       <c r="G461" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H461" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>9.75</v>
       </c>
       <c r="G462" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H462" t="n">
         <v>10100</v>
@@ -13796,7 +13796,7 @@
         <v>9.75</v>
       </c>
       <c r="G463" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H463" t="n">
         <v>5900</v>
@@ -13825,7 +13825,7 @@
         <v>9.75</v>
       </c>
       <c r="G464" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H464" t="n">
         <v>18200</v>
@@ -13854,7 +13854,7 @@
         <v>9.75</v>
       </c>
       <c r="G465" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>9.75</v>
       </c>
       <c r="G466" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H466" t="n">
         <v>10100</v>
@@ -13912,7 +13912,7 @@
         <v>9.75</v>
       </c>
       <c r="G467" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H467" t="n">
         <v>8000</v>
@@ -13941,7 +13941,7 @@
         <v>9.75</v>
       </c>
       <c r="G468" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H468" t="n">
         <v>5800</v>
@@ -13970,7 +13970,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G469" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H469" t="n">
         <v>200</v>
@@ -13999,7 +13999,7 @@
         <v>9.75</v>
       </c>
       <c r="G470" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H470" t="n">
         <v>5600</v>
@@ -14115,7 +14115,7 @@
         <v>9.75</v>
       </c>
       <c r="G474" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H474" t="n">
         <v>68300</v>
@@ -14144,7 +14144,7 @@
         <v>9.75</v>
       </c>
       <c r="G475" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H475" t="n">
         <v>88200</v>
@@ -14173,7 +14173,7 @@
         <v>9.75</v>
       </c>
       <c r="G476" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H476" t="n">
         <v>12000</v>
@@ -14260,7 +14260,7 @@
         <v>9.75</v>
       </c>
       <c r="G479" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H479" t="n">
         <v>36400</v>
@@ -14289,7 +14289,7 @@
         <v>9.75</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H480" t="n">
         <v>5300</v>
@@ -14318,7 +14318,7 @@
         <v>9.75</v>
       </c>
       <c r="G481" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H481" t="n">
         <v>22100</v>
@@ -14347,7 +14347,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G482" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H482" t="n">
         <v>80100</v>
@@ -14376,7 +14376,7 @@
         <v>9.75</v>
       </c>
       <c r="G483" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H483" t="n">
         <v>61200</v>
@@ -14405,7 +14405,7 @@
         <v>9.75</v>
       </c>
       <c r="G484" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H484" t="n">
         <v>17600</v>
@@ -14434,7 +14434,7 @@
         <v>9.75</v>
       </c>
       <c r="G485" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H485" t="n">
         <v>20000</v>
@@ -14463,7 +14463,7 @@
         <v>9.75</v>
       </c>
       <c r="G486" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H486" t="n">
         <v>34700</v>
@@ -15014,7 +15014,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G505" t="n">
-        <v>8.14641380310059</v>
+        <v>8.1464147567749</v>
       </c>
       <c r="H505" t="n">
         <v>400</v>
@@ -15130,7 +15130,7 @@
         <v>9.75</v>
       </c>
       <c r="G509" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H509" t="n">
         <v>109100</v>
@@ -15333,7 +15333,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G516" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H516" t="n">
         <v>5700</v>
@@ -15362,7 +15362,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G517" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H517" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G518" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G519" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H519" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G523" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H523" t="n">
         <v>1000</v>
@@ -15565,7 +15565,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G524" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G525" t="n">
-        <v>8.23127174377441</v>
+        <v>8.23127269744873</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15623,7 +15623,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G526" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H526" t="n">
         <v>6800</v>
@@ -15652,7 +15652,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G527" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G528" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H528" t="n">
         <v>0</v>
@@ -15710,7 +15710,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G529" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H529" t="n">
         <v>600</v>
@@ -15739,7 +15739,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G530" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H530" t="n">
         <v>0</v>
@@ -15768,7 +15768,7 @@
         <v>9.75</v>
       </c>
       <c r="G531" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H531" t="n">
         <v>200</v>
@@ -15797,7 +15797,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G532" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H532" t="n">
         <v>300</v>
@@ -15826,7 +15826,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G533" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H533" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G534" t="n">
-        <v>8.40098857879639</v>
+        <v>8.40098762512207</v>
       </c>
       <c r="H534" t="n">
         <v>100</v>
@@ -16058,7 +16058,7 @@
         <v>9.75</v>
       </c>
       <c r="G541" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H541" t="n">
         <v>1500</v>
@@ -16087,7 +16087,7 @@
         <v>9.75</v>
       </c>
       <c r="G542" t="n">
-        <v>8.27370071411133</v>
+        <v>8.27370166778564</v>
       </c>
       <c r="H542" t="n">
         <v>0</v>
@@ -16377,7 +16377,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G552" t="n">
-        <v>8.1888427734375</v>
+        <v>8.18884372711182</v>
       </c>
       <c r="H552" t="n">
         <v>1800</v>
@@ -16406,7 +16406,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G553" t="n">
-        <v>8.01912689208984</v>
+        <v>8.01912498474121</v>
       </c>
       <c r="H553" t="n">
         <v>1800</v>
@@ -16435,7 +16435,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>7.89183759689331</v>
+        <v>7.89183855056763</v>
       </c>
       <c r="H554" t="n">
         <v>2900</v>
@@ -16580,7 +16580,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G559" t="n">
-        <v>6.66138982772827</v>
+        <v>6.66139078140259</v>
       </c>
       <c r="H559" t="n">
         <v>9300</v>
@@ -16667,7 +16667,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>6.4916729927063</v>
+        <v>6.49167346954346</v>
       </c>
       <c r="H562" t="n">
         <v>3000</v>
@@ -16696,7 +16696,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G563" t="n">
-        <v>7.17054080963135</v>
+        <v>7.17054128646851</v>
       </c>
       <c r="H563" t="n">
         <v>3500</v>
@@ -16754,7 +16754,7 @@
         <v>8</v>
       </c>
       <c r="G565" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H565" t="n">
         <v>3800</v>
@@ -16783,7 +16783,7 @@
         <v>8</v>
       </c>
       <c r="G566" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H566" t="n">
         <v>3000</v>
@@ -16812,7 +16812,7 @@
         <v>8</v>
       </c>
       <c r="G567" t="n">
-        <v>6.78867816925049</v>
+        <v>6.78867769241333</v>
       </c>
       <c r="H567" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>6.4678316116333</v>
+        <v>6.46783113479614</v>
       </c>
       <c r="H573" t="n">
         <v>4700</v>
@@ -17073,7 +17073,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G576" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H576" t="n">
         <v>24700</v>
@@ -17189,7 +17189,7 @@
         <v>8.5</v>
       </c>
       <c r="G580" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H580" t="n">
         <v>1500</v>
@@ -17218,7 +17218,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G581" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H581" t="n">
         <v>200</v>
@@ -17450,7 +17450,7 @@
         <v>8.75</v>
       </c>
       <c r="G589" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H589" t="n">
         <v>1000</v>
@@ -17479,7 +17479,7 @@
         <v>8.75</v>
       </c>
       <c r="G590" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H590" t="n">
         <v>600</v>
@@ -17508,7 +17508,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G591" t="n">
-        <v>7.73517656326294</v>
+        <v>7.73517751693726</v>
       </c>
       <c r="H591" t="n">
         <v>19400</v>
@@ -17537,7 +17537,7 @@
         <v>8.75</v>
       </c>
       <c r="G592" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H592" t="n">
         <v>300</v>
@@ -17566,7 +17566,7 @@
         <v>8.75</v>
       </c>
       <c r="G593" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H593" t="n">
         <v>0</v>
@@ -17595,7 +17595,7 @@
         <v>8.75</v>
       </c>
       <c r="G594" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>8.75</v>
       </c>
       <c r="G595" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H595" t="n">
         <v>0</v>
@@ -17682,7 +17682,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G597" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H597" t="n">
         <v>2000</v>
@@ -17711,7 +17711,7 @@
         <v>8.75</v>
       </c>
       <c r="G598" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H598" t="n">
         <v>3300</v>
@@ -17740,7 +17740,7 @@
         <v>8.75</v>
       </c>
       <c r="G599" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H599" t="n">
         <v>0</v>
@@ -17769,7 +17769,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G600" t="n">
-        <v>7.56037044525146</v>
+        <v>7.56036996841431</v>
       </c>
       <c r="H600" t="n">
         <v>100</v>
@@ -17885,7 +17885,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G604" t="n">
-        <v>7.73517656326294</v>
+        <v>7.73517751693726</v>
       </c>
       <c r="H604" t="n">
         <v>700</v>
@@ -17943,7 +17943,7 @@
         <v>8.5</v>
       </c>
       <c r="G606" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H606" t="n">
         <v>1200</v>
@@ -18001,7 +18001,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>7.60407209396362</v>
+        <v>7.60407114028931</v>
       </c>
       <c r="H608" t="n">
         <v>200</v>
@@ -18175,7 +18175,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G614" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H614" t="n">
         <v>600</v>
@@ -18204,7 +18204,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G615" t="n">
-        <v>7.73517656326294</v>
+        <v>7.73517751693726</v>
       </c>
       <c r="H615" t="n">
         <v>1200</v>
@@ -18233,7 +18233,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G616" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H616" t="n">
         <v>200</v>
@@ -18262,7 +18262,7 @@
         <v>8.5</v>
       </c>
       <c r="G617" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H617" t="n">
         <v>3800</v>
@@ -18320,7 +18320,7 @@
         <v>8.5</v>
       </c>
       <c r="G619" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H619" t="n">
         <v>300</v>
@@ -18349,7 +18349,7 @@
         <v>8.5</v>
       </c>
       <c r="G620" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H620" t="n">
         <v>0</v>
@@ -18639,7 +18639,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G630" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H630" t="n">
         <v>5900</v>
@@ -18668,7 +18668,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G631" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H631" t="n">
         <v>1200</v>
@@ -18697,7 +18697,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G632" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H632" t="n">
         <v>900</v>
@@ -18726,7 +18726,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G633" t="n">
-        <v>7.34186267852783</v>
+        <v>7.34186220169067</v>
       </c>
       <c r="H633" t="n">
         <v>4200</v>
@@ -18755,7 +18755,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G634" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H634" t="n">
         <v>300</v>
@@ -18813,7 +18813,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G636" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H636" t="n">
         <v>2000</v>
@@ -18900,7 +18900,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H639" t="n">
         <v>1100</v>
@@ -18929,7 +18929,7 @@
         <v>8</v>
       </c>
       <c r="G640" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H640" t="n">
         <v>4300</v>
@@ -18958,7 +18958,7 @@
         <v>8</v>
       </c>
       <c r="G641" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H641" t="n">
         <v>500</v>
@@ -18987,7 +18987,7 @@
         <v>8</v>
       </c>
       <c r="G642" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H642" t="n">
         <v>4900</v>
@@ -19045,7 +19045,7 @@
         <v>8</v>
       </c>
       <c r="G644" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H644" t="n">
         <v>5200</v>
@@ -19074,7 +19074,7 @@
         <v>8</v>
       </c>
       <c r="G645" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H645" t="n">
         <v>1000</v>
@@ -19132,7 +19132,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G647" t="n">
-        <v>7.1233549118042</v>
+        <v>7.12335443496704</v>
       </c>
       <c r="H647" t="n">
         <v>5600</v>
@@ -19161,7 +19161,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G648" t="n">
-        <v>7.1233549118042</v>
+        <v>7.12335443496704</v>
       </c>
       <c r="H648" t="n">
         <v>2500</v>
@@ -19190,7 +19190,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G649" t="n">
-        <v>7.1233549118042</v>
+        <v>7.12335443496704</v>
       </c>
       <c r="H649" t="n">
         <v>1700</v>
@@ -19277,7 +19277,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G652" t="n">
-        <v>6.90484666824341</v>
+        <v>6.90484714508057</v>
       </c>
       <c r="H652" t="n">
         <v>2400</v>
@@ -19306,7 +19306,7 @@
         <v>8</v>
       </c>
       <c r="G653" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H653" t="n">
         <v>600</v>
@@ -19335,7 +19335,7 @@
         <v>8</v>
       </c>
       <c r="G654" t="n">
-        <v>6.99224996566772</v>
+        <v>6.99224948883057</v>
       </c>
       <c r="H654" t="n">
         <v>900</v>
@@ -19393,7 +19393,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G656" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H656" t="n">
         <v>1100</v>
@@ -19480,7 +19480,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G659" t="n">
-        <v>7.1670560836792</v>
+        <v>7.16705560684204</v>
       </c>
       <c r="H659" t="n">
         <v>5400</v>
@@ -19538,7 +19538,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G661" t="n">
-        <v>7.03595209121704</v>
+        <v>7.03595161437988</v>
       </c>
       <c r="H661" t="n">
         <v>11500</v>
@@ -19596,7 +19596,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G663" t="n">
-        <v>7.29816150665283</v>
+        <v>7.29816102981567</v>
       </c>
       <c r="H663" t="n">
         <v>11900</v>
@@ -19683,7 +19683,7 @@
         <v>8.5</v>
       </c>
       <c r="G666" t="n">
-        <v>7.42926549911499</v>
+        <v>7.42926502227783</v>
       </c>
       <c r="H666" t="n">
         <v>12000</v>
@@ -19741,7 +19741,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G668" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H668" t="n">
         <v>3000</v>
@@ -20031,7 +20031,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G678" t="n">
-        <v>7.82257890701294</v>
+        <v>7.82257986068726</v>
       </c>
       <c r="H678" t="n">
         <v>1500</v>
@@ -20118,7 +20118,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60407209396362</v>
+        <v>7.60407114028931</v>
       </c>
       <c r="H681" t="n">
         <v>1400</v>
@@ -20147,7 +20147,7 @@
         <v>8.75</v>
       </c>
       <c r="G682" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H682" t="n">
         <v>1900</v>
@@ -20205,7 +20205,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G684" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738597869873</v>
       </c>
       <c r="H684" t="n">
         <v>3100</v>
@@ -20292,7 +20292,7 @@
         <v>8.75</v>
       </c>
       <c r="G687" t="n">
-        <v>7.64777421951294</v>
+        <v>7.64777326583862</v>
       </c>
       <c r="H687" t="n">
         <v>1500</v>
@@ -20321,7 +20321,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>7.60407209396362</v>
+        <v>7.60407114028931</v>
       </c>
       <c r="H688" t="n">
         <v>1500</v>
@@ -20524,7 +20524,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G695" t="n">
-        <v>7.99738502502441</v>
+        <v>7.99738597869873</v>
       </c>
       <c r="H695" t="n">
         <v>5300</v>
@@ -20553,7 +20553,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G696" t="n">
-        <v>8.12849044799805</v>
+        <v>8.12849140167236</v>
       </c>
       <c r="H696" t="n">
         <v>5300</v>
@@ -20582,7 +20582,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G697" t="n">
-        <v>8.12849044799805</v>
+        <v>8.12849140167236</v>
       </c>
       <c r="H697" t="n">
         <v>6600</v>
@@ -20640,7 +20640,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H699" t="n">
         <v>6500</v>
@@ -20756,7 +20756,7 @@
         <v>9.25</v>
       </c>
       <c r="G703" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H703" t="n">
         <v>1400</v>
@@ -20785,7 +20785,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G704" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H704" t="n">
         <v>300</v>
@@ -20959,7 +20959,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H710" t="n">
         <v>1600</v>
@@ -21191,7 +21191,7 @@
         <v>9.25</v>
       </c>
       <c r="G718" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H718" t="n">
         <v>2600</v>
@@ -21220,7 +21220,7 @@
         <v>9.25</v>
       </c>
       <c r="G719" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H719" t="n">
         <v>900</v>
@@ -21278,7 +21278,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G721" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H721" t="n">
         <v>6800</v>
@@ -21336,7 +21336,7 @@
         <v>9.25</v>
       </c>
       <c r="G723" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H723" t="n">
         <v>26400</v>
@@ -21365,7 +21365,7 @@
         <v>9.25</v>
       </c>
       <c r="G724" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H724" t="n">
         <v>21400</v>
@@ -21394,7 +21394,7 @@
         <v>9.25</v>
       </c>
       <c r="G725" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H725" t="n">
         <v>70900</v>
@@ -21423,7 +21423,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G726" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H726" t="n">
         <v>38600</v>
@@ -21452,7 +21452,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H727" t="n">
         <v>100</v>
@@ -21481,7 +21481,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G728" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H728" t="n">
         <v>4500</v>
@@ -21510,7 +21510,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G729" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H729" t="n">
         <v>5100</v>
@@ -21539,7 +21539,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G730" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H730" t="n">
         <v>1200</v>
@@ -21568,7 +21568,7 @@
         <v>9.25</v>
       </c>
       <c r="G731" t="n">
-        <v>8.30227184295654</v>
+        <v>8.30227279663086</v>
       </c>
       <c r="H731" t="n">
         <v>300</v>
@@ -21597,7 +21597,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G732" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H732" t="n">
         <v>2600</v>
@@ -21626,7 +21626,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G733" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H733" t="n">
         <v>6400</v>
@@ -21655,7 +21655,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G734" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H734" t="n">
         <v>12300</v>
@@ -21684,7 +21684,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H735" t="n">
         <v>6900</v>
@@ -21713,7 +21713,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G736" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H736" t="n">
         <v>3000</v>
@@ -21742,7 +21742,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G737" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H737" t="n">
         <v>2000</v>
@@ -21771,7 +21771,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G738" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H738" t="n">
         <v>100</v>
@@ -21887,7 +21887,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G742" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H742" t="n">
         <v>7300</v>
@@ -21945,7 +21945,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G744" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H744" t="n">
         <v>7400</v>
@@ -22003,7 +22003,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G746" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H746" t="n">
         <v>6800</v>
@@ -22061,7 +22061,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H748" t="n">
         <v>700</v>
@@ -22119,7 +22119,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G750" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H750" t="n">
         <v>5400</v>
@@ -22148,7 +22148,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G751" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H751" t="n">
         <v>2100</v>
@@ -22177,7 +22177,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G752" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H752" t="n">
         <v>7900</v>
@@ -22206,7 +22206,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H753" t="n">
         <v>33700</v>
@@ -22235,7 +22235,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G754" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H754" t="n">
         <v>34600</v>
@@ -22264,7 +22264,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G755" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H755" t="n">
         <v>33100</v>
@@ -22322,7 +22322,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G757" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H757" t="n">
         <v>5400</v>
@@ -22351,7 +22351,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G758" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H758" t="n">
         <v>4100</v>
@@ -22438,7 +22438,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G761" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H761" t="n">
         <v>3200</v>
@@ -22467,7 +22467,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G762" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G763" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H763" t="n">
         <v>1000</v>
@@ -22612,7 +22612,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G767" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H767" t="n">
         <v>600</v>
@@ -22641,7 +22641,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G768" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H768" t="n">
         <v>1100</v>
@@ -22670,7 +22670,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G769" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H769" t="n">
         <v>1400</v>
@@ -22699,7 +22699,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G770" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H770" t="n">
         <v>0</v>
@@ -22728,7 +22728,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H771" t="n">
         <v>300</v>
@@ -22757,7 +22757,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G772" t="n">
-        <v>8.34714889526367</v>
+        <v>8.34714984893799</v>
       </c>
       <c r="H772" t="n">
         <v>2900</v>
@@ -22873,7 +22873,7 @@
         <v>10.5</v>
       </c>
       <c r="G776" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H776" t="n">
         <v>25300</v>
@@ -22960,7 +22960,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>9.96272659301758</v>
+        <v>9.96272754669189</v>
       </c>
       <c r="H779" t="n">
         <v>29900</v>
@@ -23105,7 +23105,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>9.69346332550049</v>
+        <v>9.6934642791748</v>
       </c>
       <c r="H784" t="n">
         <v>22700</v>
@@ -23134,7 +23134,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G785" t="n">
-        <v>9.69346332550049</v>
+        <v>9.6934642791748</v>
       </c>
       <c r="H785" t="n">
         <v>6500</v>
@@ -23163,7 +23163,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G786" t="n">
-        <v>9.24469375610352</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H786" t="n">
         <v>12700</v>
@@ -23192,7 +23192,7 @@
         <v>10.5</v>
       </c>
       <c r="G787" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H787" t="n">
         <v>6800</v>
@@ -23221,7 +23221,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H788" t="n">
         <v>26400</v>
@@ -23279,7 +23279,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G790" t="n">
-        <v>9.24469375610352</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H790" t="n">
         <v>4700</v>
@@ -23337,7 +23337,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G792" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H792" t="n">
         <v>18900</v>
@@ -23395,7 +23395,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H794" t="n">
         <v>3700</v>
@@ -23453,7 +23453,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G796" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H796" t="n">
         <v>1300</v>
@@ -23511,7 +23511,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G798" t="n">
-        <v>8.9305534362793</v>
+        <v>8.93055248260498</v>
       </c>
       <c r="H798" t="n">
         <v>700</v>
@@ -23540,7 +23540,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G799" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H799" t="n">
         <v>2300</v>
@@ -24004,7 +24004,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H815" t="n">
         <v>1400</v>
@@ -24091,7 +24091,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G818" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H818" t="n">
         <v>2200</v>
@@ -24236,7 +24236,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G823" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H823" t="n">
         <v>2700</v>
@@ -24265,7 +24265,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G824" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H824" t="n">
         <v>1900</v>
@@ -24294,7 +24294,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G825" t="n">
-        <v>9.24469375610352</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H825" t="n">
         <v>14600</v>
@@ -24323,7 +24323,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>9.24469375610352</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H826" t="n">
         <v>44000</v>
@@ -24352,7 +24352,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G827" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H827" t="n">
         <v>49700</v>
@@ -24410,7 +24410,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H829" t="n">
         <v>12300</v>
@@ -24439,7 +24439,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G830" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H830" t="n">
         <v>1900</v>
@@ -24468,7 +24468,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H831" t="n">
         <v>4200</v>
@@ -24497,7 +24497,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G832" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H832" t="n">
         <v>1700</v>
@@ -24526,7 +24526,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H833" t="n">
         <v>1100</v>
@@ -24584,7 +24584,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H835" t="n">
         <v>1600</v>
@@ -24642,7 +24642,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H837" t="n">
         <v>3000</v>
@@ -24729,7 +24729,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G840" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H840" t="n">
         <v>500</v>
@@ -24816,7 +24816,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G843" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H843" t="n">
         <v>6000</v>
@@ -24874,7 +24874,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H845" t="n">
         <v>3000</v>
@@ -24903,7 +24903,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H846" t="n">
         <v>2100</v>
@@ -24990,7 +24990,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G849" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H849" t="n">
         <v>3700</v>
@@ -25019,7 +25019,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G850" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H850" t="n">
         <v>1700</v>
@@ -25048,7 +25048,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G851" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H851" t="n">
         <v>2400</v>
@@ -25077,7 +25077,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G852" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H852" t="n">
         <v>2600</v>
@@ -25106,7 +25106,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H853" t="n">
         <v>1200</v>
@@ -25164,7 +25164,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G855" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H855" t="n">
         <v>1800</v>
@@ -25251,7 +25251,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G858" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H858" t="n">
         <v>3300</v>
@@ -25309,7 +25309,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G860" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H860" t="n">
         <v>8600</v>
@@ -25425,7 +25425,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G864" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H864" t="n">
         <v>2300</v>
@@ -25454,7 +25454,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G865" t="n">
-        <v>9.24469375610352</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H865" t="n">
         <v>3700</v>
@@ -25483,7 +25483,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G866" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H866" t="n">
         <v>200</v>
@@ -25512,7 +25512,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G867" t="n">
-        <v>9.24469375610352</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H867" t="n">
         <v>20600</v>
@@ -25541,7 +25541,7 @@
         <v>10.5</v>
       </c>
       <c r="G868" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H868" t="n">
         <v>2200</v>
@@ -25599,7 +25599,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G870" t="n">
-        <v>9.24469375610352</v>
+        <v>9.24469184875488</v>
       </c>
       <c r="H870" t="n">
         <v>25600</v>
@@ -25628,7 +25628,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H871" t="n">
         <v>1200</v>
@@ -25831,7 +25831,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G878" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H878" t="n">
         <v>23100</v>
@@ -25860,7 +25860,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G879" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H879" t="n">
         <v>26500</v>
@@ -25889,7 +25889,7 @@
         <v>10.5</v>
       </c>
       <c r="G880" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H880" t="n">
         <v>18700</v>
@@ -25947,7 +25947,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H882" t="n">
         <v>4500</v>
@@ -25976,7 +25976,7 @@
         <v>10.5</v>
       </c>
       <c r="G883" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H883" t="n">
         <v>6700</v>
@@ -26005,7 +26005,7 @@
         <v>10.5</v>
       </c>
       <c r="G884" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H884" t="n">
         <v>11400</v>
@@ -26034,7 +26034,7 @@
         <v>10.5</v>
       </c>
       <c r="G885" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H885" t="n">
         <v>22400</v>
@@ -26063,7 +26063,7 @@
         <v>10.5</v>
       </c>
       <c r="G886" t="n">
-        <v>9.42420101165771</v>
+        <v>9.42420196533203</v>
       </c>
       <c r="H886" t="n">
         <v>19400</v>
@@ -26121,7 +26121,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G888" t="n">
-        <v>8.9305534362793</v>
+        <v>8.93055248260498</v>
       </c>
       <c r="H888" t="n">
         <v>21000</v>
@@ -26179,7 +26179,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H890" t="n">
         <v>2500</v>
@@ -26208,7 +26208,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H891" t="n">
         <v>5500</v>
@@ -26237,7 +26237,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H892" t="n">
         <v>1200</v>
@@ -26266,7 +26266,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G893" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H893" t="n">
         <v>2100</v>
@@ -26295,7 +26295,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G894" t="n">
-        <v>9.15493869781494</v>
+        <v>9.15493774414062</v>
       </c>
       <c r="H894" t="n">
         <v>500</v>
@@ -26324,7 +26324,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G895" t="n">
-        <v>8.9305534362793</v>
+        <v>8.93055248260498</v>
       </c>
       <c r="H895" t="n">
         <v>2200</v>
@@ -26353,7 +26353,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H896" t="n">
         <v>1800</v>
@@ -26382,7 +26382,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H897" t="n">
         <v>900</v>
@@ -26440,7 +26440,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G899" t="n">
-        <v>9.06518459320068</v>
+        <v>9.06518363952637</v>
       </c>
       <c r="H899" t="n">
         <v>500</v>
@@ -26469,7 +26469,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>8.79592132568359</v>
+        <v>8.79592227935791</v>
       </c>
       <c r="H900" t="n">
         <v>3000</v>
@@ -26701,7 +26701,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G908" t="n">
-        <v>8.03300857543945</v>
+        <v>8.03300952911377</v>
       </c>
       <c r="H908" t="n">
         <v>400</v>
@@ -26730,7 +26730,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G909" t="n">
-        <v>8.03300857543945</v>
+        <v>8.03300952911377</v>
       </c>
       <c r="H909" t="n">
         <v>1800</v>
@@ -26788,7 +26788,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G911" t="n">
-        <v>7.35985231399536</v>
+        <v>7.3598518371582</v>
       </c>
       <c r="H911" t="n">
         <v>12900</v>
@@ -26904,7 +26904,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G915" t="n">
-        <v>7.80862426757812</v>
+        <v>7.80862331390381</v>
       </c>
       <c r="H915" t="n">
         <v>5300</v>
@@ -27078,7 +27078,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G921" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H921" t="n">
         <v>100</v>
@@ -27136,7 +27136,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G923" t="n">
-        <v>8.48178100585938</v>
+        <v>8.48178005218506</v>
       </c>
       <c r="H923" t="n">
         <v>1200</v>
@@ -27165,7 +27165,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G924" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H924" t="n">
         <v>500</v>
@@ -27194,7 +27194,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G925" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H925" t="n">
         <v>0</v>
@@ -27397,7 +27397,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G932" t="n">
-        <v>8.65231418609619</v>
+        <v>8.65231513977051</v>
       </c>
       <c r="H932" t="n">
         <v>500</v>
@@ -27426,7 +27426,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G933" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H933" t="n">
         <v>2200</v>
@@ -27455,7 +27455,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G934" t="n">
-        <v>8.54461002349854</v>
+        <v>8.54460906982422</v>
       </c>
       <c r="H934" t="n">
         <v>26000</v>
@@ -27484,7 +27484,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G935" t="n">
-        <v>8.70616626739502</v>
+        <v>8.70616722106934</v>
       </c>
       <c r="H935" t="n">
         <v>2500</v>
@@ -27513,7 +27513,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G936" t="n">
-        <v>8.68821716308594</v>
+        <v>8.68821620941162</v>
       </c>
       <c r="H936" t="n">
         <v>15100</v>
@@ -27542,7 +27542,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G937" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H937" t="n">
         <v>1600</v>
@@ -27571,7 +27571,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G938" t="n">
-        <v>8.61641216278076</v>
+        <v>8.61641311645508</v>
       </c>
       <c r="H938" t="n">
         <v>11000</v>
@@ -27716,7 +27716,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G943" t="n">
-        <v>8.84977245330811</v>
+        <v>8.84977340698242</v>
       </c>
       <c r="H943" t="n">
         <v>7100</v>
@@ -27919,7 +27919,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G950" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H950" t="n">
         <v>1300</v>
@@ -27948,7 +27948,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G951" t="n">
-        <v>9.3015022277832</v>
+        <v>9.30150318145752</v>
       </c>
       <c r="H951" t="n">
         <v>5000</v>
@@ -28006,7 +28006,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G953" t="n">
-        <v>9.11731433868408</v>
+        <v>9.11731338500977</v>
       </c>
       <c r="H953" t="n">
         <v>2400</v>
@@ -28093,7 +28093,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H956" t="n">
         <v>18400</v>
@@ -28354,7 +28354,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G965" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H965" t="n">
         <v>100</v>
@@ -28499,7 +28499,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>8.78577518463135</v>
+        <v>8.78577613830566</v>
       </c>
       <c r="H970" t="n">
         <v>5800</v>
@@ -28731,7 +28731,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G978" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H978" t="n">
         <v>18000</v>
@@ -28789,7 +28789,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G980" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H980" t="n">
         <v>5400</v>
@@ -28934,7 +28934,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G985" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H985" t="n">
         <v>1600</v>
@@ -28963,7 +28963,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G986" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H986" t="n">
         <v>0</v>
@@ -29108,7 +29108,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G991" t="n">
-        <v>8.14111614227295</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H991" t="n">
         <v>1100</v>
@@ -29137,7 +29137,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G992" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H992" t="n">
         <v>3200</v>
@@ -29253,7 +29253,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G996" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H996" t="n">
         <v>800</v>
@@ -29311,7 +29311,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G998" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H998" t="n">
         <v>600</v>
@@ -29340,7 +29340,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G999" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H999" t="n">
         <v>1100</v>
@@ -29398,7 +29398,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1001" t="n">
         <v>900</v>
@@ -29427,7 +29427,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1002" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1002" t="n">
         <v>2700</v>
@@ -29572,7 +29572,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.45423603057861</v>
+        <v>8.45423698425293</v>
       </c>
       <c r="H1007" t="n">
         <v>100</v>
@@ -29630,7 +29630,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1009" t="n">
         <v>2700</v>
@@ -29659,7 +29659,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1010" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1011" t="n">
         <v>0</v>
@@ -29949,7 +29949,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1020" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1020" t="n">
         <v>1400</v>
@@ -29978,7 +29978,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1021" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1021" t="n">
         <v>0</v>
@@ -30007,7 +30007,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1022" t="n">
         <v>100</v>
@@ -30065,7 +30065,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1024" t="n">
         <v>1000</v>
@@ -30123,7 +30123,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1026" t="n">
         <v>300</v>
@@ -30239,7 +30239,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1030" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1030" t="n">
         <v>300</v>
@@ -30355,7 +30355,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1034" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1034" t="n">
         <v>3900</v>
@@ -30384,7 +30384,7 @@
         <v>8.5600004196167</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.88325452804565</v>
+        <v>7.88325357437134</v>
       </c>
       <c r="H1035" t="n">
         <v>600</v>
@@ -30413,7 +30413,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1036" t="n">
-        <v>8.01218414306641</v>
+        <v>8.01218509674072</v>
       </c>
       <c r="H1036" t="n">
         <v>300</v>
@@ -30442,7 +30442,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.01218414306641</v>
+        <v>8.01218509674072</v>
       </c>
       <c r="H1037" t="n">
         <v>0</v>
@@ -30587,7 +30587,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1042" t="n">
-        <v>8.14111614227295</v>
+        <v>8.14111709594727</v>
       </c>
       <c r="H1042" t="n">
         <v>7000</v>
@@ -30616,7 +30616,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1043" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1043" t="n">
         <v>2400</v>
@@ -30674,7 +30674,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1045" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1045" t="n">
         <v>2000</v>
@@ -30703,7 +30703,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1046" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1046" t="n">
         <v>900</v>
@@ -30732,7 +30732,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1047" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1047" t="n">
         <v>500</v>
@@ -30761,7 +30761,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1048" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1048" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1050" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1050" t="n">
         <v>11300</v>
@@ -30848,7 +30848,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1051" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -30993,7 +30993,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.41739940643311</v>
+        <v>8.41740036010742</v>
       </c>
       <c r="H1056" t="n">
         <v>300</v>
@@ -31138,7 +31138,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1061" t="n">
         <v>700</v>
@@ -31167,7 +31167,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1062" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1062" t="n">
         <v>800</v>
@@ -31312,7 +31312,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1067" t="n">
         <v>3400</v>
@@ -31341,7 +31341,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1068" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -31370,7 +31370,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1069" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1069" t="n">
         <v>1000</v>
@@ -31399,7 +31399,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1070" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1070" t="n">
         <v>2800</v>
@@ -31631,7 +31631,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1078" t="n">
         <v>800</v>
@@ -31834,7 +31834,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.859450340271</v>
+        <v>8.85945129394531</v>
       </c>
       <c r="H1085" t="n">
         <v>2600</v>
@@ -31892,7 +31892,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1087" t="n">
         <v>300</v>
@@ -31921,7 +31921,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1088" t="n">
         <v>100</v>
@@ -31950,7 +31950,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1089" t="n">
         <v>0</v>
@@ -31979,7 +31979,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1090" t="n">
         <v>200</v>
@@ -32153,7 +32153,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1096" t="n">
         <v>1900</v>
@@ -32385,7 +32385,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1104" t="n">
         <v>2200</v>
@@ -32559,7 +32559,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1110" t="n">
         <v>22300</v>
@@ -32675,7 +32675,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1114" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1114" t="n">
         <v>1100</v>
@@ -32704,7 +32704,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.80419540405273</v>
+        <v>8.80419445037842</v>
       </c>
       <c r="H1115" t="n">
         <v>5200</v>
@@ -32965,7 +32965,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1124" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1124" t="n">
         <v>7600</v>
@@ -32994,7 +32994,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1125" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1125" t="n">
         <v>11000</v>
@@ -33226,7 +33226,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1133" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1133" t="n">
         <v>700</v>
@@ -33255,7 +33255,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1134" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1134" t="n">
         <v>0</v>
@@ -33284,7 +33284,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1135" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1135" t="n">
         <v>100</v>
@@ -33313,7 +33313,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1136" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1136" t="n">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1139" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1139" t="n">
         <v>3300</v>
@@ -33429,7 +33429,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1140" t="n">
-        <v>8.39898109436035</v>
+        <v>8.39898014068604</v>
       </c>
       <c r="H1140" t="n">
         <v>1000</v>
@@ -33487,7 +33487,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1142" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1142" t="n">
         <v>300</v>
@@ -33574,7 +33574,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1145" t="n">
-        <v>8.60158824920654</v>
+        <v>8.60158729553223</v>
       </c>
       <c r="H1145" t="n">
         <v>2300</v>
@@ -33603,7 +33603,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1146" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1146" t="n">
         <v>1600</v>
@@ -33719,7 +33719,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1150" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1150" t="n">
         <v>2300</v>
@@ -33864,7 +33864,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G1155" t="n">
-        <v>8.91470813751221</v>
+        <v>8.91470718383789</v>
       </c>
       <c r="H1155" t="n">
         <v>100</v>
@@ -33893,7 +33893,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.84103298187256</v>
+        <v>8.84103202819824</v>
       </c>
       <c r="H1156" t="n">
         <v>200</v>
@@ -33980,7 +33980,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1159" t="n">
-        <v>8.6568431854248</v>
+        <v>8.65684413909912</v>
       </c>
       <c r="H1159" t="n">
         <v>4200</v>
@@ -34183,7 +34183,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1166" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1166" t="n">
         <v>100</v>
@@ -34212,7 +34212,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1167" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1167" t="n">
         <v>0</v>
@@ -34241,7 +34241,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1168" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1168" t="n">
         <v>0</v>
@@ -34270,7 +34270,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1169" t="n">
         <v>0</v>
@@ -34299,7 +34299,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1170" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1170" t="n">
         <v>100</v>
@@ -34328,7 +34328,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G1171" t="n">
-        <v>8.69368171691895</v>
+        <v>8.69368076324463</v>
       </c>
       <c r="H1171" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1174" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1174" t="n">
         <v>100</v>
@@ -34705,7 +34705,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1184" t="n">
-        <v>8.47265625</v>
+        <v>8.47265529632568</v>
       </c>
       <c r="H1184" t="n">
         <v>900</v>
@@ -34792,7 +34792,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1187" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1187" t="n">
         <v>300</v>
@@ -34821,7 +34821,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1188" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1188" t="n">
         <v>0</v>
@@ -34850,7 +34850,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1189" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1189" t="n">
         <v>100</v>
@@ -35169,7 +35169,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1200" t="n">
         <v>100</v>
@@ -35198,7 +35198,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.15953636169434</v>
+        <v>8.15953540802002</v>
       </c>
       <c r="H1201" t="n">
         <v>900</v>
@@ -35227,7 +35227,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.15953636169434</v>
+        <v>8.15953540802002</v>
       </c>
       <c r="H1202" t="n">
         <v>300</v>
@@ -35256,7 +35256,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.19637298583984</v>
+        <v>8.19637203216553</v>
       </c>
       <c r="H1203" t="n">
         <v>700</v>
@@ -35430,7 +35430,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.73590326309204</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1209" t="n">
         <v>2000</v>
@@ -35546,7 +35546,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.6069712638855</v>
+        <v>7.60697174072266</v>
       </c>
       <c r="H1213" t="n">
         <v>500</v>
@@ -35691,7 +35691,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1218" t="n">
-        <v>7.22017621994019</v>
+        <v>7.22017669677734</v>
       </c>
       <c r="H1218" t="n">
         <v>19000</v>
@@ -35720,7 +35720,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>7.05440664291382</v>
+        <v>7.05440616607666</v>
       </c>
       <c r="H1219" t="n">
         <v>4300</v>
@@ -35749,7 +35749,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1220" t="n">
-        <v>7.1833381652832</v>
+        <v>7.18333864212036</v>
       </c>
       <c r="H1220" t="n">
         <v>200</v>
@@ -35894,7 +35894,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.1833381652832</v>
+        <v>7.18333864212036</v>
       </c>
       <c r="H1225" t="n">
         <v>2600</v>
@@ -36039,7 +36039,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>7.6069712638855</v>
+        <v>7.60697174072266</v>
       </c>
       <c r="H1230" t="n">
         <v>9400</v>
@@ -36097,7 +36097,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G1232" t="n">
-        <v>7.73590326309204</v>
+        <v>7.73590278625488</v>
       </c>
       <c r="H1232" t="n">
         <v>200</v>
@@ -36155,7 +36155,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G1234" t="n">
-        <v>7.71748399734497</v>
+        <v>7.71748447418213</v>
       </c>
       <c r="H1234" t="n">
         <v>21900</v>
@@ -61043,6 +61043,35 @@
         <v>3000</v>
       </c>
       <c r="I2092" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2093" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="G2093" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="H2093" t="n">
+        <v>2600</v>
+      </c>
+      <c r="I2093" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FUM.MI.xlsx
+++ b/data/FUM.MI.xlsx
@@ -485,7 +485,7 @@
         <v>9.70100021362305</v>
       </c>
       <c r="G4" t="n">
-        <v>8.23212051391602</v>
+        <v>8.2321195602417</v>
       </c>
       <c r="H4" t="n">
         <v>4100</v>
@@ -543,7 +543,7 @@
         <v>9.61100006103516</v>
       </c>
       <c r="G6" t="n">
-        <v>8.15574741363525</v>
+        <v>8.15574836730957</v>
       </c>
       <c r="H6" t="n">
         <v>14900</v>
@@ -572,7 +572,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G7" t="n">
-        <v>8.18035697937012</v>
+        <v>8.18035793304443</v>
       </c>
       <c r="H7" t="n">
         <v>6500</v>
@@ -601,7 +601,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G8" t="n">
-        <v>8.11247062683105</v>
+        <v>8.11246967315674</v>
       </c>
       <c r="H8" t="n">
         <v>7000</v>
@@ -630,7 +630,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H9" t="n">
         <v>3500</v>
@@ -659,7 +659,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G12" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H12" t="n">
         <v>3300</v>
@@ -746,7 +746,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G13" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G14" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
@@ -804,7 +804,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H15" t="n">
         <v>500</v>
@@ -833,7 +833,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G16" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H19" t="n">
         <v>9600</v>
@@ -949,7 +949,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>8.09549903869629</v>
+        <v>8.09549999237061</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G24" t="n">
-        <v>8.07852649688721</v>
+        <v>8.07852745056152</v>
       </c>
       <c r="H24" t="n">
         <v>2800</v>
@@ -1268,7 +1268,7 @@
         <v>9.50100040435791</v>
       </c>
       <c r="G31" t="n">
-        <v>8.06240367889404</v>
+        <v>8.06240463256836</v>
       </c>
       <c r="H31" t="n">
         <v>200</v>
@@ -1326,7 +1326,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G33" t="n">
-        <v>8.07513236999512</v>
+        <v>8.07513332366943</v>
       </c>
       <c r="H33" t="n">
         <v>8000</v>
@@ -1442,7 +1442,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>7.99366855621338</v>
+        <v>7.99366903305054</v>
       </c>
       <c r="H37" t="n">
         <v>12300</v>
@@ -1471,7 +1471,7 @@
         <v>9.37100028991699</v>
       </c>
       <c r="G38" t="n">
-        <v>7.95208835601807</v>
+        <v>7.95208787918091</v>
       </c>
       <c r="H38" t="n">
         <v>500</v>
@@ -1500,7 +1500,7 @@
         <v>9.33100032806396</v>
       </c>
       <c r="G39" t="n">
-        <v>7.91814565658569</v>
+        <v>7.91814470291138</v>
       </c>
       <c r="H39" t="n">
         <v>400</v>
@@ -1529,7 +1529,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G40" t="n">
-        <v>7.96227121353149</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H40" t="n">
         <v>300</v>
@@ -1558,7 +1558,7 @@
         <v>9.38300037384033</v>
       </c>
       <c r="G41" t="n">
-        <v>7.96227121353149</v>
+        <v>7.96227073669434</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G42" t="n">
-        <v>7.97924327850342</v>
+        <v>7.97924280166626</v>
       </c>
       <c r="H42" t="n">
         <v>300</v>
@@ -1616,7 +1616,7 @@
         <v>9.40299987792969</v>
       </c>
       <c r="G43" t="n">
-        <v>7.97924327850342</v>
+        <v>7.97924280166626</v>
       </c>
       <c r="H43" t="n">
         <v>1700</v>
@@ -1645,7 +1645,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G44" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H44" t="n">
         <v>600</v>
@@ -1674,7 +1674,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G45" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G46" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H46" t="n">
         <v>8000</v>
@@ -1790,7 +1790,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G49" t="n">
-        <v>7.91729545593262</v>
+        <v>7.91729593276978</v>
       </c>
       <c r="H49" t="n">
         <v>9200</v>
@@ -1819,7 +1819,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G50" t="n">
-        <v>7.85619783401489</v>
+        <v>7.85619831085205</v>
       </c>
       <c r="H50" t="n">
         <v>8700</v>
@@ -1848,7 +1848,7 @@
         <v>9.25</v>
       </c>
       <c r="G51" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H51" t="n">
         <v>16700</v>
@@ -1906,7 +1906,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G53" t="n">
-        <v>7.77473306655884</v>
+        <v>7.77473258972168</v>
       </c>
       <c r="H53" t="n">
         <v>2300</v>
@@ -2022,7 +2022,7 @@
         <v>9.25</v>
       </c>
       <c r="G57" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H57" t="n">
         <v>12300</v>
@@ -2080,7 +2080,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G59" t="n">
-        <v>7.76455116271973</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H59" t="n">
         <v>13600</v>
@@ -2138,7 +2138,7 @@
         <v>9.25</v>
       </c>
       <c r="G61" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H61" t="n">
         <v>4900</v>
@@ -2225,7 +2225,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G64" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H64" t="n">
         <v>1600</v>
@@ -2370,7 +2370,7 @@
         <v>9.20699977874756</v>
       </c>
       <c r="G69" t="n">
-        <v>7.81292009353638</v>
+        <v>7.81291961669922</v>
       </c>
       <c r="H69" t="n">
         <v>200</v>
@@ -2399,7 +2399,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G70" t="n">
-        <v>7.80528211593628</v>
+        <v>7.80528163909912</v>
       </c>
       <c r="H70" t="n">
         <v>1000</v>
@@ -2428,7 +2428,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G71" t="n">
-        <v>7.86722898483276</v>
+        <v>7.86722946166992</v>
       </c>
       <c r="H71" t="n">
         <v>800</v>
@@ -2602,7 +2602,7 @@
         <v>9.24100017547607</v>
       </c>
       <c r="G77" t="n">
-        <v>7.84177255630493</v>
+        <v>7.84177303314209</v>
       </c>
       <c r="H77" t="n">
         <v>4000</v>
@@ -2631,7 +2631,7 @@
         <v>9.18099975585938</v>
       </c>
       <c r="G78" t="n">
-        <v>7.79085683822632</v>
+        <v>7.79085636138916</v>
       </c>
       <c r="H78" t="n">
         <v>800</v>
@@ -2747,7 +2747,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G82" t="n">
-        <v>7.78406763076782</v>
+        <v>7.78406715393066</v>
       </c>
       <c r="H82" t="n">
         <v>200</v>
@@ -2776,7 +2776,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G83" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H83" t="n">
         <v>1100</v>
@@ -2805,7 +2805,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G84" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G85" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>9.19299983978271</v>
       </c>
       <c r="G86" t="n">
-        <v>7.80103921890259</v>
+        <v>7.80103969573975</v>
       </c>
       <c r="H86" t="n">
         <v>2900</v>
@@ -2892,7 +2892,7 @@
         <v>9.20400047302246</v>
       </c>
       <c r="G87" t="n">
-        <v>7.81037425994873</v>
+        <v>7.81037378311157</v>
       </c>
       <c r="H87" t="n">
         <v>2500</v>
@@ -2921,7 +2921,7 @@
         <v>9.29899978637695</v>
       </c>
       <c r="G88" t="n">
-        <v>7.89098930358887</v>
+        <v>7.89098882675171</v>
       </c>
       <c r="H88" t="n">
         <v>200</v>
@@ -2950,7 +2950,7 @@
         <v>9.20100021362305</v>
       </c>
       <c r="G89" t="n">
-        <v>7.80782794952393</v>
+        <v>7.80782747268677</v>
       </c>
       <c r="H89" t="n">
         <v>5100</v>
@@ -2979,7 +2979,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G90" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879215240479</v>
       </c>
       <c r="H90" t="n">
         <v>4500</v>
@@ -3008,7 +3008,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G91" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879215240479</v>
       </c>
       <c r="H91" t="n">
         <v>700</v>
@@ -3037,7 +3037,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G92" t="n">
-        <v>7.92408561706543</v>
+        <v>7.92408466339111</v>
       </c>
       <c r="H92" t="n">
         <v>1200</v>
@@ -3095,7 +3095,7 @@
         <v>9.15100002288818</v>
       </c>
       <c r="G94" t="n">
-        <v>7.76539897918701</v>
+        <v>7.76539850234985</v>
       </c>
       <c r="H94" t="n">
         <v>2000</v>
@@ -3124,7 +3124,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G95" t="n">
-        <v>7.76455116271973</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H95" t="n">
         <v>20300</v>
@@ -3153,7 +3153,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G96" t="n">
-        <v>7.76455116271973</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G99" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H99" t="n">
         <v>6000</v>
@@ -3269,7 +3269,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>7.67969179153442</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H100" t="n">
         <v>1200</v>
@@ -3298,7 +3298,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>7.67969179153442</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>9</v>
       </c>
       <c r="G102" t="n">
-        <v>7.63726282119751</v>
+        <v>7.63726329803467</v>
       </c>
       <c r="H102" t="n">
         <v>700</v>
@@ -3501,7 +3501,7 @@
         <v>9.10099983215332</v>
       </c>
       <c r="G108" t="n">
-        <v>7.72296953201294</v>
+        <v>7.72297048568726</v>
       </c>
       <c r="H108" t="n">
         <v>2200</v>
@@ -3559,7 +3559,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G110" t="n">
-        <v>7.71363496780396</v>
+        <v>7.71363544464111</v>
       </c>
       <c r="H110" t="n">
         <v>10000</v>
@@ -3588,7 +3588,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H111" t="n">
         <v>25500</v>
@@ -3617,7 +3617,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G112" t="n">
-        <v>7.70514917373657</v>
+        <v>7.70514869689941</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G113" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817806243896</v>
       </c>
       <c r="H113" t="n">
         <v>15900</v>
@@ -3675,7 +3675,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G114" t="n">
-        <v>7.67969179153442</v>
+        <v>7.67969131469727</v>
       </c>
       <c r="H114" t="n">
         <v>100</v>
@@ -3704,7 +3704,7 @@
         <v>9.06099987030029</v>
       </c>
       <c r="G115" t="n">
-        <v>7.68902635574341</v>
+        <v>7.68902587890625</v>
       </c>
       <c r="H115" t="n">
         <v>1500</v>
@@ -3733,7 +3733,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G116" t="n">
-        <v>7.85110569000244</v>
+        <v>7.8511061668396</v>
       </c>
       <c r="H116" t="n">
         <v>800</v>
@@ -3762,7 +3762,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G117" t="n">
-        <v>7.80273675918579</v>
+        <v>7.80273723602295</v>
       </c>
       <c r="H117" t="n">
         <v>100</v>
@@ -3791,7 +3791,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G118" t="n">
-        <v>7.68308639526367</v>
+        <v>7.68308544158936</v>
       </c>
       <c r="H118" t="n">
         <v>2400</v>
@@ -3907,7 +3907,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G122" t="n">
-        <v>7.68817853927612</v>
+        <v>7.68817806243896</v>
       </c>
       <c r="H122" t="n">
         <v>3300</v>
@@ -3936,7 +3936,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G123" t="n">
-        <v>7.7687931060791</v>
+        <v>7.76879215240479</v>
       </c>
       <c r="H123" t="n">
         <v>100</v>
@@ -3994,7 +3994,7 @@
         <v>9.26900005340576</v>
       </c>
       <c r="G125" t="n">
-        <v>7.86553192138672</v>
+        <v>7.86553144454956</v>
       </c>
       <c r="H125" t="n">
         <v>300</v>
@@ -4052,7 +4052,7 @@
         <v>9.17300033569336</v>
       </c>
       <c r="G127" t="n">
-        <v>7.78406763076782</v>
+        <v>7.78406715393066</v>
       </c>
       <c r="H127" t="n">
         <v>2000</v>
@@ -4081,7 +4081,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G128" t="n">
-        <v>7.76455116271973</v>
+        <v>7.76454973220825</v>
       </c>
       <c r="H128" t="n">
         <v>100</v>
@@ -4110,7 +4110,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.77303695678711</v>
+        <v>7.77303647994995</v>
       </c>
       <c r="H129" t="n">
         <v>200</v>
@@ -4139,7 +4139,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G130" t="n">
-        <v>7.77303695678711</v>
+        <v>7.77303647994995</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>9.25</v>
       </c>
       <c r="G133" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H133" t="n">
         <v>13900</v>
@@ -4255,7 +4255,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G134" t="n">
-        <v>7.79000759124756</v>
+        <v>7.7900071144104</v>
       </c>
       <c r="H134" t="n">
         <v>1000</v>
@@ -4284,7 +4284,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G135" t="n">
-        <v>7.79000759124756</v>
+        <v>7.7900071144104</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>9.36200046539307</v>
       </c>
       <c r="G136" t="n">
-        <v>7.94445133209229</v>
+        <v>7.94445180892944</v>
       </c>
       <c r="H136" t="n">
         <v>2500</v>
@@ -4661,7 +4661,7 @@
         <v>9.32100009918213</v>
       </c>
       <c r="G148" t="n">
-        <v>7.90965938568115</v>
+        <v>7.90965843200684</v>
       </c>
       <c r="H148" t="n">
         <v>700</v>
@@ -4719,7 +4719,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G150" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H150" t="n">
         <v>100</v>
@@ -4748,7 +4748,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G151" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G154" t="n">
-        <v>7.92832803726196</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H154" t="n">
         <v>1100</v>
@@ -4893,7 +4893,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G156" t="n">
-        <v>8.0666446685791</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H156" t="n">
         <v>100</v>
@@ -4922,7 +4922,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G157" t="n">
-        <v>8.0666446685791</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>9.50599956512451</v>
       </c>
       <c r="G158" t="n">
-        <v>8.0666446685791</v>
+        <v>8.06664562225342</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>9.34700012207031</v>
       </c>
       <c r="G159" t="n">
-        <v>7.93172168731689</v>
+        <v>7.93172121047974</v>
       </c>
       <c r="H159" t="n">
         <v>800</v>
@@ -5067,7 +5067,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G162" t="n">
-        <v>7.92153835296631</v>
+        <v>7.92153930664062</v>
       </c>
       <c r="H162" t="n">
         <v>2300</v>
@@ -5183,7 +5183,7 @@
         <v>9.3430004119873</v>
       </c>
       <c r="G166" t="n">
-        <v>7.92832803726196</v>
+        <v>7.92832708358765</v>
       </c>
       <c r="H166" t="n">
         <v>1200</v>
@@ -5212,7 +5212,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G167" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H167" t="n">
         <v>3300</v>
@@ -5241,7 +5241,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G168" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H168" t="n">
         <v>9400</v>
@@ -5270,7 +5270,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G169" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H169" t="n">
         <v>6900</v>
@@ -5299,7 +5299,7 @@
         <v>9.25</v>
       </c>
       <c r="G170" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H170" t="n">
         <v>200</v>
@@ -5328,7 +5328,7 @@
         <v>9.25</v>
       </c>
       <c r="G171" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>9.25</v>
       </c>
       <c r="G173" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H173" t="n">
         <v>200</v>
@@ -5415,7 +5415,7 @@
         <v>9.25</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84940910339355</v>
+        <v>7.84940958023071</v>
       </c>
       <c r="H174" t="n">
         <v>600</v>
@@ -5444,7 +5444,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G175" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H175" t="n">
         <v>300</v>
@@ -5502,7 +5502,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G177" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H177" t="n">
         <v>1900</v>
@@ -5589,7 +5589,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G180" t="n">
-        <v>7.97669649124146</v>
+        <v>7.97669696807861</v>
       </c>
       <c r="H180" t="n">
         <v>3800</v>
@@ -5618,7 +5618,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G181" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H181" t="n">
         <v>5000</v>
@@ -5647,7 +5647,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G182" t="n">
-        <v>7.93426704406738</v>
+        <v>7.9342679977417</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G183" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H183" t="n">
         <v>300</v>
@@ -5705,7 +5705,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G184" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H184" t="n">
         <v>300</v>
@@ -5734,7 +5734,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G185" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H185" t="n">
         <v>200</v>
@@ -5792,7 +5792,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H187" t="n">
         <v>900</v>
@@ -5850,7 +5850,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G189" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H189" t="n">
         <v>1900</v>
@@ -5966,7 +5966,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G193" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H193" t="n">
         <v>3200</v>
@@ -5995,7 +5995,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H194" t="n">
         <v>300</v>
@@ -6111,7 +6111,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H198" t="n">
         <v>4700</v>
@@ -6140,7 +6140,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H199" t="n">
         <v>400</v>
@@ -6169,7 +6169,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G200" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H200" t="n">
         <v>2000</v>
@@ -6198,7 +6198,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G201" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H201" t="n">
         <v>1500</v>
@@ -6227,7 +6227,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G202" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H202" t="n">
         <v>800</v>
@@ -6285,7 +6285,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G204" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H204" t="n">
         <v>5900</v>
@@ -6343,7 +6343,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G206" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H206" t="n">
         <v>300</v>
@@ -6430,7 +6430,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G209" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H209" t="n">
         <v>600</v>
@@ -6459,7 +6459,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H210" t="n">
         <v>600</v>
@@ -6546,7 +6546,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G213" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H213" t="n">
         <v>2600</v>
@@ -6575,7 +6575,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G214" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H214" t="n">
         <v>200</v>
@@ -6604,7 +6604,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G215" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H215" t="n">
         <v>6600</v>
@@ -6662,7 +6662,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G217" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H217" t="n">
         <v>1500</v>
@@ -6691,7 +6691,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G218" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H218" t="n">
         <v>900</v>
@@ -6720,7 +6720,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G219" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H219" t="n">
         <v>1000</v>
@@ -6807,7 +6807,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G222" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H222" t="n">
         <v>300</v>
@@ -6923,7 +6923,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H226" t="n">
         <v>100</v>
@@ -6952,7 +6952,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G227" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H227" t="n">
         <v>100</v>
@@ -7010,7 +7010,7 @@
         <v>9.75</v>
       </c>
       <c r="G229" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H229" t="n">
         <v>100</v>
@@ -7039,7 +7039,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G230" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H230" t="n">
         <v>300</v>
@@ -7068,7 +7068,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G231" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H231" t="n">
         <v>500</v>
@@ -7155,7 +7155,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H234" t="n">
         <v>100</v>
@@ -7213,7 +7213,7 @@
         <v>9.75</v>
       </c>
       <c r="G236" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H236" t="n">
         <v>800</v>
@@ -7242,7 +7242,7 @@
         <v>9.75</v>
       </c>
       <c r="G237" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H237" t="n">
         <v>100</v>
@@ -7271,7 +7271,7 @@
         <v>9.75</v>
       </c>
       <c r="G238" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H238" t="n">
         <v>3200</v>
@@ -7300,7 +7300,7 @@
         <v>9.75</v>
       </c>
       <c r="G239" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H239" t="n">
         <v>100</v>
@@ -7474,7 +7474,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H245" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G246" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H246" t="n">
         <v>1000</v>
@@ -7532,7 +7532,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H248" t="n">
         <v>700</v>
@@ -7619,7 +7619,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G250" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H250" t="n">
         <v>300</v>
@@ -7677,7 +7677,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G252" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H252" t="n">
         <v>1800</v>
@@ -7706,7 +7706,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G253" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H253" t="n">
         <v>1700</v>
@@ -7735,7 +7735,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G254" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H254" t="n">
         <v>1800</v>
@@ -7764,7 +7764,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G255" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H255" t="n">
         <v>7900</v>
@@ -7793,7 +7793,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G256" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H256" t="n">
         <v>2300</v>
@@ -7822,7 +7822,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H257" t="n">
         <v>100</v>
@@ -7851,7 +7851,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G258" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H258" t="n">
         <v>1200</v>
@@ -8315,7 +8315,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G274" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H274" t="n">
         <v>200</v>
@@ -8373,7 +8373,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H276" t="n">
         <v>100</v>
@@ -8460,7 +8460,7 @@
         <v>9.75</v>
       </c>
       <c r="G279" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H279" t="n">
         <v>28000</v>
@@ -8489,7 +8489,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H280" t="n">
         <v>100</v>
@@ -8634,7 +8634,7 @@
         <v>9.75</v>
       </c>
       <c r="G285" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H285" t="n">
         <v>200</v>
@@ -8663,7 +8663,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H286" t="n">
         <v>1900</v>
@@ -8692,7 +8692,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H287" t="n">
         <v>200</v>
@@ -8721,7 +8721,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G289" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H289" t="n">
         <v>800</v>
@@ -8953,7 +8953,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G296" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H296" t="n">
         <v>200</v>
@@ -9330,7 +9330,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H309" t="n">
         <v>500</v>
@@ -9359,7 +9359,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G310" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H310" t="n">
         <v>3300</v>
@@ -9620,7 +9620,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G319" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H319" t="n">
         <v>200</v>
@@ -9649,7 +9649,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G320" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H320" t="n">
         <v>100</v>
@@ -9678,7 +9678,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G321" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H321" t="n">
         <v>100</v>
@@ -9707,7 +9707,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G322" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H322" t="n">
         <v>4600</v>
@@ -9736,7 +9736,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G323" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H323" t="n">
         <v>26700</v>
@@ -9765,7 +9765,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G324" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H324" t="n">
         <v>100</v>
@@ -9881,7 +9881,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G328" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H328" t="n">
         <v>52800</v>
@@ -9910,7 +9910,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G329" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H329" t="n">
         <v>10000</v>
@@ -9939,7 +9939,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G330" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H330" t="n">
         <v>200</v>
@@ -9968,7 +9968,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10398483276367</v>
+        <v>8.10398578643799</v>
       </c>
       <c r="H331" t="n">
         <v>900</v>
@@ -10287,7 +10287,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G342" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H342" t="n">
         <v>100</v>
@@ -10461,7 +10461,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G348" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H348" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G349" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G352" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H352" t="n">
         <v>100</v>
@@ -10606,7 +10606,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G353" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G354" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>8.23127269744873</v>
+        <v>8.23127174377441</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>9.75</v>
       </c>
       <c r="G360" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H360" t="n">
         <v>5000</v>
@@ -10867,7 +10867,7 @@
         <v>9.75</v>
       </c>
       <c r="G362" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H362" t="n">
         <v>300</v>
@@ -10896,7 +10896,7 @@
         <v>9.75</v>
       </c>
       <c r="G363" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H363" t="n">
         <v>1100</v>
@@ -10925,7 +10925,7 @@
         <v>9.75</v>
       </c>
       <c r="G364" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G365" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H365" t="n">
         <v>100</v>
@@ -10983,7 +10983,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G366" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G367" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H367" t="n">
         <v>900</v>
@@ -11041,7 +11041,7 @@
         <v>9.75</v>
       </c>
       <c r="G368" t="n">
-        <v>8.27370166778564</v>
+        <v>8.27370071411133</v>
       </c>
       <c r="H368" t="n">
         <v>300</v>
@@ -11070,7 +11070,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G369" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H369" t="n">
         <v>100</v>
@@ -11099,7 +11099,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G370" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H370" t="n">
         <v>100</v>
@@ -11128,7 +11128,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G371" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H371" t="n">
         <v>1700</v>
@@ -11157,7 +11157,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G372" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H372" t="n">
         <v>1200</v>
@@ -11244,7 +11244,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G375" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H375" t="n">
         <v>5700</v>
@@ -11331,7 +11331,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G378" t="n">
-        <v>8.35856056213379</v>
+        <v>8.35855960845947</v>
       </c>
       <c r="H378" t="n">
         <v>30700<